--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76998800-DCD9-457A-A12A-83D68D883950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728B035C-A3B9-4C1C-8D27-75D866672AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metricas de Casos de Prueba" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="614">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -916,15 +916,6 @@
  - El sistema redirecciona a la home de Vetify</t>
   </si>
   <si>
-    <t>TS-04 Olvidé contraseña</t>
-  </si>
-  <si>
-    <t>Campos Obligatorios</t>
-  </si>
-  <si>
-    <t>Recibir Email</t>
-  </si>
-  <si>
     <t>TS-05 Cambio de Contraseña</t>
   </si>
   <si>
@@ -992,13 +983,6 @@
     <t>Credencial - Vetify - Actualizar datos personales (sólo teléfono es editable; nombre/apellido/DNI requieren llamar al 0800 122 1183)</t>
   </si>
   <si>
-    <t>El sistema permite cambiar los siguiente datos del perfil:
- - Nombre
- - Apellido
- - Número de Identificación
- - Número de teléfono</t>
-  </si>
-  <si>
     <t>1. Cambiar los datos del perfil del usuario</t>
   </si>
   <si>
@@ -2174,6 +2158,75 @@
   </si>
   <si>
     <t>Nota: 'Automatizable' = tecnicamente viable con la infraestructura actual del proyecto (aunque hoy no este hecho, ej. bloqueado solo por falta de un dato de prueba puntual, como un cupon real). 'No automatizable' = bloqueo real y practico (leer un email real, esperar una ventana de tiempo real, requiere un humano real del otro lado, restriccion de picker nativo en mobile). Ver columna Automatizable de cada hoja para el detalle fila por fila. Agregado 2026-08-14.</t>
+  </si>
+  <si>
+    <t>TS-04 IMAS-3217 - Olvidé contraseña</t>
+  </si>
+  <si>
+    <t>Acceso al flujo de reseteo desde login</t>
+  </si>
+  <si>
+    <t>Usuario en /auth/login, sin sesión iniciada.</t>
+  </si>
+  <si>
+    <t>Presionar "¿Olvidaste tu contraseña?".</t>
+  </si>
+  <si>
+    <t>No hay navegación a otra URL — se expande un sub-formulario inline con input "Correo electrónico" y botón "Enviar".</t>
+  </si>
+  <si>
+    <t>Solicitud de reset con email registrado</t>
+  </si>
+  <si>
+    <t>Usuario con el sub-formulario de reseteo expandido; existe un usuario registrado.</t>
+  </si>
+  <si>
+    <t>Ingresar el email del usuario y presionar "Enviar".</t>
+  </si>
+  <si>
+    <t>POST /api/passrecovery responde 200 con mensaje genérico; UI muestra "Te hemos enviado un correo para que puedas resetear tu contraseña".</t>
+  </si>
+  <si>
+    <t>[Negativo] Solicitud de reset con email no registrado</t>
+  </si>
+  <si>
+    <t>Usuario con el sub-formulario de reseteo expandido.</t>
+  </si>
+  <si>
+    <t>Ingresar un email no asociado a ningún usuario y presionar "Enviar".</t>
+  </si>
+  <si>
+    <t>Respuesta y mensaje idénticos al caso de email registrado — no revela si el email existe (previene user enumeration).</t>
+  </si>
+  <si>
+    <t>[Bug conocido] [Negativo] Campo email obligatorio</t>
+  </si>
+  <si>
+    <t>Usuario con el sub-formulario de reseteo expandido, campo email vacío.</t>
+  </si>
+  <si>
+    <t>Presionar "Enviar" sin ingresar email.</t>
+  </si>
+  <si>
+    <t>Backend responde 400 "email es requerido". BUG (IMAS-4198): el frontend muestra un mensaje genérico de "problemas técnicos" en vez de indicar el campo obligatorio.</t>
+  </si>
+  <si>
+    <t>[Bug conocido] [Negativo] Formato de email inválido no se valida</t>
+  </si>
+  <si>
+    <t>Ingresar un valor sin formato de email válido (sin "@") y presionar "Enviar".</t>
+  </si>
+  <si>
+    <t>BUG (IMAS-4199): no hay validación de formato — el backend responde 200 con el mismo mensaje de éxito genérico que un email válido.</t>
+  </si>
+  <si>
+    <t>TS-04 IMAS-3216 - Olvidé contraseña</t>
+  </si>
+  <si>
+    <t>TS-04 IMAS-3215 - Olvidé contraseña</t>
+  </si>
+  <si>
+    <t>El sistema permite cambiar únicamente el número de teléfono. Nombre, Apellido y Número de Identificación NO son editables: se muestra un aviso fijo indicando que deben corregirse llamando al 0800 122 1183 (confirmado en vivo 2026-08-08 — contradice el criterio original de este caso, que asumía los 4 campos editables).</t>
   </si>
 </sst>
 </file>
@@ -2577,6 +2630,15 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2597,28 +2659,19 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4470,734 +4523,734 @@
   <sheetData>
     <row r="2" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="3" spans="3:24">
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
-      <c r="K3" s="44" t="s">
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="49"/>
+      <c r="K3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="46"/>
-      <c r="S3" s="44" t="s">
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="49"/>
+      <c r="S3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="46"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="49"/>
     </row>
     <row r="4" spans="3:24">
-      <c r="C4" s="40"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="39"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="39"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="42"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="42"/>
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C5" s="37">
-        <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C345,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199)</f>
-        <v>241</v>
-      </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-      <c r="K5" s="37">
+      <c r="C5" s="40">
+        <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199)</f>
+        <v>253</v>
+      </c>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+      <c r="K5" s="40">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!G:G,"Si")</f>
-        <v>175</v>
-      </c>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="39"/>
-      <c r="S5" s="48">
+        <v>188</v>
+      </c>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="42"/>
+      <c r="S5" s="51">
         <f>K5/C5</f>
-        <v>0.72614107883817425</v>
-      </c>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="39"/>
+        <v>0.74308300395256921</v>
+      </c>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="42"/>
     </row>
     <row r="6" spans="3:24">
-      <c r="C6" s="40"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="39"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="39"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="39"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="42"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="42"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="42"/>
     </row>
     <row r="7" spans="3:24">
-      <c r="C7" s="40"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="39"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="39"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="39"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="42"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="42"/>
     </row>
     <row r="8" spans="3:24">
-      <c r="C8" s="40"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="39"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="39"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="42"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="41"/>
+      <c r="X8" s="42"/>
     </row>
     <row r="9" spans="3:24">
-      <c r="C9" s="40"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="39"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="39"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="42"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="41"/>
+      <c r="X9" s="42"/>
     </row>
     <row r="10" spans="3:24">
-      <c r="C10" s="40"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="39"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="39"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="39"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="42"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="42"/>
     </row>
     <row r="11" spans="3:24">
-      <c r="C11" s="40"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="39"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="39"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="42"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="42"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="41"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="41"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="42"/>
     </row>
     <row r="12" spans="3:24">
-      <c r="C12" s="40"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="39"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="39"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="42"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="42"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="41"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="42"/>
     </row>
     <row r="13" spans="3:24">
-      <c r="C13" s="40"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="39"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="39"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="42"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="42"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="41"/>
+      <c r="U13" s="41"/>
+      <c r="V13" s="41"/>
+      <c r="W13" s="41"/>
+      <c r="X13" s="42"/>
     </row>
     <row r="14" spans="3:24">
-      <c r="C14" s="40"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="39"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="39"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="42"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="42"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="41"/>
+      <c r="U14" s="41"/>
+      <c r="V14" s="41"/>
+      <c r="W14" s="41"/>
+      <c r="X14" s="42"/>
     </row>
     <row r="15" spans="3:24">
-      <c r="C15" s="40"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="39"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="39"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="42"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="41"/>
+      <c r="V15" s="41"/>
+      <c r="W15" s="41"/>
+      <c r="X15" s="42"/>
     </row>
     <row r="16" spans="3:24">
-      <c r="C16" s="40"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="39"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="39"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="42"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="42"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="41"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="42"/>
     </row>
     <row r="17" spans="3:24">
-      <c r="C17" s="40"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="39"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="39"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="42"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="42"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="41"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="42"/>
     </row>
     <row r="18" spans="3:24">
-      <c r="C18" s="40"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="39"/>
-      <c r="S18" s="40"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="38"/>
-      <c r="W18" s="38"/>
-      <c r="X18" s="39"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="42"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="42"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="41"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="42"/>
     </row>
     <row r="19" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="43"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="43"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="46"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="45"/>
+      <c r="P19" s="46"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="45"/>
+      <c r="U19" s="45"/>
+      <c r="V19" s="45"/>
+      <c r="W19" s="45"/>
+      <c r="X19" s="46"/>
     </row>
     <row r="22" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="23" spans="3:24">
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="46"/>
-      <c r="K23" s="44" t="s">
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="49"/>
+      <c r="K23" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="46"/>
-      <c r="S23" s="44" t="s">
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48"/>
+      <c r="P23" s="49"/>
+      <c r="S23" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="T23" s="45"/>
-      <c r="U23" s="45"/>
-      <c r="V23" s="45"/>
-      <c r="W23" s="45"/>
-      <c r="X23" s="46"/>
+      <c r="T23" s="48"/>
+      <c r="U23" s="48"/>
+      <c r="V23" s="48"/>
+      <c r="W23" s="48"/>
+      <c r="X23" s="49"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="40"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="39"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="38"/>
-      <c r="U24" s="38"/>
-      <c r="V24" s="38"/>
-      <c r="W24" s="38"/>
-      <c r="X24" s="39"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="42"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="41"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="41"/>
+      <c r="P24" s="42"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="41"/>
+      <c r="W24" s="41"/>
+      <c r="X24" s="42"/>
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C25" s="37">
+      <c r="C25" s="40">
         <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")</f>
-        <v>124</v>
-      </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="K25" s="37">
+        <v>140</v>
+      </c>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="42"/>
+      <c r="K25" s="40">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")</f>
-        <v>91</v>
-      </c>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="39"/>
-      <c r="S25" s="48">
+        <v>109</v>
+      </c>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="42"/>
+      <c r="S25" s="51">
         <f>K25/C25</f>
-        <v>0.7338709677419355</v>
-      </c>
-      <c r="T25" s="38"/>
-      <c r="U25" s="38"/>
-      <c r="V25" s="38"/>
-      <c r="W25" s="38"/>
-      <c r="X25" s="39"/>
+        <v>0.77857142857142858</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="41"/>
+      <c r="X25" s="42"/>
     </row>
     <row r="26" spans="3:24">
-      <c r="C26" s="40"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="39"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="38"/>
-      <c r="U26" s="38"/>
-      <c r="V26" s="38"/>
-      <c r="W26" s="38"/>
-      <c r="X26" s="39"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="42"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="42"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="41"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="41"/>
+      <c r="W26" s="41"/>
+      <c r="X26" s="42"/>
     </row>
     <row r="27" spans="3:24">
-      <c r="C27" s="40"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="39"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="38"/>
-      <c r="U27" s="38"/>
-      <c r="V27" s="38"/>
-      <c r="W27" s="38"/>
-      <c r="X27" s="39"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="42"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="42"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="42"/>
     </row>
     <row r="28" spans="3:24">
-      <c r="C28" s="40"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="39"/>
-      <c r="S28" s="40"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="38"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="38"/>
-      <c r="X28" s="39"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="42"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="42"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="42"/>
     </row>
     <row r="29" spans="3:24">
-      <c r="C29" s="40"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="39"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="38"/>
-      <c r="V29" s="38"/>
-      <c r="W29" s="38"/>
-      <c r="X29" s="39"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="42"/>
+      <c r="S29" s="43"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="42"/>
     </row>
     <row r="30" spans="3:24">
-      <c r="C30" s="40"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="39"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
-      <c r="V30" s="38"/>
-      <c r="W30" s="38"/>
-      <c r="X30" s="39"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="42"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="42"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="42"/>
     </row>
     <row r="31" spans="3:24">
-      <c r="C31" s="40"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="39"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="38"/>
-      <c r="M31" s="38"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="38"/>
-      <c r="P31" s="39"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="38"/>
-      <c r="U31" s="38"/>
-      <c r="V31" s="38"/>
-      <c r="W31" s="38"/>
-      <c r="X31" s="39"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="42"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="42"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41"/>
+      <c r="X31" s="42"/>
     </row>
     <row r="32" spans="3:24">
-      <c r="C32" s="40"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="38"/>
-      <c r="M32" s="38"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="39"/>
-      <c r="S32" s="40"/>
-      <c r="T32" s="38"/>
-      <c r="U32" s="38"/>
-      <c r="V32" s="38"/>
-      <c r="W32" s="38"/>
-      <c r="X32" s="39"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="42"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="42"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="41"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41"/>
+      <c r="X32" s="42"/>
     </row>
     <row r="33" spans="3:24">
-      <c r="C33" s="40"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="38"/>
-      <c r="M33" s="38"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="38"/>
-      <c r="P33" s="39"/>
-      <c r="S33" s="40"/>
-      <c r="T33" s="38"/>
-      <c r="U33" s="38"/>
-      <c r="V33" s="38"/>
-      <c r="W33" s="38"/>
-      <c r="X33" s="39"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="42"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="42"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="41"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="42"/>
     </row>
     <row r="34" spans="3:24">
-      <c r="C34" s="40"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="39"/>
-      <c r="S34" s="40"/>
-      <c r="T34" s="38"/>
-      <c r="U34" s="38"/>
-      <c r="V34" s="38"/>
-      <c r="W34" s="38"/>
-      <c r="X34" s="39"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="42"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="42"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="41"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="42"/>
     </row>
     <row r="35" spans="3:24">
-      <c r="C35" s="40"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="38"/>
-      <c r="M35" s="38"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="38"/>
-      <c r="P35" s="39"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="38"/>
-      <c r="U35" s="38"/>
-      <c r="V35" s="38"/>
-      <c r="W35" s="38"/>
-      <c r="X35" s="39"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="42"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="42"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41"/>
+      <c r="X35" s="42"/>
     </row>
     <row r="36" spans="3:24">
-      <c r="C36" s="40"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="39"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="38"/>
-      <c r="M36" s="38"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="39"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="38"/>
-      <c r="U36" s="38"/>
-      <c r="V36" s="38"/>
-      <c r="W36" s="38"/>
-      <c r="X36" s="39"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="42"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="41"/>
+      <c r="M36" s="41"/>
+      <c r="N36" s="41"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="42"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="41"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="42"/>
     </row>
     <row r="37" spans="3:24">
-      <c r="C37" s="40"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="39"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="39"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="38"/>
-      <c r="U37" s="38"/>
-      <c r="V37" s="38"/>
-      <c r="W37" s="38"/>
-      <c r="X37" s="39"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="42"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="41"/>
+      <c r="M37" s="41"/>
+      <c r="N37" s="41"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="42"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="41"/>
+      <c r="U37" s="41"/>
+      <c r="V37" s="41"/>
+      <c r="W37" s="41"/>
+      <c r="X37" s="42"/>
     </row>
     <row r="38" spans="3:24">
-      <c r="C38" s="40"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="39"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="38"/>
-      <c r="O38" s="38"/>
-      <c r="P38" s="39"/>
-      <c r="S38" s="40"/>
-      <c r="T38" s="38"/>
-      <c r="U38" s="38"/>
-      <c r="V38" s="38"/>
-      <c r="W38" s="38"/>
-      <c r="X38" s="39"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="42"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="41"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="42"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="41"/>
+      <c r="U38" s="41"/>
+      <c r="V38" s="41"/>
+      <c r="W38" s="41"/>
+      <c r="X38" s="42"/>
     </row>
     <row r="39" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="43"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="42"/>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
-      <c r="P39" s="43"/>
-      <c r="S39" s="41"/>
-      <c r="T39" s="42"/>
-      <c r="U39" s="42"/>
-      <c r="V39" s="42"/>
-      <c r="W39" s="42"/>
-      <c r="X39" s="43"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="46"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+      <c r="O39" s="45"/>
+      <c r="P39" s="46"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="45"/>
+      <c r="U39" s="45"/>
+      <c r="V39" s="45"/>
+      <c r="W39" s="45"/>
+      <c r="X39" s="46"/>
     </row>
     <row r="41" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="42" spans="3:24">
-      <c r="C42" s="44" t="s">
+      <c r="C42" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="46"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="49"/>
     </row>
     <row r="43" spans="3:24">
-      <c r="C43" s="40"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="39"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="42"/>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
@@ -5206,31 +5259,31 @@
       <c r="P43" s="28"/>
     </row>
     <row r="44" spans="3:24" ht="21" customHeight="1">
-      <c r="C44" s="48">
+      <c r="C44" s="51">
         <f>C25/C5</f>
-        <v>0.51452282157676343</v>
-      </c>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="39"/>
+        <v>0.55335968379446643</v>
+      </c>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="42"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="47" t="s">
+      <c r="L44" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="M44" s="38"/>
-      <c r="N44" s="38"/>
-      <c r="O44" s="38"/>
+      <c r="M44" s="41"/>
+      <c r="N44" s="41"/>
+      <c r="O44" s="41"/>
       <c r="P44" s="29"/>
     </row>
     <row r="45" spans="3:24">
-      <c r="C45" s="40"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="39"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="42"/>
       <c r="K45" s="28"/>
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
@@ -5239,12 +5292,12 @@
       <c r="P45" s="29"/>
     </row>
     <row r="46" spans="3:24">
-      <c r="C46" s="40"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="39"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="42"/>
       <c r="K46" s="28"/>
       <c r="L46" s="31"/>
       <c r="M46" s="28" t="s">
@@ -5255,12 +5308,12 @@
       <c r="P46" s="28"/>
     </row>
     <row r="47" spans="3:24">
-      <c r="C47" s="40"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="39"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="42"/>
       <c r="K47" s="28"/>
       <c r="L47" s="32"/>
       <c r="M47" s="28" t="s">
@@ -5271,12 +5324,12 @@
       <c r="P47" s="28"/>
     </row>
     <row r="48" spans="3:24">
-      <c r="C48" s="40"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="39"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="42"/>
       <c r="K48" s="28"/>
       <c r="L48" s="33"/>
       <c r="M48" s="28" t="s">
@@ -5287,12 +5340,12 @@
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="3:16">
-      <c r="C49" s="40"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="39"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="42"/>
       <c r="K49" s="28"/>
       <c r="L49" s="34"/>
       <c r="M49" s="28" t="s">
@@ -5303,12 +5356,12 @@
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="3:16">
-      <c r="C50" s="40"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="39"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="42"/>
       <c r="K50" s="28"/>
       <c r="L50" s="35"/>
       <c r="M50" s="28" t="s">
@@ -5319,12 +5372,12 @@
       <c r="P50" s="28"/>
     </row>
     <row r="51" spans="3:16">
-      <c r="C51" s="40"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="39"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="42"/>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -5333,250 +5386,238 @@
       <c r="P51" s="28"/>
     </row>
     <row r="52" spans="3:16">
-      <c r="C52" s="40"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="39"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="42"/>
     </row>
     <row r="53" spans="3:16">
-      <c r="C53" s="40"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="39"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="42"/>
     </row>
     <row r="54" spans="3:16">
-      <c r="C54" s="40"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="39"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="42"/>
     </row>
     <row r="55" spans="3:16">
-      <c r="C55" s="40"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="39"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="42"/>
     </row>
     <row r="56" spans="3:16">
-      <c r="C56" s="40"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="39"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="42"/>
     </row>
     <row r="57" spans="3:16">
-      <c r="C57" s="40"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="39"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="42"/>
     </row>
     <row r="58" spans="3:16" ht="15.75" customHeight="1">
-      <c r="C58" s="41"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="43"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="45"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="46"/>
     </row>
     <row r="62" spans="3:16">
-      <c r="C62" s="49" t="s">
+      <c r="C62" s="37" t="s">
+        <v>585</v>
+      </c>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="H62" s="37" t="s">
+        <v>586</v>
+      </c>
+      <c r="I62" s="37"/>
+      <c r="J62" s="37"/>
+      <c r="K62" s="37"/>
+      <c r="M62" s="37" t="s">
+        <v>587</v>
+      </c>
+      <c r="N62" s="37"/>
+      <c r="O62" s="37"/>
+      <c r="P62" s="37"/>
+    </row>
+    <row r="63" spans="3:16">
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="37"/>
+      <c r="J63" s="37"/>
+      <c r="K63" s="37"/>
+      <c r="M63" s="37"/>
+      <c r="N63" s="37"/>
+      <c r="O63" s="37"/>
+      <c r="P63" s="37"/>
+    </row>
+    <row r="64" spans="3:16">
+      <c r="C64" s="38">
+        <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
+        <v>250</v>
+      </c>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+      <c r="H64" s="38">
+        <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
+        <v>188</v>
+      </c>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="38"/>
+      <c r="M64" s="39">
+        <f t="shared" ref="M64" si="0">H64/C64</f>
+        <v>0.752</v>
+      </c>
+      <c r="N64" s="39"/>
+      <c r="O64" s="39"/>
+      <c r="P64" s="39"/>
+    </row>
+    <row r="65" spans="3:16">
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="38"/>
+      <c r="M65" s="39"/>
+      <c r="N65" s="39"/>
+      <c r="O65" s="39"/>
+      <c r="P65" s="39"/>
+    </row>
+    <row r="66" spans="3:16">
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="38"/>
+      <c r="K66" s="38"/>
+      <c r="M66" s="39"/>
+      <c r="N66" s="39"/>
+      <c r="O66" s="39"/>
+      <c r="P66" s="39"/>
+    </row>
+    <row r="69" spans="3:16">
+      <c r="C69" s="37" t="s">
+        <v>588</v>
+      </c>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="H69" s="37" t="s">
         <v>589</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="49"/>
-      <c r="F62" s="49"/>
-      <c r="H62" s="49" t="s">
-        <v>590</v>
-      </c>
-      <c r="I62" s="49"/>
-      <c r="J62" s="49"/>
-      <c r="K62" s="49"/>
-      <c r="M62" s="49" t="s">
-        <v>591</v>
-      </c>
-      <c r="N62" s="49"/>
-      <c r="O62" s="49"/>
-      <c r="P62" s="49"/>
-    </row>
-    <row r="63" spans="3:16">
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="H63" s="49"/>
-      <c r="I63" s="49"/>
-      <c r="J63" s="49"/>
-      <c r="K63" s="49"/>
-      <c r="M63" s="49"/>
-      <c r="N63" s="49"/>
-      <c r="O63" s="49"/>
-      <c r="P63" s="49"/>
-    </row>
-    <row r="64" spans="3:16">
-      <c r="C64" s="50">
-        <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
-        <v>215</v>
-      </c>
-      <c r="D64" s="50"/>
-      <c r="E64" s="50"/>
-      <c r="F64" s="50"/>
-      <c r="H64" s="50">
-        <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
-        <v>175</v>
-      </c>
-      <c r="I64" s="50"/>
-      <c r="J64" s="50"/>
-      <c r="K64" s="50"/>
-      <c r="M64" s="51">
-        <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.81395348837209303</v>
-      </c>
-      <c r="N64" s="51"/>
-      <c r="O64" s="51"/>
-      <c r="P64" s="51"/>
-    </row>
-    <row r="65" spans="3:16">
-      <c r="C65" s="50"/>
-      <c r="D65" s="50"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="H65" s="50"/>
-      <c r="I65" s="50"/>
-      <c r="J65" s="50"/>
-      <c r="K65" s="50"/>
-      <c r="M65" s="51"/>
-      <c r="N65" s="51"/>
-      <c r="O65" s="51"/>
-      <c r="P65" s="51"/>
-    </row>
-    <row r="66" spans="3:16">
-      <c r="C66" s="50"/>
-      <c r="D66" s="50"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="H66" s="50"/>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="M66" s="51"/>
-      <c r="N66" s="51"/>
-      <c r="O66" s="51"/>
-      <c r="P66" s="51"/>
-    </row>
-    <row r="69" spans="3:16">
-      <c r="C69" s="49" t="s">
-        <v>592</v>
-      </c>
-      <c r="D69" s="49"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="H69" s="49" t="s">
-        <v>593</v>
-      </c>
-      <c r="I69" s="49"/>
-      <c r="J69" s="49"/>
-      <c r="K69" s="49"/>
-      <c r="M69" s="49" t="s">
-        <v>591</v>
-      </c>
-      <c r="N69" s="49"/>
-      <c r="O69" s="49"/>
-      <c r="P69" s="49"/>
+      <c r="I69" s="37"/>
+      <c r="J69" s="37"/>
+      <c r="K69" s="37"/>
+      <c r="M69" s="37" t="s">
+        <v>587</v>
+      </c>
+      <c r="N69" s="37"/>
+      <c r="O69" s="37"/>
+      <c r="P69" s="37"/>
     </row>
     <row r="70" spans="3:16">
-      <c r="C70" s="49"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="49"/>
-      <c r="J70" s="49"/>
-      <c r="K70" s="49"/>
-      <c r="M70" s="49"/>
-      <c r="N70" s="49"/>
-      <c r="O70" s="49"/>
-      <c r="P70" s="49"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="H70" s="37"/>
+      <c r="I70" s="37"/>
+      <c r="J70" s="37"/>
+      <c r="K70" s="37"/>
+      <c r="M70" s="37"/>
+      <c r="N70" s="37"/>
+      <c r="O70" s="37"/>
+      <c r="P70" s="37"/>
     </row>
     <row r="71" spans="3:16">
-      <c r="C71" s="50">
+      <c r="C71" s="38">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
         <v>71</v>
       </c>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="H71" s="50">
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="H71" s="38">
         <f>COUNTIF(Perfil!I:I,"Si")+COUNTIF(Credenciales!I:I,"Si")+COUNTIF(Videollamadas!I:I,"Si")</f>
         <v>60</v>
       </c>
-      <c r="I71" s="50"/>
-      <c r="J71" s="50"/>
-      <c r="K71" s="50"/>
-      <c r="M71" s="51">
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="38"/>
+      <c r="M71" s="39">
         <f t="shared" ref="M71" si="1">H71/C71</f>
         <v>0.84507042253521125</v>
       </c>
-      <c r="N71" s="51"/>
-      <c r="O71" s="51"/>
-      <c r="P71" s="51"/>
+      <c r="N71" s="39"/>
+      <c r="O71" s="39"/>
+      <c r="P71" s="39"/>
     </row>
     <row r="72" spans="3:16">
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="H72" s="50"/>
-      <c r="I72" s="50"/>
-      <c r="J72" s="50"/>
-      <c r="K72" s="50"/>
-      <c r="M72" s="51"/>
-      <c r="N72" s="51"/>
-      <c r="O72" s="51"/>
-      <c r="P72" s="51"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="38"/>
+      <c r="M72" s="39"/>
+      <c r="N72" s="39"/>
+      <c r="O72" s="39"/>
+      <c r="P72" s="39"/>
     </row>
     <row r="73" spans="3:16">
-      <c r="C73" s="50"/>
-      <c r="D73" s="50"/>
-      <c r="E73" s="50"/>
-      <c r="F73" s="50"/>
-      <c r="H73" s="50"/>
-      <c r="I73" s="50"/>
-      <c r="J73" s="50"/>
-      <c r="K73" s="50"/>
-      <c r="M73" s="51"/>
-      <c r="N73" s="51"/>
-      <c r="O73" s="51"/>
-      <c r="P73" s="51"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="M73" s="39"/>
+      <c r="N73" s="39"/>
+      <c r="O73" s="39"/>
+      <c r="P73" s="39"/>
     </row>
     <row r="76" spans="3:16">
       <c r="C76" s="36" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C69:F70"/>
-    <mergeCell ref="C71:F73"/>
-    <mergeCell ref="H69:K70"/>
-    <mergeCell ref="H71:K73"/>
-    <mergeCell ref="M69:P70"/>
-    <mergeCell ref="M71:P73"/>
-    <mergeCell ref="C62:F63"/>
-    <mergeCell ref="C64:F66"/>
-    <mergeCell ref="H62:K63"/>
-    <mergeCell ref="H64:K66"/>
-    <mergeCell ref="M62:P63"/>
-    <mergeCell ref="M64:P66"/>
     <mergeCell ref="K5:P19"/>
     <mergeCell ref="K25:P39"/>
     <mergeCell ref="S3:X4"/>
@@ -5592,6 +5633,18 @@
     <mergeCell ref="C3:H4"/>
     <mergeCell ref="C25:H39"/>
     <mergeCell ref="K23:P24"/>
+    <mergeCell ref="C62:F63"/>
+    <mergeCell ref="C64:F66"/>
+    <mergeCell ref="H62:K63"/>
+    <mergeCell ref="H64:K66"/>
+    <mergeCell ref="M62:P63"/>
+    <mergeCell ref="M64:P66"/>
+    <mergeCell ref="C69:F70"/>
+    <mergeCell ref="C71:F73"/>
+    <mergeCell ref="H69:K70"/>
+    <mergeCell ref="H71:K73"/>
+    <mergeCell ref="M69:P70"/>
+    <mergeCell ref="M71:P73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5644,11 +5697,11 @@
         <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="55" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="53"/>
@@ -5657,7 +5710,7 @@
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
       <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="H2" s="56"/>
       <c r="I2" s="12" t="s">
         <v>27</v>
       </c>
@@ -5666,7 +5719,7 @@
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -5894,7 +5947,7 @@
       <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="52" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -5940,7 +5993,7 @@
         <v>27</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>27</v>
@@ -5960,7 +6013,7 @@
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="54" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -6053,7 +6106,7 @@
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="52" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -6254,7 +6307,7 @@
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="54" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -6374,7 +6427,7 @@
       <c r="A32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="52" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="22" t="s">
@@ -6521,7 +6574,7 @@
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="54" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -6574,7 +6627,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A40" s="52" t="s">
+      <c r="A40" s="55" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="53"/>
@@ -6583,7 +6636,7 @@
       <c r="E40" s="53"/>
       <c r="F40" s="53"/>
       <c r="G40" s="53"/>
-      <c r="H40" s="54"/>
+      <c r="H40" s="56"/>
       <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
@@ -6592,7 +6645,7 @@
       <c r="A41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="52" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="22" t="s">
@@ -6820,7 +6873,7 @@
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="56" t="s">
+      <c r="B50" s="54" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -6866,7 +6919,7 @@
         <v>27</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>27</v>
@@ -6886,7 +6939,7 @@
       <c r="A53" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="55" t="s">
+      <c r="B53" s="52" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="22" t="s">
@@ -6979,7 +7032,7 @@
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="56" t="s">
+      <c r="B57" s="54" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -7180,7 +7233,7 @@
       <c r="A65" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="55" t="s">
+      <c r="B65" s="52" t="s">
         <v>90</v>
       </c>
       <c r="C65" s="22" t="s">
@@ -7300,7 +7353,7 @@
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="56" t="s">
+      <c r="B70" s="54" t="s">
         <v>104</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -7447,7 +7500,7 @@
       <c r="A76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="55" t="s">
+      <c r="B76" s="52" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -7500,7 +7553,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A78" s="52" t="s">
+      <c r="A78" s="55" t="s">
         <v>140</v>
       </c>
       <c r="B78" s="53"/>
@@ -7509,7 +7562,7 @@
       <c r="E78" s="53"/>
       <c r="F78" s="53"/>
       <c r="G78" s="53"/>
-      <c r="H78" s="54"/>
+      <c r="H78" s="56"/>
       <c r="I78" s="12" t="s">
         <v>27</v>
       </c>
@@ -7518,7 +7571,7 @@
       <c r="A79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="56" t="s">
+      <c r="B79" s="54" t="s">
         <v>141</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -7609,7 +7662,7 @@
       <c r="A83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B83" s="55" t="s">
+      <c r="B83" s="52" t="s">
         <v>153</v>
       </c>
       <c r="C83" s="22" t="s">
@@ -7658,7 +7711,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A85" s="52" t="s">
+      <c r="A85" s="55" t="s">
         <v>159</v>
       </c>
       <c r="B85" s="53"/>
@@ -7667,7 +7720,7 @@
       <c r="E85" s="53"/>
       <c r="F85" s="53"/>
       <c r="G85" s="53"/>
-      <c r="H85" s="54"/>
+      <c r="H85" s="56"/>
       <c r="I85" s="12" t="s">
         <v>27</v>
       </c>
@@ -7676,7 +7729,7 @@
       <c r="A86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="56" t="s">
+      <c r="B86" s="54" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -7767,7 +7820,7 @@
       <c r="A90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="55" t="s">
+      <c r="B90" s="52" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -7827,12 +7880,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B86:B88"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="B32:B36"/>
@@ -7849,6 +7896,12 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="B19:B25"/>
     <mergeCell ref="B57:B63"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B86:B88"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="153" priority="564" operator="equal">
@@ -8033,7 +8086,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
@@ -8074,11 +8127,11 @@
         <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="55" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="53"/>
@@ -8087,13 +8140,13 @@
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
       <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:9" ht="76.5" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -8234,7 +8287,7 @@
       <c r="A9" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="52" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -8352,7 +8405,7 @@
       <c r="A14" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="54" t="s">
         <v>192</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -8495,18 +8548,27 @@
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" ht="60">
       <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="54" t="s">
-        <v>208</v>
+      <c r="B20" s="56" t="s">
+        <v>612</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>209</v>
+        <v>592</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>595</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>27</v>
@@ -8515,233 +8577,243 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" ht="60">
       <c r="A21" s="6" t="s">
         <v>167</v>
       </c>
       <c r="B21" s="53"/>
       <c r="C21" s="6" t="s">
-        <v>210</v>
+        <v>596</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>599</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>27</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-    </row>
-    <row r="23" spans="1:9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="60">
+      <c r="A22" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="75">
       <c r="A23" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B23" s="54" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>212</v>
+        <v>604</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>607</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="60">
       <c r="A24" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B24" s="53"/>
+        <v>179</v>
+      </c>
       <c r="C24" s="6" t="s">
-        <v>168</v>
+        <v>608</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>610</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>28</v>
-      </c>
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B26" s="53"/>
+        <v>161</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>208</v>
+      </c>
       <c r="C26" s="6" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B27" s="53"/>
       <c r="C27" s="6" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>28</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A28" s="52" t="s">
-        <v>216</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
-    </row>
-    <row r="29" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A29" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B29" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>166</v>
+      <c r="C28" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" s="53"/>
+      <c r="C29" s="6" t="s">
+        <v>211</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I29" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="91.5" customHeight="1">
-      <c r="A30" s="18" t="s">
-        <v>167</v>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="B30" s="53"/>
-      <c r="C30" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>170</v>
+      <c r="C30" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I30" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A31" s="18" t="s">
-        <v>171</v>
+    <row r="31" spans="1:9" ht="23.25" customHeight="1">
+      <c r="A31" s="55" t="s">
+        <v>213</v>
       </c>
       <c r="B31" s="53"/>
-      <c r="C31" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>27</v>
-      </c>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="56"/>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B32" s="53"/>
+        <v>161</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>162</v>
+      </c>
       <c r="C32" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="D32" s="18"/>
+        <v>163</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>164</v>
+      </c>
       <c r="E32" s="18" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>27</v>
@@ -8753,89 +8825,100 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="76.5" customHeight="1">
+    <row r="33" spans="1:9" ht="91.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B33" s="53"/>
       <c r="C33" s="18" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="D33" s="18"/>
       <c r="E33" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A34" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" s="53"/>
+      <c r="C34" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A35" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="53"/>
+      <c r="C35" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A36" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B36" s="53"/>
+      <c r="C36" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F36" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="G33" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="19"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-    </row>
-    <row r="35" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A35" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B35" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A36" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="B36" s="53"/>
-      <c r="C36" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>185</v>
-      </c>
       <c r="G36" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>27</v>
@@ -8844,251 +8927,269 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A37" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>27</v>
-      </c>
+    <row r="37" spans="1:9">
+      <c r="A37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
     </row>
     <row r="38" spans="1:9" ht="76.5" customHeight="1">
       <c r="A38" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A39" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="53"/>
+      <c r="C39" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A40" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="53"/>
+      <c r="C40" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A41" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B38" s="53"/>
-      <c r="C38" s="22" t="s">
+      <c r="B41" s="53"/>
+      <c r="C41" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22" t="s">
+      <c r="D41" s="22"/>
+      <c r="E41" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F38" s="22" t="s">
+      <c r="F41" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="G38" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="19"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-    </row>
-    <row r="40" spans="1:9" ht="106.5" customHeight="1">
-      <c r="A40" s="18" t="s">
+      <c r="G41" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+    </row>
+    <row r="43" spans="1:9" ht="106.5" customHeight="1">
+      <c r="A43" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B40" s="56" t="s">
+      <c r="B43" s="54" t="s">
         <v>192</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C43" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D43" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E43" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F43" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="G40" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I40" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="106.5" customHeight="1">
-      <c r="A41" s="18" t="s">
+      <c r="G43" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="106.5" customHeight="1">
+      <c r="A44" s="18" t="s">
         <v>167</v>
-      </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A42" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="F42" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A43" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B43" s="53"/>
-      <c r="C43" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="F43" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A44" s="18" t="s">
-        <v>179</v>
       </c>
       <c r="B44" s="53"/>
       <c r="C44" s="18" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="D44" s="18" t="s">
         <v>193</v>
       </c>
       <c r="E44" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A45" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B45" s="53"/>
+      <c r="C45" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A46" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" s="53"/>
+      <c r="C46" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A47" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B47" s="53"/>
+      <c r="C47" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F47" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="G44" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="19"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B46" s="54" t="s">
-        <v>208</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B47" s="53"/>
-      <c r="C47" s="6" t="s">
-        <v>210</v>
-      </c>
       <c r="G47" s="12" t="s">
         <v>27</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -9101,498 +9202,495 @@
       <c r="G48" s="19"/>
       <c r="H48" s="19"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" ht="60">
       <c r="A49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="54" t="s">
-        <v>211</v>
+      <c r="B49" s="56" t="s">
+        <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>212</v>
+        <v>592</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>595</v>
       </c>
       <c r="G49" s="12" t="s">
         <v>27</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="60">
       <c r="A50" s="6" t="s">
         <v>167</v>
       </c>
       <c r="B50" s="53"/>
       <c r="C50" s="6" t="s">
-        <v>168</v>
+        <v>596</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>599</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="60">
       <c r="A51" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B51" s="53"/>
       <c r="C51" s="6" t="s">
-        <v>213</v>
+        <v>600</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>603</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="75">
       <c r="A52" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B52" s="53"/>
       <c r="C52" s="6" t="s">
-        <v>214</v>
+        <v>604</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>607</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="60">
       <c r="A53" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B53" s="53"/>
       <c r="C53" s="6" t="s">
-        <v>215</v>
+        <v>608</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>610</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>27</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A54" s="52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="19"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" s="53"/>
+      <c r="C56" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" s="53"/>
+      <c r="C57" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B58" s="53"/>
+      <c r="C58" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="53"/>
+      <c r="C59" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="23.25" customHeight="1">
+      <c r="A60" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="B54" s="53"/>
-      <c r="C54" s="53"/>
-      <c r="D54" s="53"/>
-      <c r="E54" s="53"/>
-      <c r="F54" s="53"/>
-      <c r="G54" s="53"/>
-      <c r="H54" s="54"/>
-    </row>
-    <row r="55" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A55" s="18" t="s">
+      <c r="B60" s="53"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="56"/>
+    </row>
+    <row r="61" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A61" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B61" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C61" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D61" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E61" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="F55" s="18" t="s">
+      <c r="F61" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="G55" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H55" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I55" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="91.5" customHeight="1">
-      <c r="A56" s="18" t="s">
+      <c r="G61" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="91.5" customHeight="1">
+      <c r="A62" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="53"/>
-      <c r="C56" s="18" t="s">
+      <c r="B62" s="53"/>
+      <c r="C62" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18" t="s">
+      <c r="D62" s="18"/>
+      <c r="E62" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="F56" s="18" t="s">
+      <c r="F62" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="G56" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A57" s="18" t="s">
+      <c r="G62" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A63" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B57" s="53"/>
-      <c r="C57" s="18" t="s">
+      <c r="B63" s="53"/>
+      <c r="C63" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D63" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E63" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F57" s="18" t="s">
+      <c r="F63" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="G57" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A58" s="18" t="s">
+      <c r="G63" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H63" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A64" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B58" s="53"/>
-      <c r="C58" s="18" t="s">
+      <c r="B64" s="53"/>
+      <c r="C64" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18" t="s">
+      <c r="D64" s="18"/>
+      <c r="E64" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F58" s="18" t="s">
+      <c r="F64" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G58" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A59" s="18" t="s">
+      <c r="G64" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H64" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A65" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B59" s="53"/>
-      <c r="C59" s="18" t="s">
+      <c r="B65" s="53"/>
+      <c r="C65" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18" t="s">
+      <c r="D65" s="18"/>
+      <c r="E65" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="F59" s="18" t="s">
+      <c r="F65" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="G59" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="19"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-    </row>
-    <row r="61" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A61" s="22" t="s">
+      <c r="G65" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H65" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="19"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+    </row>
+    <row r="67" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A67" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="55" t="s">
+      <c r="B67" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="C67" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D67" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E61" s="22" t="s">
+      <c r="E67" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="F61" s="22" t="s">
+      <c r="F67" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="G61" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A62" s="22" t="s">
+      <c r="G67" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A68" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B62" s="53"/>
-      <c r="C62" s="22" t="s">
+      <c r="B68" s="53"/>
+      <c r="C68" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D68" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="E68" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="F62" s="22" t="s">
+      <c r="F68" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="G62" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A63" s="22" t="s">
+      <c r="G68" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A69" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B63" s="53"/>
-      <c r="C63" s="22" t="s">
+      <c r="B69" s="53"/>
+      <c r="C69" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D69" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E69" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F69" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="G63" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H63" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I63" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A64" s="22" t="s">
+      <c r="G69" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A70" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B64" s="53"/>
-      <c r="C64" s="22" t="s">
+      <c r="B70" s="53"/>
+      <c r="C70" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22" t="s">
+      <c r="D70" s="22"/>
+      <c r="E70" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F64" s="22" t="s">
+      <c r="F70" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="G64" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="19"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-    </row>
-    <row r="66" spans="1:9" ht="106.5" customHeight="1">
-      <c r="A66" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B66" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="G66" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H66" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="106.5" customHeight="1">
-      <c r="A67" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B67" s="53"/>
-      <c r="C67" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="G67" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H67" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A68" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="B68" s="53"/>
-      <c r="C68" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="G68" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H68" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A69" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B69" s="53"/>
-      <c r="C69" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="G69" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H69" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I69" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A70" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="B70" s="53"/>
-      <c r="C70" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="F70" s="18" t="s">
-        <v>207</v>
-      </c>
       <c r="G70" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>27</v>
@@ -9611,15 +9709,24 @@
       <c r="G71" s="19"/>
       <c r="H71" s="19"/>
     </row>
-    <row r="72" spans="1:9">
-      <c r="A72" s="6" t="s">
+    <row r="72" spans="1:9" ht="106.5" customHeight="1">
+      <c r="A72" s="18" t="s">
         <v>161</v>
       </c>
       <c r="B72" s="54" t="s">
-        <v>208</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>209</v>
+        <v>192</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>195</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>28</v>
@@ -9631,445 +9738,470 @@
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
-      <c r="A73" s="6" t="s">
+    <row r="73" spans="1:9" ht="106.5" customHeight="1">
+      <c r="A73" s="18" t="s">
         <v>167</v>
       </c>
       <c r="B73" s="53"/>
-      <c r="C73" s="6" t="s">
-        <v>210</v>
+      <c r="C73" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>197</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="A74" s="19"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-    </row>
-    <row r="75" spans="1:9">
-      <c r="A75" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A74" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" s="53"/>
+      <c r="C74" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A75" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" s="53"/>
+      <c r="C75" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A76" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B76" s="53"/>
+      <c r="C76" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="19"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+    </row>
+    <row r="78" spans="1:9" ht="60">
+      <c r="A78" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B75" s="54" t="s">
-        <v>211</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I75" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="6" t="s">
+      <c r="B78" s="56" t="s">
+        <v>611</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="60">
+      <c r="A79" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="B76" s="53"/>
-      <c r="C76" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B77" s="53"/>
-      <c r="C77" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="G77" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H77" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I77" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B78" s="53"/>
-      <c r="C78" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G78" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H78" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I78" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="B79" s="53"/>
       <c r="C79" s="6" t="s">
-        <v>215</v>
+        <v>596</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>599</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>27</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A80" s="52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="60">
+      <c r="A80" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G80" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="75">
+      <c r="A81" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="60">
+      <c r="A82" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="G82" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="19"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="19"/>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B84" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H84" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" s="53"/>
+      <c r="C85" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H85" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" s="53"/>
+      <c r="C86" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G86" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87" s="53"/>
+      <c r="C87" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="G87" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H87" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B88" s="53"/>
+      <c r="C88" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G88" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H88" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="23.25" customHeight="1">
+      <c r="A89" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="54"/>
-    </row>
-    <row r="81" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A81" s="18" t="s">
+      <c r="B89" s="53"/>
+      <c r="C89" s="53"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53"/>
+      <c r="H89" s="56"/>
+    </row>
+    <row r="90" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A90" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B81" s="56" t="s">
+      <c r="B90" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C90" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="D90" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="E81" s="18" t="s">
+      <c r="E90" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="F81" s="18" t="s">
+      <c r="F90" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="G81" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H81" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="91.5" customHeight="1">
-      <c r="A82" s="18" t="s">
+      <c r="G90" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I90" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="91.5" customHeight="1">
+      <c r="A91" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B82" s="53"/>
-      <c r="C82" s="18" t="s">
+      <c r="B91" s="53"/>
+      <c r="C91" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18" t="s">
+      <c r="D91" s="18"/>
+      <c r="E91" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="F82" s="18" t="s">
+      <c r="F91" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="G82" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H82" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I82" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A83" s="18" t="s">
+      <c r="G91" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H91" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I91" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A92" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B83" s="53"/>
-      <c r="C83" s="18" t="s">
+      <c r="B92" s="53"/>
+      <c r="C92" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="D83" s="18" t="s">
+      <c r="D92" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="E92" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F83" s="18" t="s">
+      <c r="F92" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="G83" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H83" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I83" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A84" s="18" t="s">
+      <c r="G92" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H92" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I92" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A93" s="18" t="s">
         <v>176</v>
-      </c>
-      <c r="B84" s="53"/>
-      <c r="C84" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="D84" s="18"/>
-      <c r="E84" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="F84" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H84" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A85" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="B85" s="53"/>
-      <c r="C85" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="F85" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="G85" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H85" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I85" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" s="19"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="19"/>
-    </row>
-    <row r="87" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A87" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B87" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="C87" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="D87" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E87" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="F87" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="G87" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H87" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I87" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A88" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="B88" s="53"/>
-      <c r="C88" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D88" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E88" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="F88" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="G88" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H88" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I88" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A89" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="B89" s="53"/>
-      <c r="C89" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="D89" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E89" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="F89" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="G89" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I89" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A90" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="B90" s="53"/>
-      <c r="C90" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="D90" s="22"/>
-      <c r="E90" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="F90" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="G90" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H90" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I90" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" s="19"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20"/>
-      <c r="E91" s="20"/>
-      <c r="F91" s="20"/>
-      <c r="G91" s="19"/>
-      <c r="H91" s="19"/>
-    </row>
-    <row r="92" spans="1:9" ht="106.5" customHeight="1">
-      <c r="A92" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B92" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="C92" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E92" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="F92" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="G92" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H92" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="106.5" customHeight="1">
-      <c r="A93" s="18" t="s">
-        <v>167</v>
       </c>
       <c r="B93" s="53"/>
       <c r="C93" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D93" s="18" t="s">
-        <v>193</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="D93" s="18"/>
       <c r="E93" s="18" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F93" s="18" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H93" s="12" t="s">
         <v>27</v>
@@ -10078,25 +10210,23 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="121.5" customHeight="1">
+    <row r="94" spans="1:9" ht="76.5" customHeight="1">
       <c r="A94" s="18" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B94" s="53"/>
       <c r="C94" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>193</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D94" s="18"/>
       <c r="E94" s="18" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="F94" s="18" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H94" s="12" t="s">
         <v>27</v>
@@ -10105,106 +10235,122 @@
         <v>27</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A95" s="18" t="s">
+    <row r="95" spans="1:9">
+      <c r="A95" s="19"/>
+      <c r="B95" s="20"/>
+      <c r="C95" s="20"/>
+      <c r="D95" s="20"/>
+      <c r="E95" s="20"/>
+      <c r="F95" s="20"/>
+      <c r="G95" s="19"/>
+      <c r="H95" s="19"/>
+    </row>
+    <row r="96" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A96" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B96" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D96" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E96" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="F96" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A97" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B97" s="53"/>
+      <c r="C97" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D97" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E97" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="F97" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="G97" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I97" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A98" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B98" s="53"/>
+      <c r="C98" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D98" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E98" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="F98" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="G98" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H98" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I98" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A99" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B95" s="53"/>
-      <c r="C95" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="D95" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="E95" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="F95" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="G95" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H95" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I95" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A96" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="B96" s="53"/>
-      <c r="C96" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="D96" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E96" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="F96" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="G96" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H96" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I96" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9">
-      <c r="A97" s="19"/>
-      <c r="B97" s="20"/>
-      <c r="C97" s="20"/>
-      <c r="D97" s="20"/>
-      <c r="E97" s="20"/>
-      <c r="F97" s="20"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-    </row>
-    <row r="98" spans="1:9">
-      <c r="A98" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B98" s="54" t="s">
-        <v>208</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G98" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H98" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I98" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" s="6" t="s">
-        <v>167</v>
-      </c>
       <c r="B99" s="53"/>
-      <c r="C99" s="6" t="s">
-        <v>210</v>
+      <c r="C99" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D99" s="22"/>
+      <c r="E99" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F99" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I99" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -10217,124 +10363,415 @@
       <c r="G100" s="19"/>
       <c r="H100" s="19"/>
     </row>
-    <row r="101" spans="1:9">
-      <c r="A101" s="6" t="s">
+    <row r="101" spans="1:9" ht="106.5" customHeight="1">
+      <c r="A101" s="18" t="s">
         <v>161</v>
       </c>
       <c r="B101" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="C101" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D101" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E101" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F101" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H101" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I101" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="106.5" customHeight="1">
+      <c r="A102" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B102" s="53"/>
+      <c r="C102" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F102" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="G102" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A103" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B103" s="53"/>
+      <c r="C103" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E103" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F103" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="G103" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H103" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A104" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B104" s="53"/>
+      <c r="C104" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="G104" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H104" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A105" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B105" s="53"/>
+      <c r="C105" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E105" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="F105" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="G105" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I105" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="19"/>
+      <c r="B106" s="20"/>
+      <c r="C106" s="20"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="19"/>
+      <c r="H106" s="19"/>
+    </row>
+    <row r="107" spans="1:9" ht="60">
+      <c r="A107" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B107" s="56" t="s">
+        <v>591</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="G107" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="60">
+      <c r="A108" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B108" s="53"/>
+      <c r="C108" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="G108" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H108" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="60">
+      <c r="A109" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G109" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H109" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="75">
+      <c r="A110" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="G110" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H110" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="60">
+      <c r="A111" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="G111" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="19"/>
+      <c r="B112" s="20"/>
+      <c r="C112" s="20"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="20"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="19"/>
+      <c r="H112" s="19"/>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B113" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H113" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I113" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B114" s="53"/>
+      <c r="C114" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G114" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H114" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I114" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B115" s="53"/>
+      <c r="C115" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G115" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H115" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B116" s="53"/>
+      <c r="C116" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="G116" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B117" s="53"/>
+      <c r="C117" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="G101" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H101" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I101" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9">
-      <c r="A102" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B102" s="53"/>
-      <c r="C102" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="G102" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H102" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I102" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
-      <c r="A103" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B103" s="53"/>
-      <c r="C103" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="G103" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H103" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I103" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
-      <c r="A104" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B104" s="53"/>
-      <c r="C104" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G104" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H104" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I104" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B105" s="53"/>
-      <c r="C105" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G105" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H105" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I105" s="12" t="s">
-        <v>28</v>
+      <c r="G117" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="B107:B108"/>
     <mergeCell ref="B9:B12"/>
-    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B96:B99"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="B90:B94"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B75:B79"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="B66:B70"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B61:B65"/>
     <mergeCell ref="B55:B59"/>
-    <mergeCell ref="B49:B53"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="B43:B47"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="111" priority="525" operator="equal">
@@ -10344,7 +10781,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:G27">
+  <conditionalFormatting sqref="G26:G30">
     <cfRule type="cellIs" dxfId="109" priority="446" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10352,7 +10789,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29:G33">
+  <conditionalFormatting sqref="G32:G36">
     <cfRule type="cellIs" dxfId="107" priority="414" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10360,7 +10797,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G46:G47">
+  <conditionalFormatting sqref="G49:G53">
     <cfRule type="cellIs" dxfId="105" priority="380" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10368,7 +10805,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G49:G53">
+  <conditionalFormatting sqref="G55:G59">
     <cfRule type="cellIs" dxfId="103" priority="376" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10376,7 +10813,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G55:G59">
+  <conditionalFormatting sqref="G61:G65">
     <cfRule type="cellIs" dxfId="101" priority="344" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10384,7 +10821,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G72:G73">
+  <conditionalFormatting sqref="G78:G82">
     <cfRule type="cellIs" dxfId="99" priority="309" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10392,7 +10829,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G75:G79">
+  <conditionalFormatting sqref="G84:G88">
     <cfRule type="cellIs" dxfId="97" priority="305" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10400,7 +10837,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G81:G96">
+  <conditionalFormatting sqref="G90:G105">
     <cfRule type="cellIs" dxfId="95" priority="244" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10408,7 +10845,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G98:G99">
+  <conditionalFormatting sqref="G107:G111">
     <cfRule type="cellIs" dxfId="93" priority="240" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10416,7 +10853,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G101:G105">
+  <conditionalFormatting sqref="G113:G117">
     <cfRule type="cellIs" dxfId="91" priority="236" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10424,7 +10861,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:H22">
+  <conditionalFormatting sqref="G3:H25">
     <cfRule type="cellIs" dxfId="89" priority="212" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10432,7 +10869,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34:H45">
+  <conditionalFormatting sqref="G37:H48">
     <cfRule type="cellIs" dxfId="87" priority="384" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10440,7 +10877,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G48:H48">
+  <conditionalFormatting sqref="G54:H54">
     <cfRule type="cellIs" dxfId="85" priority="434" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10448,7 +10885,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G60:H71">
+  <conditionalFormatting sqref="G66:H77">
     <cfRule type="cellIs" dxfId="83" priority="195" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10456,7 +10893,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G74:H74">
+  <conditionalFormatting sqref="G83:H83">
     <cfRule type="cellIs" dxfId="81" priority="364" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10464,7 +10901,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G97:H97">
+  <conditionalFormatting sqref="G106:H106">
     <cfRule type="cellIs" dxfId="79" priority="296" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10472,7 +10909,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G100:H100">
+  <conditionalFormatting sqref="G112:H112">
     <cfRule type="cellIs" dxfId="77" priority="294" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10480,7 +10917,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23:H33">
+  <conditionalFormatting sqref="H26:H36">
     <cfRule type="cellIs" dxfId="75" priority="216" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10488,7 +10925,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H46:H59">
+  <conditionalFormatting sqref="H49:H65">
     <cfRule type="cellIs" dxfId="73" priority="204" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10496,7 +10933,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H72:H96">
+  <conditionalFormatting sqref="H78:H105">
     <cfRule type="cellIs" dxfId="71" priority="169" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10504,7 +10941,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H98:H105">
+  <conditionalFormatting sqref="H107:H117">
     <cfRule type="cellIs" dxfId="69" priority="237" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10536,7 +10973,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I20:I21">
+  <conditionalFormatting sqref="I20:I24">
     <cfRule type="cellIs" dxfId="61" priority="47" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10544,7 +10981,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I23:I27">
+  <conditionalFormatting sqref="I26:I30">
     <cfRule type="cellIs" dxfId="59" priority="37" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10552,7 +10989,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I29:I33">
+  <conditionalFormatting sqref="I32:I36">
     <cfRule type="cellIs" dxfId="57" priority="130" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10560,7 +10997,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I35:I38">
+  <conditionalFormatting sqref="I38:I41">
     <cfRule type="cellIs" dxfId="55" priority="122" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10568,7 +11005,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I40:I44">
+  <conditionalFormatting sqref="I43:I47">
     <cfRule type="cellIs" dxfId="53" priority="112" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10576,7 +11013,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I46:I47">
+  <conditionalFormatting sqref="I49:I53">
     <cfRule type="cellIs" dxfId="51" priority="35" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10584,7 +11021,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I49:I53">
+  <conditionalFormatting sqref="I55:I59">
     <cfRule type="cellIs" dxfId="49" priority="26" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10592,7 +11029,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I55:I59">
+  <conditionalFormatting sqref="I61:I65">
     <cfRule type="cellIs" dxfId="47" priority="100" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10600,7 +11037,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I61:I64">
+  <conditionalFormatting sqref="I67:I70">
     <cfRule type="cellIs" dxfId="45" priority="92" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10608,7 +11045,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I66:I70">
+  <conditionalFormatting sqref="I72:I76">
     <cfRule type="cellIs" dxfId="43" priority="81" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10616,7 +11053,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I72:I73">
+  <conditionalFormatting sqref="I78:I82">
     <cfRule type="cellIs" dxfId="41" priority="24" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10624,7 +11061,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I75:I79">
+  <conditionalFormatting sqref="I84:I88">
     <cfRule type="cellIs" dxfId="39" priority="14" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10632,7 +11069,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I81:I85">
+  <conditionalFormatting sqref="I90:I94">
     <cfRule type="cellIs" dxfId="37" priority="70" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10640,7 +11077,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I87:I90">
+  <conditionalFormatting sqref="I96:I99">
     <cfRule type="cellIs" dxfId="35" priority="61" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10648,7 +11085,7 @@
       <formula>"Si"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I92:I96">
+  <conditionalFormatting sqref="I101:I105">
     <cfRule type="cellIs" dxfId="33" priority="52" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10656,7 +11093,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I98:I99">
+  <conditionalFormatting sqref="I107:I111">
     <cfRule type="cellIs" dxfId="31" priority="12" operator="equal">
       <formula>"Si"</formula>
     </cfRule>
@@ -10664,7 +11101,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I101:I105">
+  <conditionalFormatting sqref="I113:I117">
     <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -10673,7 +11110,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:H7 G9:H12 G14:H18 G20:H21 G23:H27 G29:H33 G35:H38 G40:H44 G46:H47 G49:H53 G55:H59 G61:H64 G66:H70 G72:H73 G75:H79 G81:H85 G87:H90 G92:H96 G98:H99 G101:H105" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:H7 G9:H12 G14:H18 G20:H24 G26:H30 G32:H36 G38:H41 G43:H47 G49:H53 G55:H59 G61:H65 G67:H70 G72:H76 G78:H82 G84:H88 G90:H94 G96:H99 G101:H105 G107:H111 G113:H117" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10721,26 +11158,26 @@
         <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="B2" s="54"/>
+        <v>215</v>
+      </c>
+      <c r="B2" s="56"/>
       <c r="C2" s="58"/>
       <c r="D2" s="53"/>
       <c r="E2" s="58"/>
@@ -10749,51 +11186,51 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="198" customHeight="1">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="76.5" customHeight="1">
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="D4" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="58" t="s">
-        <v>224</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>221</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>226</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>28</v>
@@ -10813,30 +11250,30 @@
     </row>
     <row r="5" spans="1:11" ht="45.75" customHeight="1">
       <c r="A5" s="58"/>
-      <c r="B5" s="54"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="58"/>
       <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="121.5" customHeight="1">
-      <c r="B6" s="54"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="58" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>230</v>
+        <v>613</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>28</v>
@@ -10855,92 +11292,92 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="45.75" customHeight="1">
-      <c r="B7" s="54"/>
+      <c r="B7" s="56"/>
       <c r="C7" s="58"/>
       <c r="D7" s="53"/>
       <c r="E7" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="1:11" ht="30.75" customHeight="1">
+      <c r="B8" s="56"/>
+      <c r="C8" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="1:11" ht="30.75" customHeight="1">
+      <c r="B9" s="56"/>
+      <c r="C9" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="D9" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:11" ht="91.5" customHeight="1">
+      <c r="B10" s="56"/>
+      <c r="C10" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B8" s="54"/>
-      <c r="C8" s="13" t="s">
+      <c r="D10" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E8" s="25" t="s">
+      <c r="F10" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="F8" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="G8" s="12"/>
-    </row>
-    <row r="9" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B9" s="54"/>
-      <c r="C9" s="13" t="s">
+      <c r="G10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="140.25" customHeight="1">
+      <c r="B11" s="56"/>
+      <c r="C11" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:11" ht="91.5" customHeight="1">
-      <c r="B10" s="54"/>
-      <c r="C10" s="13" t="s">
+      <c r="D11" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" s="13" t="s">
+      <c r="F11" s="13" t="s">
         <v>237</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="140.25" customHeight="1">
-      <c r="B11" s="54"/>
-      <c r="C11" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>241</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>27</v>
@@ -10970,9 +11407,9 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="57" t="s">
-        <v>242</v>
-      </c>
-      <c r="B13" s="54"/>
+        <v>238</v>
+      </c>
+      <c r="B13" s="56"/>
       <c r="C13" s="58"/>
       <c r="D13" s="53"/>
       <c r="E13" s="58"/>
@@ -11079,24 +11516,24 @@
         <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I1" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>583</v>
+      </c>
+      <c r="K1" s="15" t="s">
         <v>584</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="16"/>
@@ -11110,20 +11547,20 @@
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>247</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>27</v>
@@ -11145,18 +11582,18 @@
       <c r="A4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="56"/>
       <c r="C4" s="18" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>249</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>27</v>
@@ -11178,18 +11615,18 @@
       <c r="A5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="54"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="18" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>27</v>
@@ -11211,18 +11648,18 @@
       <c r="A6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="54"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="18" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>253</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>257</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>28</v>
@@ -11254,20 +11691,20 @@
       <c r="A8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>258</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>262</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>27</v>
@@ -11289,18 +11726,18 @@
       <c r="A9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="56"/>
       <c r="C9" s="22" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>264</v>
-      </c>
       <c r="F9" s="11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>28</v>
@@ -11322,20 +11759,20 @@
       <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="54"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="59" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="G10" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="G10" s="56" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -11355,16 +11792,16 @@
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="54"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="53"/>
       <c r="D11" s="58"/>
       <c r="E11" s="11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="G11" s="54"/>
+        <v>265</v>
+      </c>
+      <c r="G11" s="56"/>
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
@@ -11382,18 +11819,18 @@
       <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="54"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="22" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>27</v>
@@ -11413,20 +11850,20 @@
     </row>
     <row r="13" spans="1:11" ht="76.5" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="B13" s="54"/>
+        <v>270</v>
+      </c>
+      <c r="B13" s="56"/>
       <c r="C13" s="22" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>28</v>
@@ -11446,20 +11883,20 @@
     </row>
     <row r="14" spans="1:11" ht="76.5" customHeight="1">
       <c r="A14" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="56"/>
+      <c r="C14" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>277</v>
-      </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>281</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>28</v>
@@ -11479,20 +11916,20 @@
     </row>
     <row r="15" spans="1:11" ht="76.5" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="B15" s="54"/>
+        <v>278</v>
+      </c>
+      <c r="B15" s="56"/>
       <c r="C15" s="22" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>28</v>
@@ -11512,20 +11949,20 @@
     </row>
     <row r="16" spans="1:11" ht="76.5" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="B16" s="54"/>
+        <v>281</v>
+      </c>
+      <c r="B16" s="56"/>
       <c r="C16" s="22" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>27</v>
@@ -11545,20 +11982,20 @@
     </row>
     <row r="17" spans="1:11" ht="76.5" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="B17" s="54"/>
+        <v>285</v>
+      </c>
+      <c r="B17" s="56"/>
       <c r="C17" s="22" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>28</v>
@@ -11578,20 +12015,20 @@
     </row>
     <row r="18" spans="1:11" ht="121.5" customHeight="1">
       <c r="A18" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" s="56"/>
+      <c r="C18" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>292</v>
-      </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>296</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>27</v>
@@ -11611,20 +12048,20 @@
     </row>
     <row r="19" spans="1:11" ht="121.5" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="B19" s="54"/>
+        <v>293</v>
+      </c>
+      <c r="B19" s="56"/>
       <c r="C19" s="22" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>27</v>
@@ -11644,20 +12081,20 @@
     </row>
     <row r="20" spans="1:11" ht="76.5" customHeight="1">
       <c r="A20" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" s="56"/>
+      <c r="C20" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>301</v>
-      </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="22" t="s">
-        <v>302</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>305</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>27</v>
@@ -11677,20 +12114,20 @@
     </row>
     <row r="21" spans="1:11" ht="76.5" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="B21" s="54"/>
+        <v>302</v>
+      </c>
+      <c r="B21" s="56"/>
       <c r="C21" s="22" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>28</v>
@@ -11710,32 +12147,32 @@
     </row>
     <row r="22" spans="1:11" ht="76.5" customHeight="1">
       <c r="A22" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B22" s="56"/>
+      <c r="C22" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>312</v>
-      </c>
       <c r="G22" s="12" t="s">
         <v>28</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>27</v>
@@ -11743,20 +12180,20 @@
     </row>
     <row r="23" spans="1:11" ht="76.5" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="B23" s="54"/>
+        <v>309</v>
+      </c>
+      <c r="B23" s="56"/>
       <c r="C23" s="22" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>27</v>
@@ -11776,20 +12213,20 @@
     </row>
     <row r="24" spans="1:11" ht="76.5" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="B24" s="54"/>
+        <v>313</v>
+      </c>
+      <c r="B24" s="56"/>
       <c r="C24" s="22" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>28</v>
@@ -11809,21 +12246,21 @@
     </row>
     <row r="25" spans="1:11" ht="106.5" customHeight="1">
       <c r="A25" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B25" s="56"/>
+      <c r="C25" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>323</v>
-      </c>
       <c r="G25" s="12" t="s">
         <v>28</v>
       </c>
@@ -11831,7 +12268,7 @@
         <v>28</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="J25" s="12" t="s">
         <v>27</v>
@@ -11839,25 +12276,25 @@
     </row>
     <row r="26" spans="1:11" ht="106.5" customHeight="1">
       <c r="A26" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B26" s="56"/>
+      <c r="C26" s="59" t="s">
+        <v>321</v>
+      </c>
+      <c r="D26" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="D26" s="59" t="s">
-        <v>326</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="G26" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="54" t="s">
+      <c r="G26" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="56" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
@@ -11869,36 +12306,36 @@
     </row>
     <row r="27" spans="1:11" ht="60.75" customHeight="1">
       <c r="A27" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="B27" s="54"/>
+        <v>325</v>
+      </c>
+      <c r="B27" s="56"/>
       <c r="C27" s="53"/>
       <c r="D27" s="58"/>
       <c r="E27" s="11" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="G27" s="54"/>
+        <v>327</v>
+      </c>
+      <c r="G27" s="56"/>
       <c r="H27" s="58"/>
     </row>
     <row r="28" spans="1:11" ht="76.5" customHeight="1">
       <c r="A28" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B28" s="56"/>
+      <c r="C28" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="F28" s="11" t="s">
         <v>332</v>
-      </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>336</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>28</v>
@@ -11918,20 +12355,20 @@
     </row>
     <row r="29" spans="1:11" ht="76.5" customHeight="1">
       <c r="A29" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="B29" s="54"/>
+        <v>333</v>
+      </c>
+      <c r="B29" s="56"/>
       <c r="C29" s="22" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>28</v>
@@ -11951,20 +12388,20 @@
     </row>
     <row r="30" spans="1:11" ht="76.5" customHeight="1">
       <c r="A30" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="B30" s="54"/>
+        <v>337</v>
+      </c>
+      <c r="B30" s="56"/>
       <c r="C30" s="22" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>27</v>
@@ -11984,20 +12421,20 @@
     </row>
     <row r="31" spans="1:11" ht="76.5" customHeight="1">
       <c r="A31" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="B31" s="54"/>
+        <v>340</v>
+      </c>
+      <c r="B31" s="56"/>
       <c r="C31" s="22" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>28</v>
@@ -12030,19 +12467,19 @@
         <v>161</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>27</v>
@@ -12066,16 +12503,16 @@
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="18" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>27</v>
@@ -12101,20 +12538,20 @@
       <c r="A36" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F36" s="11" t="s">
         <v>353</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>357</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>27</v>
@@ -12136,18 +12573,18 @@
       <c r="A37" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="54"/>
+      <c r="B37" s="56"/>
       <c r="C37" s="23" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D37" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="E37" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="E37" s="24" t="s">
-        <v>359</v>
-      </c>
       <c r="F37" s="24" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>28</v>
@@ -12242,24 +12679,24 @@
         <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B2" s="61"/>
       <c r="C2" s="61"/>
@@ -12271,22 +12708,22 @@
     </row>
     <row r="3" spans="1:11" ht="30.75" customHeight="1">
       <c r="A3" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="F3" s="8" t="s">
         <v>363</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>367</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>27</v>
@@ -12306,20 +12743,20 @@
     </row>
     <row r="4" spans="1:11" ht="30.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B4" s="60"/>
       <c r="C4" s="8" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>28</v>
@@ -12339,20 +12776,20 @@
     </row>
     <row r="5" spans="1:11" ht="30.75" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B5" s="60"/>
       <c r="C5" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>28</v>
@@ -12372,20 +12809,20 @@
     </row>
     <row r="6" spans="1:11" ht="135" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B6" s="60"/>
       <c r="C6" s="8" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>27</v>
@@ -12405,20 +12842,20 @@
     </row>
     <row r="7" spans="1:11" ht="60.75" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B7" s="60"/>
       <c r="C7" s="8" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>27</v>
@@ -12448,7 +12885,7 @@
     </row>
     <row r="9" spans="1:11" ht="76.5" customHeight="1">
       <c r="A9" s="57" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B9" s="60"/>
       <c r="C9" s="60"/>
@@ -12460,22 +12897,22 @@
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="B10" s="55" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>385</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>389</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>393</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>27</v>
@@ -12495,20 +12932,20 @@
     </row>
     <row r="11" spans="1:11" ht="91.5" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B11" s="60"/>
       <c r="C11" s="11" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>28</v>
@@ -12528,20 +12965,20 @@
     </row>
     <row r="12" spans="1:11" ht="106.5" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B12" s="60"/>
       <c r="C12" s="11" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>28</v>
@@ -12561,20 +12998,20 @@
     </row>
     <row r="13" spans="1:11" ht="91.5" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B13" s="60"/>
       <c r="C13" s="11" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>28</v>
@@ -12594,20 +13031,20 @@
     </row>
     <row r="14" spans="1:11" ht="91.5" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B14" s="60"/>
       <c r="C14" s="11" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>28</v>
@@ -12627,20 +13064,20 @@
     </row>
     <row r="15" spans="1:11" ht="121.5" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B15" s="60"/>
       <c r="C15" s="11" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>28</v>
@@ -12660,20 +13097,20 @@
     </row>
     <row r="16" spans="1:11" ht="45" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B16" s="60"/>
       <c r="C16" s="11" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>28</v>
@@ -12693,20 +13130,20 @@
     </row>
     <row r="17" spans="1:11" ht="60.75" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B17" s="60"/>
       <c r="C17" s="11" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>28</v>
@@ -12736,7 +13173,7 @@
     </row>
     <row r="19" spans="1:11" ht="106.5" customHeight="1">
       <c r="A19" s="57" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
@@ -12748,22 +13185,22 @@
     </row>
     <row r="20" spans="1:11" ht="106.5" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B20" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>422</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>430</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>27</v>
@@ -12783,20 +13220,20 @@
     </row>
     <row r="21" spans="1:11" ht="106.5" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B21" s="60"/>
       <c r="C21" s="8" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>27</v>
@@ -12816,20 +13253,20 @@
     </row>
     <row r="22" spans="1:11" ht="45" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B22" s="60"/>
       <c r="C22" s="8" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>27</v>
@@ -12849,20 +13286,20 @@
     </row>
     <row r="23" spans="1:11" ht="45.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B23" s="60"/>
       <c r="C23" s="8" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>28</v>
@@ -12882,20 +13319,20 @@
     </row>
     <row r="24" spans="1:11" ht="60.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B24" s="60"/>
       <c r="C24" s="8" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>28</v>
@@ -12915,20 +13352,20 @@
     </row>
     <row r="25" spans="1:11" ht="60.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B25" s="60"/>
       <c r="C25" s="8" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>28</v>
@@ -12948,20 +13385,20 @@
     </row>
     <row r="26" spans="1:11" ht="75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B26" s="60"/>
       <c r="C26" s="8" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>27</v>
@@ -12981,20 +13418,20 @@
     </row>
     <row r="27" spans="1:11" ht="76.5" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B27" s="60"/>
       <c r="C27" s="8" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>28</v>
@@ -13014,20 +13451,20 @@
     </row>
     <row r="28" spans="1:11" ht="106.5" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B28" s="60"/>
       <c r="C28" s="8" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>28</v>
@@ -13047,20 +13484,20 @@
     </row>
     <row r="29" spans="1:11" ht="45.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B29" s="60"/>
       <c r="C29" s="8" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>28</v>
@@ -13080,20 +13517,20 @@
     </row>
     <row r="30" spans="1:11" ht="91.5" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B30" s="60"/>
       <c r="C30" s="8" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>27</v>
@@ -13113,20 +13550,20 @@
     </row>
     <row r="31" spans="1:11" ht="121.5" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B31" s="60"/>
       <c r="C31" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>28</v>
@@ -13146,20 +13583,20 @@
     </row>
     <row r="32" spans="1:11" ht="91.5" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B32" s="60"/>
       <c r="C32" s="8" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>28</v>
@@ -13179,20 +13616,20 @@
     </row>
     <row r="33" spans="1:11" ht="91.5" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B33" s="60"/>
       <c r="C33" s="8" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>28</v>
@@ -13212,20 +13649,20 @@
     </row>
     <row r="34" spans="1:11" ht="30" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B34" s="60"/>
       <c r="C34" s="8" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>28</v>
@@ -13245,20 +13682,20 @@
     </row>
     <row r="35" spans="1:11" ht="76.5" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B35" s="60"/>
       <c r="C35" s="8" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>27</v>
@@ -13278,20 +13715,20 @@
     </row>
     <row r="36" spans="1:11" ht="76.5" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B36" s="60"/>
       <c r="C36" s="8" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>27</v>
@@ -13311,20 +13748,20 @@
     </row>
     <row r="37" spans="1:11" ht="91.5" customHeight="1">
       <c r="A37" s="7" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B37" s="60"/>
       <c r="C37" s="8" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>28</v>
@@ -13354,7 +13791,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="57" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B39" s="60"/>
       <c r="C39" s="60"/>
@@ -13366,22 +13803,22 @@
     </row>
     <row r="40" spans="1:11" ht="45" customHeight="1">
       <c r="A40" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="B40" s="52" t="s">
+        <v>505</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="F40" s="11" t="s">
         <v>509</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>510</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>513</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>27</v>
@@ -13401,20 +13838,20 @@
     </row>
     <row r="41" spans="1:11" ht="90" customHeight="1">
       <c r="A41" s="10" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B41" s="60"/>
       <c r="C41" s="11" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>27</v>
@@ -13434,20 +13871,20 @@
     </row>
     <row r="42" spans="1:11" ht="45" customHeight="1">
       <c r="A42" s="10" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B42" s="60"/>
       <c r="C42" s="11" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>27</v>
@@ -13467,20 +13904,20 @@
     </row>
     <row r="43" spans="1:11" ht="45" customHeight="1">
       <c r="A43" s="10" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B43" s="60"/>
       <c r="C43" s="11" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>27</v>
@@ -13510,7 +13947,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="57" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B45" s="60"/>
       <c r="C45" s="60"/>
@@ -13522,22 +13959,22 @@
     </row>
     <row r="46" spans="1:11" ht="60" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B46" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="B46" s="54" t="s">
+        <v>526</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>530</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>534</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>27</v>
@@ -13557,20 +13994,20 @@
     </row>
     <row r="47" spans="1:11" ht="105" customHeight="1">
       <c r="A47" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B47" s="60"/>
       <c r="C47" s="8" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>27</v>
@@ -13590,20 +14027,20 @@
     </row>
     <row r="48" spans="1:11" ht="60" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B48" s="60"/>
       <c r="C48" s="8" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>27</v>
@@ -13623,20 +14060,20 @@
     </row>
     <row r="49" spans="1:11" ht="120" customHeight="1">
       <c r="A49" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B49" s="60"/>
       <c r="C49" s="8" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>27</v>
@@ -13656,20 +14093,20 @@
     </row>
     <row r="50" spans="1:11" ht="30" customHeight="1">
       <c r="A50" s="7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B50" s="60"/>
       <c r="C50" s="8" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>28</v>
@@ -13689,20 +14126,20 @@
     </row>
     <row r="51" spans="1:11" ht="30" customHeight="1">
       <c r="A51" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B51" s="60"/>
       <c r="C51" s="8" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>28</v>
@@ -13722,20 +14159,20 @@
     </row>
     <row r="52" spans="1:11" ht="30">
       <c r="A52" s="7" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B52" s="60"/>
       <c r="C52" s="8" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>28</v>
@@ -13755,20 +14192,20 @@
     </row>
     <row r="53" spans="1:11" ht="75" customHeight="1">
       <c r="A53" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B53" s="60"/>
       <c r="C53" s="8" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>27</v>
@@ -13788,7 +14225,7 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="57" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B55" s="60"/>
       <c r="C55" s="60"/>
@@ -13800,22 +14237,22 @@
     </row>
     <row r="56" spans="1:11" ht="60" customHeight="1">
       <c r="A56" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B56" s="38" t="s">
-        <v>564</v>
+        <v>358</v>
+      </c>
+      <c r="B56" s="41" t="s">
+        <v>560</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>27</v>
@@ -13835,20 +14272,20 @@
     </row>
     <row r="57" spans="1:11" ht="60" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B57" s="60"/>
       <c r="C57" s="8" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>27</v>
@@ -13868,20 +14305,20 @@
     </row>
     <row r="58" spans="1:11" ht="60" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B58" s="60"/>
       <c r="C58" s="8" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>27</v>
@@ -13901,20 +14338,20 @@
     </row>
     <row r="59" spans="1:11" ht="45" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B59" s="60"/>
       <c r="C59" s="8" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>27</v>
@@ -13934,20 +14371,20 @@
     </row>
     <row r="60" spans="1:11" ht="45" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B60" s="60"/>
       <c r="C60" s="8" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>28</v>
@@ -14074,15 +14511,15 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+        <v>215</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14142,15 +14579,15 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+        <v>215</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728B035C-A3B9-4C1C-8D27-75D866672AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA228187-C254-439A-A3A9-4C429D0BFE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="619">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -2227,6 +2227,22 @@
   </si>
   <si>
     <t>El sistema permite cambiar únicamente el número de teléfono. Nombre, Apellido y Número de Identificación NO son editables: se muestra un aviso fijo indicando que deben corregirse llamando al 0800 122 1183 (confirmado en vivo 2026-08-08 — contradice el criterio original de este caso, que asumía los 4 campos editables).</t>
+  </si>
+  <si>
+    <t>TS-01 Reintegros - Cuentas de acreditacion e historial (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>Reintegros - Vetify - Muestra la seccion de cuentas de acreditacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario autenticado con un plan vigente.</t>
+  </si>
+  <si>
+    <t>1. Abrir el menu lateral.
+2. Presionar "Reintegros".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - La pantalla carga con la seccion "Cuentas de acreditacion" visible (unica seccion confirmada sin depender del historial, que hoy falla por BUG-007/IMAS-4279 en la cuenta usada para probarlo).</t>
   </si>
 </sst>
 </file>
@@ -2536,7 +2552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2630,15 +2646,6 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2659,19 +2666,28 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2688,6 +2704,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4523,734 +4542,734 @@
   <sheetData>
     <row r="2" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="3" spans="3:24">
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
-      <c r="K3" s="47" t="s">
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="46"/>
+      <c r="K3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="49"/>
-      <c r="S3" s="47" t="s">
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="46"/>
+      <c r="S3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="49"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="46"/>
     </row>
     <row r="4" spans="3:24">
-      <c r="C4" s="43"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="42"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="42"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="39"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="39"/>
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C5" s="40">
+      <c r="C5" s="37">
         <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199)</f>
-        <v>253</v>
-      </c>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-      <c r="K5" s="40">
+        <v>254</v>
+      </c>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
+      <c r="K5" s="37">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!G:G,"Si")</f>
         <v>188</v>
       </c>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="42"/>
-      <c r="S5" s="51">
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="39"/>
+      <c r="S5" s="48">
         <f>K5/C5</f>
-        <v>0.74308300395256921</v>
-      </c>
-      <c r="T5" s="41"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="42"/>
+        <v>0.74015748031496065</v>
+      </c>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="38"/>
+      <c r="X5" s="39"/>
     </row>
     <row r="6" spans="3:24">
-      <c r="C6" s="43"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="42"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="42"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="42"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="39"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="39"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="39"/>
     </row>
     <row r="7" spans="3:24">
-      <c r="C7" s="43"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="42"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="42"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="39"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="39"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="39"/>
     </row>
     <row r="8" spans="3:24">
-      <c r="C8" s="43"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="42"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="42"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="39"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="39"/>
     </row>
     <row r="9" spans="3:24">
-      <c r="C9" s="43"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="42"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="42"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="42"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="39"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="39"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="39"/>
     </row>
     <row r="10" spans="3:24">
-      <c r="C10" s="43"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="42"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="42"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="39"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="39"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="39"/>
     </row>
     <row r="11" spans="3:24">
-      <c r="C11" s="43"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="42"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="41"/>
-      <c r="X11" s="42"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="39"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="39"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="39"/>
     </row>
     <row r="12" spans="3:24">
-      <c r="C12" s="43"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="42"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="42"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="39"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="39"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="39"/>
     </row>
     <row r="13" spans="3:24">
-      <c r="C13" s="43"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="42"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="42"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="41"/>
-      <c r="X13" s="42"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="39"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="39"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="39"/>
     </row>
     <row r="14" spans="3:24">
-      <c r="C14" s="43"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="42"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="42"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="41"/>
-      <c r="X14" s="42"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="39"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="39"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="39"/>
     </row>
     <row r="15" spans="3:24">
-      <c r="C15" s="43"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="42"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="42"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="39"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="39"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="39"/>
     </row>
     <row r="16" spans="3:24">
-      <c r="C16" s="43"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="42"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="42"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="42"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="39"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="39"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="39"/>
     </row>
     <row r="17" spans="3:24">
-      <c r="C17" s="43"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="42"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="42"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="41"/>
-      <c r="X17" s="42"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="39"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="39"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
+      <c r="V17" s="38"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="39"/>
     </row>
     <row r="18" spans="3:24">
-      <c r="C18" s="43"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="42"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="42"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="39"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="39"/>
+      <c r="S18" s="40"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="39"/>
     </row>
     <row r="19" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C19" s="44"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="46"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="46"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="45"/>
-      <c r="U19" s="45"/>
-      <c r="V19" s="45"/>
-      <c r="W19" s="45"/>
-      <c r="X19" s="46"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="43"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="42"/>
+      <c r="V19" s="42"/>
+      <c r="W19" s="42"/>
+      <c r="X19" s="43"/>
     </row>
     <row r="22" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="23" spans="3:24">
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="49"/>
-      <c r="K23" s="47" t="s">
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
+      <c r="K23" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="48"/>
-      <c r="P23" s="49"/>
-      <c r="S23" s="47" t="s">
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="46"/>
+      <c r="S23" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="T23" s="48"/>
-      <c r="U23" s="48"/>
-      <c r="V23" s="48"/>
-      <c r="W23" s="48"/>
-      <c r="X23" s="49"/>
+      <c r="T23" s="45"/>
+      <c r="U23" s="45"/>
+      <c r="V23" s="45"/>
+      <c r="W23" s="45"/>
+      <c r="X23" s="46"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="43"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="42"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="42"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="42"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="39"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="38"/>
+      <c r="V24" s="38"/>
+      <c r="W24" s="38"/>
+      <c r="X24" s="39"/>
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C25" s="40">
+      <c r="C25" s="37">
         <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")</f>
         <v>140</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="42"/>
-      <c r="K25" s="40">
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="39"/>
+      <c r="K25" s="37">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")</f>
         <v>109</v>
       </c>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="42"/>
-      <c r="S25" s="51">
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="39"/>
+      <c r="S25" s="48">
         <f>K25/C25</f>
         <v>0.77857142857142858</v>
       </c>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="41"/>
-      <c r="W25" s="41"/>
-      <c r="X25" s="42"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="38"/>
+      <c r="W25" s="38"/>
+      <c r="X25" s="39"/>
     </row>
     <row r="26" spans="3:24">
-      <c r="C26" s="43"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="42"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="42"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="41"/>
-      <c r="X26" s="42"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="39"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="39"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="39"/>
     </row>
     <row r="27" spans="3:24">
-      <c r="C27" s="43"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="42"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="42"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="41"/>
-      <c r="X27" s="42"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="39"/>
+      <c r="S27" s="40"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="38"/>
+      <c r="V27" s="38"/>
+      <c r="W27" s="38"/>
+      <c r="X27" s="39"/>
     </row>
     <row r="28" spans="3:24">
-      <c r="C28" s="43"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="42"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="42"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="42"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="39"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="39"/>
+      <c r="S28" s="40"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="38"/>
+      <c r="X28" s="39"/>
     </row>
     <row r="29" spans="3:24">
-      <c r="C29" s="43"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="42"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="42"/>
-      <c r="S29" s="43"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="41"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="42"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="39"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="39"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="38"/>
+      <c r="V29" s="38"/>
+      <c r="W29" s="38"/>
+      <c r="X29" s="39"/>
     </row>
     <row r="30" spans="3:24">
-      <c r="C30" s="43"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="42"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="42"/>
-      <c r="S30" s="43"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="42"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="39"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="39"/>
+      <c r="S30" s="40"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="38"/>
+      <c r="V30" s="38"/>
+      <c r="W30" s="38"/>
+      <c r="X30" s="39"/>
     </row>
     <row r="31" spans="3:24">
-      <c r="C31" s="43"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="42"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="42"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="42"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="39"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="39"/>
+      <c r="S31" s="40"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+      <c r="W31" s="38"/>
+      <c r="X31" s="39"/>
     </row>
     <row r="32" spans="3:24">
-      <c r="C32" s="43"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="42"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="41"/>
-      <c r="M32" s="41"/>
-      <c r="N32" s="41"/>
-      <c r="O32" s="41"/>
-      <c r="P32" s="42"/>
-      <c r="S32" s="43"/>
-      <c r="T32" s="41"/>
-      <c r="U32" s="41"/>
-      <c r="V32" s="41"/>
-      <c r="W32" s="41"/>
-      <c r="X32" s="42"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="39"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="39"/>
+      <c r="S32" s="40"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="38"/>
+      <c r="X32" s="39"/>
     </row>
     <row r="33" spans="3:24">
-      <c r="C33" s="43"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="42"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="42"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="42"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="39"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="39"/>
+      <c r="S33" s="40"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="38"/>
+      <c r="V33" s="38"/>
+      <c r="W33" s="38"/>
+      <c r="X33" s="39"/>
     </row>
     <row r="34" spans="3:24">
-      <c r="C34" s="43"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="42"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="42"/>
-      <c r="S34" s="43"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="41"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="41"/>
-      <c r="X34" s="42"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="39"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="39"/>
+      <c r="S34" s="40"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="38"/>
+      <c r="V34" s="38"/>
+      <c r="W34" s="38"/>
+      <c r="X34" s="39"/>
     </row>
     <row r="35" spans="3:24">
-      <c r="C35" s="43"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="42"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="42"/>
-      <c r="S35" s="43"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
-      <c r="V35" s="41"/>
-      <c r="W35" s="41"/>
-      <c r="X35" s="42"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="39"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="39"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="38"/>
+      <c r="V35" s="38"/>
+      <c r="W35" s="38"/>
+      <c r="X35" s="39"/>
     </row>
     <row r="36" spans="3:24">
-      <c r="C36" s="43"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="42"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="42"/>
-      <c r="S36" s="43"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="42"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="39"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
+      <c r="P36" s="39"/>
+      <c r="S36" s="40"/>
+      <c r="T36" s="38"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="39"/>
     </row>
     <row r="37" spans="3:24">
-      <c r="C37" s="43"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="42"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
-      <c r="N37" s="41"/>
-      <c r="O37" s="41"/>
-      <c r="P37" s="42"/>
-      <c r="S37" s="43"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="41"/>
-      <c r="V37" s="41"/>
-      <c r="W37" s="41"/>
-      <c r="X37" s="42"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="39"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="38"/>
+      <c r="P37" s="39"/>
+      <c r="S37" s="40"/>
+      <c r="T37" s="38"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="38"/>
+      <c r="W37" s="38"/>
+      <c r="X37" s="39"/>
     </row>
     <row r="38" spans="3:24">
-      <c r="C38" s="43"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="42"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="42"/>
-      <c r="S38" s="43"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-      <c r="V38" s="41"/>
-      <c r="W38" s="41"/>
-      <c r="X38" s="42"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="39"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="39"/>
+      <c r="S38" s="40"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="38"/>
+      <c r="V38" s="38"/>
+      <c r="W38" s="38"/>
+      <c r="X38" s="39"/>
     </row>
     <row r="39" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C39" s="44"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="46"/>
-      <c r="K39" s="44"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="46"/>
-      <c r="S39" s="44"/>
-      <c r="T39" s="45"/>
-      <c r="U39" s="45"/>
-      <c r="V39" s="45"/>
-      <c r="W39" s="45"/>
-      <c r="X39" s="46"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="43"/>
+      <c r="K39" s="41"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="42"/>
+      <c r="N39" s="42"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="43"/>
+      <c r="S39" s="41"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="42"/>
+      <c r="V39" s="42"/>
+      <c r="W39" s="42"/>
+      <c r="X39" s="43"/>
     </row>
     <row r="41" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="42" spans="3:24">
-      <c r="C42" s="47" t="s">
+      <c r="C42" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="49"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="46"/>
     </row>
     <row r="43" spans="3:24">
-      <c r="C43" s="43"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="42"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="39"/>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
@@ -5259,31 +5278,31 @@
       <c r="P43" s="28"/>
     </row>
     <row r="44" spans="3:24" ht="21" customHeight="1">
-      <c r="C44" s="51">
+      <c r="C44" s="48">
         <f>C25/C5</f>
-        <v>0.55335968379446643</v>
-      </c>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="42"/>
+        <v>0.55118110236220474</v>
+      </c>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="39"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="50" t="s">
+      <c r="L44" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="M44" s="41"/>
-      <c r="N44" s="41"/>
-      <c r="O44" s="41"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
       <c r="P44" s="29"/>
     </row>
     <row r="45" spans="3:24">
-      <c r="C45" s="43"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="42"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="39"/>
       <c r="K45" s="28"/>
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
@@ -5292,12 +5311,12 @@
       <c r="P45" s="29"/>
     </row>
     <row r="46" spans="3:24">
-      <c r="C46" s="43"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="42"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="39"/>
       <c r="K46" s="28"/>
       <c r="L46" s="31"/>
       <c r="M46" s="28" t="s">
@@ -5308,12 +5327,12 @@
       <c r="P46" s="28"/>
     </row>
     <row r="47" spans="3:24">
-      <c r="C47" s="43"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="42"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="39"/>
       <c r="K47" s="28"/>
       <c r="L47" s="32"/>
       <c r="M47" s="28" t="s">
@@ -5324,12 +5343,12 @@
       <c r="P47" s="28"/>
     </row>
     <row r="48" spans="3:24">
-      <c r="C48" s="43"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="42"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="39"/>
       <c r="K48" s="28"/>
       <c r="L48" s="33"/>
       <c r="M48" s="28" t="s">
@@ -5340,12 +5359,12 @@
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="3:16">
-      <c r="C49" s="43"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="42"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="39"/>
       <c r="K49" s="28"/>
       <c r="L49" s="34"/>
       <c r="M49" s="28" t="s">
@@ -5356,12 +5375,12 @@
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="3:16">
-      <c r="C50" s="43"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="42"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="39"/>
       <c r="K50" s="28"/>
       <c r="L50" s="35"/>
       <c r="M50" s="28" t="s">
@@ -5372,12 +5391,12 @@
       <c r="P50" s="28"/>
     </row>
     <row r="51" spans="3:16">
-      <c r="C51" s="43"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="42"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="39"/>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -5386,230 +5405,230 @@
       <c r="P51" s="28"/>
     </row>
     <row r="52" spans="3:16">
-      <c r="C52" s="43"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="42"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="39"/>
     </row>
     <row r="53" spans="3:16">
-      <c r="C53" s="43"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="42"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="39"/>
     </row>
     <row r="54" spans="3:16">
-      <c r="C54" s="43"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="42"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="39"/>
     </row>
     <row r="55" spans="3:16">
-      <c r="C55" s="43"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="42"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="39"/>
     </row>
     <row r="56" spans="3:16">
-      <c r="C56" s="43"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="42"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="39"/>
     </row>
     <row r="57" spans="3:16">
-      <c r="C57" s="43"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="42"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="39"/>
     </row>
     <row r="58" spans="3:16" ht="15.75" customHeight="1">
-      <c r="C58" s="44"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="46"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="43"/>
     </row>
     <row r="62" spans="3:16">
-      <c r="C62" s="37" t="s">
+      <c r="C62" s="49" t="s">
         <v>585</v>
       </c>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="H62" s="37" t="s">
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="H62" s="49" t="s">
         <v>586</v>
       </c>
-      <c r="I62" s="37"/>
-      <c r="J62" s="37"/>
-      <c r="K62" s="37"/>
-      <c r="M62" s="37" t="s">
+      <c r="I62" s="49"/>
+      <c r="J62" s="49"/>
+      <c r="K62" s="49"/>
+      <c r="M62" s="49" t="s">
         <v>587</v>
       </c>
-      <c r="N62" s="37"/>
-      <c r="O62" s="37"/>
-      <c r="P62" s="37"/>
+      <c r="N62" s="49"/>
+      <c r="O62" s="49"/>
+      <c r="P62" s="49"/>
     </row>
     <row r="63" spans="3:16">
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37"/>
-      <c r="J63" s="37"/>
-      <c r="K63" s="37"/>
-      <c r="M63" s="37"/>
-      <c r="N63" s="37"/>
-      <c r="O63" s="37"/>
-      <c r="P63" s="37"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
+      <c r="M63" s="49"/>
+      <c r="N63" s="49"/>
+      <c r="O63" s="49"/>
+      <c r="P63" s="49"/>
     </row>
     <row r="64" spans="3:16">
-      <c r="C64" s="38">
+      <c r="C64" s="50">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
         <v>250</v>
       </c>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="H64" s="38">
+      <c r="D64" s="50"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="50"/>
+      <c r="H64" s="50">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
         <v>188</v>
       </c>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
-      <c r="M64" s="39">
+      <c r="I64" s="50"/>
+      <c r="J64" s="50"/>
+      <c r="K64" s="50"/>
+      <c r="M64" s="51">
         <f t="shared" ref="M64" si="0">H64/C64</f>
         <v>0.752</v>
       </c>
-      <c r="N64" s="39"/>
-      <c r="O64" s="39"/>
-      <c r="P64" s="39"/>
+      <c r="N64" s="51"/>
+      <c r="O64" s="51"/>
+      <c r="P64" s="51"/>
     </row>
     <row r="65" spans="3:16">
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="38"/>
-      <c r="M65" s="39"/>
-      <c r="N65" s="39"/>
-      <c r="O65" s="39"/>
-      <c r="P65" s="39"/>
+      <c r="C65" s="50"/>
+      <c r="D65" s="50"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="H65" s="50"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="50"/>
+      <c r="K65" s="50"/>
+      <c r="M65" s="51"/>
+      <c r="N65" s="51"/>
+      <c r="O65" s="51"/>
+      <c r="P65" s="51"/>
     </row>
     <row r="66" spans="3:16">
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="38"/>
-      <c r="M66" s="39"/>
-      <c r="N66" s="39"/>
-      <c r="O66" s="39"/>
-      <c r="P66" s="39"/>
+      <c r="C66" s="50"/>
+      <c r="D66" s="50"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="H66" s="50"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="50"/>
+      <c r="M66" s="51"/>
+      <c r="N66" s="51"/>
+      <c r="O66" s="51"/>
+      <c r="P66" s="51"/>
     </row>
     <row r="69" spans="3:16">
-      <c r="C69" s="37" t="s">
+      <c r="C69" s="49" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="H69" s="37" t="s">
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="H69" s="49" t="s">
         <v>589</v>
       </c>
-      <c r="I69" s="37"/>
-      <c r="J69" s="37"/>
-      <c r="K69" s="37"/>
-      <c r="M69" s="37" t="s">
+      <c r="I69" s="49"/>
+      <c r="J69" s="49"/>
+      <c r="K69" s="49"/>
+      <c r="M69" s="49" t="s">
         <v>587</v>
       </c>
-      <c r="N69" s="37"/>
-      <c r="O69" s="37"/>
-      <c r="P69" s="37"/>
+      <c r="N69" s="49"/>
+      <c r="O69" s="49"/>
+      <c r="P69" s="49"/>
     </row>
     <row r="70" spans="3:16">
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
-      <c r="J70" s="37"/>
-      <c r="K70" s="37"/>
-      <c r="M70" s="37"/>
-      <c r="N70" s="37"/>
-      <c r="O70" s="37"/>
-      <c r="P70" s="37"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="49"/>
+      <c r="J70" s="49"/>
+      <c r="K70" s="49"/>
+      <c r="M70" s="49"/>
+      <c r="N70" s="49"/>
+      <c r="O70" s="49"/>
+      <c r="P70" s="49"/>
     </row>
     <row r="71" spans="3:16">
-      <c r="C71" s="38">
+      <c r="C71" s="50">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
         <v>71</v>
       </c>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38"/>
-      <c r="H71" s="38">
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="H71" s="50">
         <f>COUNTIF(Perfil!I:I,"Si")+COUNTIF(Credenciales!I:I,"Si")+COUNTIF(Videollamadas!I:I,"Si")</f>
         <v>60</v>
       </c>
-      <c r="I71" s="38"/>
-      <c r="J71" s="38"/>
-      <c r="K71" s="38"/>
-      <c r="M71" s="39">
+      <c r="I71" s="50"/>
+      <c r="J71" s="50"/>
+      <c r="K71" s="50"/>
+      <c r="M71" s="51">
         <f t="shared" ref="M71" si="1">H71/C71</f>
         <v>0.84507042253521125</v>
       </c>
-      <c r="N71" s="39"/>
-      <c r="O71" s="39"/>
-      <c r="P71" s="39"/>
+      <c r="N71" s="51"/>
+      <c r="O71" s="51"/>
+      <c r="P71" s="51"/>
     </row>
     <row r="72" spans="3:16">
-      <c r="C72" s="38"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="38"/>
-      <c r="H72" s="38"/>
-      <c r="I72" s="38"/>
-      <c r="J72" s="38"/>
-      <c r="K72" s="38"/>
-      <c r="M72" s="39"/>
-      <c r="N72" s="39"/>
-      <c r="O72" s="39"/>
-      <c r="P72" s="39"/>
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
+      <c r="F72" s="50"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="50"/>
+      <c r="J72" s="50"/>
+      <c r="K72" s="50"/>
+      <c r="M72" s="51"/>
+      <c r="N72" s="51"/>
+      <c r="O72" s="51"/>
+      <c r="P72" s="51"/>
     </row>
     <row r="73" spans="3:16">
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="38"/>
-      <c r="M73" s="39"/>
-      <c r="N73" s="39"/>
-      <c r="O73" s="39"/>
-      <c r="P73" s="39"/>
+      <c r="C73" s="50"/>
+      <c r="D73" s="50"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="H73" s="50"/>
+      <c r="I73" s="50"/>
+      <c r="J73" s="50"/>
+      <c r="K73" s="50"/>
+      <c r="M73" s="51"/>
+      <c r="N73" s="51"/>
+      <c r="O73" s="51"/>
+      <c r="P73" s="51"/>
     </row>
     <row r="76" spans="3:16">
       <c r="C76" s="36" t="s">
@@ -5618,6 +5637,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C69:F70"/>
+    <mergeCell ref="C71:F73"/>
+    <mergeCell ref="H69:K70"/>
+    <mergeCell ref="H71:K73"/>
+    <mergeCell ref="M69:P70"/>
+    <mergeCell ref="M71:P73"/>
+    <mergeCell ref="C62:F63"/>
+    <mergeCell ref="C64:F66"/>
+    <mergeCell ref="H62:K63"/>
+    <mergeCell ref="H64:K66"/>
+    <mergeCell ref="M62:P63"/>
+    <mergeCell ref="M64:P66"/>
     <mergeCell ref="K5:P19"/>
     <mergeCell ref="K25:P39"/>
     <mergeCell ref="S3:X4"/>
@@ -5633,18 +5664,6 @@
     <mergeCell ref="C3:H4"/>
     <mergeCell ref="C25:H39"/>
     <mergeCell ref="K23:P24"/>
-    <mergeCell ref="C62:F63"/>
-    <mergeCell ref="C64:F66"/>
-    <mergeCell ref="H62:K63"/>
-    <mergeCell ref="H64:K66"/>
-    <mergeCell ref="M62:P63"/>
-    <mergeCell ref="M64:P66"/>
-    <mergeCell ref="C69:F70"/>
-    <mergeCell ref="C71:F73"/>
-    <mergeCell ref="H69:K70"/>
-    <mergeCell ref="H71:K73"/>
-    <mergeCell ref="M69:P70"/>
-    <mergeCell ref="M71:P73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5701,7 +5720,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="52" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="53"/>
@@ -5710,7 +5729,7 @@
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
       <c r="G2" s="53"/>
-      <c r="H2" s="56"/>
+      <c r="H2" s="54"/>
       <c r="I2" s="12" t="s">
         <v>27</v>
       </c>
@@ -5719,7 +5738,7 @@
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="56" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -5947,7 +5966,7 @@
       <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="55" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -6013,7 +6032,7 @@
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="56" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -6106,7 +6125,7 @@
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="55" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -6307,7 +6326,7 @@
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="56" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -6427,7 +6446,7 @@
       <c r="A32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="55" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="22" t="s">
@@ -6574,7 +6593,7 @@
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="56" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -6627,7 +6646,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="52" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="53"/>
@@ -6636,7 +6655,7 @@
       <c r="E40" s="53"/>
       <c r="F40" s="53"/>
       <c r="G40" s="53"/>
-      <c r="H40" s="56"/>
+      <c r="H40" s="54"/>
       <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
@@ -6645,7 +6664,7 @@
       <c r="A41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="52" t="s">
+      <c r="B41" s="55" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="22" t="s">
@@ -6873,7 +6892,7 @@
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="54" t="s">
+      <c r="B50" s="56" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -6939,7 +6958,7 @@
       <c r="A53" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="52" t="s">
+      <c r="B53" s="55" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="22" t="s">
@@ -7032,7 +7051,7 @@
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="54" t="s">
+      <c r="B57" s="56" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -7233,7 +7252,7 @@
       <c r="A65" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="52" t="s">
+      <c r="B65" s="55" t="s">
         <v>90</v>
       </c>
       <c r="C65" s="22" t="s">
@@ -7353,7 +7372,7 @@
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="54" t="s">
+      <c r="B70" s="56" t="s">
         <v>104</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -7500,7 +7519,7 @@
       <c r="A76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="52" t="s">
+      <c r="B76" s="55" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -7553,7 +7572,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A78" s="55" t="s">
+      <c r="A78" s="52" t="s">
         <v>140</v>
       </c>
       <c r="B78" s="53"/>
@@ -7562,7 +7581,7 @@
       <c r="E78" s="53"/>
       <c r="F78" s="53"/>
       <c r="G78" s="53"/>
-      <c r="H78" s="56"/>
+      <c r="H78" s="54"/>
       <c r="I78" s="12" t="s">
         <v>27</v>
       </c>
@@ -7571,7 +7590,7 @@
       <c r="A79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="54" t="s">
+      <c r="B79" s="56" t="s">
         <v>141</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -7662,7 +7681,7 @@
       <c r="A83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B83" s="52" t="s">
+      <c r="B83" s="55" t="s">
         <v>153</v>
       </c>
       <c r="C83" s="22" t="s">
@@ -7711,7 +7730,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A85" s="55" t="s">
+      <c r="A85" s="52" t="s">
         <v>159</v>
       </c>
       <c r="B85" s="53"/>
@@ -7720,7 +7739,7 @@
       <c r="E85" s="53"/>
       <c r="F85" s="53"/>
       <c r="G85" s="53"/>
-      <c r="H85" s="56"/>
+      <c r="H85" s="54"/>
       <c r="I85" s="12" t="s">
         <v>27</v>
       </c>
@@ -7729,7 +7748,7 @@
       <c r="A86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="54" t="s">
+      <c r="B86" s="56" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -7820,7 +7839,7 @@
       <c r="A90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="52" t="s">
+      <c r="B90" s="55" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -7880,6 +7899,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B86:B88"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="B32:B36"/>
@@ -7896,12 +7921,6 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="B19:B25"/>
     <mergeCell ref="B57:B63"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B86:B88"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="153" priority="564" operator="equal">
@@ -8131,7 +8150,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="52" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="53"/>
@@ -8140,13 +8159,13 @@
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
       <c r="G2" s="53"/>
-      <c r="H2" s="56"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:9" ht="76.5" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="56" t="s">
         <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -8287,7 +8306,7 @@
       <c r="A9" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="55" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -8405,7 +8424,7 @@
       <c r="A14" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="56" t="s">
         <v>192</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -8552,7 +8571,7 @@
       <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="54" t="s">
         <v>612</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -8696,7 +8715,7 @@
       <c r="A26" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="54" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -8785,7 +8804,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="52" t="s">
         <v>213</v>
       </c>
       <c r="B31" s="53"/>
@@ -8794,13 +8813,13 @@
       <c r="E31" s="53"/>
       <c r="F31" s="53"/>
       <c r="G31" s="53"/>
-      <c r="H31" s="56"/>
+      <c r="H31" s="54"/>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="56" t="s">
         <v>162</v>
       </c>
       <c r="C32" s="18" t="s">
@@ -8941,7 +8960,7 @@
       <c r="A38" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="52" t="s">
+      <c r="B38" s="55" t="s">
         <v>182</v>
       </c>
       <c r="C38" s="22" t="s">
@@ -9059,7 +9078,7 @@
       <c r="A43" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="56" t="s">
         <v>192</v>
       </c>
       <c r="C43" s="18" t="s">
@@ -9206,7 +9225,7 @@
       <c r="A49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="56" t="s">
+      <c r="B49" s="54" t="s">
         <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -9350,7 +9369,7 @@
       <c r="A55" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B55" s="54" t="s">
         <v>208</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -9439,7 +9458,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A60" s="55" t="s">
+      <c r="A60" s="52" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="53"/>
@@ -9448,13 +9467,13 @@
       <c r="E60" s="53"/>
       <c r="F60" s="53"/>
       <c r="G60" s="53"/>
-      <c r="H60" s="56"/>
+      <c r="H60" s="54"/>
     </row>
     <row r="61" spans="1:9" ht="76.5" customHeight="1">
       <c r="A61" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="54" t="s">
+      <c r="B61" s="56" t="s">
         <v>162</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -9595,7 +9614,7 @@
       <c r="A67" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B67" s="52" t="s">
+      <c r="B67" s="55" t="s">
         <v>182</v>
       </c>
       <c r="C67" s="22" t="s">
@@ -9713,7 +9732,7 @@
       <c r="A72" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="54" t="s">
+      <c r="B72" s="56" t="s">
         <v>192</v>
       </c>
       <c r="C72" s="18" t="s">
@@ -9860,7 +9879,7 @@
       <c r="A78" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="56" t="s">
+      <c r="B78" s="54" t="s">
         <v>611</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -10004,7 +10023,7 @@
       <c r="A84" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="56" t="s">
+      <c r="B84" s="54" t="s">
         <v>208</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -10093,7 +10112,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A89" s="55" t="s">
+      <c r="A89" s="52" t="s">
         <v>159</v>
       </c>
       <c r="B89" s="53"/>
@@ -10102,13 +10121,13 @@
       <c r="E89" s="53"/>
       <c r="F89" s="53"/>
       <c r="G89" s="53"/>
-      <c r="H89" s="56"/>
+      <c r="H89" s="54"/>
     </row>
     <row r="90" spans="1:9" ht="76.5" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="54" t="s">
+      <c r="B90" s="56" t="s">
         <v>162</v>
       </c>
       <c r="C90" s="18" t="s">
@@ -10249,7 +10268,7 @@
       <c r="A96" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B96" s="52" t="s">
+      <c r="B96" s="55" t="s">
         <v>182</v>
       </c>
       <c r="C96" s="22" t="s">
@@ -10367,7 +10386,7 @@
       <c r="A101" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="54" t="s">
+      <c r="B101" s="56" t="s">
         <v>192</v>
       </c>
       <c r="C101" s="18" t="s">
@@ -10514,7 +10533,7 @@
       <c r="A107" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B107" s="56" t="s">
+      <c r="B107" s="54" t="s">
         <v>591</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -10658,7 +10677,7 @@
       <c r="A113" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B113" s="56" t="s">
+      <c r="B113" s="54" t="s">
         <v>208</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -10748,14 +10767,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B113:B117"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B107:B108"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B96:B99"/>
     <mergeCell ref="A2:H2"/>
@@ -10772,6 +10783,14 @@
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="B43:B47"/>
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="B107:B108"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="111" priority="525" operator="equal">
@@ -11177,7 +11196,7 @@
       <c r="A2" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="56"/>
+      <c r="B2" s="54"/>
       <c r="C2" s="58"/>
       <c r="D2" s="53"/>
       <c r="E2" s="58"/>
@@ -11186,7 +11205,7 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="198" customHeight="1">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -11218,8 +11237,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="58" t="s">
         <v>221</v>
       </c>
@@ -11250,7 +11269,7 @@
     </row>
     <row r="5" spans="1:11" ht="45.75" customHeight="1">
       <c r="A5" s="58"/>
-      <c r="B5" s="56"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="58"/>
       <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
@@ -11262,7 +11281,7 @@
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="121.5" customHeight="1">
-      <c r="B6" s="56"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="58" t="s">
         <v>226</v>
       </c>
@@ -11292,7 +11311,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="45.75" customHeight="1">
-      <c r="B7" s="56"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="58"/>
       <c r="D7" s="53"/>
       <c r="E7" s="13" t="s">
@@ -11304,7 +11323,7 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B8" s="56"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="13" t="s">
         <v>229</v>
       </c>
@@ -11320,7 +11339,7 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B9" s="56"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="13" t="s">
         <v>231</v>
       </c>
@@ -11336,7 +11355,7 @@
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
-      <c r="B10" s="56"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="13" t="s">
         <v>232</v>
       </c>
@@ -11366,7 +11385,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="140.25" customHeight="1">
-      <c r="B11" s="56"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="13" t="s">
         <v>235</v>
       </c>
@@ -11409,7 +11428,7 @@
       <c r="A13" s="57" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="56"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="58"/>
       <c r="D13" s="53"/>
       <c r="E13" s="58"/>
@@ -11547,7 +11566,7 @@
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="56" t="s">
         <v>239</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -11582,7 +11601,7 @@
       <c r="A4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="56"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="18" t="s">
         <v>244</v>
       </c>
@@ -11615,7 +11634,7 @@
       <c r="A5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="56"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="18" t="s">
         <v>247</v>
       </c>
@@ -11648,7 +11667,7 @@
       <c r="A6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="56"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="18" t="s">
         <v>251</v>
       </c>
@@ -11691,7 +11710,7 @@
       <c r="A8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="55" t="s">
         <v>254</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -11726,7 +11745,7 @@
       <c r="A9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="56"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="22" t="s">
         <v>259</v>
       </c>
@@ -11759,7 +11778,7 @@
       <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="56"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="59" t="s">
         <v>262</v>
       </c>
@@ -11772,7 +11791,7 @@
       <c r="F10" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G10" s="56" t="s">
+      <c r="G10" s="54" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -11792,7 +11811,7 @@
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="56"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="53"/>
       <c r="D11" s="58"/>
       <c r="E11" s="11" t="s">
@@ -11801,7 +11820,7 @@
       <c r="F11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G11" s="56"/>
+      <c r="G11" s="54"/>
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
@@ -11819,7 +11838,7 @@
       <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="56"/>
+      <c r="B12" s="54"/>
       <c r="C12" s="22" t="s">
         <v>267</v>
       </c>
@@ -11852,7 +11871,7 @@
       <c r="A13" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="56"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="22" t="s">
         <v>271</v>
       </c>
@@ -11885,7 +11904,7 @@
       <c r="A14" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B14" s="56"/>
+      <c r="B14" s="54"/>
       <c r="C14" s="22" t="s">
         <v>274</v>
       </c>
@@ -11918,7 +11937,7 @@
       <c r="A15" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="56"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="22" t="s">
         <v>279</v>
       </c>
@@ -11951,7 +11970,7 @@
       <c r="A16" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="56"/>
+      <c r="B16" s="54"/>
       <c r="C16" s="22" t="s">
         <v>282</v>
       </c>
@@ -11984,7 +12003,7 @@
       <c r="A17" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="56"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="22" t="s">
         <v>286</v>
       </c>
@@ -12017,7 +12036,7 @@
       <c r="A18" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B18" s="56"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="22" t="s">
         <v>289</v>
       </c>
@@ -12050,7 +12069,7 @@
       <c r="A19" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="56"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="22" t="s">
         <v>294</v>
       </c>
@@ -12083,7 +12102,7 @@
       <c r="A20" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="56"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="22" t="s">
         <v>298</v>
       </c>
@@ -12116,7 +12135,7 @@
       <c r="A21" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="56"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="22" t="s">
         <v>303</v>
       </c>
@@ -12149,7 +12168,7 @@
       <c r="A22" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="56"/>
+      <c r="B22" s="54"/>
       <c r="C22" s="22" t="s">
         <v>305</v>
       </c>
@@ -12182,7 +12201,7 @@
       <c r="A23" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="56"/>
+      <c r="B23" s="54"/>
       <c r="C23" s="22" t="s">
         <v>310</v>
       </c>
@@ -12215,7 +12234,7 @@
       <c r="A24" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B24" s="56"/>
+      <c r="B24" s="54"/>
       <c r="C24" s="22" t="s">
         <v>314</v>
       </c>
@@ -12248,7 +12267,7 @@
       <c r="A25" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="56"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="22" t="s">
         <v>316</v>
       </c>
@@ -12278,7 +12297,7 @@
       <c r="A26" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="56"/>
+      <c r="B26" s="54"/>
       <c r="C26" s="59" t="s">
         <v>321</v>
       </c>
@@ -12291,10 +12310,10 @@
       <c r="F26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="G26" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="56" t="s">
+      <c r="G26" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="54" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
@@ -12308,7 +12327,7 @@
       <c r="A27" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="56"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="53"/>
       <c r="D27" s="58"/>
       <c r="E27" s="11" t="s">
@@ -12317,14 +12336,14 @@
       <c r="F27" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G27" s="56"/>
+      <c r="G27" s="54"/>
       <c r="H27" s="58"/>
     </row>
     <row r="28" spans="1:11" ht="76.5" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B28" s="56"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="22" t="s">
         <v>329</v>
       </c>
@@ -12357,7 +12376,7 @@
       <c r="A29" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B29" s="56"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="22" t="s">
         <v>334</v>
       </c>
@@ -12390,7 +12409,7 @@
       <c r="A30" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B30" s="56"/>
+      <c r="B30" s="54"/>
       <c r="C30" s="22" t="s">
         <v>338</v>
       </c>
@@ -12423,7 +12442,7 @@
       <c r="A31" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B31" s="56"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="22" t="s">
         <v>341</v>
       </c>
@@ -12538,7 +12557,7 @@
       <c r="A36" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="54" t="s">
+      <c r="B36" s="56" t="s">
         <v>349</v>
       </c>
       <c r="C36" s="22" t="s">
@@ -12573,7 +12592,7 @@
       <c r="A37" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="56"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="23" t="s">
         <v>354</v>
       </c>
@@ -12710,7 +12729,7 @@
       <c r="A3" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="56" t="s">
         <v>359</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -12899,7 +12918,7 @@
       <c r="A10" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="55" t="s">
         <v>385</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -13187,7 +13206,7 @@
       <c r="A20" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="56" t="s">
         <v>422</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -13805,7 +13824,7 @@
       <c r="A40" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B40" s="52" t="s">
+      <c r="B40" s="55" t="s">
         <v>505</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -13961,7 +13980,7 @@
       <c r="A46" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B46" s="54" t="s">
+      <c r="B46" s="56" t="s">
         <v>526</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -14239,7 +14258,7 @@
       <c r="A56" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B56" s="41" t="s">
+      <c r="B56" s="38" t="s">
         <v>560</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -14471,7 +14490,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30.7109375" customWidth="1"/>
@@ -14513,13 +14532,39 @@
       <c r="A2" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+    </row>
+    <row r="3" spans="1:8" ht="30">
+      <c r="A3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E3" s="62" t="s">
+        <v>617</v>
+      </c>
+      <c r="F3" t="s">
+        <v>618</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14581,13 +14626,13 @@
       <c r="A2" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA228187-C254-439A-A3A9-4C429D0BFE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3F6A3A-1DD1-4625-AE09-7F04C559B93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metricas de Casos de Prueba" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="Videollamadas" sheetId="6" r:id="rId6"/>
     <sheet name="Reintegros" sheetId="7" r:id="rId7"/>
     <sheet name="Misceláneas" sheetId="8" r:id="rId8"/>
+    <sheet name="Control de Acceso" sheetId="9" r:id="rId9"/>
+    <sheet name="Sistema Caído" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="695">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -2244,6 +2246,244 @@
   <si>
     <t xml:space="preserve"> - La pantalla carga con la seccion "Cuentas de acreditacion" visible (unica seccion confirmada sin depender del historial, que hoy falla por BUG-007/IMAS-4279 en la cuenta usada para probarlo).</t>
   </si>
+  <si>
+    <t>TS-03 Mascotas (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>Ve al menos una mascota en Mis mascotas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario autenticado con al menos una mascota.</t>
+  </si>
+  <si>
+    <t>1. Ir a "Mis mascotas" desde el menu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra al menos 1 tarjeta de mascota.</t>
+  </si>
+  <si>
+    <t>TS-06 Planes (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>Ve al menos un plan en Planes y coberturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario autenticado con al menos un plan.</t>
+  </si>
+  <si>
+    <t>1. Ir a "Planes y coberturas" desde el menu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra al menos 1 plan en el acordeon.</t>
+  </si>
+  <si>
+    <t>TS-05 Servicios (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>Ve el acceso a Videollamada en Servicios</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario autenticado.</t>
+  </si>
+  <si>
+    <t>1. Ir a "Servicios" desde el menu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra el acceso a Videollamada.</t>
+  </si>
+  <si>
+    <t>Ve las tarjetas de Emergencias y Asistencia presencial en Servicios</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestran las tarjetas de Emergencias y Asistencia presencial.</t>
+  </si>
+  <si>
+    <t>TS-01 Ayuda (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>Muestra los canales de contacto (Emergencias y Atencion al cliente)</t>
+  </si>
+  <si>
+    <t>1. Ir a "Ayuda" desde el menu lateral.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestran los canales de contacto reales (telefonos y email).</t>
+  </si>
+  <si>
+    <t>TS-01 Historial de atencion (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>Muestra la historia clinica de una mascota</t>
+  </si>
+  <si>
+    <t>1. Ir a "Historial de atencion" desde el menu.
+2. Elegir la primera mascota.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra la historia clinica de esa mascota.</t>
+  </si>
+  <si>
+    <t>TS-01 Vetify PLUS (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>Abre vetifyplus.com en el navegador del sistema</t>
+  </si>
+  <si>
+    <t>1. Tocar "Vetify PLUS" desde el menu lateral.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se abre un navegador externo con vetifyplus.com.</t>
+  </si>
+  <si>
+    <t>TS-01 Asistencia a domicilio (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>"Llamanos por telefono" abre el marcador del sistema</t>
+  </si>
+  <si>
+    <t>1. Ir a "Asistencia a domicilio" desde el menu.
+2. Elegir "Llamanos por telefono".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se abre el marcador telefonico nativo del dispositivo.</t>
+  </si>
+  <si>
+    <t>TS-01 Facturas (Mobile, sin equivalente Desktop)</t>
+  </si>
+  <si>
+    <t>Muestra el estado vacio cuando no hay facturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario autenticado sin facturas emitidas.</t>
+  </si>
+  <si>
+    <t>1. Ir a "Facturas" desde el menu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Se muestra el estado vacio ("No tenes facturas disponibles...").</t>
+  </si>
+  <si>
+    <t>TS-01 IMAS-3742 - Validacion de acceso durante la autenticacion</t>
+  </si>
+  <si>
+    <t>[No valida CA01] Usuario sin cuenta registrada en Ike es rechazado</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario con al menos un plan vigente, exclusivamente de Vetify (sin ningun plan de Ike, sin cuenta registrada en el sistema de identidad de Ike).</t>
+  </si>
+  <si>
+    <t>1. Ir a la pantalla de login de la WebApp de Ike.
+2. Iniciar sesion con las credenciales del usuario Vetify-only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El sistema no otorga acceso a la WebApp de Ike.
+IMPORTANTE: este caso NO valida el CA01 real - el rechazo es de Auth0 (la cuenta nunca se registro en el tenant de identidad de Ike), no evidencia de que el control de acceso por plan funcione. Ver CP-06.</t>
+  </si>
+  <si>
+    <t>[Brecha de cobertura] CA02 - Usuario con plan habilitado de Ike accede normalmente</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario con un plan de Ike habilitado.</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesion con ese usuario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El sistema otorga acceso normalmente.</t>
+  </si>
+  <si>
+    <t>[Brecha de cobertura] CA03 - Usuario con planes de Vetify e Ike accede sin inconvenientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario con planes de Vetify y de Ike simultaneamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El sistema otorga acceso sin inconvenientes.</t>
+  </si>
+  <si>
+    <t>[Brecha de cobertura] Usuario sin ningun plan (ni Vetify ni Ike) no accede</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario sin ningun plan provisionado en el sistema de identidad de Ike.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El sistema no otorga acceso.</t>
+  </si>
+  <si>
+    <t>[Brecha de cobertura] CA05 - El cambio no afecta el login de otros tipos de usuario</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuarios con plan de Ike (CP-02/CP-03).</t>
+  </si>
+  <si>
+    <t>1. Repetir CP-02/CP-03 para confirmar que no hay regresion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Sin regresion en el login de otros tipos de usuario.</t>
+  </si>
+  <si>
+    <t>[Brecha de cobertura] CA01 - Usuario con cuenta en Ike pero SOLO plan de Vetify no accede</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario con cuenta/identidad SI registrada en el tenant de Auth0 de Ike, pero sin ningun plan de Ike asociado (no confundir con CP-01, que nunca se registro).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El sistema NO otorga acceso a la WebApp de Ike. Este es el CA01 real de la HU.</t>
+  </si>
+  <si>
+    <t>TS-01 IMAS-3860 - Caida general del sistema</t>
+  </si>
+  <si>
+    <t>La pantalla de indisponibilidad aparece sin acciones y se oculta al restablecerse el servicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario autenticado en Home.</t>
+  </si>
+  <si>
+    <t>1. Bloquear el endpoint bootstrap del API y recargar la pagina.
+2. Esperar a que el heartbeat detecte la caida (2 fallos consecutivos).
+3. Restablecer el servicio sin recargar la pagina.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - La pantalla de indisponibilidad general reemplaza toda la navegacion, sin botones ni enlaces.
+ - Al restablecerse el servicio, la pantalla se oculta automaticamente sin intervencion del usuario (regresion IMAS-4159).</t>
+  </si>
+  <si>
+    <t>El aviso de indisponibilidad es consistente en todas las pantallas (regresion IMAS-4158)</t>
+  </si>
+  <si>
+    <t>1. Para cada pantalla de la WebApp (Mis Mascotas, Mi Perfil, Servicios, Mis Turnos, Mis Planes): cargarla, bloquear el endpoint bootstrap y recargar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El aviso de indisponibilidad general aparece en TODAS las pantallas, no solo en Home.</t>
+  </si>
+  <si>
+    <t>TS-02 IMAS-3860 - Caida de una funcionalidad puntual (Videollamada)</t>
+  </si>
+  <si>
+    <t>Modal de funcionalidad no disponible con CTA "Ir al inicio"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Usuario autenticado, con al menos una mascota con plan activo.</t>
+  </si>
+  <si>
+    <t>1. Completar el formulario de videollamada hasta la pantalla de revision.
+2. Bloquear el endpoint de creacion del turno y presionar "Confirmar videollamada".
+3. Presionar "Ir al inicio" en el modal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - El modal de funcionalidad no disponible se muestra sobre la revision, sin reemplazarla.
+ - Incluye el CTA "Ir al inicio", que redirecciona correctamente al Home.</t>
+  </si>
+  <si>
+    <t>El resto de la aplicacion sigue operativo con la funcionalidad puntual caida</t>
+  </si>
+  <si>
+    <t>1. Con el servicio de Videollamada caido, navegar a Mis Mascotas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Mis Mascotas carga con normalidad, sin verse afectada por la caida puntual de Videollamada.</t>
+  </si>
 </sst>
 </file>
 
@@ -2252,7 +2492,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,#00%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2337,8 +2577,15 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2426,6 +2673,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2552,7 +2805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2646,6 +2899,21 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2704,9 +2972,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4542,734 +4807,734 @@
   <sheetData>
     <row r="2" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="3" spans="3:24">
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
-      <c r="K3" s="44" t="s">
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="51"/>
+      <c r="K3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="46"/>
-      <c r="S3" s="44" t="s">
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="S3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="46"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="50"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="51"/>
     </row>
     <row r="4" spans="3:24">
-      <c r="C4" s="40"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="39"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="39"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="44"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="44"/>
+      <c r="S4" s="45"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="44"/>
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C5" s="37">
-        <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199)</f>
-        <v>254</v>
-      </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-      <c r="K5" s="37">
-        <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!G:G,"Si")</f>
-        <v>188</v>
-      </c>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="39"/>
-      <c r="S5" s="48">
+      <c r="C5" s="42">
+        <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199)</f>
+        <v>273</v>
+      </c>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
+      <c r="K5" s="42">
+        <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")</f>
+        <v>202</v>
+      </c>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="44"/>
+      <c r="S5" s="53">
         <f>K5/C5</f>
-        <v>0.74015748031496065</v>
-      </c>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="39"/>
+        <v>0.73992673992673996</v>
+      </c>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="44"/>
     </row>
     <row r="6" spans="3:24">
-      <c r="C6" s="40"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="39"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="39"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="39"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="44"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="44"/>
     </row>
     <row r="7" spans="3:24">
-      <c r="C7" s="40"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="39"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="39"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="39"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="44"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="44"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="44"/>
     </row>
     <row r="8" spans="3:24">
-      <c r="C8" s="40"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="39"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="39"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="44"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="44"/>
     </row>
     <row r="9" spans="3:24">
-      <c r="C9" s="40"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="39"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="39"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="44"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="44"/>
     </row>
     <row r="10" spans="3:24">
-      <c r="C10" s="40"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="39"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="39"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="39"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="44"/>
+      <c r="S10" s="45"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="44"/>
     </row>
     <row r="11" spans="3:24">
-      <c r="C11" s="40"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="39"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="39"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="44"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="44"/>
+      <c r="S11" s="45"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="44"/>
     </row>
     <row r="12" spans="3:24">
-      <c r="C12" s="40"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="39"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="39"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="44"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="44"/>
     </row>
     <row r="13" spans="3:24">
-      <c r="C13" s="40"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="39"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="39"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="44"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="44"/>
     </row>
     <row r="14" spans="3:24">
-      <c r="C14" s="40"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="39"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="39"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="44"/>
+      <c r="S14" s="45"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="43"/>
+      <c r="W14" s="43"/>
+      <c r="X14" s="44"/>
     </row>
     <row r="15" spans="3:24">
-      <c r="C15" s="40"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="39"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="39"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="44"/>
+      <c r="S15" s="45"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="44"/>
     </row>
     <row r="16" spans="3:24">
-      <c r="C16" s="40"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="39"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="39"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="44"/>
+      <c r="S16" s="45"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="44"/>
     </row>
     <row r="17" spans="3:24">
-      <c r="C17" s="40"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="39"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="39"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="44"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="43"/>
+      <c r="W17" s="43"/>
+      <c r="X17" s="44"/>
     </row>
     <row r="18" spans="3:24">
-      <c r="C18" s="40"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="39"/>
-      <c r="S18" s="40"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="38"/>
-      <c r="W18" s="38"/>
-      <c r="X18" s="39"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="44"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
+      <c r="X18" s="44"/>
     </row>
     <row r="19" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="43"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="43"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="48"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="48"/>
     </row>
     <row r="22" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="23" spans="3:24">
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="46"/>
-      <c r="K23" s="44" t="s">
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="51"/>
+      <c r="K23" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="46"/>
-      <c r="S23" s="44" t="s">
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="51"/>
+      <c r="S23" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="T23" s="45"/>
-      <c r="U23" s="45"/>
-      <c r="V23" s="45"/>
-      <c r="W23" s="45"/>
-      <c r="X23" s="46"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="51"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="40"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="39"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="38"/>
-      <c r="U24" s="38"/>
-      <c r="V24" s="38"/>
-      <c r="W24" s="38"/>
-      <c r="X24" s="39"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="44"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="43"/>
+      <c r="U24" s="43"/>
+      <c r="V24" s="43"/>
+      <c r="W24" s="43"/>
+      <c r="X24" s="44"/>
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C25" s="37">
-        <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")</f>
-        <v>140</v>
-      </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="K25" s="37">
-        <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")</f>
-        <v>109</v>
-      </c>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="39"/>
-      <c r="S25" s="48">
+      <c r="C25" s="42">
+        <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")</f>
+        <v>146</v>
+      </c>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
+      <c r="K25" s="42">
+        <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")</f>
+        <v>114</v>
+      </c>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="44"/>
+      <c r="S25" s="53">
         <f>K25/C25</f>
-        <v>0.77857142857142858</v>
-      </c>
-      <c r="T25" s="38"/>
-      <c r="U25" s="38"/>
-      <c r="V25" s="38"/>
-      <c r="W25" s="38"/>
-      <c r="X25" s="39"/>
+        <v>0.78082191780821919</v>
+      </c>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43"/>
+      <c r="V25" s="43"/>
+      <c r="W25" s="43"/>
+      <c r="X25" s="44"/>
     </row>
     <row r="26" spans="3:24">
-      <c r="C26" s="40"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="39"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="38"/>
-      <c r="U26" s="38"/>
-      <c r="V26" s="38"/>
-      <c r="W26" s="38"/>
-      <c r="X26" s="39"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="44"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="X26" s="44"/>
     </row>
     <row r="27" spans="3:24">
-      <c r="C27" s="40"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="39"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="38"/>
-      <c r="U27" s="38"/>
-      <c r="V27" s="38"/>
-      <c r="W27" s="38"/>
-      <c r="X27" s="39"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="44"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="43"/>
+      <c r="V27" s="43"/>
+      <c r="W27" s="43"/>
+      <c r="X27" s="44"/>
     </row>
     <row r="28" spans="3:24">
-      <c r="C28" s="40"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="39"/>
-      <c r="S28" s="40"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="38"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="38"/>
-      <c r="X28" s="39"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="44"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="43"/>
+      <c r="W28" s="43"/>
+      <c r="X28" s="44"/>
     </row>
     <row r="29" spans="3:24">
-      <c r="C29" s="40"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="39"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="38"/>
-      <c r="V29" s="38"/>
-      <c r="W29" s="38"/>
-      <c r="X29" s="39"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="44"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="43"/>
+      <c r="U29" s="43"/>
+      <c r="V29" s="43"/>
+      <c r="W29" s="43"/>
+      <c r="X29" s="44"/>
     </row>
     <row r="30" spans="3:24">
-      <c r="C30" s="40"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="39"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
-      <c r="V30" s="38"/>
-      <c r="W30" s="38"/>
-      <c r="X30" s="39"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="44"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="44"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
+      <c r="V30" s="43"/>
+      <c r="W30" s="43"/>
+      <c r="X30" s="44"/>
     </row>
     <row r="31" spans="3:24">
-      <c r="C31" s="40"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="39"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="38"/>
-      <c r="M31" s="38"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="38"/>
-      <c r="P31" s="39"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="38"/>
-      <c r="U31" s="38"/>
-      <c r="V31" s="38"/>
-      <c r="W31" s="38"/>
-      <c r="X31" s="39"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="44"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="44"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="43"/>
+      <c r="U31" s="43"/>
+      <c r="V31" s="43"/>
+      <c r="W31" s="43"/>
+      <c r="X31" s="44"/>
     </row>
     <row r="32" spans="3:24">
-      <c r="C32" s="40"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="38"/>
-      <c r="M32" s="38"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="39"/>
-      <c r="S32" s="40"/>
-      <c r="T32" s="38"/>
-      <c r="U32" s="38"/>
-      <c r="V32" s="38"/>
-      <c r="W32" s="38"/>
-      <c r="X32" s="39"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="44"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="44"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="43"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="43"/>
+      <c r="W32" s="43"/>
+      <c r="X32" s="44"/>
     </row>
     <row r="33" spans="3:24">
-      <c r="C33" s="40"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="38"/>
-      <c r="M33" s="38"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="38"/>
-      <c r="P33" s="39"/>
-      <c r="S33" s="40"/>
-      <c r="T33" s="38"/>
-      <c r="U33" s="38"/>
-      <c r="V33" s="38"/>
-      <c r="W33" s="38"/>
-      <c r="X33" s="39"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="44"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="44"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="43"/>
+      <c r="U33" s="43"/>
+      <c r="V33" s="43"/>
+      <c r="W33" s="43"/>
+      <c r="X33" s="44"/>
     </row>
     <row r="34" spans="3:24">
-      <c r="C34" s="40"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="39"/>
-      <c r="S34" s="40"/>
-      <c r="T34" s="38"/>
-      <c r="U34" s="38"/>
-      <c r="V34" s="38"/>
-      <c r="W34" s="38"/>
-      <c r="X34" s="39"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="44"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="44"/>
     </row>
     <row r="35" spans="3:24">
-      <c r="C35" s="40"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="38"/>
-      <c r="M35" s="38"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="38"/>
-      <c r="P35" s="39"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="38"/>
-      <c r="U35" s="38"/>
-      <c r="V35" s="38"/>
-      <c r="W35" s="38"/>
-      <c r="X35" s="39"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="44"/>
+      <c r="S35" s="45"/>
+      <c r="T35" s="43"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
+      <c r="W35" s="43"/>
+      <c r="X35" s="44"/>
     </row>
     <row r="36" spans="3:24">
-      <c r="C36" s="40"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="39"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="38"/>
-      <c r="M36" s="38"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="39"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="38"/>
-      <c r="U36" s="38"/>
-      <c r="V36" s="38"/>
-      <c r="W36" s="38"/>
-      <c r="X36" s="39"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="44"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="44"/>
+      <c r="S36" s="45"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
+      <c r="W36" s="43"/>
+      <c r="X36" s="44"/>
     </row>
     <row r="37" spans="3:24">
-      <c r="C37" s="40"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="39"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="39"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="38"/>
-      <c r="U37" s="38"/>
-      <c r="V37" s="38"/>
-      <c r="W37" s="38"/>
-      <c r="X37" s="39"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="44"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="44"/>
+      <c r="S37" s="45"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="43"/>
+      <c r="V37" s="43"/>
+      <c r="W37" s="43"/>
+      <c r="X37" s="44"/>
     </row>
     <row r="38" spans="3:24">
-      <c r="C38" s="40"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="39"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="38"/>
-      <c r="O38" s="38"/>
-      <c r="P38" s="39"/>
-      <c r="S38" s="40"/>
-      <c r="T38" s="38"/>
-      <c r="U38" s="38"/>
-      <c r="V38" s="38"/>
-      <c r="W38" s="38"/>
-      <c r="X38" s="39"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="44"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="44"/>
+      <c r="S38" s="45"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="43"/>
+      <c r="V38" s="43"/>
+      <c r="W38" s="43"/>
+      <c r="X38" s="44"/>
     </row>
     <row r="39" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="43"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="42"/>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
-      <c r="P39" s="43"/>
-      <c r="S39" s="41"/>
-      <c r="T39" s="42"/>
-      <c r="U39" s="42"/>
-      <c r="V39" s="42"/>
-      <c r="W39" s="42"/>
-      <c r="X39" s="43"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="48"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="47"/>
+      <c r="N39" s="47"/>
+      <c r="O39" s="47"/>
+      <c r="P39" s="48"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="47"/>
+      <c r="U39" s="47"/>
+      <c r="V39" s="47"/>
+      <c r="W39" s="47"/>
+      <c r="X39" s="48"/>
     </row>
     <row r="41" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="42" spans="3:24">
-      <c r="C42" s="44" t="s">
+      <c r="C42" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="46"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="51"/>
     </row>
     <row r="43" spans="3:24">
-      <c r="C43" s="40"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="39"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="44"/>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
@@ -5278,31 +5543,31 @@
       <c r="P43" s="28"/>
     </row>
     <row r="44" spans="3:24" ht="21" customHeight="1">
-      <c r="C44" s="48">
+      <c r="C44" s="53">
         <f>C25/C5</f>
-        <v>0.55118110236220474</v>
-      </c>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="39"/>
+        <v>0.53479853479853479</v>
+      </c>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="44"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="47" t="s">
+      <c r="L44" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="M44" s="38"/>
-      <c r="N44" s="38"/>
-      <c r="O44" s="38"/>
+      <c r="M44" s="43"/>
+      <c r="N44" s="43"/>
+      <c r="O44" s="43"/>
       <c r="P44" s="29"/>
     </row>
     <row r="45" spans="3:24">
-      <c r="C45" s="40"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="39"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="44"/>
       <c r="K45" s="28"/>
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
@@ -5311,12 +5576,12 @@
       <c r="P45" s="29"/>
     </row>
     <row r="46" spans="3:24">
-      <c r="C46" s="40"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="39"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="44"/>
       <c r="K46" s="28"/>
       <c r="L46" s="31"/>
       <c r="M46" s="28" t="s">
@@ -5327,12 +5592,12 @@
       <c r="P46" s="28"/>
     </row>
     <row r="47" spans="3:24">
-      <c r="C47" s="40"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="39"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="44"/>
       <c r="K47" s="28"/>
       <c r="L47" s="32"/>
       <c r="M47" s="28" t="s">
@@ -5343,12 +5608,12 @@
       <c r="P47" s="28"/>
     </row>
     <row r="48" spans="3:24">
-      <c r="C48" s="40"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="39"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="44"/>
       <c r="K48" s="28"/>
       <c r="L48" s="33"/>
       <c r="M48" s="28" t="s">
@@ -5359,12 +5624,12 @@
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="3:16">
-      <c r="C49" s="40"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="39"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="44"/>
       <c r="K49" s="28"/>
       <c r="L49" s="34"/>
       <c r="M49" s="28" t="s">
@@ -5375,12 +5640,12 @@
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="3:16">
-      <c r="C50" s="40"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="39"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="44"/>
       <c r="K50" s="28"/>
       <c r="L50" s="35"/>
       <c r="M50" s="28" t="s">
@@ -5391,12 +5656,12 @@
       <c r="P50" s="28"/>
     </row>
     <row r="51" spans="3:16">
-      <c r="C51" s="40"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="39"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="44"/>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -5405,230 +5670,230 @@
       <c r="P51" s="28"/>
     </row>
     <row r="52" spans="3:16">
-      <c r="C52" s="40"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="39"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="44"/>
     </row>
     <row r="53" spans="3:16">
-      <c r="C53" s="40"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="39"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="44"/>
     </row>
     <row r="54" spans="3:16">
-      <c r="C54" s="40"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="39"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="44"/>
     </row>
     <row r="55" spans="3:16">
-      <c r="C55" s="40"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="39"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="44"/>
     </row>
     <row r="56" spans="3:16">
-      <c r="C56" s="40"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="39"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="44"/>
     </row>
     <row r="57" spans="3:16">
-      <c r="C57" s="40"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="39"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="44"/>
     </row>
     <row r="58" spans="3:16" ht="15.75" customHeight="1">
-      <c r="C58" s="41"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="43"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="48"/>
     </row>
     <row r="62" spans="3:16">
-      <c r="C62" s="49" t="s">
+      <c r="C62" s="54" t="s">
         <v>585</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="49"/>
-      <c r="F62" s="49"/>
-      <c r="H62" s="49" t="s">
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="H62" s="54" t="s">
         <v>586</v>
       </c>
-      <c r="I62" s="49"/>
-      <c r="J62" s="49"/>
-      <c r="K62" s="49"/>
-      <c r="M62" s="49" t="s">
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
+      <c r="M62" s="54" t="s">
         <v>587</v>
       </c>
-      <c r="N62" s="49"/>
-      <c r="O62" s="49"/>
-      <c r="P62" s="49"/>
+      <c r="N62" s="54"/>
+      <c r="O62" s="54"/>
+      <c r="P62" s="54"/>
     </row>
     <row r="63" spans="3:16">
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="H63" s="49"/>
-      <c r="I63" s="49"/>
-      <c r="J63" s="49"/>
-      <c r="K63" s="49"/>
-      <c r="M63" s="49"/>
-      <c r="N63" s="49"/>
-      <c r="O63" s="49"/>
-      <c r="P63" s="49"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="H63" s="54"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
+      <c r="M63" s="54"/>
+      <c r="N63" s="54"/>
+      <c r="O63" s="54"/>
+      <c r="P63" s="54"/>
     </row>
     <row r="64" spans="3:16">
-      <c r="C64" s="50">
+      <c r="C64" s="55">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
         <v>250</v>
       </c>
-      <c r="D64" s="50"/>
-      <c r="E64" s="50"/>
-      <c r="F64" s="50"/>
-      <c r="H64" s="50">
+      <c r="D64" s="55"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="55"/>
+      <c r="H64" s="55">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
         <v>188</v>
       </c>
-      <c r="I64" s="50"/>
-      <c r="J64" s="50"/>
-      <c r="K64" s="50"/>
-      <c r="M64" s="51">
+      <c r="I64" s="55"/>
+      <c r="J64" s="55"/>
+      <c r="K64" s="55"/>
+      <c r="M64" s="56">
         <f t="shared" ref="M64" si="0">H64/C64</f>
         <v>0.752</v>
       </c>
-      <c r="N64" s="51"/>
-      <c r="O64" s="51"/>
-      <c r="P64" s="51"/>
+      <c r="N64" s="56"/>
+      <c r="O64" s="56"/>
+      <c r="P64" s="56"/>
     </row>
     <row r="65" spans="3:16">
-      <c r="C65" s="50"/>
-      <c r="D65" s="50"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="H65" s="50"/>
-      <c r="I65" s="50"/>
-      <c r="J65" s="50"/>
-      <c r="K65" s="50"/>
-      <c r="M65" s="51"/>
-      <c r="N65" s="51"/>
-      <c r="O65" s="51"/>
-      <c r="P65" s="51"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="H65" s="55"/>
+      <c r="I65" s="55"/>
+      <c r="J65" s="55"/>
+      <c r="K65" s="55"/>
+      <c r="M65" s="56"/>
+      <c r="N65" s="56"/>
+      <c r="O65" s="56"/>
+      <c r="P65" s="56"/>
     </row>
     <row r="66" spans="3:16">
-      <c r="C66" s="50"/>
-      <c r="D66" s="50"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="H66" s="50"/>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="M66" s="51"/>
-      <c r="N66" s="51"/>
-      <c r="O66" s="51"/>
-      <c r="P66" s="51"/>
+      <c r="C66" s="55"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="H66" s="55"/>
+      <c r="I66" s="55"/>
+      <c r="J66" s="55"/>
+      <c r="K66" s="55"/>
+      <c r="M66" s="56"/>
+      <c r="N66" s="56"/>
+      <c r="O66" s="56"/>
+      <c r="P66" s="56"/>
     </row>
     <row r="69" spans="3:16">
-      <c r="C69" s="49" t="s">
+      <c r="C69" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="49"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="H69" s="49" t="s">
+      <c r="D69" s="54"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="54"/>
+      <c r="H69" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="I69" s="49"/>
-      <c r="J69" s="49"/>
-      <c r="K69" s="49"/>
-      <c r="M69" s="49" t="s">
+      <c r="I69" s="54"/>
+      <c r="J69" s="54"/>
+      <c r="K69" s="54"/>
+      <c r="M69" s="54" t="s">
         <v>587</v>
       </c>
-      <c r="N69" s="49"/>
-      <c r="O69" s="49"/>
-      <c r="P69" s="49"/>
+      <c r="N69" s="54"/>
+      <c r="O69" s="54"/>
+      <c r="P69" s="54"/>
     </row>
     <row r="70" spans="3:16">
-      <c r="C70" s="49"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="49"/>
-      <c r="J70" s="49"/>
-      <c r="K70" s="49"/>
-      <c r="M70" s="49"/>
-      <c r="N70" s="49"/>
-      <c r="O70" s="49"/>
-      <c r="P70" s="49"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="H70" s="54"/>
+      <c r="I70" s="54"/>
+      <c r="J70" s="54"/>
+      <c r="K70" s="54"/>
+      <c r="M70" s="54"/>
+      <c r="N70" s="54"/>
+      <c r="O70" s="54"/>
+      <c r="P70" s="54"/>
     </row>
     <row r="71" spans="3:16">
-      <c r="C71" s="50">
+      <c r="C71" s="55">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
         <v>71</v>
       </c>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="H71" s="50">
+      <c r="D71" s="55"/>
+      <c r="E71" s="55"/>
+      <c r="F71" s="55"/>
+      <c r="H71" s="55">
         <f>COUNTIF(Perfil!I:I,"Si")+COUNTIF(Credenciales!I:I,"Si")+COUNTIF(Videollamadas!I:I,"Si")</f>
         <v>60</v>
       </c>
-      <c r="I71" s="50"/>
-      <c r="J71" s="50"/>
-      <c r="K71" s="50"/>
-      <c r="M71" s="51">
+      <c r="I71" s="55"/>
+      <c r="J71" s="55"/>
+      <c r="K71" s="55"/>
+      <c r="M71" s="56">
         <f t="shared" ref="M71" si="1">H71/C71</f>
         <v>0.84507042253521125</v>
       </c>
-      <c r="N71" s="51"/>
-      <c r="O71" s="51"/>
-      <c r="P71" s="51"/>
+      <c r="N71" s="56"/>
+      <c r="O71" s="56"/>
+      <c r="P71" s="56"/>
     </row>
     <row r="72" spans="3:16">
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="H72" s="50"/>
-      <c r="I72" s="50"/>
-      <c r="J72" s="50"/>
-      <c r="K72" s="50"/>
-      <c r="M72" s="51"/>
-      <c r="N72" s="51"/>
-      <c r="O72" s="51"/>
-      <c r="P72" s="51"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="55"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="55"/>
+      <c r="M72" s="56"/>
+      <c r="N72" s="56"/>
+      <c r="O72" s="56"/>
+      <c r="P72" s="56"/>
     </row>
     <row r="73" spans="3:16">
-      <c r="C73" s="50"/>
-      <c r="D73" s="50"/>
-      <c r="E73" s="50"/>
-      <c r="F73" s="50"/>
-      <c r="H73" s="50"/>
-      <c r="I73" s="50"/>
-      <c r="J73" s="50"/>
-      <c r="K73" s="50"/>
-      <c r="M73" s="51"/>
-      <c r="N73" s="51"/>
-      <c r="O73" s="51"/>
-      <c r="P73" s="51"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="55"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="55"/>
+      <c r="J73" s="55"/>
+      <c r="K73" s="55"/>
+      <c r="M73" s="56"/>
+      <c r="N73" s="56"/>
+      <c r="O73" s="56"/>
+      <c r="P73" s="56"/>
     </row>
     <row r="76" spans="3:16">
       <c r="C76" s="36" t="s">
@@ -5670,6 +5935,164 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68DB5A19-D19A-4841-8487-499A0FE9BB4D}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="68.5703125" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="50.5703125" customWidth="1"/>
+    <col min="6" max="6" width="37.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+    </row>
+    <row r="3" spans="1:8" ht="105">
+      <c r="A3" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>679</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>680</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>681</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>682</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>683</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45">
+      <c r="A4" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40" t="s">
+        <v>684</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>631</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>685</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>686</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="75">
+      <c r="A5" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>688</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>689</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>690</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>691</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45">
+      <c r="A6" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40" t="s">
+        <v>692</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>631</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>693</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>694</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
@@ -5720,16 +6143,16 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
       <c r="I2" s="12" t="s">
         <v>27</v>
       </c>
@@ -5738,7 +6161,7 @@
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="61" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -5767,7 +6190,7 @@
       <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="53"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="18" t="s">
         <v>30</v>
       </c>
@@ -5794,7 +6217,7 @@
       <c r="A5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="53"/>
+      <c r="B5" s="58"/>
       <c r="C5" s="18" t="s">
         <v>33</v>
       </c>
@@ -5821,7 +6244,7 @@
       <c r="A6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="53"/>
+      <c r="B6" s="58"/>
       <c r="C6" s="18" t="s">
         <v>38</v>
       </c>
@@ -5848,7 +6271,7 @@
       <c r="A7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="53"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="18" t="s">
         <v>41</v>
       </c>
@@ -5875,7 +6298,7 @@
       <c r="A8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="53"/>
+      <c r="B8" s="58"/>
       <c r="C8" s="18" t="s">
         <v>44</v>
       </c>
@@ -5902,7 +6325,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="53"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="18" t="s">
         <v>46</v>
       </c>
@@ -5929,7 +6352,7 @@
       <c r="A10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="53"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="18" t="s">
         <v>50</v>
       </c>
@@ -5966,7 +6389,7 @@
       <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="60" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -5995,7 +6418,7 @@
       <c r="A13" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="53"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="22" t="s">
         <v>55</v>
       </c>
@@ -6032,7 +6455,7 @@
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="61" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -6061,7 +6484,7 @@
       <c r="A16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="53"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="18" t="s">
         <v>62</v>
       </c>
@@ -6088,7 +6511,7 @@
       <c r="A17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="53"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="18" t="s">
         <v>66</v>
       </c>
@@ -6125,7 +6548,7 @@
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="60" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -6154,7 +6577,7 @@
       <c r="A20" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="53"/>
+      <c r="B20" s="58"/>
       <c r="C20" s="22" t="s">
         <v>73</v>
       </c>
@@ -6181,7 +6604,7 @@
       <c r="A21" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="53"/>
+      <c r="B21" s="58"/>
       <c r="C21" s="22" t="s">
         <v>77</v>
       </c>
@@ -6208,7 +6631,7 @@
       <c r="A22" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="53"/>
+      <c r="B22" s="58"/>
       <c r="C22" s="22" t="s">
         <v>80</v>
       </c>
@@ -6235,7 +6658,7 @@
       <c r="A23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="53"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="22" t="s">
         <v>82</v>
       </c>
@@ -6262,7 +6685,7 @@
       <c r="A24" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="53"/>
+      <c r="B24" s="58"/>
       <c r="C24" s="26" t="s">
         <v>86</v>
       </c>
@@ -6289,7 +6712,7 @@
       <c r="A25" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="53"/>
+      <c r="B25" s="58"/>
       <c r="C25" s="22" t="s">
         <v>88</v>
       </c>
@@ -6326,7 +6749,7 @@
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="61" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -6355,7 +6778,7 @@
       <c r="A28" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="53"/>
+      <c r="B28" s="58"/>
       <c r="C28" s="18" t="s">
         <v>95</v>
       </c>
@@ -6382,7 +6805,7 @@
       <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="53"/>
+      <c r="B29" s="58"/>
       <c r="C29" s="18" t="s">
         <v>98</v>
       </c>
@@ -6409,7 +6832,7 @@
       <c r="A30" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="53"/>
+      <c r="B30" s="58"/>
       <c r="C30" s="18" t="s">
         <v>101</v>
       </c>
@@ -6446,7 +6869,7 @@
       <c r="A32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="60" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="22" t="s">
@@ -6475,7 +6898,7 @@
       <c r="A33" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="53"/>
+      <c r="B33" s="58"/>
       <c r="C33" s="22" t="s">
         <v>109</v>
       </c>
@@ -6502,7 +6925,7 @@
       <c r="A34" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="53"/>
+      <c r="B34" s="58"/>
       <c r="C34" s="22" t="s">
         <v>95</v>
       </c>
@@ -6529,7 +6952,7 @@
       <c r="A35" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="53"/>
+      <c r="B35" s="58"/>
       <c r="C35" s="22" t="s">
         <v>114</v>
       </c>
@@ -6556,7 +6979,7 @@
       <c r="A36" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="53"/>
+      <c r="B36" s="58"/>
       <c r="C36" s="22" t="s">
         <v>117</v>
       </c>
@@ -6593,7 +7016,7 @@
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="61" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -6622,7 +7045,7 @@
       <c r="A39" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="53"/>
+      <c r="B39" s="58"/>
       <c r="C39" s="18" t="s">
         <v>124</v>
       </c>
@@ -6646,16 +7069,16 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A40" s="52" t="s">
+      <c r="A40" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="B40" s="53"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="54"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="59"/>
       <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
@@ -6664,7 +7087,7 @@
       <c r="A41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="60" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="22" t="s">
@@ -6693,7 +7116,7 @@
       <c r="A42" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="53"/>
+      <c r="B42" s="58"/>
       <c r="C42" s="22" t="s">
         <v>30</v>
       </c>
@@ -6720,7 +7143,7 @@
       <c r="A43" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="53"/>
+      <c r="B43" s="58"/>
       <c r="C43" s="22" t="s">
         <v>33</v>
       </c>
@@ -6747,7 +7170,7 @@
       <c r="A44" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B44" s="53"/>
+      <c r="B44" s="58"/>
       <c r="C44" s="22" t="s">
         <v>38</v>
       </c>
@@ -6774,7 +7197,7 @@
       <c r="A45" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="53"/>
+      <c r="B45" s="58"/>
       <c r="C45" s="22" t="s">
         <v>41</v>
       </c>
@@ -6801,7 +7224,7 @@
       <c r="A46" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="53"/>
+      <c r="B46" s="58"/>
       <c r="C46" s="22" t="s">
         <v>44</v>
       </c>
@@ -6828,7 +7251,7 @@
       <c r="A47" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="53"/>
+      <c r="B47" s="58"/>
       <c r="C47" s="22" t="s">
         <v>46</v>
       </c>
@@ -6855,7 +7278,7 @@
       <c r="A48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="53"/>
+      <c r="B48" s="58"/>
       <c r="C48" s="22" t="s">
         <v>50</v>
       </c>
@@ -6892,7 +7315,7 @@
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="56" t="s">
+      <c r="B50" s="61" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -6921,7 +7344,7 @@
       <c r="A51" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="53"/>
+      <c r="B51" s="58"/>
       <c r="C51" s="18" t="s">
         <v>55</v>
       </c>
@@ -6958,7 +7381,7 @@
       <c r="A53" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="55" t="s">
+      <c r="B53" s="60" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="22" t="s">
@@ -6987,7 +7410,7 @@
       <c r="A54" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B54" s="53"/>
+      <c r="B54" s="58"/>
       <c r="C54" s="22" t="s">
         <v>62</v>
       </c>
@@ -7014,7 +7437,7 @@
       <c r="A55" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B55" s="53"/>
+      <c r="B55" s="58"/>
       <c r="C55" s="22" t="s">
         <v>66</v>
       </c>
@@ -7051,7 +7474,7 @@
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="56" t="s">
+      <c r="B57" s="61" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -7080,7 +7503,7 @@
       <c r="A58" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B58" s="53"/>
+      <c r="B58" s="58"/>
       <c r="C58" s="18" t="s">
         <v>73</v>
       </c>
@@ -7107,7 +7530,7 @@
       <c r="A59" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B59" s="53"/>
+      <c r="B59" s="58"/>
       <c r="C59" s="18" t="s">
         <v>77</v>
       </c>
@@ -7134,7 +7557,7 @@
       <c r="A60" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B60" s="53"/>
+      <c r="B60" s="58"/>
       <c r="C60" s="18" t="s">
         <v>80</v>
       </c>
@@ -7161,7 +7584,7 @@
       <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="53"/>
+      <c r="B61" s="58"/>
       <c r="C61" s="18" t="s">
         <v>82</v>
       </c>
@@ -7188,7 +7611,7 @@
       <c r="A62" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B62" s="53"/>
+      <c r="B62" s="58"/>
       <c r="C62" s="27" t="s">
         <v>86</v>
       </c>
@@ -7215,7 +7638,7 @@
       <c r="A63" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B63" s="53"/>
+      <c r="B63" s="58"/>
       <c r="C63" s="18" t="s">
         <v>88</v>
       </c>
@@ -7252,7 +7675,7 @@
       <c r="A65" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="55" t="s">
+      <c r="B65" s="60" t="s">
         <v>90</v>
       </c>
       <c r="C65" s="22" t="s">
@@ -7281,7 +7704,7 @@
       <c r="A66" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B66" s="53"/>
+      <c r="B66" s="58"/>
       <c r="C66" s="22" t="s">
         <v>95</v>
       </c>
@@ -7308,7 +7731,7 @@
       <c r="A67" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B67" s="53"/>
+      <c r="B67" s="58"/>
       <c r="C67" s="22" t="s">
         <v>98</v>
       </c>
@@ -7335,7 +7758,7 @@
       <c r="A68" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B68" s="53"/>
+      <c r="B68" s="58"/>
       <c r="C68" s="22" t="s">
         <v>101</v>
       </c>
@@ -7372,7 +7795,7 @@
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="56" t="s">
+      <c r="B70" s="61" t="s">
         <v>104</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -7401,7 +7824,7 @@
       <c r="A71" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B71" s="53"/>
+      <c r="B71" s="58"/>
       <c r="C71" s="18" t="s">
         <v>109</v>
       </c>
@@ -7428,7 +7851,7 @@
       <c r="A72" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B72" s="53"/>
+      <c r="B72" s="58"/>
       <c r="C72" s="18" t="s">
         <v>95</v>
       </c>
@@ -7455,7 +7878,7 @@
       <c r="A73" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B73" s="53"/>
+      <c r="B73" s="58"/>
       <c r="C73" s="18" t="s">
         <v>114</v>
       </c>
@@ -7482,7 +7905,7 @@
       <c r="A74" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B74" s="53"/>
+      <c r="B74" s="58"/>
       <c r="C74" s="18" t="s">
         <v>117</v>
       </c>
@@ -7519,7 +7942,7 @@
       <c r="A76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="55" t="s">
+      <c r="B76" s="60" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -7548,7 +7971,7 @@
       <c r="A77" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B77" s="53"/>
+      <c r="B77" s="58"/>
       <c r="C77" s="22" t="s">
         <v>124</v>
       </c>
@@ -7572,16 +7995,16 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A78" s="52" t="s">
+      <c r="A78" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="B78" s="53"/>
-      <c r="C78" s="53"/>
-      <c r="D78" s="53"/>
-      <c r="E78" s="53"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
-      <c r="H78" s="54"/>
+      <c r="B78" s="58"/>
+      <c r="C78" s="58"/>
+      <c r="D78" s="58"/>
+      <c r="E78" s="58"/>
+      <c r="F78" s="58"/>
+      <c r="G78" s="58"/>
+      <c r="H78" s="59"/>
       <c r="I78" s="12" t="s">
         <v>27</v>
       </c>
@@ -7590,7 +8013,7 @@
       <c r="A79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="56" t="s">
+      <c r="B79" s="61" t="s">
         <v>141</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -7619,7 +8042,7 @@
       <c r="A80" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B80" s="53"/>
+      <c r="B80" s="58"/>
       <c r="C80" s="18" t="s">
         <v>146</v>
       </c>
@@ -7644,7 +8067,7 @@
       <c r="A81" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B81" s="53"/>
+      <c r="B81" s="58"/>
       <c r="C81" s="18" t="s">
         <v>149</v>
       </c>
@@ -7681,7 +8104,7 @@
       <c r="A83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B83" s="55" t="s">
+      <c r="B83" s="60" t="s">
         <v>153</v>
       </c>
       <c r="C83" s="22" t="s">
@@ -7708,7 +8131,7 @@
       <c r="A84" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B84" s="53"/>
+      <c r="B84" s="58"/>
       <c r="C84" s="22" t="s">
         <v>156</v>
       </c>
@@ -7730,16 +8153,16 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A85" s="52" t="s">
+      <c r="A85" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="B85" s="53"/>
-      <c r="C85" s="53"/>
-      <c r="D85" s="53"/>
-      <c r="E85" s="53"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
-      <c r="H85" s="54"/>
+      <c r="B85" s="58"/>
+      <c r="C85" s="58"/>
+      <c r="D85" s="58"/>
+      <c r="E85" s="58"/>
+      <c r="F85" s="58"/>
+      <c r="G85" s="58"/>
+      <c r="H85" s="59"/>
       <c r="I85" s="12" t="s">
         <v>27</v>
       </c>
@@ -7748,7 +8171,7 @@
       <c r="A86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="56" t="s">
+      <c r="B86" s="61" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -7777,7 +8200,7 @@
       <c r="A87" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B87" s="53"/>
+      <c r="B87" s="58"/>
       <c r="C87" s="18" t="s">
         <v>146</v>
       </c>
@@ -7802,7 +8225,7 @@
       <c r="A88" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B88" s="53"/>
+      <c r="B88" s="58"/>
       <c r="C88" s="18" t="s">
         <v>149</v>
       </c>
@@ -7839,7 +8262,7 @@
       <c r="A90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="55" t="s">
+      <c r="B90" s="60" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -7866,7 +8289,7 @@
       <c r="A91" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B91" s="53"/>
+      <c r="B91" s="58"/>
       <c r="C91" s="22" t="s">
         <v>156</v>
       </c>
@@ -8150,22 +8573,22 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:9" ht="76.5" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -8194,7 +8617,7 @@
       <c r="A4" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="53"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="18" t="s">
         <v>168</v>
       </c>
@@ -8219,7 +8642,7 @@
       <c r="A5" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="53"/>
+      <c r="B5" s="58"/>
       <c r="C5" s="18" t="s">
         <v>172</v>
       </c>
@@ -8246,7 +8669,7 @@
       <c r="A6" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="53"/>
+      <c r="B6" s="58"/>
       <c r="C6" s="18" t="s">
         <v>177</v>
       </c>
@@ -8271,7 +8694,7 @@
       <c r="A7" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="53"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="18" t="s">
         <v>95</v>
       </c>
@@ -8306,7 +8729,7 @@
       <c r="A9" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -8335,7 +8758,7 @@
       <c r="A10" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="53"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="22" t="s">
         <v>186</v>
       </c>
@@ -8362,7 +8785,7 @@
       <c r="A11" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B11" s="53"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="22" t="s">
         <v>188</v>
       </c>
@@ -8389,7 +8812,7 @@
       <c r="A12" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="53"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="22" t="s">
         <v>95</v>
       </c>
@@ -8424,7 +8847,7 @@
       <c r="A14" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -8453,7 +8876,7 @@
       <c r="A15" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B15" s="53"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="18" t="s">
         <v>91</v>
       </c>
@@ -8480,7 +8903,7 @@
       <c r="A16" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B16" s="53"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="18" t="s">
         <v>198</v>
       </c>
@@ -8507,7 +8930,7 @@
       <c r="A17" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B17" s="53"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="18" t="s">
         <v>201</v>
       </c>
@@ -8534,7 +8957,7 @@
       <c r="A18" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="53"/>
+      <c r="B18" s="58"/>
       <c r="C18" s="18" t="s">
         <v>205</v>
       </c>
@@ -8571,7 +8994,7 @@
       <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="59" t="s">
         <v>612</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -8600,7 +9023,7 @@
       <c r="A21" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B21" s="53"/>
+      <c r="B21" s="58"/>
       <c r="C21" s="6" t="s">
         <v>596</v>
       </c>
@@ -8715,7 +9138,7 @@
       <c r="A26" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -8735,7 +9158,7 @@
       <c r="A27" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="53"/>
+      <c r="B27" s="58"/>
       <c r="C27" s="6" t="s">
         <v>168</v>
       </c>
@@ -8753,7 +9176,7 @@
       <c r="A28" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B28" s="53"/>
+      <c r="B28" s="58"/>
       <c r="C28" s="6" t="s">
         <v>210</v>
       </c>
@@ -8771,7 +9194,7 @@
       <c r="A29" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B29" s="53"/>
+      <c r="B29" s="58"/>
       <c r="C29" s="6" t="s">
         <v>211</v>
       </c>
@@ -8789,7 +9212,7 @@
       <c r="A30" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B30" s="53"/>
+      <c r="B30" s="58"/>
       <c r="C30" s="6" t="s">
         <v>212</v>
       </c>
@@ -8804,22 +9227,22 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A31" s="52" t="s">
+      <c r="A31" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="54"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="59"/>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C32" s="18" t="s">
@@ -8848,7 +9271,7 @@
       <c r="A33" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B33" s="53"/>
+      <c r="B33" s="58"/>
       <c r="C33" s="18" t="s">
         <v>168</v>
       </c>
@@ -8873,7 +9296,7 @@
       <c r="A34" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="53"/>
+      <c r="B34" s="58"/>
       <c r="C34" s="18" t="s">
         <v>172</v>
       </c>
@@ -8900,7 +9323,7 @@
       <c r="A35" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B35" s="53"/>
+      <c r="B35" s="58"/>
       <c r="C35" s="18" t="s">
         <v>177</v>
       </c>
@@ -8925,7 +9348,7 @@
       <c r="A36" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="53"/>
+      <c r="B36" s="58"/>
       <c r="C36" s="18" t="s">
         <v>95</v>
       </c>
@@ -8960,7 +9383,7 @@
       <c r="A38" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="55" t="s">
+      <c r="B38" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C38" s="22" t="s">
@@ -8989,7 +9412,7 @@
       <c r="A39" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="53"/>
+      <c r="B39" s="58"/>
       <c r="C39" s="22" t="s">
         <v>186</v>
       </c>
@@ -9016,7 +9439,7 @@
       <c r="A40" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B40" s="53"/>
+      <c r="B40" s="58"/>
       <c r="C40" s="22" t="s">
         <v>188</v>
       </c>
@@ -9043,7 +9466,7 @@
       <c r="A41" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B41" s="53"/>
+      <c r="B41" s="58"/>
       <c r="C41" s="22" t="s">
         <v>95</v>
       </c>
@@ -9078,7 +9501,7 @@
       <c r="A43" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="56" t="s">
+      <c r="B43" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C43" s="18" t="s">
@@ -9107,7 +9530,7 @@
       <c r="A44" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B44" s="53"/>
+      <c r="B44" s="58"/>
       <c r="C44" s="18" t="s">
         <v>91</v>
       </c>
@@ -9134,7 +9557,7 @@
       <c r="A45" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B45" s="53"/>
+      <c r="B45" s="58"/>
       <c r="C45" s="18" t="s">
         <v>198</v>
       </c>
@@ -9161,7 +9584,7 @@
       <c r="A46" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B46" s="53"/>
+      <c r="B46" s="58"/>
       <c r="C46" s="18" t="s">
         <v>201</v>
       </c>
@@ -9188,7 +9611,7 @@
       <c r="A47" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B47" s="53"/>
+      <c r="B47" s="58"/>
       <c r="C47" s="18" t="s">
         <v>205</v>
       </c>
@@ -9225,7 +9648,7 @@
       <c r="A49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="54" t="s">
+      <c r="B49" s="59" t="s">
         <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -9254,7 +9677,7 @@
       <c r="A50" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B50" s="53"/>
+      <c r="B50" s="58"/>
       <c r="C50" s="6" t="s">
         <v>596</v>
       </c>
@@ -9369,7 +9792,7 @@
       <c r="A55" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="54" t="s">
+      <c r="B55" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -9389,7 +9812,7 @@
       <c r="A56" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="53"/>
+      <c r="B56" s="58"/>
       <c r="C56" s="6" t="s">
         <v>168</v>
       </c>
@@ -9407,7 +9830,7 @@
       <c r="A57" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B57" s="53"/>
+      <c r="B57" s="58"/>
       <c r="C57" s="6" t="s">
         <v>210</v>
       </c>
@@ -9425,7 +9848,7 @@
       <c r="A58" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B58" s="53"/>
+      <c r="B58" s="58"/>
       <c r="C58" s="6" t="s">
         <v>211</v>
       </c>
@@ -9443,7 +9866,7 @@
       <c r="A59" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B59" s="53"/>
+      <c r="B59" s="58"/>
       <c r="C59" s="6" t="s">
         <v>212</v>
       </c>
@@ -9458,22 +9881,22 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A60" s="52" t="s">
+      <c r="A60" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="B60" s="53"/>
-      <c r="C60" s="53"/>
-      <c r="D60" s="53"/>
-      <c r="E60" s="53"/>
-      <c r="F60" s="53"/>
-      <c r="G60" s="53"/>
-      <c r="H60" s="54"/>
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="59"/>
     </row>
     <row r="61" spans="1:9" ht="76.5" customHeight="1">
       <c r="A61" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="56" t="s">
+      <c r="B61" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -9502,7 +9925,7 @@
       <c r="A62" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B62" s="53"/>
+      <c r="B62" s="58"/>
       <c r="C62" s="18" t="s">
         <v>168</v>
       </c>
@@ -9527,7 +9950,7 @@
       <c r="A63" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B63" s="53"/>
+      <c r="B63" s="58"/>
       <c r="C63" s="18" t="s">
         <v>172</v>
       </c>
@@ -9554,7 +9977,7 @@
       <c r="A64" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B64" s="53"/>
+      <c r="B64" s="58"/>
       <c r="C64" s="18" t="s">
         <v>177</v>
       </c>
@@ -9579,7 +10002,7 @@
       <c r="A65" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B65" s="53"/>
+      <c r="B65" s="58"/>
       <c r="C65" s="18" t="s">
         <v>95</v>
       </c>
@@ -9614,7 +10037,7 @@
       <c r="A67" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B67" s="55" t="s">
+      <c r="B67" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C67" s="22" t="s">
@@ -9643,7 +10066,7 @@
       <c r="A68" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B68" s="53"/>
+      <c r="B68" s="58"/>
       <c r="C68" s="22" t="s">
         <v>186</v>
       </c>
@@ -9670,7 +10093,7 @@
       <c r="A69" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B69" s="53"/>
+      <c r="B69" s="58"/>
       <c r="C69" s="22" t="s">
         <v>188</v>
       </c>
@@ -9697,7 +10120,7 @@
       <c r="A70" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B70" s="53"/>
+      <c r="B70" s="58"/>
       <c r="C70" s="22" t="s">
         <v>95</v>
       </c>
@@ -9732,7 +10155,7 @@
       <c r="A72" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="56" t="s">
+      <c r="B72" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C72" s="18" t="s">
@@ -9761,7 +10184,7 @@
       <c r="A73" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B73" s="53"/>
+      <c r="B73" s="58"/>
       <c r="C73" s="18" t="s">
         <v>91</v>
       </c>
@@ -9788,7 +10211,7 @@
       <c r="A74" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="53"/>
+      <c r="B74" s="58"/>
       <c r="C74" s="18" t="s">
         <v>198</v>
       </c>
@@ -9815,7 +10238,7 @@
       <c r="A75" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B75" s="53"/>
+      <c r="B75" s="58"/>
       <c r="C75" s="18" t="s">
         <v>201</v>
       </c>
@@ -9842,7 +10265,7 @@
       <c r="A76" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B76" s="53"/>
+      <c r="B76" s="58"/>
       <c r="C76" s="18" t="s">
         <v>205</v>
       </c>
@@ -9879,7 +10302,7 @@
       <c r="A78" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="54" t="s">
+      <c r="B78" s="59" t="s">
         <v>611</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -9908,7 +10331,7 @@
       <c r="A79" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B79" s="53"/>
+      <c r="B79" s="58"/>
       <c r="C79" s="6" t="s">
         <v>596</v>
       </c>
@@ -10023,7 +10446,7 @@
       <c r="A84" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="54" t="s">
+      <c r="B84" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -10043,7 +10466,7 @@
       <c r="A85" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B85" s="53"/>
+      <c r="B85" s="58"/>
       <c r="C85" s="6" t="s">
         <v>168</v>
       </c>
@@ -10061,7 +10484,7 @@
       <c r="A86" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B86" s="53"/>
+      <c r="B86" s="58"/>
       <c r="C86" s="6" t="s">
         <v>210</v>
       </c>
@@ -10079,7 +10502,7 @@
       <c r="A87" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B87" s="53"/>
+      <c r="B87" s="58"/>
       <c r="C87" s="6" t="s">
         <v>211</v>
       </c>
@@ -10097,7 +10520,7 @@
       <c r="A88" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B88" s="53"/>
+      <c r="B88" s="58"/>
       <c r="C88" s="6" t="s">
         <v>212</v>
       </c>
@@ -10112,22 +10535,22 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A89" s="52" t="s">
+      <c r="A89" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="B89" s="53"/>
-      <c r="C89" s="53"/>
-      <c r="D89" s="53"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
-      <c r="H89" s="54"/>
+      <c r="B89" s="58"/>
+      <c r="C89" s="58"/>
+      <c r="D89" s="58"/>
+      <c r="E89" s="58"/>
+      <c r="F89" s="58"/>
+      <c r="G89" s="58"/>
+      <c r="H89" s="59"/>
     </row>
     <row r="90" spans="1:9" ht="76.5" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="56" t="s">
+      <c r="B90" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C90" s="18" t="s">
@@ -10156,7 +10579,7 @@
       <c r="A91" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B91" s="53"/>
+      <c r="B91" s="58"/>
       <c r="C91" s="18" t="s">
         <v>168</v>
       </c>
@@ -10181,7 +10604,7 @@
       <c r="A92" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B92" s="53"/>
+      <c r="B92" s="58"/>
       <c r="C92" s="18" t="s">
         <v>172</v>
       </c>
@@ -10208,7 +10631,7 @@
       <c r="A93" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B93" s="53"/>
+      <c r="B93" s="58"/>
       <c r="C93" s="18" t="s">
         <v>177</v>
       </c>
@@ -10233,7 +10656,7 @@
       <c r="A94" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B94" s="53"/>
+      <c r="B94" s="58"/>
       <c r="C94" s="18" t="s">
         <v>95</v>
       </c>
@@ -10268,7 +10691,7 @@
       <c r="A96" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B96" s="55" t="s">
+      <c r="B96" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C96" s="22" t="s">
@@ -10297,7 +10720,7 @@
       <c r="A97" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B97" s="53"/>
+      <c r="B97" s="58"/>
       <c r="C97" s="22" t="s">
         <v>186</v>
       </c>
@@ -10324,7 +10747,7 @@
       <c r="A98" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B98" s="53"/>
+      <c r="B98" s="58"/>
       <c r="C98" s="22" t="s">
         <v>188</v>
       </c>
@@ -10351,7 +10774,7 @@
       <c r="A99" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B99" s="53"/>
+      <c r="B99" s="58"/>
       <c r="C99" s="22" t="s">
         <v>95</v>
       </c>
@@ -10386,7 +10809,7 @@
       <c r="A101" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="56" t="s">
+      <c r="B101" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C101" s="18" t="s">
@@ -10415,7 +10838,7 @@
       <c r="A102" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B102" s="53"/>
+      <c r="B102" s="58"/>
       <c r="C102" s="18" t="s">
         <v>91</v>
       </c>
@@ -10442,7 +10865,7 @@
       <c r="A103" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B103" s="53"/>
+      <c r="B103" s="58"/>
       <c r="C103" s="18" t="s">
         <v>198</v>
       </c>
@@ -10469,7 +10892,7 @@
       <c r="A104" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B104" s="53"/>
+      <c r="B104" s="58"/>
       <c r="C104" s="18" t="s">
         <v>201</v>
       </c>
@@ -10496,7 +10919,7 @@
       <c r="A105" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B105" s="53"/>
+      <c r="B105" s="58"/>
       <c r="C105" s="18" t="s">
         <v>205</v>
       </c>
@@ -10533,7 +10956,7 @@
       <c r="A107" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B107" s="54" t="s">
+      <c r="B107" s="59" t="s">
         <v>591</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -10562,7 +10985,7 @@
       <c r="A108" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B108" s="53"/>
+      <c r="B108" s="58"/>
       <c r="C108" s="6" t="s">
         <v>596</v>
       </c>
@@ -10677,7 +11100,7 @@
       <c r="A113" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B113" s="54" t="s">
+      <c r="B113" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -10697,7 +11120,7 @@
       <c r="A114" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B114" s="53"/>
+      <c r="B114" s="58"/>
       <c r="C114" s="6" t="s">
         <v>168</v>
       </c>
@@ -10715,7 +11138,7 @@
       <c r="A115" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B115" s="53"/>
+      <c r="B115" s="58"/>
       <c r="C115" s="6" t="s">
         <v>210</v>
       </c>
@@ -10733,7 +11156,7 @@
       <c r="A116" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B116" s="53"/>
+      <c r="B116" s="58"/>
       <c r="C116" s="6" t="s">
         <v>211</v>
       </c>
@@ -10751,7 +11174,7 @@
       <c r="A117" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B117" s="53"/>
+      <c r="B117" s="58"/>
       <c r="C117" s="6" t="s">
         <v>212</v>
       </c>
@@ -11193,19 +11616,19 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="198" customHeight="1">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="59" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -11237,12 +11660,12 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="58" t="s">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="63" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="58" t="s">
         <v>218</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -11268,10 +11691,10 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="45.75" customHeight="1">
-      <c r="A5" s="58"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="53"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="6" t="s">
         <v>224</v>
       </c>
@@ -11281,11 +11704,11 @@
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="121.5" customHeight="1">
-      <c r="B6" s="54"/>
-      <c r="C6" s="58" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="58" t="s">
         <v>218</v>
       </c>
       <c r="E6" s="13" t="s">
@@ -11311,9 +11734,9 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="45.75" customHeight="1">
-      <c r="B7" s="54"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="53"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="58"/>
       <c r="E7" s="13" t="s">
         <v>227</v>
       </c>
@@ -11323,7 +11746,7 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B8" s="54"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="13" t="s">
         <v>229</v>
       </c>
@@ -11339,7 +11762,7 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B9" s="54"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="13" t="s">
         <v>231</v>
       </c>
@@ -11355,7 +11778,7 @@
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
-      <c r="B10" s="54"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="13" t="s">
         <v>232</v>
       </c>
@@ -11385,7 +11808,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="140.25" customHeight="1">
-      <c r="B11" s="54"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="13" t="s">
         <v>235</v>
       </c>
@@ -11425,15 +11848,15 @@
       <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
       <c r="H13" s="2"/>
     </row>
   </sheetData>
@@ -11566,7 +11989,7 @@
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="61" t="s">
         <v>239</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -11601,7 +12024,7 @@
       <c r="A4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="59"/>
       <c r="C4" s="18" t="s">
         <v>244</v>
       </c>
@@ -11634,7 +12057,7 @@
       <c r="A5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="54"/>
+      <c r="B5" s="59"/>
       <c r="C5" s="18" t="s">
         <v>247</v>
       </c>
@@ -11667,7 +12090,7 @@
       <c r="A6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="54"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="18" t="s">
         <v>251</v>
       </c>
@@ -11710,7 +12133,7 @@
       <c r="A8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="60" t="s">
         <v>254</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -11745,7 +12168,7 @@
       <c r="A9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="22" t="s">
         <v>259</v>
       </c>
@@ -11778,11 +12201,11 @@
       <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="59" t="s">
+      <c r="B10" s="59"/>
+      <c r="C10" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="64" t="s">
         <v>263</v>
       </c>
       <c r="E10" s="11" t="s">
@@ -11791,7 +12214,7 @@
       <c r="F10" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="59" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -11811,16 +12234,16 @@
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="58"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="63"/>
       <c r="E11" s="11" t="s">
         <v>266</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G11" s="54"/>
+      <c r="G11" s="59"/>
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
@@ -11838,7 +12261,7 @@
       <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="54"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="22" t="s">
         <v>267</v>
       </c>
@@ -11871,7 +12294,7 @@
       <c r="A13" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="54"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="22" t="s">
         <v>271</v>
       </c>
@@ -11904,7 +12327,7 @@
       <c r="A14" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B14" s="54"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="22" t="s">
         <v>274</v>
       </c>
@@ -11937,7 +12360,7 @@
       <c r="A15" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="54"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="22" t="s">
         <v>279</v>
       </c>
@@ -11970,7 +12393,7 @@
       <c r="A16" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="54"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="22" t="s">
         <v>282</v>
       </c>
@@ -12003,7 +12426,7 @@
       <c r="A17" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="54"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="22" t="s">
         <v>286</v>
       </c>
@@ -12036,7 +12459,7 @@
       <c r="A18" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B18" s="54"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="22" t="s">
         <v>289</v>
       </c>
@@ -12069,7 +12492,7 @@
       <c r="A19" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="54"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="22" t="s">
         <v>294</v>
       </c>
@@ -12102,7 +12525,7 @@
       <c r="A20" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="54"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="22" t="s">
         <v>298</v>
       </c>
@@ -12135,7 +12558,7 @@
       <c r="A21" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="54"/>
+      <c r="B21" s="59"/>
       <c r="C21" s="22" t="s">
         <v>303</v>
       </c>
@@ -12168,7 +12591,7 @@
       <c r="A22" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="54"/>
+      <c r="B22" s="59"/>
       <c r="C22" s="22" t="s">
         <v>305</v>
       </c>
@@ -12201,7 +12624,7 @@
       <c r="A23" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="54"/>
+      <c r="B23" s="59"/>
       <c r="C23" s="22" t="s">
         <v>310</v>
       </c>
@@ -12234,7 +12657,7 @@
       <c r="A24" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B24" s="54"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="22" t="s">
         <v>314</v>
       </c>
@@ -12267,7 +12690,7 @@
       <c r="A25" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="54"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="22" t="s">
         <v>316</v>
       </c>
@@ -12297,11 +12720,11 @@
       <c r="A26" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="59" t="s">
+      <c r="B26" s="59"/>
+      <c r="C26" s="64" t="s">
         <v>321</v>
       </c>
-      <c r="D26" s="59" t="s">
+      <c r="D26" s="64" t="s">
         <v>322</v>
       </c>
       <c r="E26" s="11" t="s">
@@ -12310,10 +12733,10 @@
       <c r="F26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="G26" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="54" t="s">
+      <c r="G26" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="59" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
@@ -12327,23 +12750,23 @@
       <c r="A27" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="54"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="58"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="63"/>
       <c r="E27" s="11" t="s">
         <v>326</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G27" s="54"/>
-      <c r="H27" s="58"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:11" ht="76.5" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B28" s="54"/>
+      <c r="B28" s="59"/>
       <c r="C28" s="22" t="s">
         <v>329</v>
       </c>
@@ -12376,7 +12799,7 @@
       <c r="A29" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B29" s="54"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="22" t="s">
         <v>334</v>
       </c>
@@ -12409,7 +12832,7 @@
       <c r="A30" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B30" s="54"/>
+      <c r="B30" s="59"/>
       <c r="C30" s="22" t="s">
         <v>338</v>
       </c>
@@ -12442,7 +12865,7 @@
       <c r="A31" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B31" s="54"/>
+      <c r="B31" s="59"/>
       <c r="C31" s="22" t="s">
         <v>341</v>
       </c>
@@ -12557,7 +12980,7 @@
       <c r="A36" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="61" t="s">
         <v>349</v>
       </c>
       <c r="C36" s="22" t="s">
@@ -12592,7 +13015,7 @@
       <c r="A37" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="54"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="23" t="s">
         <v>354</v>
       </c>
@@ -12714,22 +13137,22 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="62" t="s">
         <v>357</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
     </row>
     <row r="3" spans="1:11" ht="30.75" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="61" t="s">
         <v>359</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -12764,7 +13187,7 @@
       <c r="A4" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="65"/>
       <c r="C4" s="8" t="s">
         <v>365</v>
       </c>
@@ -12797,7 +13220,7 @@
       <c r="A5" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B5" s="60"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="8" t="s">
         <v>370</v>
       </c>
@@ -12830,7 +13253,7 @@
       <c r="A6" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B6" s="60"/>
+      <c r="B6" s="65"/>
       <c r="C6" s="8" t="s">
         <v>375</v>
       </c>
@@ -12863,7 +13286,7 @@
       <c r="A7" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="65"/>
       <c r="C7" s="8" t="s">
         <v>380</v>
       </c>
@@ -12903,22 +13326,22 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="62" t="s">
         <v>384</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="60"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
       <c r="A10" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="60" t="s">
         <v>385</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -12953,7 +13376,7 @@
       <c r="A11" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="65"/>
       <c r="C11" s="11" t="s">
         <v>390</v>
       </c>
@@ -12986,7 +13409,7 @@
       <c r="A12" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B12" s="60"/>
+      <c r="B12" s="65"/>
       <c r="C12" s="11" t="s">
         <v>394</v>
       </c>
@@ -13019,7 +13442,7 @@
       <c r="A13" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="B13" s="60"/>
+      <c r="B13" s="65"/>
       <c r="C13" s="11" t="s">
         <v>398</v>
       </c>
@@ -13052,7 +13475,7 @@
       <c r="A14" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="B14" s="60"/>
+      <c r="B14" s="65"/>
       <c r="C14" s="11" t="s">
         <v>402</v>
       </c>
@@ -13085,7 +13508,7 @@
       <c r="A15" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="B15" s="60"/>
+      <c r="B15" s="65"/>
       <c r="C15" s="11" t="s">
         <v>407</v>
       </c>
@@ -13118,7 +13541,7 @@
       <c r="A16" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B16" s="60"/>
+      <c r="B16" s="65"/>
       <c r="C16" s="11" t="s">
         <v>412</v>
       </c>
@@ -13151,7 +13574,7 @@
       <c r="A17" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="B17" s="60"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="11" t="s">
         <v>417</v>
       </c>
@@ -13191,22 +13614,22 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:11" ht="106.5" customHeight="1">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="62" t="s">
         <v>421</v>
       </c>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="60"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="65"/>
     </row>
     <row r="20" spans="1:11" ht="106.5" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="61" t="s">
         <v>422</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -13241,7 +13664,7 @@
       <c r="A21" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="B21" s="60"/>
+      <c r="B21" s="65"/>
       <c r="C21" s="8" t="s">
         <v>427</v>
       </c>
@@ -13274,7 +13697,7 @@
       <c r="A22" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="65"/>
       <c r="C22" s="8" t="s">
         <v>431</v>
       </c>
@@ -13307,7 +13730,7 @@
       <c r="A23" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B23" s="60"/>
+      <c r="B23" s="65"/>
       <c r="C23" s="8" t="s">
         <v>435</v>
       </c>
@@ -13340,7 +13763,7 @@
       <c r="A24" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B24" s="60"/>
+      <c r="B24" s="65"/>
       <c r="C24" s="8" t="s">
         <v>439</v>
       </c>
@@ -13373,7 +13796,7 @@
       <c r="A25" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B25" s="60"/>
+      <c r="B25" s="65"/>
       <c r="C25" s="8" t="s">
         <v>443</v>
       </c>
@@ -13406,7 +13829,7 @@
       <c r="A26" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="B26" s="60"/>
+      <c r="B26" s="65"/>
       <c r="C26" s="8" t="s">
         <v>447</v>
       </c>
@@ -13439,7 +13862,7 @@
       <c r="A27" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B27" s="60"/>
+      <c r="B27" s="65"/>
       <c r="C27" s="8" t="s">
         <v>451</v>
       </c>
@@ -13472,7 +13895,7 @@
       <c r="A28" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="B28" s="60"/>
+      <c r="B28" s="65"/>
       <c r="C28" s="8" t="s">
         <v>456</v>
       </c>
@@ -13505,7 +13928,7 @@
       <c r="A29" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B29" s="60"/>
+      <c r="B29" s="65"/>
       <c r="C29" s="8" t="s">
         <v>461</v>
       </c>
@@ -13538,7 +13961,7 @@
       <c r="A30" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="B30" s="60"/>
+      <c r="B30" s="65"/>
       <c r="C30" s="8" t="s">
         <v>466</v>
       </c>
@@ -13571,7 +13994,7 @@
       <c r="A31" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="B31" s="60"/>
+      <c r="B31" s="65"/>
       <c r="C31" s="8" t="s">
         <v>471</v>
       </c>
@@ -13604,7 +14027,7 @@
       <c r="A32" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B32" s="60"/>
+      <c r="B32" s="65"/>
       <c r="C32" s="8" t="s">
         <v>476</v>
       </c>
@@ -13637,7 +14060,7 @@
       <c r="A33" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="B33" s="60"/>
+      <c r="B33" s="65"/>
       <c r="C33" s="8" t="s">
         <v>481</v>
       </c>
@@ -13670,7 +14093,7 @@
       <c r="A34" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="B34" s="60"/>
+      <c r="B34" s="65"/>
       <c r="C34" s="8" t="s">
         <v>486</v>
       </c>
@@ -13703,7 +14126,7 @@
       <c r="A35" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="B35" s="60"/>
+      <c r="B35" s="65"/>
       <c r="C35" s="8" t="s">
         <v>491</v>
       </c>
@@ -13736,7 +14159,7 @@
       <c r="A36" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="B36" s="60"/>
+      <c r="B36" s="65"/>
       <c r="C36" s="8" t="s">
         <v>496</v>
       </c>
@@ -13769,7 +14192,7 @@
       <c r="A37" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="B37" s="60"/>
+      <c r="B37" s="65"/>
       <c r="C37" s="8" t="s">
         <v>499</v>
       </c>
@@ -13809,22 +14232,22 @@
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="62" t="s">
         <v>503</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="60"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="65"/>
     </row>
     <row r="40" spans="1:11" ht="45" customHeight="1">
       <c r="A40" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="60" t="s">
         <v>505</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -13859,7 +14282,7 @@
       <c r="A41" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="B41" s="60"/>
+      <c r="B41" s="65"/>
       <c r="C41" s="11" t="s">
         <v>511</v>
       </c>
@@ -13892,7 +14315,7 @@
       <c r="A42" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="B42" s="60"/>
+      <c r="B42" s="65"/>
       <c r="C42" s="11" t="s">
         <v>516</v>
       </c>
@@ -13925,7 +14348,7 @@
       <c r="A43" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="B43" s="60"/>
+      <c r="B43" s="65"/>
       <c r="C43" s="11" t="s">
         <v>521</v>
       </c>
@@ -13965,22 +14388,22 @@
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="57" t="s">
+      <c r="A45" s="62" t="s">
         <v>525</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="60"/>
-      <c r="F45" s="53"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="60"/>
+      <c r="B45" s="65"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="65"/>
+      <c r="E45" s="65"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="66"/>
+      <c r="H45" s="65"/>
     </row>
     <row r="46" spans="1:11" ht="60" customHeight="1">
       <c r="A46" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="61" t="s">
         <v>526</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -14015,7 +14438,7 @@
       <c r="A47" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="B47" s="60"/>
+      <c r="B47" s="65"/>
       <c r="C47" s="8" t="s">
         <v>531</v>
       </c>
@@ -14048,7 +14471,7 @@
       <c r="A48" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B48" s="60"/>
+      <c r="B48" s="65"/>
       <c r="C48" s="8" t="s">
         <v>535</v>
       </c>
@@ -14081,7 +14504,7 @@
       <c r="A49" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B49" s="60"/>
+      <c r="B49" s="65"/>
       <c r="C49" s="8" t="s">
         <v>539</v>
       </c>
@@ -14114,7 +14537,7 @@
       <c r="A50" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B50" s="60"/>
+      <c r="B50" s="65"/>
       <c r="C50" s="8" t="s">
         <v>543</v>
       </c>
@@ -14147,7 +14570,7 @@
       <c r="A51" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B51" s="60"/>
+      <c r="B51" s="65"/>
       <c r="C51" s="8" t="s">
         <v>547</v>
       </c>
@@ -14180,7 +14603,7 @@
       <c r="A52" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="B52" s="60"/>
+      <c r="B52" s="65"/>
       <c r="C52" s="8" t="s">
         <v>551</v>
       </c>
@@ -14213,7 +14636,7 @@
       <c r="A53" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B53" s="60"/>
+      <c r="B53" s="65"/>
       <c r="C53" s="8" t="s">
         <v>555</v>
       </c>
@@ -14243,22 +14666,22 @@
       </c>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="57" t="s">
+      <c r="A55" s="62" t="s">
         <v>559</v>
       </c>
-      <c r="B55" s="60"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="60"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="60"/>
+      <c r="B55" s="65"/>
+      <c r="C55" s="65"/>
+      <c r="D55" s="65"/>
+      <c r="E55" s="65"/>
+      <c r="F55" s="58"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="65"/>
     </row>
     <row r="56" spans="1:11" ht="60" customHeight="1">
       <c r="A56" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B56" s="38" t="s">
+      <c r="B56" s="43" t="s">
         <v>560</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -14293,7 +14716,7 @@
       <c r="A57" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="B57" s="60"/>
+      <c r="B57" s="65"/>
       <c r="C57" s="8" t="s">
         <v>564</v>
       </c>
@@ -14326,7 +14749,7 @@
       <c r="A58" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B58" s="60"/>
+      <c r="B58" s="65"/>
       <c r="C58" s="8" t="s">
         <v>568</v>
       </c>
@@ -14359,7 +14782,7 @@
       <c r="A59" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B59" s="60"/>
+      <c r="B59" s="65"/>
       <c r="C59" s="8" t="s">
         <v>572</v>
       </c>
@@ -14392,7 +14815,7 @@
       <c r="A60" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B60" s="60"/>
+      <c r="B60" s="65"/>
       <c r="C60" s="8" t="s">
         <v>576</v>
       </c>
@@ -14529,16 +14952,16 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8" ht="30">
       <c r="A3" t="s">
@@ -14553,7 +14976,7 @@
       <c r="D3" t="s">
         <v>616</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="37" t="s">
         <v>617</v>
       </c>
       <c r="F3" t="s">
@@ -14584,7 +15007,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30.7109375" customWidth="1"/>
@@ -14623,16 +15046,247 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D3" t="s">
+        <v>621</v>
+      </c>
+      <c r="E3" t="s">
+        <v>622</v>
+      </c>
+      <c r="F3" t="s">
+        <v>623</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>624</v>
+      </c>
+      <c r="C4" t="s">
+        <v>625</v>
+      </c>
+      <c r="D4" t="s">
+        <v>626</v>
+      </c>
+      <c r="E4" t="s">
+        <v>627</v>
+      </c>
+      <c r="F4" t="s">
+        <v>628</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" t="s">
+        <v>629</v>
+      </c>
+      <c r="C5" t="s">
+        <v>630</v>
+      </c>
+      <c r="D5" t="s">
+        <v>631</v>
+      </c>
+      <c r="E5" t="s">
+        <v>632</v>
+      </c>
+      <c r="F5" t="s">
+        <v>633</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" t="s">
+        <v>634</v>
+      </c>
+      <c r="D6" t="s">
+        <v>631</v>
+      </c>
+      <c r="E6" t="s">
+        <v>632</v>
+      </c>
+      <c r="F6" t="s">
+        <v>635</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C7" t="s">
+        <v>637</v>
+      </c>
+      <c r="D7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E7" t="s">
+        <v>638</v>
+      </c>
+      <c r="F7" t="s">
+        <v>639</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30">
+      <c r="A8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" t="s">
+        <v>640</v>
+      </c>
+      <c r="C8" t="s">
+        <v>641</v>
+      </c>
+      <c r="D8" t="s">
+        <v>621</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>642</v>
+      </c>
+      <c r="F8" t="s">
+        <v>643</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C9" t="s">
+        <v>645</v>
+      </c>
+      <c r="D9" t="s">
+        <v>631</v>
+      </c>
+      <c r="E9" t="s">
+        <v>646</v>
+      </c>
+      <c r="F9" t="s">
+        <v>647</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30">
+      <c r="A10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" t="s">
+        <v>648</v>
+      </c>
+      <c r="C10" t="s">
+        <v>649</v>
+      </c>
+      <c r="D10" t="s">
+        <v>631</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>650</v>
+      </c>
+      <c r="F10" t="s">
+        <v>651</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>281</v>
+      </c>
+      <c r="B11" t="s">
+        <v>652</v>
+      </c>
+      <c r="C11" t="s">
+        <v>653</v>
+      </c>
+      <c r="D11" t="s">
+        <v>654</v>
+      </c>
+      <c r="E11" t="s">
+        <v>655</v>
+      </c>
+      <c r="F11" t="s">
+        <v>656</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14648,4 +15302,208 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C926D52-B3E2-4768-8C3A-0CFE92252B83}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="68.5703125" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="50.5703125" customWidth="1"/>
+    <col min="6" max="6" width="37.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+    </row>
+    <row r="3" spans="1:8" ht="120">
+      <c r="A3" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>657</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>658</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>659</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>660</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>661</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30">
+      <c r="A4" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40" t="s">
+        <v>662</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>663</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>664</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>665</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30">
+      <c r="A5" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40" t="s">
+        <v>666</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>667</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>664</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>668</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30">
+      <c r="A6" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40" t="s">
+        <v>669</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>670</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>664</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>671</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30">
+      <c r="A7" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40" t="s">
+        <v>672</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>673</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>674</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>675</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="60">
+      <c r="A8" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40" t="s">
+        <v>676</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>677</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>664</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>678</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3F6A3A-1DD1-4625-AE09-7F04C559B93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC7EDF8-291D-44D7-90E5-3B3220A8C45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2914,6 +2914,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2934,28 +2943,19 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4807,734 +4807,734 @@
   <sheetData>
     <row r="2" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="3" spans="3:24">
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51"/>
-      <c r="K3" s="49" t="s">
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
+      <c r="K3" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="51"/>
-      <c r="S3" s="49" t="s">
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="54"/>
+      <c r="S3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="51"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="54"/>
     </row>
     <row r="4" spans="3:24">
-      <c r="C4" s="45"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="44"/>
-      <c r="S4" s="45"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="44"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="47"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="47"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="47"/>
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C5" s="42">
+      <c r="C5" s="45">
         <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199)</f>
         <v>273</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
-      <c r="K5" s="42">
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+      <c r="K5" s="45">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")</f>
-        <v>202</v>
-      </c>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="44"/>
-      <c r="S5" s="53">
+        <v>204</v>
+      </c>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="47"/>
+      <c r="S5" s="56">
         <f>K5/C5</f>
-        <v>0.73992673992673996</v>
-      </c>
-      <c r="T5" s="43"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="43"/>
-      <c r="X5" s="44"/>
+        <v>0.74725274725274726</v>
+      </c>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="47"/>
     </row>
     <row r="6" spans="3:24">
-      <c r="C6" s="45"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="44"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="44"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="47"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="47"/>
     </row>
     <row r="7" spans="3:24">
-      <c r="C7" s="45"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="44"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="43"/>
-      <c r="X7" s="44"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="47"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="47"/>
     </row>
     <row r="8" spans="3:24">
-      <c r="C8" s="45"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="44"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="43"/>
-      <c r="X8" s="44"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="47"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="47"/>
     </row>
     <row r="9" spans="3:24">
-      <c r="C9" s="45"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="44"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="44"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="47"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="47"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="47"/>
     </row>
     <row r="10" spans="3:24">
-      <c r="C10" s="45"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="44"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="44"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="47"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="47"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="47"/>
     </row>
     <row r="11" spans="3:24">
-      <c r="C11" s="45"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="44"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="44"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="44"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="47"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="47"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="47"/>
     </row>
     <row r="12" spans="3:24">
-      <c r="C12" s="45"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="44"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="44"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="47"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="47"/>
     </row>
     <row r="13" spans="3:24">
-      <c r="C13" s="45"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="44"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="44"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="47"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="46"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="47"/>
     </row>
     <row r="14" spans="3:24">
-      <c r="C14" s="45"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="44"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="44"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="47"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="47"/>
     </row>
     <row r="15" spans="3:24">
-      <c r="C15" s="45"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="44"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="44"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="47"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="47"/>
     </row>
     <row r="16" spans="3:24">
-      <c r="C16" s="45"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="44"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="44"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="47"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="47"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="47"/>
     </row>
     <row r="17" spans="3:24">
-      <c r="C17" s="45"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="44"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="44"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="43"/>
-      <c r="X17" s="44"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="47"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="47"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="47"/>
     </row>
     <row r="18" spans="3:24">
-      <c r="C18" s="45"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="44"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="44"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="44"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="47"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="47"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="47"/>
     </row>
     <row r="19" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C19" s="46"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="48"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="51"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="51"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="50"/>
+      <c r="X19" s="51"/>
     </row>
     <row r="22" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="23" spans="3:24">
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="51"/>
-      <c r="K23" s="49" t="s">
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="54"/>
+      <c r="K23" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="51"/>
-      <c r="S23" s="49" t="s">
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="54"/>
+      <c r="S23" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="51"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
+      <c r="V23" s="53"/>
+      <c r="W23" s="53"/>
+      <c r="X23" s="54"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="45"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="44"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="43"/>
-      <c r="X24" s="44"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="47"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="47"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="47"/>
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C25" s="42">
+      <c r="C25" s="45">
         <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")</f>
         <v>146</v>
       </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44"/>
-      <c r="K25" s="42">
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="47"/>
+      <c r="K25" s="45">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")</f>
-        <v>114</v>
-      </c>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="44"/>
-      <c r="S25" s="53">
+        <v>116</v>
+      </c>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="47"/>
+      <c r="S25" s="56">
         <f>K25/C25</f>
-        <v>0.78082191780821919</v>
-      </c>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="43"/>
-      <c r="X25" s="44"/>
+        <v>0.79452054794520544</v>
+      </c>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="47"/>
     </row>
     <row r="26" spans="3:24">
-      <c r="C26" s="45"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="44"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="X26" s="44"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="47"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="47"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="47"/>
     </row>
     <row r="27" spans="3:24">
-      <c r="C27" s="45"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="44"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="43"/>
-      <c r="U27" s="43"/>
-      <c r="V27" s="43"/>
-      <c r="W27" s="43"/>
-      <c r="X27" s="44"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="47"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="47"/>
     </row>
     <row r="28" spans="3:24">
-      <c r="C28" s="45"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="44"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="43"/>
-      <c r="W28" s="43"/>
-      <c r="X28" s="44"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="47"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="47"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="47"/>
     </row>
     <row r="29" spans="3:24">
-      <c r="C29" s="45"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="44"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="44"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="43"/>
-      <c r="V29" s="43"/>
-      <c r="W29" s="43"/>
-      <c r="X29" s="44"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="47"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="47"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="47"/>
     </row>
     <row r="30" spans="3:24">
-      <c r="C30" s="45"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="44"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="44"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="43"/>
-      <c r="U30" s="43"/>
-      <c r="V30" s="43"/>
-      <c r="W30" s="43"/>
-      <c r="X30" s="44"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="47"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="47"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="47"/>
     </row>
     <row r="31" spans="3:24">
-      <c r="C31" s="45"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="44"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="44"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="43"/>
-      <c r="V31" s="43"/>
-      <c r="W31" s="43"/>
-      <c r="X31" s="44"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="47"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="47"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="47"/>
     </row>
     <row r="32" spans="3:24">
-      <c r="C32" s="45"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="44"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="43"/>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="44"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="43"/>
-      <c r="U32" s="43"/>
-      <c r="V32" s="43"/>
-      <c r="W32" s="43"/>
-      <c r="X32" s="44"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="47"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
+      <c r="P32" s="47"/>
+      <c r="S32" s="48"/>
+      <c r="T32" s="46"/>
+      <c r="U32" s="46"/>
+      <c r="V32" s="46"/>
+      <c r="W32" s="46"/>
+      <c r="X32" s="47"/>
     </row>
     <row r="33" spans="3:24">
-      <c r="C33" s="45"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="44"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="44"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="43"/>
-      <c r="V33" s="43"/>
-      <c r="W33" s="43"/>
-      <c r="X33" s="44"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="47"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="47"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="47"/>
     </row>
     <row r="34" spans="3:24">
-      <c r="C34" s="45"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="44"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="44"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="43"/>
-      <c r="U34" s="43"/>
-      <c r="V34" s="43"/>
-      <c r="W34" s="43"/>
-      <c r="X34" s="44"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="47"/>
+      <c r="S34" s="48"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="V34" s="46"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="47"/>
     </row>
     <row r="35" spans="3:24">
-      <c r="C35" s="45"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="44"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="44"/>
-      <c r="S35" s="45"/>
-      <c r="T35" s="43"/>
-      <c r="U35" s="43"/>
-      <c r="V35" s="43"/>
-      <c r="W35" s="43"/>
-      <c r="X35" s="44"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="47"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="47"/>
+      <c r="S35" s="48"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="46"/>
+      <c r="V35" s="46"/>
+      <c r="W35" s="46"/>
+      <c r="X35" s="47"/>
     </row>
     <row r="36" spans="3:24">
-      <c r="C36" s="45"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="44"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="44"/>
-      <c r="S36" s="45"/>
-      <c r="T36" s="43"/>
-      <c r="U36" s="43"/>
-      <c r="V36" s="43"/>
-      <c r="W36" s="43"/>
-      <c r="X36" s="44"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="47"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="47"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="46"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="47"/>
     </row>
     <row r="37" spans="3:24">
-      <c r="C37" s="45"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="44"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="44"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="43"/>
-      <c r="U37" s="43"/>
-      <c r="V37" s="43"/>
-      <c r="W37" s="43"/>
-      <c r="X37" s="44"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="47"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="47"/>
+      <c r="S37" s="48"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="46"/>
+      <c r="W37" s="46"/>
+      <c r="X37" s="47"/>
     </row>
     <row r="38" spans="3:24">
-      <c r="C38" s="45"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="44"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="43"/>
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
-      <c r="O38" s="43"/>
-      <c r="P38" s="44"/>
-      <c r="S38" s="45"/>
-      <c r="T38" s="43"/>
-      <c r="U38" s="43"/>
-      <c r="V38" s="43"/>
-      <c r="W38" s="43"/>
-      <c r="X38" s="44"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="47"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="47"/>
+      <c r="S38" s="48"/>
+      <c r="T38" s="46"/>
+      <c r="U38" s="46"/>
+      <c r="V38" s="46"/>
+      <c r="W38" s="46"/>
+      <c r="X38" s="47"/>
     </row>
     <row r="39" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C39" s="46"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="47"/>
-      <c r="O39" s="47"/>
-      <c r="P39" s="48"/>
-      <c r="S39" s="46"/>
-      <c r="T39" s="47"/>
-      <c r="U39" s="47"/>
-      <c r="V39" s="47"/>
-      <c r="W39" s="47"/>
-      <c r="X39" s="48"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="51"/>
+      <c r="K39" s="49"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="50"/>
+      <c r="P39" s="51"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="50"/>
+      <c r="V39" s="50"/>
+      <c r="W39" s="50"/>
+      <c r="X39" s="51"/>
     </row>
     <row r="41" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="42" spans="3:24">
-      <c r="C42" s="49" t="s">
+      <c r="C42" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="51"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="54"/>
     </row>
     <row r="43" spans="3:24">
-      <c r="C43" s="45"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="44"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="47"/>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
@@ -5543,31 +5543,31 @@
       <c r="P43" s="28"/>
     </row>
     <row r="44" spans="3:24" ht="21" customHeight="1">
-      <c r="C44" s="53">
+      <c r="C44" s="56">
         <f>C25/C5</f>
         <v>0.53479853479853479</v>
       </c>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="44"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="52" t="s">
+      <c r="L44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="M44" s="43"/>
-      <c r="N44" s="43"/>
-      <c r="O44" s="43"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="46"/>
+      <c r="O44" s="46"/>
       <c r="P44" s="29"/>
     </row>
     <row r="45" spans="3:24">
-      <c r="C45" s="45"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="44"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="47"/>
       <c r="K45" s="28"/>
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
@@ -5576,12 +5576,12 @@
       <c r="P45" s="29"/>
     </row>
     <row r="46" spans="3:24">
-      <c r="C46" s="45"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="44"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="47"/>
       <c r="K46" s="28"/>
       <c r="L46" s="31"/>
       <c r="M46" s="28" t="s">
@@ -5592,12 +5592,12 @@
       <c r="P46" s="28"/>
     </row>
     <row r="47" spans="3:24">
-      <c r="C47" s="45"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="44"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="47"/>
       <c r="K47" s="28"/>
       <c r="L47" s="32"/>
       <c r="M47" s="28" t="s">
@@ -5608,12 +5608,12 @@
       <c r="P47" s="28"/>
     </row>
     <row r="48" spans="3:24">
-      <c r="C48" s="45"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="44"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="47"/>
       <c r="K48" s="28"/>
       <c r="L48" s="33"/>
       <c r="M48" s="28" t="s">
@@ -5624,12 +5624,12 @@
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="3:16">
-      <c r="C49" s="45"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="44"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="47"/>
       <c r="K49" s="28"/>
       <c r="L49" s="34"/>
       <c r="M49" s="28" t="s">
@@ -5640,12 +5640,12 @@
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="3:16">
-      <c r="C50" s="45"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="44"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="47"/>
       <c r="K50" s="28"/>
       <c r="L50" s="35"/>
       <c r="M50" s="28" t="s">
@@ -5656,12 +5656,12 @@
       <c r="P50" s="28"/>
     </row>
     <row r="51" spans="3:16">
-      <c r="C51" s="45"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="44"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="47"/>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -5670,230 +5670,230 @@
       <c r="P51" s="28"/>
     </row>
     <row r="52" spans="3:16">
-      <c r="C52" s="45"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="44"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="47"/>
     </row>
     <row r="53" spans="3:16">
-      <c r="C53" s="45"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="44"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="47"/>
     </row>
     <row r="54" spans="3:16">
-      <c r="C54" s="45"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="44"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="47"/>
     </row>
     <row r="55" spans="3:16">
-      <c r="C55" s="45"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="44"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="47"/>
     </row>
     <row r="56" spans="3:16">
-      <c r="C56" s="45"/>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="43"/>
-      <c r="H56" s="44"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="47"/>
     </row>
     <row r="57" spans="3:16">
-      <c r="C57" s="45"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="44"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="47"/>
     </row>
     <row r="58" spans="3:16" ht="15.75" customHeight="1">
-      <c r="C58" s="46"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="48"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
+      <c r="H58" s="51"/>
     </row>
     <row r="62" spans="3:16">
-      <c r="C62" s="54" t="s">
+      <c r="C62" s="42" t="s">
         <v>585</v>
       </c>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="54"/>
-      <c r="H62" s="54" t="s">
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="H62" s="42" t="s">
         <v>586</v>
       </c>
-      <c r="I62" s="54"/>
-      <c r="J62" s="54"/>
-      <c r="K62" s="54"/>
-      <c r="M62" s="54" t="s">
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
+      <c r="M62" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="N62" s="54"/>
-      <c r="O62" s="54"/>
-      <c r="P62" s="54"/>
+      <c r="N62" s="42"/>
+      <c r="O62" s="42"/>
+      <c r="P62" s="42"/>
     </row>
     <row r="63" spans="3:16">
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="54"/>
-      <c r="H63" s="54"/>
-      <c r="I63" s="54"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
-      <c r="M63" s="54"/>
-      <c r="N63" s="54"/>
-      <c r="O63" s="54"/>
-      <c r="P63" s="54"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
+      <c r="M63" s="42"/>
+      <c r="N63" s="42"/>
+      <c r="O63" s="42"/>
+      <c r="P63" s="42"/>
     </row>
     <row r="64" spans="3:16">
-      <c r="C64" s="55">
+      <c r="C64" s="43">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
         <v>250</v>
       </c>
-      <c r="D64" s="55"/>
-      <c r="E64" s="55"/>
-      <c r="F64" s="55"/>
-      <c r="H64" s="55">
+      <c r="D64" s="43"/>
+      <c r="E64" s="43"/>
+      <c r="F64" s="43"/>
+      <c r="H64" s="43">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
-        <v>188</v>
-      </c>
-      <c r="I64" s="55"/>
-      <c r="J64" s="55"/>
-      <c r="K64" s="55"/>
-      <c r="M64" s="56">
+        <v>190</v>
+      </c>
+      <c r="I64" s="43"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="43"/>
+      <c r="M64" s="44">
         <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.752</v>
-      </c>
-      <c r="N64" s="56"/>
-      <c r="O64" s="56"/>
-      <c r="P64" s="56"/>
+        <v>0.76</v>
+      </c>
+      <c r="N64" s="44"/>
+      <c r="O64" s="44"/>
+      <c r="P64" s="44"/>
     </row>
     <row r="65" spans="3:16">
-      <c r="C65" s="55"/>
-      <c r="D65" s="55"/>
-      <c r="E65" s="55"/>
-      <c r="F65" s="55"/>
-      <c r="H65" s="55"/>
-      <c r="I65" s="55"/>
-      <c r="J65" s="55"/>
-      <c r="K65" s="55"/>
-      <c r="M65" s="56"/>
-      <c r="N65" s="56"/>
-      <c r="O65" s="56"/>
-      <c r="P65" s="56"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44"/>
+      <c r="P65" s="44"/>
     </row>
     <row r="66" spans="3:16">
-      <c r="C66" s="55"/>
-      <c r="D66" s="55"/>
-      <c r="E66" s="55"/>
-      <c r="F66" s="55"/>
-      <c r="H66" s="55"/>
-      <c r="I66" s="55"/>
-      <c r="J66" s="55"/>
-      <c r="K66" s="55"/>
-      <c r="M66" s="56"/>
-      <c r="N66" s="56"/>
-      <c r="O66" s="56"/>
-      <c r="P66" s="56"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="43"/>
+      <c r="M66" s="44"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="44"/>
+      <c r="P66" s="44"/>
     </row>
     <row r="69" spans="3:16">
-      <c r="C69" s="54" t="s">
+      <c r="C69" s="42" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="54"/>
-      <c r="E69" s="54"/>
-      <c r="F69" s="54"/>
-      <c r="H69" s="54" t="s">
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="H69" s="42" t="s">
         <v>589</v>
       </c>
-      <c r="I69" s="54"/>
-      <c r="J69" s="54"/>
-      <c r="K69" s="54"/>
-      <c r="M69" s="54" t="s">
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
+      <c r="M69" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="N69" s="54"/>
-      <c r="O69" s="54"/>
-      <c r="P69" s="54"/>
+      <c r="N69" s="42"/>
+      <c r="O69" s="42"/>
+      <c r="P69" s="42"/>
     </row>
     <row r="70" spans="3:16">
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="54"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="54"/>
-      <c r="J70" s="54"/>
-      <c r="K70" s="54"/>
-      <c r="M70" s="54"/>
-      <c r="N70" s="54"/>
-      <c r="O70" s="54"/>
-      <c r="P70" s="54"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
+      <c r="M70" s="42"/>
+      <c r="N70" s="42"/>
+      <c r="O70" s="42"/>
+      <c r="P70" s="42"/>
     </row>
     <row r="71" spans="3:16">
-      <c r="C71" s="55">
+      <c r="C71" s="43">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
         <v>71</v>
       </c>
-      <c r="D71" s="55"/>
-      <c r="E71" s="55"/>
-      <c r="F71" s="55"/>
-      <c r="H71" s="55">
+      <c r="D71" s="43"/>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
+      <c r="H71" s="43">
         <f>COUNTIF(Perfil!I:I,"Si")+COUNTIF(Credenciales!I:I,"Si")+COUNTIF(Videollamadas!I:I,"Si")</f>
         <v>60</v>
       </c>
-      <c r="I71" s="55"/>
-      <c r="J71" s="55"/>
-      <c r="K71" s="55"/>
-      <c r="M71" s="56">
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+      <c r="M71" s="44">
         <f t="shared" ref="M71" si="1">H71/C71</f>
         <v>0.84507042253521125</v>
       </c>
-      <c r="N71" s="56"/>
-      <c r="O71" s="56"/>
-      <c r="P71" s="56"/>
+      <c r="N71" s="44"/>
+      <c r="O71" s="44"/>
+      <c r="P71" s="44"/>
     </row>
     <row r="72" spans="3:16">
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="55"/>
-      <c r="H72" s="55"/>
-      <c r="I72" s="55"/>
-      <c r="J72" s="55"/>
-      <c r="K72" s="55"/>
-      <c r="M72" s="56"/>
-      <c r="N72" s="56"/>
-      <c r="O72" s="56"/>
-      <c r="P72" s="56"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+      <c r="M72" s="44"/>
+      <c r="N72" s="44"/>
+      <c r="O72" s="44"/>
+      <c r="P72" s="44"/>
     </row>
     <row r="73" spans="3:16">
-      <c r="C73" s="55"/>
-      <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="55"/>
-      <c r="H73" s="55"/>
-      <c r="I73" s="55"/>
-      <c r="J73" s="55"/>
-      <c r="K73" s="55"/>
-      <c r="M73" s="56"/>
-      <c r="N73" s="56"/>
-      <c r="O73" s="56"/>
-      <c r="P73" s="56"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="H73" s="43"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="43"/>
+      <c r="M73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
     </row>
     <row r="76" spans="3:16">
       <c r="C76" s="36" t="s">
@@ -5902,18 +5902,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C69:F70"/>
-    <mergeCell ref="C71:F73"/>
-    <mergeCell ref="H69:K70"/>
-    <mergeCell ref="H71:K73"/>
-    <mergeCell ref="M69:P70"/>
-    <mergeCell ref="M71:P73"/>
-    <mergeCell ref="C62:F63"/>
-    <mergeCell ref="C64:F66"/>
-    <mergeCell ref="H62:K63"/>
-    <mergeCell ref="H64:K66"/>
-    <mergeCell ref="M62:P63"/>
-    <mergeCell ref="M64:P66"/>
     <mergeCell ref="K5:P19"/>
     <mergeCell ref="K25:P39"/>
     <mergeCell ref="S3:X4"/>
@@ -5929,6 +5917,18 @@
     <mergeCell ref="C3:H4"/>
     <mergeCell ref="C25:H39"/>
     <mergeCell ref="K23:P24"/>
+    <mergeCell ref="C62:F63"/>
+    <mergeCell ref="C64:F66"/>
+    <mergeCell ref="H62:K63"/>
+    <mergeCell ref="H64:K66"/>
+    <mergeCell ref="M62:P63"/>
+    <mergeCell ref="M64:P66"/>
+    <mergeCell ref="C69:F70"/>
+    <mergeCell ref="C71:F73"/>
+    <mergeCell ref="H69:K70"/>
+    <mergeCell ref="H71:K73"/>
+    <mergeCell ref="M69:P70"/>
+    <mergeCell ref="M71:P73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -6152,7 +6152,7 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="H2" s="61"/>
       <c r="I2" s="12" t="s">
         <v>27</v>
       </c>
@@ -6161,7 +6161,7 @@
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -6389,7 +6389,7 @@
       <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="57" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -6435,7 +6435,7 @@
         <v>27</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>27</v>
@@ -6455,7 +6455,7 @@
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="59" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -6548,7 +6548,7 @@
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="57" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -6749,7 +6749,7 @@
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="59" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -6869,7 +6869,7 @@
       <c r="A32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="57" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="22" t="s">
@@ -7016,7 +7016,7 @@
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="59" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -7069,7 +7069,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="60" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="58"/>
@@ -7078,7 +7078,7 @@
       <c r="E40" s="58"/>
       <c r="F40" s="58"/>
       <c r="G40" s="58"/>
-      <c r="H40" s="59"/>
+      <c r="H40" s="61"/>
       <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
@@ -7087,7 +7087,7 @@
       <c r="A41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="57" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="22" t="s">
@@ -7315,7 +7315,7 @@
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="61" t="s">
+      <c r="B50" s="59" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -7361,7 +7361,7 @@
         <v>27</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I51" s="12" t="s">
         <v>27</v>
@@ -7381,7 +7381,7 @@
       <c r="A53" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="57" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="22" t="s">
@@ -7474,7 +7474,7 @@
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="61" t="s">
+      <c r="B57" s="59" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -7675,7 +7675,7 @@
       <c r="A65" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="57" t="s">
         <v>90</v>
       </c>
       <c r="C65" s="22" t="s">
@@ -7795,7 +7795,7 @@
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="61" t="s">
+      <c r="B70" s="59" t="s">
         <v>104</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -7942,7 +7942,7 @@
       <c r="A76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="60" t="s">
+      <c r="B76" s="57" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -7995,7 +7995,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A78" s="57" t="s">
+      <c r="A78" s="60" t="s">
         <v>140</v>
       </c>
       <c r="B78" s="58"/>
@@ -8004,7 +8004,7 @@
       <c r="E78" s="58"/>
       <c r="F78" s="58"/>
       <c r="G78" s="58"/>
-      <c r="H78" s="59"/>
+      <c r="H78" s="61"/>
       <c r="I78" s="12" t="s">
         <v>27</v>
       </c>
@@ -8013,7 +8013,7 @@
       <c r="A79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="61" t="s">
+      <c r="B79" s="59" t="s">
         <v>141</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -8104,7 +8104,7 @@
       <c r="A83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B83" s="60" t="s">
+      <c r="B83" s="57" t="s">
         <v>153</v>
       </c>
       <c r="C83" s="22" t="s">
@@ -8153,7 +8153,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A85" s="57" t="s">
+      <c r="A85" s="60" t="s">
         <v>159</v>
       </c>
       <c r="B85" s="58"/>
@@ -8162,7 +8162,7 @@
       <c r="E85" s="58"/>
       <c r="F85" s="58"/>
       <c r="G85" s="58"/>
-      <c r="H85" s="59"/>
+      <c r="H85" s="61"/>
       <c r="I85" s="12" t="s">
         <v>27</v>
       </c>
@@ -8171,7 +8171,7 @@
       <c r="A86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="61" t="s">
+      <c r="B86" s="59" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -8262,7 +8262,7 @@
       <c r="A90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="60" t="s">
+      <c r="B90" s="57" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -8322,12 +8322,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B86:B88"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="B32:B36"/>
@@ -8344,6 +8338,12 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="B19:B25"/>
     <mergeCell ref="B57:B63"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B86:B88"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="153" priority="564" operator="equal">
@@ -8573,7 +8573,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -8582,13 +8582,13 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="1:9" ht="76.5" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -8729,7 +8729,7 @@
       <c r="A9" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -8847,7 +8847,7 @@
       <c r="A14" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -8994,7 +8994,7 @@
       <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="61" t="s">
         <v>612</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -9138,7 +9138,7 @@
       <c r="A26" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -9227,7 +9227,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="60" t="s">
         <v>213</v>
       </c>
       <c r="B31" s="58"/>
@@ -9236,13 +9236,13 @@
       <c r="E31" s="58"/>
       <c r="F31" s="58"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="59"/>
+      <c r="H31" s="61"/>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C32" s="18" t="s">
@@ -9383,7 +9383,7 @@
       <c r="A38" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C38" s="22" t="s">
@@ -9501,7 +9501,7 @@
       <c r="A43" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C43" s="18" t="s">
@@ -9648,7 +9648,7 @@
       <c r="A49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="59" t="s">
+      <c r="B49" s="61" t="s">
         <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -9792,7 +9792,7 @@
       <c r="A55" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="59" t="s">
+      <c r="B55" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -9881,7 +9881,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A60" s="57" t="s">
+      <c r="A60" s="60" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="58"/>
@@ -9890,13 +9890,13 @@
       <c r="E60" s="58"/>
       <c r="F60" s="58"/>
       <c r="G60" s="58"/>
-      <c r="H60" s="59"/>
+      <c r="H60" s="61"/>
     </row>
     <row r="61" spans="1:9" ht="76.5" customHeight="1">
       <c r="A61" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="61" t="s">
+      <c r="B61" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -10037,7 +10037,7 @@
       <c r="A67" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B67" s="60" t="s">
+      <c r="B67" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C67" s="22" t="s">
@@ -10155,7 +10155,7 @@
       <c r="A72" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="61" t="s">
+      <c r="B72" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C72" s="18" t="s">
@@ -10302,7 +10302,7 @@
       <c r="A78" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="59" t="s">
+      <c r="B78" s="61" t="s">
         <v>611</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -10446,7 +10446,7 @@
       <c r="A84" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="59" t="s">
+      <c r="B84" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -10535,7 +10535,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A89" s="57" t="s">
+      <c r="A89" s="60" t="s">
         <v>159</v>
       </c>
       <c r="B89" s="58"/>
@@ -10544,13 +10544,13 @@
       <c r="E89" s="58"/>
       <c r="F89" s="58"/>
       <c r="G89" s="58"/>
-      <c r="H89" s="59"/>
+      <c r="H89" s="61"/>
     </row>
     <row r="90" spans="1:9" ht="76.5" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="61" t="s">
+      <c r="B90" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C90" s="18" t="s">
@@ -10691,7 +10691,7 @@
       <c r="A96" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B96" s="60" t="s">
+      <c r="B96" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C96" s="22" t="s">
@@ -10809,7 +10809,7 @@
       <c r="A101" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="61" t="s">
+      <c r="B101" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C101" s="18" t="s">
@@ -10956,7 +10956,7 @@
       <c r="A107" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B107" s="59" t="s">
+      <c r="B107" s="61" t="s">
         <v>591</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -11100,7 +11100,7 @@
       <c r="A113" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B113" s="59" t="s">
+      <c r="B113" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -11190,6 +11190,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="B107:B108"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B96:B99"/>
     <mergeCell ref="A2:H2"/>
@@ -11206,14 +11214,6 @@
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="B43:B47"/>
-    <mergeCell ref="B113:B117"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B107:B108"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="111" priority="525" operator="equal">
@@ -11619,7 +11619,7 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="59"/>
+      <c r="B2" s="61"/>
       <c r="C2" s="63"/>
       <c r="D2" s="58"/>
       <c r="E2" s="63"/>
@@ -11628,7 +11628,7 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="198" customHeight="1">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -11660,8 +11660,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="59"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="63" t="s">
         <v>221</v>
       </c>
@@ -11692,7 +11692,7 @@
     </row>
     <row r="5" spans="1:11" ht="45.75" customHeight="1">
       <c r="A5" s="63"/>
-      <c r="B5" s="59"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="63"/>
       <c r="D5" s="58"/>
       <c r="E5" s="6" t="s">
@@ -11704,7 +11704,7 @@
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="121.5" customHeight="1">
-      <c r="B6" s="59"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="63" t="s">
         <v>226</v>
       </c>
@@ -11734,7 +11734,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="45.75" customHeight="1">
-      <c r="B7" s="59"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="63"/>
       <c r="D7" s="58"/>
       <c r="E7" s="13" t="s">
@@ -11746,7 +11746,7 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B8" s="59"/>
+      <c r="B8" s="61"/>
       <c r="C8" s="13" t="s">
         <v>229</v>
       </c>
@@ -11762,7 +11762,7 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B9" s="59"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="13" t="s">
         <v>231</v>
       </c>
@@ -11778,7 +11778,7 @@
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
-      <c r="B10" s="59"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="13" t="s">
         <v>232</v>
       </c>
@@ -11808,7 +11808,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="140.25" customHeight="1">
-      <c r="B11" s="59"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="13" t="s">
         <v>235</v>
       </c>
@@ -11851,7 +11851,7 @@
       <c r="A13" s="62" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="59"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="63"/>
       <c r="D13" s="58"/>
       <c r="E13" s="63"/>
@@ -11989,7 +11989,7 @@
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>239</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -12024,7 +12024,7 @@
       <c r="A4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="59"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="18" t="s">
         <v>244</v>
       </c>
@@ -12057,7 +12057,7 @@
       <c r="A5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="59"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="18" t="s">
         <v>247</v>
       </c>
@@ -12090,7 +12090,7 @@
       <c r="A6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="59"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="18" t="s">
         <v>251</v>
       </c>
@@ -12133,7 +12133,7 @@
       <c r="A8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="57" t="s">
         <v>254</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -12168,7 +12168,7 @@
       <c r="A9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="59"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="22" t="s">
         <v>259</v>
       </c>
@@ -12201,7 +12201,7 @@
       <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="59"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="64" t="s">
         <v>262</v>
       </c>
@@ -12214,7 +12214,7 @@
       <c r="F10" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="61" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -12234,7 +12234,7 @@
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="59"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="58"/>
       <c r="D11" s="63"/>
       <c r="E11" s="11" t="s">
@@ -12243,7 +12243,7 @@
       <c r="F11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G11" s="59"/>
+      <c r="G11" s="61"/>
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
@@ -12261,7 +12261,7 @@
       <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="59"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="22" t="s">
         <v>267</v>
       </c>
@@ -12294,7 +12294,7 @@
       <c r="A13" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="59"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="22" t="s">
         <v>271</v>
       </c>
@@ -12327,7 +12327,7 @@
       <c r="A14" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B14" s="59"/>
+      <c r="B14" s="61"/>
       <c r="C14" s="22" t="s">
         <v>274</v>
       </c>
@@ -12360,7 +12360,7 @@
       <c r="A15" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="59"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="22" t="s">
         <v>279</v>
       </c>
@@ -12393,7 +12393,7 @@
       <c r="A16" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="59"/>
+      <c r="B16" s="61"/>
       <c r="C16" s="22" t="s">
         <v>282</v>
       </c>
@@ -12426,7 +12426,7 @@
       <c r="A17" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="59"/>
+      <c r="B17" s="61"/>
       <c r="C17" s="22" t="s">
         <v>286</v>
       </c>
@@ -12459,7 +12459,7 @@
       <c r="A18" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B18" s="59"/>
+      <c r="B18" s="61"/>
       <c r="C18" s="22" t="s">
         <v>289</v>
       </c>
@@ -12492,7 +12492,7 @@
       <c r="A19" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="59"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="22" t="s">
         <v>294</v>
       </c>
@@ -12525,7 +12525,7 @@
       <c r="A20" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="59"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="22" t="s">
         <v>298</v>
       </c>
@@ -12558,7 +12558,7 @@
       <c r="A21" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="59"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="22" t="s">
         <v>303</v>
       </c>
@@ -12591,7 +12591,7 @@
       <c r="A22" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="59"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="22" t="s">
         <v>305</v>
       </c>
@@ -12624,7 +12624,7 @@
       <c r="A23" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="59"/>
+      <c r="B23" s="61"/>
       <c r="C23" s="22" t="s">
         <v>310</v>
       </c>
@@ -12657,7 +12657,7 @@
       <c r="A24" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B24" s="59"/>
+      <c r="B24" s="61"/>
       <c r="C24" s="22" t="s">
         <v>314</v>
       </c>
@@ -12690,7 +12690,7 @@
       <c r="A25" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="59"/>
+      <c r="B25" s="61"/>
       <c r="C25" s="22" t="s">
         <v>316</v>
       </c>
@@ -12720,7 +12720,7 @@
       <c r="A26" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="59"/>
+      <c r="B26" s="61"/>
       <c r="C26" s="64" t="s">
         <v>321</v>
       </c>
@@ -12733,10 +12733,10 @@
       <c r="F26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="G26" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="59" t="s">
+      <c r="G26" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="61" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
@@ -12750,7 +12750,7 @@
       <c r="A27" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="59"/>
+      <c r="B27" s="61"/>
       <c r="C27" s="58"/>
       <c r="D27" s="63"/>
       <c r="E27" s="11" t="s">
@@ -12759,14 +12759,14 @@
       <c r="F27" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G27" s="59"/>
+      <c r="G27" s="61"/>
       <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:11" ht="76.5" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B28" s="59"/>
+      <c r="B28" s="61"/>
       <c r="C28" s="22" t="s">
         <v>329</v>
       </c>
@@ -12799,7 +12799,7 @@
       <c r="A29" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B29" s="59"/>
+      <c r="B29" s="61"/>
       <c r="C29" s="22" t="s">
         <v>334</v>
       </c>
@@ -12832,7 +12832,7 @@
       <c r="A30" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B30" s="59"/>
+      <c r="B30" s="61"/>
       <c r="C30" s="22" t="s">
         <v>338</v>
       </c>
@@ -12865,7 +12865,7 @@
       <c r="A31" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B31" s="59"/>
+      <c r="B31" s="61"/>
       <c r="C31" s="22" t="s">
         <v>341</v>
       </c>
@@ -12980,7 +12980,7 @@
       <c r="A36" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="61" t="s">
+      <c r="B36" s="59" t="s">
         <v>349</v>
       </c>
       <c r="C36" s="22" t="s">
@@ -13015,7 +13015,7 @@
       <c r="A37" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="59"/>
+      <c r="B37" s="61"/>
       <c r="C37" s="23" t="s">
         <v>354</v>
       </c>
@@ -13152,7 +13152,7 @@
       <c r="A3" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>359</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -13341,7 +13341,7 @@
       <c r="A10" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="57" t="s">
         <v>385</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -13629,7 +13629,7 @@
       <c r="A20" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>422</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -14247,7 +14247,7 @@
       <c r="A40" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="57" t="s">
         <v>505</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -14403,7 +14403,7 @@
       <c r="A46" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="59" t="s">
         <v>526</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -14681,7 +14681,7 @@
       <c r="A56" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B56" s="43" t="s">
+      <c r="B56" s="46" t="s">
         <v>560</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -14955,13 +14955,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:8" ht="30">
       <c r="A3" t="s">
@@ -15049,13 +15049,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC7EDF8-291D-44D7-90E5-3B3220A8C45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C03D12F-F020-468E-89A9-19A8A2672CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2914,15 +2914,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2943,19 +2934,28 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4807,734 +4807,734 @@
   <sheetData>
     <row r="2" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="3" spans="3:24">
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
-      <c r="K3" s="52" t="s">
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="51"/>
+      <c r="K3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="54"/>
-      <c r="S3" s="52" t="s">
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="S3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="54"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="50"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="51"/>
     </row>
     <row r="4" spans="3:24">
-      <c r="C4" s="48"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="47"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="47"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="47"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="44"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="44"/>
+      <c r="S4" s="45"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="44"/>
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C5" s="45">
+      <c r="C5" s="42">
         <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199)</f>
         <v>273</v>
       </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
-      <c r="K5" s="45">
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
+      <c r="K5" s="42">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")</f>
-        <v>204</v>
-      </c>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="47"/>
-      <c r="S5" s="56">
+        <v>206</v>
+      </c>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="44"/>
+      <c r="S5" s="53">
         <f>K5/C5</f>
-        <v>0.74725274725274726</v>
-      </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="47"/>
+        <v>0.75457875457875456</v>
+      </c>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="44"/>
     </row>
     <row r="6" spans="3:24">
-      <c r="C6" s="48"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="47"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="47"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="44"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="44"/>
     </row>
     <row r="7" spans="3:24">
-      <c r="C7" s="48"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="47"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="47"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="44"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="44"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="44"/>
     </row>
     <row r="8" spans="3:24">
-      <c r="C8" s="48"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="47"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="46"/>
-      <c r="V8" s="46"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="47"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="44"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="44"/>
     </row>
     <row r="9" spans="3:24">
-      <c r="C9" s="48"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="47"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="47"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="47"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="44"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="44"/>
     </row>
     <row r="10" spans="3:24">
-      <c r="C10" s="48"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="47"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="46"/>
-      <c r="P10" s="47"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="47"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="44"/>
+      <c r="S10" s="45"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="44"/>
     </row>
     <row r="11" spans="3:24">
-      <c r="C11" s="48"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="47"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="47"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="47"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="44"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="44"/>
+      <c r="S11" s="45"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="44"/>
     </row>
     <row r="12" spans="3:24">
-      <c r="C12" s="48"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="47"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="47"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="46"/>
-      <c r="V12" s="46"/>
-      <c r="W12" s="46"/>
-      <c r="X12" s="47"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="44"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="44"/>
     </row>
     <row r="13" spans="3:24">
-      <c r="C13" s="48"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="47"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="47"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
-      <c r="V13" s="46"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="47"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="44"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="44"/>
     </row>
     <row r="14" spans="3:24">
-      <c r="C14" s="48"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="47"/>
-      <c r="S14" s="48"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="46"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="47"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="44"/>
+      <c r="S14" s="45"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="43"/>
+      <c r="W14" s="43"/>
+      <c r="X14" s="44"/>
     </row>
     <row r="15" spans="3:24">
-      <c r="C15" s="48"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="47"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="47"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="44"/>
+      <c r="S15" s="45"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="44"/>
     </row>
     <row r="16" spans="3:24">
-      <c r="C16" s="48"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="47"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="47"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="47"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="44"/>
+      <c r="S16" s="45"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="44"/>
     </row>
     <row r="17" spans="3:24">
-      <c r="C17" s="48"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="47"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="47"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="47"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="44"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="43"/>
+      <c r="W17" s="43"/>
+      <c r="X17" s="44"/>
     </row>
     <row r="18" spans="3:24">
-      <c r="C18" s="48"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="47"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="47"/>
-      <c r="S18" s="48"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="46"/>
-      <c r="V18" s="46"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="47"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="44"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
+      <c r="X18" s="44"/>
     </row>
     <row r="19" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C19" s="49"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="51"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="51"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="50"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="51"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="48"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="48"/>
     </row>
     <row r="22" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="23" spans="3:24">
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="54"/>
-      <c r="K23" s="52" t="s">
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="51"/>
+      <c r="K23" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="54"/>
-      <c r="S23" s="52" t="s">
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="51"/>
+      <c r="S23" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="T23" s="53"/>
-      <c r="U23" s="53"/>
-      <c r="V23" s="53"/>
-      <c r="W23" s="53"/>
-      <c r="X23" s="54"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="51"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="48"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="47"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="47"/>
-      <c r="S24" s="48"/>
-      <c r="T24" s="46"/>
-      <c r="U24" s="46"/>
-      <c r="V24" s="46"/>
-      <c r="W24" s="46"/>
-      <c r="X24" s="47"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="44"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="43"/>
+      <c r="U24" s="43"/>
+      <c r="V24" s="43"/>
+      <c r="W24" s="43"/>
+      <c r="X24" s="44"/>
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C25" s="45">
+      <c r="C25" s="42">
         <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")</f>
         <v>146</v>
       </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="47"/>
-      <c r="K25" s="45">
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
+      <c r="K25" s="42">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")</f>
-        <v>116</v>
-      </c>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
-      <c r="P25" s="47"/>
-      <c r="S25" s="56">
+        <v>118</v>
+      </c>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="44"/>
+      <c r="S25" s="53">
         <f>K25/C25</f>
-        <v>0.79452054794520544</v>
-      </c>
-      <c r="T25" s="46"/>
-      <c r="U25" s="46"/>
-      <c r="V25" s="46"/>
-      <c r="W25" s="46"/>
-      <c r="X25" s="47"/>
+        <v>0.80821917808219179</v>
+      </c>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43"/>
+      <c r="V25" s="43"/>
+      <c r="W25" s="43"/>
+      <c r="X25" s="44"/>
     </row>
     <row r="26" spans="3:24">
-      <c r="C26" s="48"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="47"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="47"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="47"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="44"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="X26" s="44"/>
     </row>
     <row r="27" spans="3:24">
-      <c r="C27" s="48"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="47"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46"/>
-      <c r="X27" s="47"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="44"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="43"/>
+      <c r="V27" s="43"/>
+      <c r="W27" s="43"/>
+      <c r="X27" s="44"/>
     </row>
     <row r="28" spans="3:24">
-      <c r="C28" s="48"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="47"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="47"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="47"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="44"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="43"/>
+      <c r="W28" s="43"/>
+      <c r="X28" s="44"/>
     </row>
     <row r="29" spans="3:24">
-      <c r="C29" s="48"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="47"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
-      <c r="O29" s="46"/>
-      <c r="P29" s="47"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="46"/>
-      <c r="U29" s="46"/>
-      <c r="V29" s="46"/>
-      <c r="W29" s="46"/>
-      <c r="X29" s="47"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="44"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="43"/>
+      <c r="U29" s="43"/>
+      <c r="V29" s="43"/>
+      <c r="W29" s="43"/>
+      <c r="X29" s="44"/>
     </row>
     <row r="30" spans="3:24">
-      <c r="C30" s="48"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="47"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="47"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="46"/>
-      <c r="V30" s="46"/>
-      <c r="W30" s="46"/>
-      <c r="X30" s="47"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="44"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="44"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
+      <c r="V30" s="43"/>
+      <c r="W30" s="43"/>
+      <c r="X30" s="44"/>
     </row>
     <row r="31" spans="3:24">
-      <c r="C31" s="48"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="47"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="46"/>
-      <c r="P31" s="47"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="46"/>
-      <c r="U31" s="46"/>
-      <c r="V31" s="46"/>
-      <c r="W31" s="46"/>
-      <c r="X31" s="47"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="44"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="44"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="43"/>
+      <c r="U31" s="43"/>
+      <c r="V31" s="43"/>
+      <c r="W31" s="43"/>
+      <c r="X31" s="44"/>
     </row>
     <row r="32" spans="3:24">
-      <c r="C32" s="48"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="47"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
-      <c r="O32" s="46"/>
-      <c r="P32" s="47"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="46"/>
-      <c r="U32" s="46"/>
-      <c r="V32" s="46"/>
-      <c r="W32" s="46"/>
-      <c r="X32" s="47"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="44"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="44"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="43"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="43"/>
+      <c r="W32" s="43"/>
+      <c r="X32" s="44"/>
     </row>
     <row r="33" spans="3:24">
-      <c r="C33" s="48"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="47"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="46"/>
-      <c r="P33" s="47"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="46"/>
-      <c r="U33" s="46"/>
-      <c r="V33" s="46"/>
-      <c r="W33" s="46"/>
-      <c r="X33" s="47"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="44"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="44"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="43"/>
+      <c r="U33" s="43"/>
+      <c r="V33" s="43"/>
+      <c r="W33" s="43"/>
+      <c r="X33" s="44"/>
     </row>
     <row r="34" spans="3:24">
-      <c r="C34" s="48"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="47"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="46"/>
-      <c r="P34" s="47"/>
-      <c r="S34" s="48"/>
-      <c r="T34" s="46"/>
-      <c r="U34" s="46"/>
-      <c r="V34" s="46"/>
-      <c r="W34" s="46"/>
-      <c r="X34" s="47"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="44"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="44"/>
     </row>
     <row r="35" spans="3:24">
-      <c r="C35" s="48"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="47"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="46"/>
-      <c r="P35" s="47"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="46"/>
-      <c r="U35" s="46"/>
-      <c r="V35" s="46"/>
-      <c r="W35" s="46"/>
-      <c r="X35" s="47"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="44"/>
+      <c r="S35" s="45"/>
+      <c r="T35" s="43"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
+      <c r="W35" s="43"/>
+      <c r="X35" s="44"/>
     </row>
     <row r="36" spans="3:24">
-      <c r="C36" s="48"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="47"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="46"/>
-      <c r="P36" s="47"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="46"/>
-      <c r="U36" s="46"/>
-      <c r="V36" s="46"/>
-      <c r="W36" s="46"/>
-      <c r="X36" s="47"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="44"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="44"/>
+      <c r="S36" s="45"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
+      <c r="W36" s="43"/>
+      <c r="X36" s="44"/>
     </row>
     <row r="37" spans="3:24">
-      <c r="C37" s="48"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="47"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-      <c r="O37" s="46"/>
-      <c r="P37" s="47"/>
-      <c r="S37" s="48"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="46"/>
-      <c r="W37" s="46"/>
-      <c r="X37" s="47"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="44"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="44"/>
+      <c r="S37" s="45"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="43"/>
+      <c r="V37" s="43"/>
+      <c r="W37" s="43"/>
+      <c r="X37" s="44"/>
     </row>
     <row r="38" spans="3:24">
-      <c r="C38" s="48"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="47"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-      <c r="O38" s="46"/>
-      <c r="P38" s="47"/>
-      <c r="S38" s="48"/>
-      <c r="T38" s="46"/>
-      <c r="U38" s="46"/>
-      <c r="V38" s="46"/>
-      <c r="W38" s="46"/>
-      <c r="X38" s="47"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="44"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="44"/>
+      <c r="S38" s="45"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="43"/>
+      <c r="V38" s="43"/>
+      <c r="W38" s="43"/>
+      <c r="X38" s="44"/>
     </row>
     <row r="39" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C39" s="49"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="51"/>
-      <c r="S39" s="49"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="51"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="48"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="47"/>
+      <c r="N39" s="47"/>
+      <c r="O39" s="47"/>
+      <c r="P39" s="48"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="47"/>
+      <c r="U39" s="47"/>
+      <c r="V39" s="47"/>
+      <c r="W39" s="47"/>
+      <c r="X39" s="48"/>
     </row>
     <row r="41" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="42" spans="3:24">
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="53"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="54"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="51"/>
     </row>
     <row r="43" spans="3:24">
-      <c r="C43" s="48"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="47"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="44"/>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
@@ -5543,31 +5543,31 @@
       <c r="P43" s="28"/>
     </row>
     <row r="44" spans="3:24" ht="21" customHeight="1">
-      <c r="C44" s="56">
+      <c r="C44" s="53">
         <f>C25/C5</f>
         <v>0.53479853479853479</v>
       </c>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="47"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="44"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="55" t="s">
+      <c r="L44" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
-      <c r="O44" s="46"/>
+      <c r="M44" s="43"/>
+      <c r="N44" s="43"/>
+      <c r="O44" s="43"/>
       <c r="P44" s="29"/>
     </row>
     <row r="45" spans="3:24">
-      <c r="C45" s="48"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="47"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="44"/>
       <c r="K45" s="28"/>
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
@@ -5576,12 +5576,12 @@
       <c r="P45" s="29"/>
     </row>
     <row r="46" spans="3:24">
-      <c r="C46" s="48"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="47"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="44"/>
       <c r="K46" s="28"/>
       <c r="L46" s="31"/>
       <c r="M46" s="28" t="s">
@@ -5592,12 +5592,12 @@
       <c r="P46" s="28"/>
     </row>
     <row r="47" spans="3:24">
-      <c r="C47" s="48"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="47"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="44"/>
       <c r="K47" s="28"/>
       <c r="L47" s="32"/>
       <c r="M47" s="28" t="s">
@@ -5608,12 +5608,12 @@
       <c r="P47" s="28"/>
     </row>
     <row r="48" spans="3:24">
-      <c r="C48" s="48"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="47"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="44"/>
       <c r="K48" s="28"/>
       <c r="L48" s="33"/>
       <c r="M48" s="28" t="s">
@@ -5624,12 +5624,12 @@
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="3:16">
-      <c r="C49" s="48"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="47"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="44"/>
       <c r="K49" s="28"/>
       <c r="L49" s="34"/>
       <c r="M49" s="28" t="s">
@@ -5640,12 +5640,12 @@
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="3:16">
-      <c r="C50" s="48"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="47"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="44"/>
       <c r="K50" s="28"/>
       <c r="L50" s="35"/>
       <c r="M50" s="28" t="s">
@@ -5656,12 +5656,12 @@
       <c r="P50" s="28"/>
     </row>
     <row r="51" spans="3:16">
-      <c r="C51" s="48"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="47"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="44"/>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -5670,230 +5670,230 @@
       <c r="P51" s="28"/>
     </row>
     <row r="52" spans="3:16">
-      <c r="C52" s="48"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="47"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="44"/>
     </row>
     <row r="53" spans="3:16">
-      <c r="C53" s="48"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="47"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="44"/>
     </row>
     <row r="54" spans="3:16">
-      <c r="C54" s="48"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="47"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="44"/>
     </row>
     <row r="55" spans="3:16">
-      <c r="C55" s="48"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="47"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="44"/>
     </row>
     <row r="56" spans="3:16">
-      <c r="C56" s="48"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="47"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="44"/>
     </row>
     <row r="57" spans="3:16">
-      <c r="C57" s="48"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="47"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="44"/>
     </row>
     <row r="58" spans="3:16" ht="15.75" customHeight="1">
-      <c r="C58" s="49"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
-      <c r="H58" s="51"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="48"/>
     </row>
     <row r="62" spans="3:16">
-      <c r="C62" s="42" t="s">
+      <c r="C62" s="54" t="s">
         <v>585</v>
       </c>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="H62" s="42" t="s">
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="H62" s="54" t="s">
         <v>586</v>
       </c>
-      <c r="I62" s="42"/>
-      <c r="J62" s="42"/>
-      <c r="K62" s="42"/>
-      <c r="M62" s="42" t="s">
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
+      <c r="M62" s="54" t="s">
         <v>587</v>
       </c>
-      <c r="N62" s="42"/>
-      <c r="O62" s="42"/>
-      <c r="P62" s="42"/>
+      <c r="N62" s="54"/>
+      <c r="O62" s="54"/>
+      <c r="P62" s="54"/>
     </row>
     <row r="63" spans="3:16">
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="42"/>
-      <c r="K63" s="42"/>
-      <c r="M63" s="42"/>
-      <c r="N63" s="42"/>
-      <c r="O63" s="42"/>
-      <c r="P63" s="42"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="H63" s="54"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
+      <c r="M63" s="54"/>
+      <c r="N63" s="54"/>
+      <c r="O63" s="54"/>
+      <c r="P63" s="54"/>
     </row>
     <row r="64" spans="3:16">
-      <c r="C64" s="43">
+      <c r="C64" s="55">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
         <v>250</v>
       </c>
-      <c r="D64" s="43"/>
-      <c r="E64" s="43"/>
-      <c r="F64" s="43"/>
-      <c r="H64" s="43">
+      <c r="D64" s="55"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="55"/>
+      <c r="H64" s="55">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
-        <v>190</v>
-      </c>
-      <c r="I64" s="43"/>
-      <c r="J64" s="43"/>
-      <c r="K64" s="43"/>
-      <c r="M64" s="44">
+        <v>192</v>
+      </c>
+      <c r="I64" s="55"/>
+      <c r="J64" s="55"/>
+      <c r="K64" s="55"/>
+      <c r="M64" s="56">
         <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.76</v>
-      </c>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
-      <c r="P64" s="44"/>
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="N64" s="56"/>
+      <c r="O64" s="56"/>
+      <c r="P64" s="56"/>
     </row>
     <row r="65" spans="3:16">
-      <c r="C65" s="43"/>
-      <c r="D65" s="43"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
-      <c r="H65" s="43"/>
-      <c r="I65" s="43"/>
-      <c r="J65" s="43"/>
-      <c r="K65" s="43"/>
-      <c r="M65" s="44"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="44"/>
-      <c r="P65" s="44"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="H65" s="55"/>
+      <c r="I65" s="55"/>
+      <c r="J65" s="55"/>
+      <c r="K65" s="55"/>
+      <c r="M65" s="56"/>
+      <c r="N65" s="56"/>
+      <c r="O65" s="56"/>
+      <c r="P65" s="56"/>
     </row>
     <row r="66" spans="3:16">
-      <c r="C66" s="43"/>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="H66" s="43"/>
-      <c r="I66" s="43"/>
-      <c r="J66" s="43"/>
-      <c r="K66" s="43"/>
-      <c r="M66" s="44"/>
-      <c r="N66" s="44"/>
-      <c r="O66" s="44"/>
-      <c r="P66" s="44"/>
+      <c r="C66" s="55"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="H66" s="55"/>
+      <c r="I66" s="55"/>
+      <c r="J66" s="55"/>
+      <c r="K66" s="55"/>
+      <c r="M66" s="56"/>
+      <c r="N66" s="56"/>
+      <c r="O66" s="56"/>
+      <c r="P66" s="56"/>
     </row>
     <row r="69" spans="3:16">
-      <c r="C69" s="42" t="s">
+      <c r="C69" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="H69" s="42" t="s">
+      <c r="D69" s="54"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="54"/>
+      <c r="H69" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="I69" s="42"/>
-      <c r="J69" s="42"/>
-      <c r="K69" s="42"/>
-      <c r="M69" s="42" t="s">
+      <c r="I69" s="54"/>
+      <c r="J69" s="54"/>
+      <c r="K69" s="54"/>
+      <c r="M69" s="54" t="s">
         <v>587</v>
       </c>
-      <c r="N69" s="42"/>
-      <c r="O69" s="42"/>
-      <c r="P69" s="42"/>
+      <c r="N69" s="54"/>
+      <c r="O69" s="54"/>
+      <c r="P69" s="54"/>
     </row>
     <row r="70" spans="3:16">
-      <c r="C70" s="42"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="H70" s="42"/>
-      <c r="I70" s="42"/>
-      <c r="J70" s="42"/>
-      <c r="K70" s="42"/>
-      <c r="M70" s="42"/>
-      <c r="N70" s="42"/>
-      <c r="O70" s="42"/>
-      <c r="P70" s="42"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="H70" s="54"/>
+      <c r="I70" s="54"/>
+      <c r="J70" s="54"/>
+      <c r="K70" s="54"/>
+      <c r="M70" s="54"/>
+      <c r="N70" s="54"/>
+      <c r="O70" s="54"/>
+      <c r="P70" s="54"/>
     </row>
     <row r="71" spans="3:16">
-      <c r="C71" s="43">
+      <c r="C71" s="55">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
         <v>71</v>
       </c>
-      <c r="D71" s="43"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="H71" s="43">
+      <c r="D71" s="55"/>
+      <c r="E71" s="55"/>
+      <c r="F71" s="55"/>
+      <c r="H71" s="55">
         <f>COUNTIF(Perfil!I:I,"Si")+COUNTIF(Credenciales!I:I,"Si")+COUNTIF(Videollamadas!I:I,"Si")</f>
         <v>60</v>
       </c>
-      <c r="I71" s="43"/>
-      <c r="J71" s="43"/>
-      <c r="K71" s="43"/>
-      <c r="M71" s="44">
+      <c r="I71" s="55"/>
+      <c r="J71" s="55"/>
+      <c r="K71" s="55"/>
+      <c r="M71" s="56">
         <f t="shared" ref="M71" si="1">H71/C71</f>
         <v>0.84507042253521125</v>
       </c>
-      <c r="N71" s="44"/>
-      <c r="O71" s="44"/>
-      <c r="P71" s="44"/>
+      <c r="N71" s="56"/>
+      <c r="O71" s="56"/>
+      <c r="P71" s="56"/>
     </row>
     <row r="72" spans="3:16">
-      <c r="C72" s="43"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="H72" s="43"/>
-      <c r="I72" s="43"/>
-      <c r="J72" s="43"/>
-      <c r="K72" s="43"/>
-      <c r="M72" s="44"/>
-      <c r="N72" s="44"/>
-      <c r="O72" s="44"/>
-      <c r="P72" s="44"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="55"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="55"/>
+      <c r="M72" s="56"/>
+      <c r="N72" s="56"/>
+      <c r="O72" s="56"/>
+      <c r="P72" s="56"/>
     </row>
     <row r="73" spans="3:16">
-      <c r="C73" s="43"/>
-      <c r="D73" s="43"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
-      <c r="H73" s="43"/>
-      <c r="I73" s="43"/>
-      <c r="J73" s="43"/>
-      <c r="K73" s="43"/>
-      <c r="M73" s="44"/>
-      <c r="N73" s="44"/>
-      <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="55"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="55"/>
+      <c r="J73" s="55"/>
+      <c r="K73" s="55"/>
+      <c r="M73" s="56"/>
+      <c r="N73" s="56"/>
+      <c r="O73" s="56"/>
+      <c r="P73" s="56"/>
     </row>
     <row r="76" spans="3:16">
       <c r="C76" s="36" t="s">
@@ -5902,6 +5902,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C69:F70"/>
+    <mergeCell ref="C71:F73"/>
+    <mergeCell ref="H69:K70"/>
+    <mergeCell ref="H71:K73"/>
+    <mergeCell ref="M69:P70"/>
+    <mergeCell ref="M71:P73"/>
+    <mergeCell ref="C62:F63"/>
+    <mergeCell ref="C64:F66"/>
+    <mergeCell ref="H62:K63"/>
+    <mergeCell ref="H64:K66"/>
+    <mergeCell ref="M62:P63"/>
+    <mergeCell ref="M64:P66"/>
     <mergeCell ref="K5:P19"/>
     <mergeCell ref="K25:P39"/>
     <mergeCell ref="S3:X4"/>
@@ -5917,18 +5929,6 @@
     <mergeCell ref="C3:H4"/>
     <mergeCell ref="C25:H39"/>
     <mergeCell ref="K23:P24"/>
-    <mergeCell ref="C62:F63"/>
-    <mergeCell ref="C64:F66"/>
-    <mergeCell ref="H62:K63"/>
-    <mergeCell ref="H64:K66"/>
-    <mergeCell ref="M62:P63"/>
-    <mergeCell ref="M64:P66"/>
-    <mergeCell ref="C69:F70"/>
-    <mergeCell ref="C71:F73"/>
-    <mergeCell ref="H69:K70"/>
-    <mergeCell ref="H71:K73"/>
-    <mergeCell ref="M69:P70"/>
-    <mergeCell ref="M71:P73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6143,7 +6143,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="57" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -6152,7 +6152,7 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="61"/>
+      <c r="H2" s="59"/>
       <c r="I2" s="12" t="s">
         <v>27</v>
       </c>
@@ -6161,7 +6161,7 @@
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -6180,7 +6180,7 @@
         <v>27</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>27</v>
@@ -6288,7 +6288,7 @@
         <v>27</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>27</v>
@@ -6389,7 +6389,7 @@
       <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="60" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -6455,7 +6455,7 @@
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="61" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -6548,7 +6548,7 @@
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="60" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -6749,7 +6749,7 @@
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="61" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -6869,7 +6869,7 @@
       <c r="A32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="60" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="22" t="s">
@@ -7016,7 +7016,7 @@
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="61" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -7069,7 +7069,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="57" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="58"/>
@@ -7078,7 +7078,7 @@
       <c r="E40" s="58"/>
       <c r="F40" s="58"/>
       <c r="G40" s="58"/>
-      <c r="H40" s="61"/>
+      <c r="H40" s="59"/>
       <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
@@ -7087,7 +7087,7 @@
       <c r="A41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="57" t="s">
+      <c r="B41" s="60" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="22" t="s">
@@ -7315,7 +7315,7 @@
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="61" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -7381,7 +7381,7 @@
       <c r="A53" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="60" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="22" t="s">
@@ -7474,7 +7474,7 @@
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="59" t="s">
+      <c r="B57" s="61" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -7675,7 +7675,7 @@
       <c r="A65" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="57" t="s">
+      <c r="B65" s="60" t="s">
         <v>90</v>
       </c>
       <c r="C65" s="22" t="s">
@@ -7795,7 +7795,7 @@
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="59" t="s">
+      <c r="B70" s="61" t="s">
         <v>104</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -7942,7 +7942,7 @@
       <c r="A76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="60" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -7995,7 +7995,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A78" s="60" t="s">
+      <c r="A78" s="57" t="s">
         <v>140</v>
       </c>
       <c r="B78" s="58"/>
@@ -8004,7 +8004,7 @@
       <c r="E78" s="58"/>
       <c r="F78" s="58"/>
       <c r="G78" s="58"/>
-      <c r="H78" s="61"/>
+      <c r="H78" s="59"/>
       <c r="I78" s="12" t="s">
         <v>27</v>
       </c>
@@ -8013,7 +8013,7 @@
       <c r="A79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="59" t="s">
+      <c r="B79" s="61" t="s">
         <v>141</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -8104,7 +8104,7 @@
       <c r="A83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B83" s="57" t="s">
+      <c r="B83" s="60" t="s">
         <v>153</v>
       </c>
       <c r="C83" s="22" t="s">
@@ -8153,7 +8153,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A85" s="60" t="s">
+      <c r="A85" s="57" t="s">
         <v>159</v>
       </c>
       <c r="B85" s="58"/>
@@ -8162,7 +8162,7 @@
       <c r="E85" s="58"/>
       <c r="F85" s="58"/>
       <c r="G85" s="58"/>
-      <c r="H85" s="61"/>
+      <c r="H85" s="59"/>
       <c r="I85" s="12" t="s">
         <v>27</v>
       </c>
@@ -8171,7 +8171,7 @@
       <c r="A86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="59" t="s">
+      <c r="B86" s="61" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -8262,7 +8262,7 @@
       <c r="A90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="57" t="s">
+      <c r="B90" s="60" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -8322,6 +8322,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B86:B88"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="B32:B36"/>
@@ -8338,12 +8344,6 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="B19:B25"/>
     <mergeCell ref="B57:B63"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B86:B88"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="153" priority="564" operator="equal">
@@ -8573,7 +8573,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="57" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -8582,13 +8582,13 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="61"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:9" ht="76.5" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -8729,7 +8729,7 @@
       <c r="A9" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -8847,7 +8847,7 @@
       <c r="A14" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -8994,7 +8994,7 @@
       <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>612</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -9138,7 +9138,7 @@
       <c r="A26" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -9227,7 +9227,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="57" t="s">
         <v>213</v>
       </c>
       <c r="B31" s="58"/>
@@ -9236,13 +9236,13 @@
       <c r="E31" s="58"/>
       <c r="F31" s="58"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="61"/>
+      <c r="H31" s="59"/>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C32" s="18" t="s">
@@ -9383,7 +9383,7 @@
       <c r="A38" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C38" s="22" t="s">
@@ -9501,7 +9501,7 @@
       <c r="A43" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="59" t="s">
+      <c r="B43" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C43" s="18" t="s">
@@ -9648,7 +9648,7 @@
       <c r="A49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="61" t="s">
+      <c r="B49" s="59" t="s">
         <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -9792,7 +9792,7 @@
       <c r="A55" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="61" t="s">
+      <c r="B55" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -9881,7 +9881,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A60" s="60" t="s">
+      <c r="A60" s="57" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="58"/>
@@ -9890,13 +9890,13 @@
       <c r="E60" s="58"/>
       <c r="F60" s="58"/>
       <c r="G60" s="58"/>
-      <c r="H60" s="61"/>
+      <c r="H60" s="59"/>
     </row>
     <row r="61" spans="1:9" ht="76.5" customHeight="1">
       <c r="A61" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="59" t="s">
+      <c r="B61" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -10037,7 +10037,7 @@
       <c r="A67" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B67" s="57" t="s">
+      <c r="B67" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C67" s="22" t="s">
@@ -10155,7 +10155,7 @@
       <c r="A72" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="59" t="s">
+      <c r="B72" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C72" s="18" t="s">
@@ -10302,7 +10302,7 @@
       <c r="A78" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="61" t="s">
+      <c r="B78" s="59" t="s">
         <v>611</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -10446,7 +10446,7 @@
       <c r="A84" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="61" t="s">
+      <c r="B84" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -10535,7 +10535,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A89" s="60" t="s">
+      <c r="A89" s="57" t="s">
         <v>159</v>
       </c>
       <c r="B89" s="58"/>
@@ -10544,13 +10544,13 @@
       <c r="E89" s="58"/>
       <c r="F89" s="58"/>
       <c r="G89" s="58"/>
-      <c r="H89" s="61"/>
+      <c r="H89" s="59"/>
     </row>
     <row r="90" spans="1:9" ht="76.5" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="59" t="s">
+      <c r="B90" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C90" s="18" t="s">
@@ -10691,7 +10691,7 @@
       <c r="A96" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B96" s="57" t="s">
+      <c r="B96" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C96" s="22" t="s">
@@ -10809,7 +10809,7 @@
       <c r="A101" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="59" t="s">
+      <c r="B101" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C101" s="18" t="s">
@@ -10956,7 +10956,7 @@
       <c r="A107" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B107" s="61" t="s">
+      <c r="B107" s="59" t="s">
         <v>591</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -11100,7 +11100,7 @@
       <c r="A113" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B113" s="61" t="s">
+      <c r="B113" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -11190,14 +11190,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B113:B117"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B107:B108"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B96:B99"/>
     <mergeCell ref="A2:H2"/>
@@ -11214,6 +11206,14 @@
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="B43:B47"/>
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="B107:B108"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="111" priority="525" operator="equal">
@@ -11619,7 +11619,7 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="61"/>
+      <c r="B2" s="59"/>
       <c r="C2" s="63"/>
       <c r="D2" s="58"/>
       <c r="E2" s="63"/>
@@ -11628,7 +11628,7 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="198" customHeight="1">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -11660,8 +11660,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
       <c r="C4" s="63" t="s">
         <v>221</v>
       </c>
@@ -11692,7 +11692,7 @@
     </row>
     <row r="5" spans="1:11" ht="45.75" customHeight="1">
       <c r="A5" s="63"/>
-      <c r="B5" s="61"/>
+      <c r="B5" s="59"/>
       <c r="C5" s="63"/>
       <c r="D5" s="58"/>
       <c r="E5" s="6" t="s">
@@ -11704,7 +11704,7 @@
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="121.5" customHeight="1">
-      <c r="B6" s="61"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="63" t="s">
         <v>226</v>
       </c>
@@ -11734,7 +11734,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="45.75" customHeight="1">
-      <c r="B7" s="61"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="63"/>
       <c r="D7" s="58"/>
       <c r="E7" s="13" t="s">
@@ -11746,7 +11746,7 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B8" s="61"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="13" t="s">
         <v>229</v>
       </c>
@@ -11762,7 +11762,7 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B9" s="61"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="13" t="s">
         <v>231</v>
       </c>
@@ -11778,7 +11778,7 @@
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
-      <c r="B10" s="61"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="13" t="s">
         <v>232</v>
       </c>
@@ -11808,7 +11808,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="140.25" customHeight="1">
-      <c r="B11" s="61"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="13" t="s">
         <v>235</v>
       </c>
@@ -11851,7 +11851,7 @@
       <c r="A13" s="62" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="61"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="63"/>
       <c r="D13" s="58"/>
       <c r="E13" s="63"/>
@@ -11989,7 +11989,7 @@
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>239</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -12024,7 +12024,7 @@
       <c r="A4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="61"/>
+      <c r="B4" s="59"/>
       <c r="C4" s="18" t="s">
         <v>244</v>
       </c>
@@ -12057,7 +12057,7 @@
       <c r="A5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="61"/>
+      <c r="B5" s="59"/>
       <c r="C5" s="18" t="s">
         <v>247</v>
       </c>
@@ -12090,7 +12090,7 @@
       <c r="A6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="61"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="18" t="s">
         <v>251</v>
       </c>
@@ -12133,7 +12133,7 @@
       <c r="A8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="60" t="s">
         <v>254</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -12168,7 +12168,7 @@
       <c r="A9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="61"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="22" t="s">
         <v>259</v>
       </c>
@@ -12201,7 +12201,7 @@
       <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="61"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="64" t="s">
         <v>262</v>
       </c>
@@ -12214,7 +12214,7 @@
       <c r="F10" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G10" s="61" t="s">
+      <c r="G10" s="59" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -12234,7 +12234,7 @@
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="61"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="58"/>
       <c r="D11" s="63"/>
       <c r="E11" s="11" t="s">
@@ -12243,7 +12243,7 @@
       <c r="F11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G11" s="61"/>
+      <c r="G11" s="59"/>
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
@@ -12261,7 +12261,7 @@
       <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="61"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="22" t="s">
         <v>267</v>
       </c>
@@ -12294,7 +12294,7 @@
       <c r="A13" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="61"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="22" t="s">
         <v>271</v>
       </c>
@@ -12327,7 +12327,7 @@
       <c r="A14" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B14" s="61"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="22" t="s">
         <v>274</v>
       </c>
@@ -12360,7 +12360,7 @@
       <c r="A15" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="61"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="22" t="s">
         <v>279</v>
       </c>
@@ -12393,7 +12393,7 @@
       <c r="A16" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="22" t="s">
         <v>282</v>
       </c>
@@ -12426,7 +12426,7 @@
       <c r="A17" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="61"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="22" t="s">
         <v>286</v>
       </c>
@@ -12459,7 +12459,7 @@
       <c r="A18" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B18" s="61"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="22" t="s">
         <v>289</v>
       </c>
@@ -12492,7 +12492,7 @@
       <c r="A19" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="22" t="s">
         <v>294</v>
       </c>
@@ -12525,7 +12525,7 @@
       <c r="A20" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="61"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="22" t="s">
         <v>298</v>
       </c>
@@ -12558,7 +12558,7 @@
       <c r="A21" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="61"/>
+      <c r="B21" s="59"/>
       <c r="C21" s="22" t="s">
         <v>303</v>
       </c>
@@ -12591,7 +12591,7 @@
       <c r="A22" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="59"/>
       <c r="C22" s="22" t="s">
         <v>305</v>
       </c>
@@ -12624,7 +12624,7 @@
       <c r="A23" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="61"/>
+      <c r="B23" s="59"/>
       <c r="C23" s="22" t="s">
         <v>310</v>
       </c>
@@ -12657,7 +12657,7 @@
       <c r="A24" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B24" s="61"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="22" t="s">
         <v>314</v>
       </c>
@@ -12690,7 +12690,7 @@
       <c r="A25" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="61"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="22" t="s">
         <v>316</v>
       </c>
@@ -12720,7 +12720,7 @@
       <c r="A26" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="61"/>
+      <c r="B26" s="59"/>
       <c r="C26" s="64" t="s">
         <v>321</v>
       </c>
@@ -12733,10 +12733,10 @@
       <c r="F26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="G26" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="61" t="s">
+      <c r="G26" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="59" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
@@ -12750,7 +12750,7 @@
       <c r="A27" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="61"/>
+      <c r="B27" s="59"/>
       <c r="C27" s="58"/>
       <c r="D27" s="63"/>
       <c r="E27" s="11" t="s">
@@ -12759,14 +12759,14 @@
       <c r="F27" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G27" s="61"/>
+      <c r="G27" s="59"/>
       <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:11" ht="76.5" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B28" s="61"/>
+      <c r="B28" s="59"/>
       <c r="C28" s="22" t="s">
         <v>329</v>
       </c>
@@ -12799,7 +12799,7 @@
       <c r="A29" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B29" s="61"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="22" t="s">
         <v>334</v>
       </c>
@@ -12832,7 +12832,7 @@
       <c r="A30" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B30" s="61"/>
+      <c r="B30" s="59"/>
       <c r="C30" s="22" t="s">
         <v>338</v>
       </c>
@@ -12865,7 +12865,7 @@
       <c r="A31" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B31" s="61"/>
+      <c r="B31" s="59"/>
       <c r="C31" s="22" t="s">
         <v>341</v>
       </c>
@@ -12980,7 +12980,7 @@
       <c r="A36" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="59" t="s">
+      <c r="B36" s="61" t="s">
         <v>349</v>
       </c>
       <c r="C36" s="22" t="s">
@@ -13015,7 +13015,7 @@
       <c r="A37" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="61"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="23" t="s">
         <v>354</v>
       </c>
@@ -13152,7 +13152,7 @@
       <c r="A3" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>359</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -13341,7 +13341,7 @@
       <c r="A10" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="60" t="s">
         <v>385</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -13629,7 +13629,7 @@
       <c r="A20" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="61" t="s">
         <v>422</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -14247,7 +14247,7 @@
       <c r="A40" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="60" t="s">
         <v>505</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -14403,7 +14403,7 @@
       <c r="A46" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B46" s="59" t="s">
+      <c r="B46" s="61" t="s">
         <v>526</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -14681,7 +14681,7 @@
       <c r="A56" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B56" s="46" t="s">
+      <c r="B56" s="43" t="s">
         <v>560</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -14955,13 +14955,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8" ht="30">
       <c r="A3" t="s">
@@ -15049,13 +15049,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C03D12F-F020-468E-89A9-19A8A2672CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430CF183-2E6E-4CCB-89FF-0E2D30C95C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4863,8 +4863,8 @@
       <c r="G5" s="43"/>
       <c r="H5" s="44"/>
       <c r="K5" s="42">
-        <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")</f>
-        <v>206</v>
+        <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!H:H,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")</f>
+        <v>209</v>
       </c>
       <c r="L5" s="43"/>
       <c r="M5" s="43"/>
@@ -4873,7 +4873,7 @@
       <c r="P5" s="44"/>
       <c r="S5" s="53">
         <f>K5/C5</f>
-        <v>0.75457875457875456</v>
+        <v>0.76556776556776551</v>
       </c>
       <c r="T5" s="43"/>
       <c r="U5" s="43"/>
@@ -5220,7 +5220,7 @@
       <c r="H25" s="44"/>
       <c r="K25" s="42">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")</f>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L25" s="43"/>
       <c r="M25" s="43"/>
@@ -5229,7 +5229,7 @@
       <c r="P25" s="44"/>
       <c r="S25" s="53">
         <f>K25/C25</f>
-        <v>0.80821917808219179</v>
+        <v>0.82191780821917804</v>
       </c>
       <c r="T25" s="43"/>
       <c r="U25" s="43"/>
@@ -5769,14 +5769,14 @@
       <c r="F64" s="55"/>
       <c r="H64" s="55">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I64" s="55"/>
       <c r="J64" s="55"/>
       <c r="K64" s="55"/>
       <c r="M64" s="56">
         <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.76800000000000002</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="N64" s="56"/>
       <c r="O64" s="56"/>
@@ -6207,7 +6207,7 @@
         <v>27</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>27</v>
@@ -6315,7 +6315,7 @@
         <v>27</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>27</v>

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430CF183-2E6E-4CCB-89FF-0E2D30C95C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDC0837-B709-4498-9EE2-B5649FBCE041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metricas de Casos de Prueba" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Misceláneas" sheetId="8" r:id="rId8"/>
     <sheet name="Control de Acceso" sheetId="9" r:id="rId9"/>
     <sheet name="Sistema Caído" sheetId="10" r:id="rId10"/>
+    <sheet name="Funcionalidades Pendientes" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2659" uniqueCount="733">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -2483,6 +2484,120 @@
   </si>
   <si>
     <t xml:space="preserve"> - Mis Mascotas carga con normalidad, sin verse afectada por la caida puntual de Videollamada.</t>
+  </si>
+  <si>
+    <t>TS-02 Flujo de Solicitud (identificado via reconciliacion con roadmap PO, 2026-08-29, pendiente de diseno)</t>
+  </si>
+  <si>
+    <t>Solicitud de reintegro completa</t>
+  </si>
+  <si>
+    <t>Carga de documentacion (comprobantes)</t>
+  </si>
+  <si>
+    <t>Validacion de campos del formulario</t>
+  </si>
+  <si>
+    <t>Reintegro con datos invalidos</t>
+  </si>
+  <si>
+    <t>Consulta de estado de una solicitud</t>
+  </si>
+  <si>
+    <t>Mascotas (identificado via reconciliacion con roadmap PO, 2026-08-29, pendiente de diseno)</t>
+  </si>
+  <si>
+    <t>Detalle completo de una mascota (datos, plan, servicios asociados)</t>
+  </si>
+  <si>
+    <t>Cambio o seleccion de mascota activa</t>
+  </si>
+  <si>
+    <t>TS-05 Encuesta CE (identificado via reconciliacion con roadmap PO, 2026-08-29, pendiente de diseno)</t>
+  </si>
+  <si>
+    <t>Disparo de encuesta de experiencia posterior a carga de credencial</t>
+  </si>
+  <si>
+    <t>Titulo</t>
+  </si>
+  <si>
+    <t>TS-01 Sesion y Cuenta (Identificado via reconciliacion con roadmap de la PO, 2026-08-29, pendiente de diseno)</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t>Acceso a contenido protegido tras hacer logout</t>
+  </si>
+  <si>
+    <t>Persistencia de sesion ante un refresh de pagina</t>
+  </si>
+  <si>
+    <t>Cambio de contrasena desde un usuario ya autenticado</t>
+  </si>
+  <si>
+    <t>Cambio de contrasena con la contrasena actual incorrecta</t>
+  </si>
+  <si>
+    <t>Tour de onboarding la primera vez que se loguea</t>
+  </si>
+  <si>
+    <t>Tour de onboarding no vuelve a aparecer en el segundo login</t>
+  </si>
+  <si>
+    <t>TS-02 Prestadores y Red (Identificado via reconciliacion con roadmap de la PO, 2026-08-29, pendiente de diseno)</t>
+  </si>
+  <si>
+    <t>Acceso al mapa de veterinarias</t>
+  </si>
+  <si>
+    <t>Busqueda de veterinarias por ubicacion o filtros</t>
+  </si>
+  <si>
+    <t>Detalle de una veterinaria</t>
+  </si>
+  <si>
+    <t>Mapa sin resultados disponibles</t>
+  </si>
+  <si>
+    <t>Atencion de Red</t>
+  </si>
+  <si>
+    <t>TS-03 Cobertura y Condicionados (Identificado via reconciliacion con roadmap de la PO, 2026-08-29, pendiente de diseno)</t>
+  </si>
+  <si>
+    <t>Consulta del documento de condicionado del plan</t>
+  </si>
+  <si>
+    <t>Descarga del documento de condicionado</t>
+  </si>
+  <si>
+    <t>Plan sin condicionado disponible</t>
+  </si>
+  <si>
+    <t>TS-04 Vetify Plus (Identificado via reconciliacion con roadmap de la PO, 2026-08-29, pendiente de diseno)</t>
+  </si>
+  <si>
+    <t>Contratar otro plan adicional desde la WebApp</t>
+  </si>
+  <si>
+    <t>Plan no elegible para el usuario</t>
+  </si>
+  <si>
+    <t>TS-05 Regresion Transversal (Identificado via reconciliacion con roadmap de la PO, 2026-08-29, pendiente de diseno)</t>
+  </si>
+  <si>
+    <t>Persistencia de sesion al navegar entre modulos</t>
+  </si>
+  <si>
+    <t>Navegacion principal (menu y rutas entre funcionalidades criticas)</t>
+  </si>
+  <si>
+    <t>Acceso directo a una ruta protegida sin autenticacion</t>
+  </si>
+  <si>
+    <t>Compatibilidad de permisos y funcionalidades visibles segun plan</t>
   </si>
 </sst>
 </file>
@@ -4854,8 +4969,8 @@
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
       <c r="C5" s="42">
-        <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199)</f>
-        <v>273</v>
+        <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199,'Funcionalidades Pendientes'!C2:C199)</f>
+        <v>302</v>
       </c>
       <c r="D5" s="43"/>
       <c r="E5" s="43"/>
@@ -4863,7 +4978,7 @@
       <c r="G5" s="43"/>
       <c r="H5" s="44"/>
       <c r="K5" s="42">
-        <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!H:H,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")</f>
+        <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!H:H,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")+COUNTIF('Funcionalidades Pendientes'!H:H,"Si")</f>
         <v>209</v>
       </c>
       <c r="L5" s="43"/>
@@ -4873,7 +4988,7 @@
       <c r="P5" s="44"/>
       <c r="S5" s="53">
         <f>K5/C5</f>
-        <v>0.76556776556776551</v>
+        <v>0.69205298013245031</v>
       </c>
       <c r="T5" s="43"/>
       <c r="U5" s="43"/>
@@ -5210,8 +5325,8 @@
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
       <c r="C25" s="42">
-        <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")</f>
-        <v>146</v>
+        <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")+COUNTIF('Funcionalidades Pendientes'!G:G,"Si")</f>
+        <v>166</v>
       </c>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
@@ -5219,7 +5334,7 @@
       <c r="G25" s="43"/>
       <c r="H25" s="44"/>
       <c r="K25" s="42">
-        <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")</f>
+        <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")+COUNTIFS('Funcionalidades Pendientes'!G:G,"Si",'Funcionalidades Pendientes'!H:H,"Si")</f>
         <v>120</v>
       </c>
       <c r="L25" s="43"/>
@@ -5229,7 +5344,7 @@
       <c r="P25" s="44"/>
       <c r="S25" s="53">
         <f>K25/C25</f>
-        <v>0.82191780821917804</v>
+        <v>0.72289156626506024</v>
       </c>
       <c r="T25" s="43"/>
       <c r="U25" s="43"/>
@@ -5545,7 +5660,7 @@
     <row r="44" spans="3:24" ht="21" customHeight="1">
       <c r="C44" s="53">
         <f>C25/C5</f>
-        <v>0.53479853479853479</v>
+        <v>0.54966887417218546</v>
       </c>
       <c r="D44" s="43"/>
       <c r="E44" s="43"/>
@@ -5762,7 +5877,7 @@
     <row r="64" spans="3:16">
       <c r="C64" s="55">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D64" s="55"/>
       <c r="E64" s="55"/>
@@ -5776,7 +5891,7 @@
       <c r="K64" s="55"/>
       <c r="M64" s="56">
         <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.77600000000000002</v>
+        <v>0.76679841897233203</v>
       </c>
       <c r="N64" s="56"/>
       <c r="O64" s="56"/>
@@ -5847,7 +5962,7 @@
     <row r="71" spans="3:16">
       <c r="C71" s="55">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D71" s="55"/>
       <c r="E71" s="55"/>
@@ -5861,7 +5976,7 @@
       <c r="K71" s="55"/>
       <c r="M71" s="56">
         <f t="shared" ref="M71" si="1">H71/C71</f>
-        <v>0.84507042253521125</v>
+        <v>0.81081081081081086</v>
       </c>
       <c r="N71" s="56"/>
       <c r="O71" s="56"/>
@@ -6086,6 +6201,540 @@
       </c>
       <c r="H6" s="40" t="s">
         <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6B8ACB-ADC5-47C1-A8C9-3AE499AC78D8}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C2" t="s">
+        <v>708</v>
+      </c>
+      <c r="D2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" t="s">
+        <v>710</v>
+      </c>
+      <c r="D4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" t="s">
+        <v>711</v>
+      </c>
+      <c r="D5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" t="s">
+        <v>712</v>
+      </c>
+      <c r="D6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" t="s">
+        <v>713</v>
+      </c>
+      <c r="D7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" t="s">
+        <v>230</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" t="s">
+        <v>714</v>
+      </c>
+      <c r="D8" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" t="s">
+        <v>230</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" t="s">
+        <v>715</v>
+      </c>
+      <c r="C10" t="s">
+        <v>716</v>
+      </c>
+      <c r="D10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" t="s">
+        <v>717</v>
+      </c>
+      <c r="D11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" t="s">
+        <v>718</v>
+      </c>
+      <c r="D12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E12" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" t="s">
+        <v>230</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" t="s">
+        <v>719</v>
+      </c>
+      <c r="D13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" t="s">
+        <v>720</v>
+      </c>
+      <c r="D14" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" t="s">
+        <v>230</v>
+      </c>
+      <c r="G14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" t="s">
+        <v>721</v>
+      </c>
+      <c r="C16" t="s">
+        <v>722</v>
+      </c>
+      <c r="D16" t="s">
+        <v>230</v>
+      </c>
+      <c r="E16" t="s">
+        <v>230</v>
+      </c>
+      <c r="F16" t="s">
+        <v>230</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" t="s">
+        <v>723</v>
+      </c>
+      <c r="D17" t="s">
+        <v>230</v>
+      </c>
+      <c r="E17" t="s">
+        <v>230</v>
+      </c>
+      <c r="F17" t="s">
+        <v>230</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" t="s">
+        <v>724</v>
+      </c>
+      <c r="D18" t="s">
+        <v>230</v>
+      </c>
+      <c r="E18" t="s">
+        <v>230</v>
+      </c>
+      <c r="F18" t="s">
+        <v>230</v>
+      </c>
+      <c r="G18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" t="s">
+        <v>725</v>
+      </c>
+      <c r="C20" t="s">
+        <v>726</v>
+      </c>
+      <c r="D20" t="s">
+        <v>230</v>
+      </c>
+      <c r="E20" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" t="s">
+        <v>230</v>
+      </c>
+      <c r="G20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" t="s">
+        <v>727</v>
+      </c>
+      <c r="D21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" t="s">
+        <v>230</v>
+      </c>
+      <c r="F21" t="s">
+        <v>230</v>
+      </c>
+      <c r="G21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>161</v>
+      </c>
+      <c r="B23" t="s">
+        <v>728</v>
+      </c>
+      <c r="C23" t="s">
+        <v>729</v>
+      </c>
+      <c r="D23" t="s">
+        <v>230</v>
+      </c>
+      <c r="E23" t="s">
+        <v>230</v>
+      </c>
+      <c r="F23" t="s">
+        <v>230</v>
+      </c>
+      <c r="G23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" t="s">
+        <v>730</v>
+      </c>
+      <c r="D24" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" t="s">
+        <v>230</v>
+      </c>
+      <c r="F24" t="s">
+        <v>230</v>
+      </c>
+      <c r="G24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" t="s">
+        <v>731</v>
+      </c>
+      <c r="D25" t="s">
+        <v>230</v>
+      </c>
+      <c r="E25" t="s">
+        <v>230</v>
+      </c>
+      <c r="F25" t="s">
+        <v>230</v>
+      </c>
+      <c r="G25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" t="s">
+        <v>732</v>
+      </c>
+      <c r="D26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E26" t="s">
+        <v>230</v>
+      </c>
+      <c r="F26" t="s">
+        <v>230</v>
+      </c>
+      <c r="G26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -11565,7 +12214,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="13" customWidth="1"/>
@@ -11858,6 +12507,67 @@
       <c r="F13" s="63"/>
       <c r="G13" s="63"/>
       <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" ht="60">
+      <c r="B14" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>702</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="C15" s="13" t="s">
+        <v>703</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -11924,7 +12634,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12" customWidth="1"/>
@@ -13041,6 +13751,38 @@
         <v>27</v>
       </c>
       <c r="K37" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="60">
+      <c r="B38" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K38" s="13" t="s">
         <v>27</v>
       </c>
     </row>
@@ -14913,7 +15655,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30.7109375" customWidth="1"/>
@@ -14987,6 +15729,124 @@
       </c>
       <c r="H3" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>695</v>
+      </c>
+      <c r="C4" t="s">
+        <v>696</v>
+      </c>
+      <c r="D4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" t="s">
+        <v>697</v>
+      </c>
+      <c r="D5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" t="s">
+        <v>698</v>
+      </c>
+      <c r="D6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" t="s">
+        <v>699</v>
+      </c>
+      <c r="D7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" t="s">
+        <v>230</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" t="s">
+        <v>700</v>
+      </c>
+      <c r="D8" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" t="s">
+        <v>230</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDC0837-B709-4498-9EE2-B5649FBCE041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC03823F-BDAF-4524-B9EA-0983DDACD442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2659" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2685" uniqueCount="780">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -2598,6 +2598,147 @@
   </si>
   <si>
     <t>Compatibilidad de permisos y funcionalidades visibles segun plan</t>
+  </si>
+  <si>
+    <t>Usuario logueado en la WebApp.</t>
+  </si>
+  <si>
+    <t>1. Abrir el menu lateral (boton Mas). 2. Presionar Cerrar sesion (data-cy=logoutButton, confirmado en vivo 2026-08-30, mismo selector que ya usa la app mobile).</t>
+  </si>
+  <si>
+    <t>El sistema redirige a la pantalla de login (auth login) y la sesion queda invalidada.</t>
+  </si>
+  <si>
+    <t>Usuario recien deslogueado.</t>
+  </si>
+  <si>
+    <t>1. Navegar directamente a una ruta protegida (ej. Mis Mascotas).</t>
+  </si>
+  <si>
+    <t>El sistema redirige a login preservando la ruta original como parametro, sin mostrar contenido protegido. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>1. Estando logueado, recargar la pagina por completo (equivalente a F5).</t>
+  </si>
+  <si>
+    <t>La sesion persiste, el usuario sigue autenticado sin necesidad de loguearse de nuevo. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>CONFIRMADO EN VIVO 2026-08-30: la funcionalidad no existe en el producto. La opcion Editar datos en Perfil solo permite modificar Telefono y Direccion -- no hay ningun campo ni flujo de cambio de contrasena estando autenticado. No es un gap de automatizacion, es una funcionalidad no construida todavia.</t>
+  </si>
+  <si>
+    <t>Mismo motivo que la fila anterior: no existe la funcionalidad base de cambio de contrasena logueado.</t>
+  </si>
+  <si>
+    <t>Cuenta que nunca completo el tour de bienvenida.</t>
+  </si>
+  <si>
+    <t>1. Loguearse por primera vez. 2. Se ve un banner de bienvenida con boton Comenzar. 3. Presionarlo y avanzar los 3 pasos con Continuar (Atras y Omitir tambien disponibles).</t>
+  </si>
+  <si>
+    <t>El tour muestra 3 pasos reales con contenido distinto cada uno (paso 1: Tu credencial siempre a mano; paso 2: Tus servicios mas cerca; paso 3) y se cierra solo al terminar. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>Cuenta que ya completo el tour una vez (ver fila anterior).</t>
+  </si>
+  <si>
+    <t>1. Cerrar sesion. 2. Loguearse de nuevo con la misma cuenta.</t>
+  </si>
+  <si>
+    <t>El banner de bienvenida y el tour no vuelven a aparecer. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>1. Abrir el menu lateral. 2. Presionar el item Veterinarias (data-cy=vetifyMenuItem-veterinarias).</t>
+  </si>
+  <si>
+    <t>Se abre un modal Buscar veterinaria con un combobox de ubicacion y un mapa de Google Maps embebido, funcional. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>1. Con el modal de mapa abierto, escribir una ubicacion real (ej. Palermo, Buenos Aires) en el combobox Ingresa la ubicacion.</t>
+  </si>
+  <si>
+    <t>Aparece un listbox con sugerencias reales de Google Places; seleccionar una recentra el mapa. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>CONFIRMADO EN VIVO 2026-08-30: los resultados de veterinarias cercanas solo se renderizan como pines dentro del iframe de Google Maps (cross-origin) -- no existe una lista de resultados fuera del mapa. Automatizar el click en un pin especifico y su detalle es tecnicamente fragil con Playwright (limitacion conocida de iframes de terceros), no simplemente falta de tiempo.</t>
+  </si>
+  <si>
+    <t>Parcial</t>
+  </si>
+  <si>
+    <t>Misma limitacion que la fila anterior: sin una senal fuera del iframe, confirmar de forma confiable un estado sin resultados es igual de fragil.</t>
+  </si>
+  <si>
+    <t>1. Ir a Planes y coberturas. 2. Expandir un plan (ej. VETIFY 100 EMERGENCIA x1). 3. Presionar Condiciones del Servicio.</t>
+  </si>
+  <si>
+    <t>CONFIRMADO EN VIVO 2026-08-30: no se encontro ningun punto de entrada a este flujo explorando Home, Perfil y Planes y coberturas. El unico item Vetify Plus del menu abre vetifyplus.com (programa de descuentos externo, feature distinta a comprar un plan adicional). Podria no existir todavia como funcionalidad.</t>
+  </si>
+  <si>
+    <t>Depende de que exista la fila anterior -- mismo estado.</t>
+  </si>
+  <si>
+    <t>1. Logueado, navegar entre al menos 2 secciones distintas (ej. Mis Mascotas y Planes y coberturas).</t>
+  </si>
+  <si>
+    <t>La sesion persiste sin redirigir a login en ningun momento. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>Confirmar que los 15 items reales del menu lateral (Inicio, Ayuda, Perfil, Mascotas, Planes y coberturas, Emergencias, Asistencia presencial, Asistencia a domicilio, Videollamada, Historial de atencion, Veterinarias, Reintegros, Cooper, Vetify Plus, Facturas -- listado completo confirmado en vivo 2026-08-30) navegan cada uno a su seccion esperada.</t>
+  </si>
+  <si>
+    <t>Cada item de menu abre su seccion correspondiente sin error.</t>
+  </si>
+  <si>
+    <t>1. Sin sesion iniciada, navegar directo a una ruta protegida (ej. Mis Mascotas).</t>
+  </si>
+  <si>
+    <t>Redirige a login preservando la ruta original. Confirmado en vivo 2026-08-30 (mismo comportamiento que la fila de Acceso posterior a logout del grupo Sesion y Cuenta).</t>
+  </si>
+  <si>
+    <t>Una cuenta Vetify Adquirente y otra OSDE Capitado.</t>
+  </si>
+  <si>
+    <t>1. Loguear ambas cuentas por separado. 2. Comparar los items del menu lateral de cada una.</t>
+  </si>
+  <si>
+    <t>La cuenta Adquirente muestra el item Vetify Plus en el menu; la cuenta OSDE Capitado NO lo muestra -- confirmado en vivo 2026-08-30, coincide con la regla de negocio ya documentada (Vetify Plus aplica a todos los productos menos OSDE).</t>
+  </si>
+  <si>
+    <t>PROBADO EN VIVO 2026-08-30 con 2 cuentas distintas (Vetify Adquirente y OSDE Capitado con historial real de reintegros pagados). AMBAS fallan al llegar al selector de Mascota en el wizard Nuevo reintegro: la primera con un error generico Algo salio mal, la segunda con No hay mascotas registradas para tu documento pese a tener reintegros pagados a nombre de esa mascota. Posible bug real, no confirmado si es de datos de las cuentas de prueba o de la funcionalidad en si -- pendiente de que Alan lo revise directamente antes de automatizar.</t>
+  </si>
+  <si>
+    <t>Depende de destrabar la fila anterior (Solicitud de reintegro) para poder llegar a este paso del wizard.</t>
+  </si>
+  <si>
+    <t>Depende de destrabar la fila de Solicitud de reintegro.</t>
+  </si>
+  <si>
+    <t>Cuenta con reintegros previos ya cargados (ej. la cuenta OSDE Capitado usada en esta validacion, con historial real Pagado/Solicitado/Desaprobado).</t>
+  </si>
+  <si>
+    <t>1. En la pantalla de Reintegros, presionar Acceder al historial.</t>
+  </si>
+  <si>
+    <t>Se ve el historial real agrupado por estado (Pagado, Solicitado, Desaprobado) con nombre de mascota, tipo de comprobante, fecha y monto de cada reintegro. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>Usuario con al menos una mascota con credencial completa.</t>
+  </si>
+  <si>
+    <t>1. Ir a Mis Mascotas. 2. Presionar la card de una mascota (petCredentialCard).</t>
+  </si>
+  <si>
+    <t>Navega a una vista de detalle real con nombre, raza, edad, plan asociado y boton Bajar credencial. Confirmado en vivo 2026-08-30.</t>
+  </si>
+  <si>
+    <t>Pendiente de una cuenta con 2 o mas mascotas con credencial completa y sana -- la unica cuenta del pool con 2 planes disponible el 2026-08-30 mostro datos degradados (0 mascotas visibles, Planes y coberturas vacio) pese a que su propia nota decia que ambos planes estaban completados. Ver hallazgo de salud del pool en decision-log.md.</t>
+  </si>
+  <si>
+    <t>PROBADO EN VIVO 2026-08-30: la interaccion funciona perfecto de forma manual (Playwright MCP), pero automatizarla con Playwright falla de forma reproducible -- la pestana nueva navega directo a un PDF y ninguna forma de esperar la navegacion (waitForLoadState, waitForURL con load/commit, expect.poll sobre url()) resuelve de forma confiable; en un intento devolvio la URL literal ':'. Se probaron 4 estrategias distintas en 7 rondas. Es un problema tecnico real del entorno de test con este patron de popup+PDF, no falta de esfuerzo.</t>
+  </si>
+  <si>
+    <t>Mismo hallazgo que la fila anterior (Consulta de condicionado) -- automatizacion del popup de PDF no resuelta pese a 7 rondas de intentos.</t>
   </si>
 </sst>
 </file>
@@ -4979,7 +5120,7 @@
       <c r="H5" s="44"/>
       <c r="K5" s="42">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!H:H,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")+COUNTIF('Funcionalidades Pendientes'!H:H,"Si")</f>
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="L5" s="43"/>
       <c r="M5" s="43"/>
@@ -4988,7 +5129,7 @@
       <c r="P5" s="44"/>
       <c r="S5" s="53">
         <f>K5/C5</f>
-        <v>0.69205298013245031</v>
+        <v>0.73509933774834435</v>
       </c>
       <c r="T5" s="43"/>
       <c r="U5" s="43"/>
@@ -5335,7 +5476,7 @@
       <c r="H25" s="44"/>
       <c r="K25" s="42">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")+COUNTIFS('Funcionalidades Pendientes'!G:G,"Si",'Funcionalidades Pendientes'!H:H,"Si")</f>
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="L25" s="43"/>
       <c r="M25" s="43"/>
@@ -5344,7 +5485,7 @@
       <c r="P25" s="44"/>
       <c r="S25" s="53">
         <f>K25/C25</f>
-        <v>0.72289156626506024</v>
+        <v>0.79518072289156627</v>
       </c>
       <c r="T25" s="43"/>
       <c r="U25" s="43"/>
@@ -5884,14 +6025,14 @@
       <c r="F64" s="55"/>
       <c r="H64" s="55">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I64" s="55"/>
       <c r="J64" s="55"/>
       <c r="K64" s="55"/>
       <c r="M64" s="56">
         <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.76679841897233203</v>
+        <v>0.77075098814229248</v>
       </c>
       <c r="N64" s="56"/>
       <c r="O64" s="56"/>
@@ -6210,10 +6351,10 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6B8ACB-ADC5-47C1-A8C9-3AE499AC78D8}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -6238,8 +6379,11 @@
       <c r="H1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -6250,22 +6394,25 @@
         <v>708</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>733</v>
       </c>
       <c r="E2" t="s">
-        <v>230</v>
+        <v>734</v>
       </c>
       <c r="F2" t="s">
-        <v>230</v>
+        <v>735</v>
       </c>
       <c r="G2" t="s">
         <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>167</v>
       </c>
@@ -6273,22 +6420,25 @@
         <v>709</v>
       </c>
       <c r="D3" t="s">
-        <v>230</v>
+        <v>736</v>
       </c>
       <c r="E3" t="s">
-        <v>230</v>
+        <v>737</v>
       </c>
       <c r="F3" t="s">
-        <v>230</v>
+        <v>738</v>
       </c>
       <c r="G3" t="s">
         <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>171</v>
       </c>
@@ -6299,19 +6449,22 @@
         <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>230</v>
+        <v>739</v>
       </c>
       <c r="F4" t="s">
-        <v>230</v>
+        <v>740</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -6325,7 +6478,7 @@
         <v>230</v>
       </c>
       <c r="F5" t="s">
-        <v>230</v>
+        <v>741</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -6333,8 +6486,11 @@
       <c r="H5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>179</v>
       </c>
@@ -6348,7 +6504,7 @@
         <v>230</v>
       </c>
       <c r="F6" t="s">
-        <v>230</v>
+        <v>742</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -6356,8 +6512,11 @@
       <c r="H6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>270</v>
       </c>
@@ -6365,22 +6524,25 @@
         <v>713</v>
       </c>
       <c r="D7" t="s">
-        <v>230</v>
+        <v>743</v>
       </c>
       <c r="E7" t="s">
-        <v>230</v>
+        <v>744</v>
       </c>
       <c r="F7" t="s">
-        <v>230</v>
+        <v>745</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>273</v>
       </c>
@@ -6388,22 +6550,25 @@
         <v>714</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>746</v>
       </c>
       <c r="E8" t="s">
-        <v>230</v>
+        <v>747</v>
       </c>
       <c r="F8" t="s">
-        <v>230</v>
+        <v>748</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>161</v>
       </c>
@@ -6417,19 +6582,22 @@
         <v>230</v>
       </c>
       <c r="E10" t="s">
-        <v>230</v>
+        <v>749</v>
       </c>
       <c r="F10" t="s">
-        <v>230</v>
+        <v>750</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>167</v>
       </c>
@@ -6440,19 +6608,22 @@
         <v>230</v>
       </c>
       <c r="E11" t="s">
-        <v>230</v>
+        <v>751</v>
       </c>
       <c r="F11" t="s">
-        <v>230</v>
+        <v>752</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>171</v>
       </c>
@@ -6466,7 +6637,7 @@
         <v>230</v>
       </c>
       <c r="F12" t="s">
-        <v>230</v>
+        <v>753</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -6474,8 +6645,11 @@
       <c r="H12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>176</v>
       </c>
@@ -6489,7 +6663,7 @@
         <v>230</v>
       </c>
       <c r="F13" t="s">
-        <v>230</v>
+        <v>755</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -6497,8 +6671,11 @@
       <c r="H13" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>179</v>
       </c>
@@ -6521,7 +6698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>161</v>
       </c>
@@ -6535,10 +6712,10 @@
         <v>230</v>
       </c>
       <c r="E16" t="s">
-        <v>230</v>
+        <v>756</v>
       </c>
       <c r="F16" t="s">
-        <v>230</v>
+        <v>778</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -6546,8 +6723,11 @@
       <c r="H16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>167</v>
       </c>
@@ -6561,7 +6741,7 @@
         <v>230</v>
       </c>
       <c r="F17" t="s">
-        <v>230</v>
+        <v>779</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -6569,8 +6749,11 @@
       <c r="H17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>171</v>
       </c>
@@ -6593,7 +6776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>161</v>
       </c>
@@ -6610,7 +6793,7 @@
         <v>230</v>
       </c>
       <c r="F20" t="s">
-        <v>230</v>
+        <v>757</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
@@ -6618,8 +6801,11 @@
       <c r="H20" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>167</v>
       </c>
@@ -6633,7 +6819,7 @@
         <v>230</v>
       </c>
       <c r="F21" t="s">
-        <v>230</v>
+        <v>758</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
@@ -6641,8 +6827,11 @@
       <c r="H21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>161</v>
       </c>
@@ -6656,19 +6845,22 @@
         <v>230</v>
       </c>
       <c r="E23" t="s">
-        <v>230</v>
+        <v>759</v>
       </c>
       <c r="F23" t="s">
-        <v>230</v>
+        <v>760</v>
       </c>
       <c r="G23" t="s">
         <v>27</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>167</v>
       </c>
@@ -6679,19 +6871,22 @@
         <v>230</v>
       </c>
       <c r="E24" t="s">
-        <v>230</v>
+        <v>761</v>
       </c>
       <c r="F24" t="s">
-        <v>230</v>
+        <v>762</v>
       </c>
       <c r="G24" t="s">
         <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>171</v>
       </c>
@@ -6702,19 +6897,22 @@
         <v>230</v>
       </c>
       <c r="E25" t="s">
-        <v>230</v>
+        <v>763</v>
       </c>
       <c r="F25" t="s">
-        <v>230</v>
+        <v>764</v>
       </c>
       <c r="G25" t="s">
         <v>27</v>
       </c>
       <c r="H25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>176</v>
       </c>
@@ -6722,19 +6920,22 @@
         <v>732</v>
       </c>
       <c r="D26" t="s">
-        <v>230</v>
+        <v>765</v>
       </c>
       <c r="E26" t="s">
-        <v>230</v>
+        <v>766</v>
       </c>
       <c r="F26" t="s">
-        <v>230</v>
+        <v>767</v>
       </c>
       <c r="G26" t="s">
         <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="I26" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -12508,7 +12709,7 @@
       <c r="G13" s="63"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="60">
+    <row r="14" spans="1:11" ht="90">
       <c r="B14" s="12" t="s">
         <v>701</v>
       </c>
@@ -12516,19 +12717,19 @@
         <v>702</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>230</v>
+        <v>774</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>230</v>
+        <v>775</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>230</v>
+        <v>776</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>27</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>28</v>
@@ -12540,7 +12741,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" ht="225">
       <c r="C15" s="13" t="s">
         <v>703</v>
       </c>
@@ -12551,7 +12752,7 @@
         <v>230</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>230</v>
+        <v>777</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>27</v>
@@ -15655,7 +15856,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30.7109375" customWidth="1"/>
@@ -15667,7 +15868,7 @@
     <col min="8" max="8" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1">
+    <row r="1" spans="1:9" s="3" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -15692,8 +15893,11 @@
       <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
@@ -15705,7 +15909,7 @@
       <c r="G2" s="43"/>
       <c r="H2" s="43"/>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:9" ht="30">
       <c r="A3" t="s">
         <v>161</v>
       </c>
@@ -15731,7 +15935,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>167</v>
       </c>
@@ -15748,7 +15952,7 @@
         <v>230</v>
       </c>
       <c r="F4" t="s">
-        <v>230</v>
+        <v>768</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
@@ -15756,8 +15960,11 @@
       <c r="H4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>171</v>
       </c>
@@ -15771,7 +15978,7 @@
         <v>230</v>
       </c>
       <c r="F5" t="s">
-        <v>230</v>
+        <v>769</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -15779,8 +15986,11 @@
       <c r="H5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -15794,7 +16004,7 @@
         <v>230</v>
       </c>
       <c r="F6" t="s">
-        <v>230</v>
+        <v>770</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
@@ -15802,8 +16012,11 @@
       <c r="H6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>179</v>
       </c>
@@ -15817,7 +16030,7 @@
         <v>230</v>
       </c>
       <c r="F7" t="s">
-        <v>230</v>
+        <v>770</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -15825,8 +16038,11 @@
       <c r="H7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>270</v>
       </c>
@@ -15834,19 +16050,22 @@
         <v>700</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>771</v>
       </c>
       <c r="E8" t="s">
-        <v>230</v>
+        <v>772</v>
       </c>
       <c r="F8" t="s">
-        <v>230</v>
+        <v>773</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\ike\vetify-automation\automation\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC03823F-BDAF-4524-B9EA-0983DDACD442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42E3632-39DC-4CEC-B65A-A0667ECD9908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2685" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="786">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -2705,9 +2705,6 @@
     <t>La cuenta Adquirente muestra el item Vetify Plus en el menu; la cuenta OSDE Capitado NO lo muestra -- confirmado en vivo 2026-08-30, coincide con la regla de negocio ya documentada (Vetify Plus aplica a todos los productos menos OSDE).</t>
   </si>
   <si>
-    <t>PROBADO EN VIVO 2026-08-30 con 2 cuentas distintas (Vetify Adquirente y OSDE Capitado con historial real de reintegros pagados). AMBAS fallan al llegar al selector de Mascota en el wizard Nuevo reintegro: la primera con un error generico Algo salio mal, la segunda con No hay mascotas registradas para tu documento pese a tener reintegros pagados a nombre de esa mascota. Posible bug real, no confirmado si es de datos de las cuentas de prueba o de la funcionalidad en si -- pendiente de que Alan lo revise directamente antes de automatizar.</t>
-  </si>
-  <si>
     <t>Depende de destrabar la fila anterior (Solicitud de reintegro) para poder llegar a este paso del wizard.</t>
   </si>
   <si>
@@ -2739,6 +2736,27 @@
   </si>
   <si>
     <t>Mismo hallazgo que la fila anterior (Consulta de condicionado) -- automatizacion del popup de PDF no resuelta pese a 7 rondas de intentos.</t>
+  </si>
+  <si>
+    <t>Usuario completa la carga de una credencial de mascota por primera vez.</t>
+  </si>
+  <si>
+    <t>1. Completar el formulario de alta de mascota. 2. Llegar a la pantalla de felicitacion (credencial lista). 3. Observar si aparece alguna encuesta de satisfaccion.</t>
+  </si>
+  <si>
+    <t>PROBADO EN VIVO 2026-08-30: se inspeccionaron los 19 bundles JS que carga la webapp. El unico codigo relacionado a survey es la libreria de terceros Hotjar; en el codigo propio de la app (_app) la unica llamada a window.hj es hj(identify) para analytics, sin ningun trigger custom atado a completar una credencial. Si esta encuesta existe, es config del dashboard de Hotjar (targeting por URL o tiempo), invisible al codigo y no deterministica. No es automatizable con Playwright de forma confiable.</t>
+  </si>
+  <si>
+    <t>Cuenta con un plan/producto cuyo campo pathCondicionado no tenga PDF mapeado.</t>
+  </si>
+  <si>
+    <t>1. Ir a Planes y coberturas con esa cuenta. 2. Expandir el plan. 3. Observar el comportamiento sin condicionado disponible.</t>
+  </si>
+  <si>
+    <t>PROBADO EN VIVO 2026-08-30: se confirmo que pathCondicionado es un campo real devuelto por el backend (GET plans engage por dni) -- el escenario es tecnicamente posible. Se intento escanear las 5 cuentas con storageState cacheado pegandole directo a la API (APIRequestContext), pero devolvio 401 en las 5: esa API usa un bearer token de localStorage que solo se adjunta con un navegador real, no replicable solo con cookies. Encontrar una cuenta real con este dato faltante necesitaria loguearse una por una (unas 24 cuentas) sin garantia de exito, o que dev/PO indique que producto/grupo especifico lo tiene. Ademas comparte el mismo bloqueo de popup+PDF ya documentado sin resolver en el caso base (CP-01/CP-02 de esta misma seccion).</t>
+  </si>
+  <si>
+    <t>PROBADO EN VIVO 2026-08-30 con 3 cuentas distintas en total. La llamada que falla es GET reintegros mascotas, 400 codigo VAL-002 Holder document must be a 7 or 8 digit DNI -- confirmado que es el mismo bug ya reportado en docs/bugs/BUG-007, Jira IMAS-4279, estado En Progreso (Mariana Navarro). No es un misterio nuevo: es un bug de backend ya trackeado que bloquea el wizard para toda cuenta cuyo DNI no tenga 7-8 digitos. Automatizacion queda pendiente de que se resuelva IMAS-4279, no de mas investigacion propia.</t>
   </si>
 </sst>
 </file>
@@ -3170,6 +3188,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3190,28 +3217,19 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5063,734 +5081,734 @@
   <sheetData>
     <row r="2" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="3" spans="3:24">
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51"/>
-      <c r="K3" s="49" t="s">
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
+      <c r="K3" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="51"/>
-      <c r="S3" s="49" t="s">
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="54"/>
+      <c r="S3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="51"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="54"/>
     </row>
     <row r="4" spans="3:24">
-      <c r="C4" s="45"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="44"/>
-      <c r="S4" s="45"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="44"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="47"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="47"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="47"/>
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C5" s="42">
+      <c r="C5" s="45">
         <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199,'Funcionalidades Pendientes'!C2:C199)</f>
         <v>302</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
-      <c r="K5" s="42">
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+      <c r="K5" s="45">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!H:H,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")+COUNTIF('Funcionalidades Pendientes'!H:H,"Si")</f>
         <v>222</v>
       </c>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="44"/>
-      <c r="S5" s="53">
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="47"/>
+      <c r="S5" s="56">
         <f>K5/C5</f>
         <v>0.73509933774834435</v>
       </c>
-      <c r="T5" s="43"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="43"/>
-      <c r="X5" s="44"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="47"/>
     </row>
     <row r="6" spans="3:24">
-      <c r="C6" s="45"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="44"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="44"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="47"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="47"/>
     </row>
     <row r="7" spans="3:24">
-      <c r="C7" s="45"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="44"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="43"/>
-      <c r="X7" s="44"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="47"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="47"/>
     </row>
     <row r="8" spans="3:24">
-      <c r="C8" s="45"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="44"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="43"/>
-      <c r="X8" s="44"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="47"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="47"/>
     </row>
     <row r="9" spans="3:24">
-      <c r="C9" s="45"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="44"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="44"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="47"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="47"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="47"/>
     </row>
     <row r="10" spans="3:24">
-      <c r="C10" s="45"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="44"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="44"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="47"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="47"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="47"/>
     </row>
     <row r="11" spans="3:24">
-      <c r="C11" s="45"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="44"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="44"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="44"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="47"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="47"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="47"/>
     </row>
     <row r="12" spans="3:24">
-      <c r="C12" s="45"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="44"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="44"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="47"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="47"/>
     </row>
     <row r="13" spans="3:24">
-      <c r="C13" s="45"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="44"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="44"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="47"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="46"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="47"/>
     </row>
     <row r="14" spans="3:24">
-      <c r="C14" s="45"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="44"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="44"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="47"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="47"/>
     </row>
     <row r="15" spans="3:24">
-      <c r="C15" s="45"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="44"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="44"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="47"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="47"/>
     </row>
     <row r="16" spans="3:24">
-      <c r="C16" s="45"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="44"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="44"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="47"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="47"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="47"/>
     </row>
     <row r="17" spans="3:24">
-      <c r="C17" s="45"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="44"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="44"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="43"/>
-      <c r="X17" s="44"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="47"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="47"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="47"/>
     </row>
     <row r="18" spans="3:24">
-      <c r="C18" s="45"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="44"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="44"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="44"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="47"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="47"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="47"/>
     </row>
     <row r="19" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C19" s="46"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="48"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="51"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="51"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="50"/>
+      <c r="X19" s="51"/>
     </row>
     <row r="22" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="23" spans="3:24">
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="51"/>
-      <c r="K23" s="49" t="s">
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="54"/>
+      <c r="K23" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="51"/>
-      <c r="S23" s="49" t="s">
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="54"/>
+      <c r="S23" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="51"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
+      <c r="V23" s="53"/>
+      <c r="W23" s="53"/>
+      <c r="X23" s="54"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="45"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="44"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="43"/>
-      <c r="X24" s="44"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="47"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="47"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="47"/>
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C25" s="42">
+      <c r="C25" s="45">
         <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")+COUNTIF('Funcionalidades Pendientes'!G:G,"Si")</f>
         <v>166</v>
       </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44"/>
-      <c r="K25" s="42">
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="47"/>
+      <c r="K25" s="45">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")+COUNTIFS('Funcionalidades Pendientes'!G:G,"Si",'Funcionalidades Pendientes'!H:H,"Si")</f>
         <v>132</v>
       </c>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="44"/>
-      <c r="S25" s="53">
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="47"/>
+      <c r="S25" s="56">
         <f>K25/C25</f>
         <v>0.79518072289156627</v>
       </c>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="43"/>
-      <c r="X25" s="44"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="47"/>
     </row>
     <row r="26" spans="3:24">
-      <c r="C26" s="45"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="44"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="X26" s="44"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="47"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="47"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="47"/>
     </row>
     <row r="27" spans="3:24">
-      <c r="C27" s="45"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="44"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="43"/>
-      <c r="U27" s="43"/>
-      <c r="V27" s="43"/>
-      <c r="W27" s="43"/>
-      <c r="X27" s="44"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="47"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="47"/>
     </row>
     <row r="28" spans="3:24">
-      <c r="C28" s="45"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="44"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="43"/>
-      <c r="W28" s="43"/>
-      <c r="X28" s="44"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="47"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="47"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="47"/>
     </row>
     <row r="29" spans="3:24">
-      <c r="C29" s="45"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="44"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="44"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="43"/>
-      <c r="V29" s="43"/>
-      <c r="W29" s="43"/>
-      <c r="X29" s="44"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="47"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="47"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="47"/>
     </row>
     <row r="30" spans="3:24">
-      <c r="C30" s="45"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="44"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="44"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="43"/>
-      <c r="U30" s="43"/>
-      <c r="V30" s="43"/>
-      <c r="W30" s="43"/>
-      <c r="X30" s="44"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="47"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="47"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="47"/>
     </row>
     <row r="31" spans="3:24">
-      <c r="C31" s="45"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="44"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="44"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="43"/>
-      <c r="V31" s="43"/>
-      <c r="W31" s="43"/>
-      <c r="X31" s="44"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="47"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="47"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="47"/>
     </row>
     <row r="32" spans="3:24">
-      <c r="C32" s="45"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="44"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="43"/>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="44"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="43"/>
-      <c r="U32" s="43"/>
-      <c r="V32" s="43"/>
-      <c r="W32" s="43"/>
-      <c r="X32" s="44"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="47"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
+      <c r="P32" s="47"/>
+      <c r="S32" s="48"/>
+      <c r="T32" s="46"/>
+      <c r="U32" s="46"/>
+      <c r="V32" s="46"/>
+      <c r="W32" s="46"/>
+      <c r="X32" s="47"/>
     </row>
     <row r="33" spans="3:24">
-      <c r="C33" s="45"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="44"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="44"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="43"/>
-      <c r="V33" s="43"/>
-      <c r="W33" s="43"/>
-      <c r="X33" s="44"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="47"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="47"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="47"/>
     </row>
     <row r="34" spans="3:24">
-      <c r="C34" s="45"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="44"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="44"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="43"/>
-      <c r="U34" s="43"/>
-      <c r="V34" s="43"/>
-      <c r="W34" s="43"/>
-      <c r="X34" s="44"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="47"/>
+      <c r="S34" s="48"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="V34" s="46"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="47"/>
     </row>
     <row r="35" spans="3:24">
-      <c r="C35" s="45"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="44"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="44"/>
-      <c r="S35" s="45"/>
-      <c r="T35" s="43"/>
-      <c r="U35" s="43"/>
-      <c r="V35" s="43"/>
-      <c r="W35" s="43"/>
-      <c r="X35" s="44"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="47"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="47"/>
+      <c r="S35" s="48"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="46"/>
+      <c r="V35" s="46"/>
+      <c r="W35" s="46"/>
+      <c r="X35" s="47"/>
     </row>
     <row r="36" spans="3:24">
-      <c r="C36" s="45"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="44"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="44"/>
-      <c r="S36" s="45"/>
-      <c r="T36" s="43"/>
-      <c r="U36" s="43"/>
-      <c r="V36" s="43"/>
-      <c r="W36" s="43"/>
-      <c r="X36" s="44"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="47"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="47"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="46"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="47"/>
     </row>
     <row r="37" spans="3:24">
-      <c r="C37" s="45"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="44"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="44"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="43"/>
-      <c r="U37" s="43"/>
-      <c r="V37" s="43"/>
-      <c r="W37" s="43"/>
-      <c r="X37" s="44"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="47"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="47"/>
+      <c r="S37" s="48"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="46"/>
+      <c r="W37" s="46"/>
+      <c r="X37" s="47"/>
     </row>
     <row r="38" spans="3:24">
-      <c r="C38" s="45"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="44"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="43"/>
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
-      <c r="O38" s="43"/>
-      <c r="P38" s="44"/>
-      <c r="S38" s="45"/>
-      <c r="T38" s="43"/>
-      <c r="U38" s="43"/>
-      <c r="V38" s="43"/>
-      <c r="W38" s="43"/>
-      <c r="X38" s="44"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="47"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="47"/>
+      <c r="S38" s="48"/>
+      <c r="T38" s="46"/>
+      <c r="U38" s="46"/>
+      <c r="V38" s="46"/>
+      <c r="W38" s="46"/>
+      <c r="X38" s="47"/>
     </row>
     <row r="39" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C39" s="46"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="47"/>
-      <c r="O39" s="47"/>
-      <c r="P39" s="48"/>
-      <c r="S39" s="46"/>
-      <c r="T39" s="47"/>
-      <c r="U39" s="47"/>
-      <c r="V39" s="47"/>
-      <c r="W39" s="47"/>
-      <c r="X39" s="48"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="51"/>
+      <c r="K39" s="49"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="50"/>
+      <c r="P39" s="51"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="50"/>
+      <c r="V39" s="50"/>
+      <c r="W39" s="50"/>
+      <c r="X39" s="51"/>
     </row>
     <row r="41" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="42" spans="3:24">
-      <c r="C42" s="49" t="s">
+      <c r="C42" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="51"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="54"/>
     </row>
     <row r="43" spans="3:24">
-      <c r="C43" s="45"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="44"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="47"/>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
@@ -5799,31 +5817,31 @@
       <c r="P43" s="28"/>
     </row>
     <row r="44" spans="3:24" ht="21" customHeight="1">
-      <c r="C44" s="53">
+      <c r="C44" s="56">
         <f>C25/C5</f>
         <v>0.54966887417218546</v>
       </c>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="44"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="52" t="s">
+      <c r="L44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="M44" s="43"/>
-      <c r="N44" s="43"/>
-      <c r="O44" s="43"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="46"/>
+      <c r="O44" s="46"/>
       <c r="P44" s="29"/>
     </row>
     <row r="45" spans="3:24">
-      <c r="C45" s="45"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="44"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="47"/>
       <c r="K45" s="28"/>
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
@@ -5832,12 +5850,12 @@
       <c r="P45" s="29"/>
     </row>
     <row r="46" spans="3:24">
-      <c r="C46" s="45"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="44"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="47"/>
       <c r="K46" s="28"/>
       <c r="L46" s="31"/>
       <c r="M46" s="28" t="s">
@@ -5848,12 +5866,12 @@
       <c r="P46" s="28"/>
     </row>
     <row r="47" spans="3:24">
-      <c r="C47" s="45"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="44"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="47"/>
       <c r="K47" s="28"/>
       <c r="L47" s="32"/>
       <c r="M47" s="28" t="s">
@@ -5864,12 +5882,12 @@
       <c r="P47" s="28"/>
     </row>
     <row r="48" spans="3:24">
-      <c r="C48" s="45"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="44"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="47"/>
       <c r="K48" s="28"/>
       <c r="L48" s="33"/>
       <c r="M48" s="28" t="s">
@@ -5880,12 +5898,12 @@
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="3:16">
-      <c r="C49" s="45"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="44"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="47"/>
       <c r="K49" s="28"/>
       <c r="L49" s="34"/>
       <c r="M49" s="28" t="s">
@@ -5896,12 +5914,12 @@
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="3:16">
-      <c r="C50" s="45"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="44"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="47"/>
       <c r="K50" s="28"/>
       <c r="L50" s="35"/>
       <c r="M50" s="28" t="s">
@@ -5912,12 +5930,12 @@
       <c r="P50" s="28"/>
     </row>
     <row r="51" spans="3:16">
-      <c r="C51" s="45"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="44"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="47"/>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -5926,230 +5944,230 @@
       <c r="P51" s="28"/>
     </row>
     <row r="52" spans="3:16">
-      <c r="C52" s="45"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="44"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="47"/>
     </row>
     <row r="53" spans="3:16">
-      <c r="C53" s="45"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="44"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="47"/>
     </row>
     <row r="54" spans="3:16">
-      <c r="C54" s="45"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="44"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="47"/>
     </row>
     <row r="55" spans="3:16">
-      <c r="C55" s="45"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="44"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="47"/>
     </row>
     <row r="56" spans="3:16">
-      <c r="C56" s="45"/>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="43"/>
-      <c r="H56" s="44"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="47"/>
     </row>
     <row r="57" spans="3:16">
-      <c r="C57" s="45"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="44"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="47"/>
     </row>
     <row r="58" spans="3:16" ht="15.75" customHeight="1">
-      <c r="C58" s="46"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="48"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
+      <c r="H58" s="51"/>
     </row>
     <row r="62" spans="3:16">
-      <c r="C62" s="54" t="s">
+      <c r="C62" s="42" t="s">
         <v>585</v>
       </c>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="54"/>
-      <c r="H62" s="54" t="s">
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="H62" s="42" t="s">
         <v>586</v>
       </c>
-      <c r="I62" s="54"/>
-      <c r="J62" s="54"/>
-      <c r="K62" s="54"/>
-      <c r="M62" s="54" t="s">
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
+      <c r="M62" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="N62" s="54"/>
-      <c r="O62" s="54"/>
-      <c r="P62" s="54"/>
+      <c r="N62" s="42"/>
+      <c r="O62" s="42"/>
+      <c r="P62" s="42"/>
     </row>
     <row r="63" spans="3:16">
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="54"/>
-      <c r="H63" s="54"/>
-      <c r="I63" s="54"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
-      <c r="M63" s="54"/>
-      <c r="N63" s="54"/>
-      <c r="O63" s="54"/>
-      <c r="P63" s="54"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
+      <c r="M63" s="42"/>
+      <c r="N63" s="42"/>
+      <c r="O63" s="42"/>
+      <c r="P63" s="42"/>
     </row>
     <row r="64" spans="3:16">
-      <c r="C64" s="55">
+      <c r="C64" s="43">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
-        <v>253</v>
-      </c>
-      <c r="D64" s="55"/>
-      <c r="E64" s="55"/>
-      <c r="F64" s="55"/>
-      <c r="H64" s="55">
+        <v>252</v>
+      </c>
+      <c r="D64" s="43"/>
+      <c r="E64" s="43"/>
+      <c r="F64" s="43"/>
+      <c r="H64" s="43">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
         <v>195</v>
       </c>
-      <c r="I64" s="55"/>
-      <c r="J64" s="55"/>
-      <c r="K64" s="55"/>
-      <c r="M64" s="56">
+      <c r="I64" s="43"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="43"/>
+      <c r="M64" s="44">
         <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.77075098814229248</v>
-      </c>
-      <c r="N64" s="56"/>
-      <c r="O64" s="56"/>
-      <c r="P64" s="56"/>
+        <v>0.77380952380952384</v>
+      </c>
+      <c r="N64" s="44"/>
+      <c r="O64" s="44"/>
+      <c r="P64" s="44"/>
     </row>
     <row r="65" spans="3:16">
-      <c r="C65" s="55"/>
-      <c r="D65" s="55"/>
-      <c r="E65" s="55"/>
-      <c r="F65" s="55"/>
-      <c r="H65" s="55"/>
-      <c r="I65" s="55"/>
-      <c r="J65" s="55"/>
-      <c r="K65" s="55"/>
-      <c r="M65" s="56"/>
-      <c r="N65" s="56"/>
-      <c r="O65" s="56"/>
-      <c r="P65" s="56"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44"/>
+      <c r="P65" s="44"/>
     </row>
     <row r="66" spans="3:16">
-      <c r="C66" s="55"/>
-      <c r="D66" s="55"/>
-      <c r="E66" s="55"/>
-      <c r="F66" s="55"/>
-      <c r="H66" s="55"/>
-      <c r="I66" s="55"/>
-      <c r="J66" s="55"/>
-      <c r="K66" s="55"/>
-      <c r="M66" s="56"/>
-      <c r="N66" s="56"/>
-      <c r="O66" s="56"/>
-      <c r="P66" s="56"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="43"/>
+      <c r="M66" s="44"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="44"/>
+      <c r="P66" s="44"/>
     </row>
     <row r="69" spans="3:16">
-      <c r="C69" s="54" t="s">
+      <c r="C69" s="42" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="54"/>
-      <c r="E69" s="54"/>
-      <c r="F69" s="54"/>
-      <c r="H69" s="54" t="s">
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="H69" s="42" t="s">
         <v>589</v>
       </c>
-      <c r="I69" s="54"/>
-      <c r="J69" s="54"/>
-      <c r="K69" s="54"/>
-      <c r="M69" s="54" t="s">
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
+      <c r="M69" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="N69" s="54"/>
-      <c r="O69" s="54"/>
-      <c r="P69" s="54"/>
+      <c r="N69" s="42"/>
+      <c r="O69" s="42"/>
+      <c r="P69" s="42"/>
     </row>
     <row r="70" spans="3:16">
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="54"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="54"/>
-      <c r="J70" s="54"/>
-      <c r="K70" s="54"/>
-      <c r="M70" s="54"/>
-      <c r="N70" s="54"/>
-      <c r="O70" s="54"/>
-      <c r="P70" s="54"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
+      <c r="M70" s="42"/>
+      <c r="N70" s="42"/>
+      <c r="O70" s="42"/>
+      <c r="P70" s="42"/>
     </row>
     <row r="71" spans="3:16">
-      <c r="C71" s="55">
+      <c r="C71" s="43">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
-        <v>74</v>
-      </c>
-      <c r="D71" s="55"/>
-      <c r="E71" s="55"/>
-      <c r="F71" s="55"/>
-      <c r="H71" s="55">
+        <v>73</v>
+      </c>
+      <c r="D71" s="43"/>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
+      <c r="H71" s="43">
         <f>COUNTIF(Perfil!I:I,"Si")+COUNTIF(Credenciales!I:I,"Si")+COUNTIF(Videollamadas!I:I,"Si")</f>
         <v>60</v>
       </c>
-      <c r="I71" s="55"/>
-      <c r="J71" s="55"/>
-      <c r="K71" s="55"/>
-      <c r="M71" s="56">
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+      <c r="M71" s="44">
         <f t="shared" ref="M71" si="1">H71/C71</f>
-        <v>0.81081081081081086</v>
-      </c>
-      <c r="N71" s="56"/>
-      <c r="O71" s="56"/>
-      <c r="P71" s="56"/>
+        <v>0.82191780821917804</v>
+      </c>
+      <c r="N71" s="44"/>
+      <c r="O71" s="44"/>
+      <c r="P71" s="44"/>
     </row>
     <row r="72" spans="3:16">
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="55"/>
-      <c r="H72" s="55"/>
-      <c r="I72" s="55"/>
-      <c r="J72" s="55"/>
-      <c r="K72" s="55"/>
-      <c r="M72" s="56"/>
-      <c r="N72" s="56"/>
-      <c r="O72" s="56"/>
-      <c r="P72" s="56"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+      <c r="M72" s="44"/>
+      <c r="N72" s="44"/>
+      <c r="O72" s="44"/>
+      <c r="P72" s="44"/>
     </row>
     <row r="73" spans="3:16">
-      <c r="C73" s="55"/>
-      <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="55"/>
-      <c r="H73" s="55"/>
-      <c r="I73" s="55"/>
-      <c r="J73" s="55"/>
-      <c r="K73" s="55"/>
-      <c r="M73" s="56"/>
-      <c r="N73" s="56"/>
-      <c r="O73" s="56"/>
-      <c r="P73" s="56"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="H73" s="43"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="43"/>
+      <c r="M73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
     </row>
     <row r="76" spans="3:16">
       <c r="C76" s="36" t="s">
@@ -6158,18 +6176,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C69:F70"/>
-    <mergeCell ref="C71:F73"/>
-    <mergeCell ref="H69:K70"/>
-    <mergeCell ref="H71:K73"/>
-    <mergeCell ref="M69:P70"/>
-    <mergeCell ref="M71:P73"/>
-    <mergeCell ref="C62:F63"/>
-    <mergeCell ref="C64:F66"/>
-    <mergeCell ref="H62:K63"/>
-    <mergeCell ref="H64:K66"/>
-    <mergeCell ref="M62:P63"/>
-    <mergeCell ref="M64:P66"/>
     <mergeCell ref="K5:P19"/>
     <mergeCell ref="K25:P39"/>
     <mergeCell ref="S3:X4"/>
@@ -6185,6 +6191,18 @@
     <mergeCell ref="C3:H4"/>
     <mergeCell ref="C25:H39"/>
     <mergeCell ref="K23:P24"/>
+    <mergeCell ref="C62:F63"/>
+    <mergeCell ref="C64:F66"/>
+    <mergeCell ref="H62:K63"/>
+    <mergeCell ref="H64:K66"/>
+    <mergeCell ref="M62:P63"/>
+    <mergeCell ref="M64:P66"/>
+    <mergeCell ref="C69:F70"/>
+    <mergeCell ref="C71:F73"/>
+    <mergeCell ref="H69:K70"/>
+    <mergeCell ref="H71:K73"/>
+    <mergeCell ref="M69:P70"/>
+    <mergeCell ref="M71:P73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6715,7 +6733,7 @@
         <v>756</v>
       </c>
       <c r="F16" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -6741,7 +6759,7 @@
         <v>230</v>
       </c>
       <c r="F17" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -6761,18 +6779,21 @@
         <v>724</v>
       </c>
       <c r="D18" t="s">
-        <v>230</v>
+        <v>782</v>
       </c>
       <c r="E18" t="s">
-        <v>230</v>
+        <v>783</v>
       </c>
       <c r="F18" t="s">
-        <v>230</v>
+        <v>784</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
       </c>
       <c r="H18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" t="s">
         <v>28</v>
       </c>
     </row>
@@ -6993,7 +7014,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -7002,7 +7023,7 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="H2" s="61"/>
       <c r="I2" s="12" t="s">
         <v>27</v>
       </c>
@@ -7011,7 +7032,7 @@
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -7239,7 +7260,7 @@
       <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="57" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -7305,7 +7326,7 @@
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="59" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -7398,7 +7419,7 @@
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="57" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -7599,7 +7620,7 @@
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="59" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -7719,7 +7740,7 @@
       <c r="A32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="57" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="22" t="s">
@@ -7866,7 +7887,7 @@
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="59" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -7919,7 +7940,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="60" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="58"/>
@@ -7928,7 +7949,7 @@
       <c r="E40" s="58"/>
       <c r="F40" s="58"/>
       <c r="G40" s="58"/>
-      <c r="H40" s="59"/>
+      <c r="H40" s="61"/>
       <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
@@ -7937,7 +7958,7 @@
       <c r="A41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="57" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="22" t="s">
@@ -8165,7 +8186,7 @@
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="61" t="s">
+      <c r="B50" s="59" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -8231,7 +8252,7 @@
       <c r="A53" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="57" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="22" t="s">
@@ -8324,7 +8345,7 @@
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="61" t="s">
+      <c r="B57" s="59" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -8525,7 +8546,7 @@
       <c r="A65" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="57" t="s">
         <v>90</v>
       </c>
       <c r="C65" s="22" t="s">
@@ -8645,7 +8666,7 @@
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="61" t="s">
+      <c r="B70" s="59" t="s">
         <v>104</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -8792,7 +8813,7 @@
       <c r="A76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="60" t="s">
+      <c r="B76" s="57" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -8845,7 +8866,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A78" s="57" t="s">
+      <c r="A78" s="60" t="s">
         <v>140</v>
       </c>
       <c r="B78" s="58"/>
@@ -8854,7 +8875,7 @@
       <c r="E78" s="58"/>
       <c r="F78" s="58"/>
       <c r="G78" s="58"/>
-      <c r="H78" s="59"/>
+      <c r="H78" s="61"/>
       <c r="I78" s="12" t="s">
         <v>27</v>
       </c>
@@ -8863,7 +8884,7 @@
       <c r="A79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="61" t="s">
+      <c r="B79" s="59" t="s">
         <v>141</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -8954,7 +8975,7 @@
       <c r="A83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B83" s="60" t="s">
+      <c r="B83" s="57" t="s">
         <v>153</v>
       </c>
       <c r="C83" s="22" t="s">
@@ -9003,7 +9024,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A85" s="57" t="s">
+      <c r="A85" s="60" t="s">
         <v>159</v>
       </c>
       <c r="B85" s="58"/>
@@ -9012,7 +9033,7 @@
       <c r="E85" s="58"/>
       <c r="F85" s="58"/>
       <c r="G85" s="58"/>
-      <c r="H85" s="59"/>
+      <c r="H85" s="61"/>
       <c r="I85" s="12" t="s">
         <v>27</v>
       </c>
@@ -9021,7 +9042,7 @@
       <c r="A86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="61" t="s">
+      <c r="B86" s="59" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -9112,7 +9133,7 @@
       <c r="A90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="60" t="s">
+      <c r="B90" s="57" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -9172,12 +9193,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B86:B88"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="B32:B36"/>
@@ -9194,6 +9209,12 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="B19:B25"/>
     <mergeCell ref="B57:B63"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B86:B88"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="153" priority="564" operator="equal">
@@ -9423,7 +9444,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -9432,13 +9453,13 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="1:9" ht="76.5" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -9579,7 +9600,7 @@
       <c r="A9" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -9697,7 +9718,7 @@
       <c r="A14" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -9844,7 +9865,7 @@
       <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="61" t="s">
         <v>612</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -9988,7 +10009,7 @@
       <c r="A26" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -10077,7 +10098,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="60" t="s">
         <v>213</v>
       </c>
       <c r="B31" s="58"/>
@@ -10086,13 +10107,13 @@
       <c r="E31" s="58"/>
       <c r="F31" s="58"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="59"/>
+      <c r="H31" s="61"/>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C32" s="18" t="s">
@@ -10233,7 +10254,7 @@
       <c r="A38" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C38" s="22" t="s">
@@ -10351,7 +10372,7 @@
       <c r="A43" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C43" s="18" t="s">
@@ -10498,7 +10519,7 @@
       <c r="A49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="59" t="s">
+      <c r="B49" s="61" t="s">
         <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -10642,7 +10663,7 @@
       <c r="A55" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="59" t="s">
+      <c r="B55" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -10731,7 +10752,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A60" s="57" t="s">
+      <c r="A60" s="60" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="58"/>
@@ -10740,13 +10761,13 @@
       <c r="E60" s="58"/>
       <c r="F60" s="58"/>
       <c r="G60" s="58"/>
-      <c r="H60" s="59"/>
+      <c r="H60" s="61"/>
     </row>
     <row r="61" spans="1:9" ht="76.5" customHeight="1">
       <c r="A61" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="61" t="s">
+      <c r="B61" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -10887,7 +10908,7 @@
       <c r="A67" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B67" s="60" t="s">
+      <c r="B67" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C67" s="22" t="s">
@@ -11005,7 +11026,7 @@
       <c r="A72" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="61" t="s">
+      <c r="B72" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C72" s="18" t="s">
@@ -11152,7 +11173,7 @@
       <c r="A78" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="59" t="s">
+      <c r="B78" s="61" t="s">
         <v>611</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -11296,7 +11317,7 @@
       <c r="A84" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="59" t="s">
+      <c r="B84" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -11385,7 +11406,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A89" s="57" t="s">
+      <c r="A89" s="60" t="s">
         <v>159</v>
       </c>
       <c r="B89" s="58"/>
@@ -11394,13 +11415,13 @@
       <c r="E89" s="58"/>
       <c r="F89" s="58"/>
       <c r="G89" s="58"/>
-      <c r="H89" s="59"/>
+      <c r="H89" s="61"/>
     </row>
     <row r="90" spans="1:9" ht="76.5" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="61" t="s">
+      <c r="B90" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C90" s="18" t="s">
@@ -11541,7 +11562,7 @@
       <c r="A96" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B96" s="60" t="s">
+      <c r="B96" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C96" s="22" t="s">
@@ -11659,7 +11680,7 @@
       <c r="A101" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="61" t="s">
+      <c r="B101" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C101" s="18" t="s">
@@ -11806,7 +11827,7 @@
       <c r="A107" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B107" s="59" t="s">
+      <c r="B107" s="61" t="s">
         <v>591</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -11950,7 +11971,7 @@
       <c r="A113" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B113" s="59" t="s">
+      <c r="B113" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -12040,6 +12061,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="B107:B108"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B96:B99"/>
     <mergeCell ref="A2:H2"/>
@@ -12056,14 +12085,6 @@
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="B43:B47"/>
-    <mergeCell ref="B113:B117"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B107:B108"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="111" priority="525" operator="equal">
@@ -12469,7 +12490,7 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="59"/>
+      <c r="B2" s="61"/>
       <c r="C2" s="63"/>
       <c r="D2" s="58"/>
       <c r="E2" s="63"/>
@@ -12478,7 +12499,7 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="198" customHeight="1">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -12510,8 +12531,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="59"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="63" t="s">
         <v>221</v>
       </c>
@@ -12542,7 +12563,7 @@
     </row>
     <row r="5" spans="1:11" ht="45.75" customHeight="1">
       <c r="A5" s="63"/>
-      <c r="B5" s="59"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="63"/>
       <c r="D5" s="58"/>
       <c r="E5" s="6" t="s">
@@ -12554,7 +12575,7 @@
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="121.5" customHeight="1">
-      <c r="B6" s="59"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="63" t="s">
         <v>226</v>
       </c>
@@ -12584,7 +12605,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="45.75" customHeight="1">
-      <c r="B7" s="59"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="63"/>
       <c r="D7" s="58"/>
       <c r="E7" s="13" t="s">
@@ -12596,7 +12617,7 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B8" s="59"/>
+      <c r="B8" s="61"/>
       <c r="C8" s="13" t="s">
         <v>229</v>
       </c>
@@ -12612,7 +12633,7 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B9" s="59"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="13" t="s">
         <v>231</v>
       </c>
@@ -12628,7 +12649,7 @@
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
-      <c r="B10" s="59"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="13" t="s">
         <v>232</v>
       </c>
@@ -12658,7 +12679,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="140.25" customHeight="1">
-      <c r="B11" s="59"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="13" t="s">
         <v>235</v>
       </c>
@@ -12701,7 +12722,7 @@
       <c r="A13" s="62" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="59"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="63"/>
       <c r="D13" s="58"/>
       <c r="E13" s="63"/>
@@ -12717,13 +12738,13 @@
         <v>702</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>774</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F14" s="13" t="s">
         <v>775</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>776</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>27</v>
@@ -12752,7 +12773,7 @@
         <v>230</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>27</v>
@@ -12900,7 +12921,7 @@
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>239</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -12935,7 +12956,7 @@
       <c r="A4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="59"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="18" t="s">
         <v>244</v>
       </c>
@@ -12968,7 +12989,7 @@
       <c r="A5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="59"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="18" t="s">
         <v>247</v>
       </c>
@@ -13001,7 +13022,7 @@
       <c r="A6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="59"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="18" t="s">
         <v>251</v>
       </c>
@@ -13044,7 +13065,7 @@
       <c r="A8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="57" t="s">
         <v>254</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -13079,7 +13100,7 @@
       <c r="A9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="59"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="22" t="s">
         <v>259</v>
       </c>
@@ -13112,7 +13133,7 @@
       <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="59"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="64" t="s">
         <v>262</v>
       </c>
@@ -13125,7 +13146,7 @@
       <c r="F10" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="61" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -13145,7 +13166,7 @@
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="59"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="58"/>
       <c r="D11" s="63"/>
       <c r="E11" s="11" t="s">
@@ -13154,7 +13175,7 @@
       <c r="F11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G11" s="59"/>
+      <c r="G11" s="61"/>
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
@@ -13172,7 +13193,7 @@
       <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="59"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="22" t="s">
         <v>267</v>
       </c>
@@ -13205,7 +13226,7 @@
       <c r="A13" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="59"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="22" t="s">
         <v>271</v>
       </c>
@@ -13238,7 +13259,7 @@
       <c r="A14" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B14" s="59"/>
+      <c r="B14" s="61"/>
       <c r="C14" s="22" t="s">
         <v>274</v>
       </c>
@@ -13271,7 +13292,7 @@
       <c r="A15" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="59"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="22" t="s">
         <v>279</v>
       </c>
@@ -13304,7 +13325,7 @@
       <c r="A16" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="59"/>
+      <c r="B16" s="61"/>
       <c r="C16" s="22" t="s">
         <v>282</v>
       </c>
@@ -13337,7 +13358,7 @@
       <c r="A17" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="59"/>
+      <c r="B17" s="61"/>
       <c r="C17" s="22" t="s">
         <v>286</v>
       </c>
@@ -13370,7 +13391,7 @@
       <c r="A18" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B18" s="59"/>
+      <c r="B18" s="61"/>
       <c r="C18" s="22" t="s">
         <v>289</v>
       </c>
@@ -13403,7 +13424,7 @@
       <c r="A19" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="59"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="22" t="s">
         <v>294</v>
       </c>
@@ -13436,7 +13457,7 @@
       <c r="A20" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="59"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="22" t="s">
         <v>298</v>
       </c>
@@ -13469,7 +13490,7 @@
       <c r="A21" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="59"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="22" t="s">
         <v>303</v>
       </c>
@@ -13502,7 +13523,7 @@
       <c r="A22" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="59"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="22" t="s">
         <v>305</v>
       </c>
@@ -13535,7 +13556,7 @@
       <c r="A23" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="59"/>
+      <c r="B23" s="61"/>
       <c r="C23" s="22" t="s">
         <v>310</v>
       </c>
@@ -13568,7 +13589,7 @@
       <c r="A24" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B24" s="59"/>
+      <c r="B24" s="61"/>
       <c r="C24" s="22" t="s">
         <v>314</v>
       </c>
@@ -13601,7 +13622,7 @@
       <c r="A25" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="59"/>
+      <c r="B25" s="61"/>
       <c r="C25" s="22" t="s">
         <v>316</v>
       </c>
@@ -13631,7 +13652,7 @@
       <c r="A26" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="59"/>
+      <c r="B26" s="61"/>
       <c r="C26" s="64" t="s">
         <v>321</v>
       </c>
@@ -13644,10 +13665,10 @@
       <c r="F26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="G26" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="59" t="s">
+      <c r="G26" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="61" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
@@ -13661,7 +13682,7 @@
       <c r="A27" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="59"/>
+      <c r="B27" s="61"/>
       <c r="C27" s="58"/>
       <c r="D27" s="63"/>
       <c r="E27" s="11" t="s">
@@ -13670,14 +13691,14 @@
       <c r="F27" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G27" s="59"/>
+      <c r="G27" s="61"/>
       <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:11" ht="76.5" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B28" s="59"/>
+      <c r="B28" s="61"/>
       <c r="C28" s="22" t="s">
         <v>329</v>
       </c>
@@ -13710,7 +13731,7 @@
       <c r="A29" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B29" s="59"/>
+      <c r="B29" s="61"/>
       <c r="C29" s="22" t="s">
         <v>334</v>
       </c>
@@ -13743,7 +13764,7 @@
       <c r="A30" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B30" s="59"/>
+      <c r="B30" s="61"/>
       <c r="C30" s="22" t="s">
         <v>338</v>
       </c>
@@ -13776,7 +13797,7 @@
       <c r="A31" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B31" s="59"/>
+      <c r="B31" s="61"/>
       <c r="C31" s="22" t="s">
         <v>341</v>
       </c>
@@ -13891,7 +13912,7 @@
       <c r="A36" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="61" t="s">
+      <c r="B36" s="59" t="s">
         <v>349</v>
       </c>
       <c r="C36" s="22" t="s">
@@ -13926,7 +13947,7 @@
       <c r="A37" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="59"/>
+      <c r="B37" s="61"/>
       <c r="C37" s="23" t="s">
         <v>354</v>
       </c>
@@ -13955,7 +13976,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="60">
+    <row r="38" spans="1:11" ht="240">
       <c r="B38" s="12" t="s">
         <v>704</v>
       </c>
@@ -13963,13 +13984,13 @@
         <v>705</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>230</v>
+        <v>779</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>230</v>
+        <v>780</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>230</v>
+        <v>781</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>28</v>
@@ -13981,10 +14002,10 @@
         <v>28</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -14095,7 +14116,7 @@
       <c r="A3" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>359</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -14284,7 +14305,7 @@
       <c r="A10" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="57" t="s">
         <v>385</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -14572,7 +14593,7 @@
       <c r="A20" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>422</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -15190,7 +15211,7 @@
       <c r="A40" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="57" t="s">
         <v>505</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -15346,7 +15367,7 @@
       <c r="A46" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="59" t="s">
         <v>526</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -15624,7 +15645,7 @@
       <c r="A56" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B56" s="43" t="s">
+      <c r="B56" s="46" t="s">
         <v>560</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -15901,13 +15922,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:9" ht="30">
       <c r="A3" t="s">
@@ -15952,7 +15973,7 @@
         <v>230</v>
       </c>
       <c r="F4" t="s">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
@@ -15978,7 +15999,7 @@
         <v>230</v>
       </c>
       <c r="F5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -16004,7 +16025,7 @@
         <v>230</v>
       </c>
       <c r="F6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
@@ -16030,7 +16051,7 @@
         <v>230</v>
       </c>
       <c r="F7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -16050,13 +16071,13 @@
         <v>700</v>
       </c>
       <c r="D8" t="s">
+        <v>770</v>
+      </c>
+      <c r="E8" t="s">
         <v>771</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>772</v>
-      </c>
-      <c r="F8" t="s">
-        <v>773</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
@@ -16128,13 +16149,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42E3632-39DC-4CEC-B65A-A0667ECD9908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29E309-7E6E-4E39-9E79-7BE971ADC978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="804">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -2757,6 +2757,60 @@
   </si>
   <si>
     <t>PROBADO EN VIVO 2026-08-30 con 3 cuentas distintas en total. La llamada que falla es GET reintegros mascotas, 400 codigo VAL-002 Holder document must be a 7 or 8 digit DNI -- confirmado que es el mismo bug ya reportado en docs/bugs/BUG-007, Jira IMAS-4279, estado En Progreso (Mariana Navarro). No es un misterio nuevo: es un bug de backend ya trackeado que bloquea el wizard para toda cuenta cuyo DNI no tenga 7-8 digitos. Automatizacion queda pendiente de que se resuelva IMAS-4279, no de mas investigacion propia.</t>
+  </si>
+  <si>
+    <t>TS-06 Beneficios - Banner Cooper (IMAS-4356/IMAS-4435)</t>
+  </si>
+  <si>
+    <t>Banner Cooper visible en Home - Vetify B2C</t>
+  </si>
+  <si>
+    <t>Usuario Vetify B2C logueado.</t>
+  </si>
+  <si>
+    <t>1. Cargar Home.</t>
+  </si>
+  <si>
+    <t>El banner Ir a Cooper es visible (Beneficio exclusivo clientes Vetify, 20% off primer servicio). Verificado en Desktop y Mobile (Android).</t>
+  </si>
+  <si>
+    <t>Banner Cooper visible en Home - OSDE Capitado</t>
+  </si>
+  <si>
+    <t>Usuario OSDE Capitado logueado.</t>
+  </si>
+  <si>
+    <t>El banner Ir a Cooper es visible. Verificado en Desktop y Mobile (Android).</t>
+  </si>
+  <si>
+    <t>Banner Cooper visible en Home - OSDE Adquirente</t>
+  </si>
+  <si>
+    <t>Usuario OSDE Adquirente logueado.</t>
+  </si>
+  <si>
+    <t>El banner Ir a Cooper es visible (IMAS-4465, confirmado corregido). Verificado en Desktop y Mobile (Android), con 3 cuentas distintas incluida una de compra real.</t>
+  </si>
+  <si>
+    <t>Menu Beneficios - Vetify B2C ve Cooper y Vetify PLUS</t>
+  </si>
+  <si>
+    <t>1. Cargar Home y abrir el menu lateral.</t>
+  </si>
+  <si>
+    <t>La seccion Beneficios muestra Cooper y Vetify PLUS juntos. Verificado en Desktop y Mobile (Android).</t>
+  </si>
+  <si>
+    <t>Menu Beneficios - OSDE Capitado NO ve Vetify PLUS</t>
+  </si>
+  <si>
+    <t>El item Vetify PLUS no aparece (IMAS-4463, confirmado corregido). Verificado en Desktop y Mobile (Android).</t>
+  </si>
+  <si>
+    <t>Menu Beneficios - OSDE Capitado ve Cooper</t>
+  </si>
+  <si>
+    <t>El item Cooper es visible dentro de Beneficios. Verificado en Desktop y Mobile (Android). Nota: el menu de OSDE Adquirente depende del producto real (policyId) de la cuenta, no del segmento -- no automatizado con una asercion fija a proposito, ver docs/conocimiento-sistema.md.</t>
   </si>
 </sst>
 </file>
@@ -3188,15 +3242,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3217,19 +3262,28 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5081,734 +5135,734 @@
   <sheetData>
     <row r="2" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="3" spans="3:24">
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
-      <c r="K3" s="52" t="s">
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="51"/>
+      <c r="K3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="54"/>
-      <c r="S3" s="52" t="s">
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="S3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="54"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="50"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="51"/>
     </row>
     <row r="4" spans="3:24">
-      <c r="C4" s="48"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="47"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="47"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="47"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="44"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="44"/>
+      <c r="S4" s="45"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="44"/>
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C5" s="45">
+      <c r="C5" s="42">
         <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199,'Funcionalidades Pendientes'!C2:C199)</f>
-        <v>302</v>
-      </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
-      <c r="K5" s="45">
+        <v>308</v>
+      </c>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
+      <c r="K5" s="42">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!H:H,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")+COUNTIF('Funcionalidades Pendientes'!H:H,"Si")</f>
-        <v>222</v>
-      </c>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="47"/>
-      <c r="S5" s="56">
+        <v>228</v>
+      </c>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="44"/>
+      <c r="S5" s="53">
         <f>K5/C5</f>
-        <v>0.73509933774834435</v>
-      </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="47"/>
+        <v>0.74025974025974028</v>
+      </c>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="44"/>
     </row>
     <row r="6" spans="3:24">
-      <c r="C6" s="48"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="47"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="47"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="44"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="44"/>
     </row>
     <row r="7" spans="3:24">
-      <c r="C7" s="48"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="47"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="47"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="44"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="44"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="44"/>
     </row>
     <row r="8" spans="3:24">
-      <c r="C8" s="48"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="47"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="46"/>
-      <c r="V8" s="46"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="47"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="44"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="44"/>
     </row>
     <row r="9" spans="3:24">
-      <c r="C9" s="48"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="47"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="47"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="47"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="44"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="44"/>
     </row>
     <row r="10" spans="3:24">
-      <c r="C10" s="48"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="47"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="46"/>
-      <c r="P10" s="47"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="47"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="44"/>
+      <c r="S10" s="45"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="44"/>
     </row>
     <row r="11" spans="3:24">
-      <c r="C11" s="48"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="47"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="47"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="47"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="44"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="44"/>
+      <c r="S11" s="45"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="44"/>
     </row>
     <row r="12" spans="3:24">
-      <c r="C12" s="48"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="47"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="47"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="46"/>
-      <c r="V12" s="46"/>
-      <c r="W12" s="46"/>
-      <c r="X12" s="47"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="44"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="44"/>
     </row>
     <row r="13" spans="3:24">
-      <c r="C13" s="48"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="47"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="47"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
-      <c r="V13" s="46"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="47"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="44"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="44"/>
     </row>
     <row r="14" spans="3:24">
-      <c r="C14" s="48"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="47"/>
-      <c r="S14" s="48"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="46"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="47"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="44"/>
+      <c r="S14" s="45"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="43"/>
+      <c r="W14" s="43"/>
+      <c r="X14" s="44"/>
     </row>
     <row r="15" spans="3:24">
-      <c r="C15" s="48"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="47"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="47"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="44"/>
+      <c r="S15" s="45"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="44"/>
     </row>
     <row r="16" spans="3:24">
-      <c r="C16" s="48"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="47"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="47"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="47"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="44"/>
+      <c r="S16" s="45"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="44"/>
     </row>
     <row r="17" spans="3:24">
-      <c r="C17" s="48"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="47"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="47"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="47"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="44"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="43"/>
+      <c r="W17" s="43"/>
+      <c r="X17" s="44"/>
     </row>
     <row r="18" spans="3:24">
-      <c r="C18" s="48"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="47"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="47"/>
-      <c r="S18" s="48"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="46"/>
-      <c r="V18" s="46"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="47"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="44"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
+      <c r="X18" s="44"/>
     </row>
     <row r="19" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C19" s="49"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="51"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="51"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="50"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="51"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="48"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="48"/>
     </row>
     <row r="22" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="23" spans="3:24">
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="54"/>
-      <c r="K23" s="52" t="s">
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="51"/>
+      <c r="K23" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="54"/>
-      <c r="S23" s="52" t="s">
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="51"/>
+      <c r="S23" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="T23" s="53"/>
-      <c r="U23" s="53"/>
-      <c r="V23" s="53"/>
-      <c r="W23" s="53"/>
-      <c r="X23" s="54"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="51"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="48"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="47"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="47"/>
-      <c r="S24" s="48"/>
-      <c r="T24" s="46"/>
-      <c r="U24" s="46"/>
-      <c r="V24" s="46"/>
-      <c r="W24" s="46"/>
-      <c r="X24" s="47"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="44"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="43"/>
+      <c r="U24" s="43"/>
+      <c r="V24" s="43"/>
+      <c r="W24" s="43"/>
+      <c r="X24" s="44"/>
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C25" s="45">
+      <c r="C25" s="42">
         <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")+COUNTIF('Funcionalidades Pendientes'!G:G,"Si")</f>
-        <v>166</v>
-      </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="47"/>
-      <c r="K25" s="45">
+        <v>172</v>
+      </c>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
+      <c r="K25" s="42">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")+COUNTIFS('Funcionalidades Pendientes'!G:G,"Si",'Funcionalidades Pendientes'!H:H,"Si")</f>
-        <v>132</v>
-      </c>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
-      <c r="P25" s="47"/>
-      <c r="S25" s="56">
+        <v>138</v>
+      </c>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="44"/>
+      <c r="S25" s="53">
         <f>K25/C25</f>
-        <v>0.79518072289156627</v>
-      </c>
-      <c r="T25" s="46"/>
-      <c r="U25" s="46"/>
-      <c r="V25" s="46"/>
-      <c r="W25" s="46"/>
-      <c r="X25" s="47"/>
+        <v>0.80232558139534882</v>
+      </c>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43"/>
+      <c r="V25" s="43"/>
+      <c r="W25" s="43"/>
+      <c r="X25" s="44"/>
     </row>
     <row r="26" spans="3:24">
-      <c r="C26" s="48"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="47"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="47"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="47"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="44"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="X26" s="44"/>
     </row>
     <row r="27" spans="3:24">
-      <c r="C27" s="48"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="47"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46"/>
-      <c r="X27" s="47"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="44"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="43"/>
+      <c r="V27" s="43"/>
+      <c r="W27" s="43"/>
+      <c r="X27" s="44"/>
     </row>
     <row r="28" spans="3:24">
-      <c r="C28" s="48"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="47"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="47"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="47"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="44"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="43"/>
+      <c r="W28" s="43"/>
+      <c r="X28" s="44"/>
     </row>
     <row r="29" spans="3:24">
-      <c r="C29" s="48"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="47"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
-      <c r="O29" s="46"/>
-      <c r="P29" s="47"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="46"/>
-      <c r="U29" s="46"/>
-      <c r="V29" s="46"/>
-      <c r="W29" s="46"/>
-      <c r="X29" s="47"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="44"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="43"/>
+      <c r="U29" s="43"/>
+      <c r="V29" s="43"/>
+      <c r="W29" s="43"/>
+      <c r="X29" s="44"/>
     </row>
     <row r="30" spans="3:24">
-      <c r="C30" s="48"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="47"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="47"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="46"/>
-      <c r="V30" s="46"/>
-      <c r="W30" s="46"/>
-      <c r="X30" s="47"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="44"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="44"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
+      <c r="V30" s="43"/>
+      <c r="W30" s="43"/>
+      <c r="X30" s="44"/>
     </row>
     <row r="31" spans="3:24">
-      <c r="C31" s="48"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="47"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="46"/>
-      <c r="P31" s="47"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="46"/>
-      <c r="U31" s="46"/>
-      <c r="V31" s="46"/>
-      <c r="W31" s="46"/>
-      <c r="X31" s="47"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="44"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="44"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="43"/>
+      <c r="U31" s="43"/>
+      <c r="V31" s="43"/>
+      <c r="W31" s="43"/>
+      <c r="X31" s="44"/>
     </row>
     <row r="32" spans="3:24">
-      <c r="C32" s="48"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="47"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
-      <c r="O32" s="46"/>
-      <c r="P32" s="47"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="46"/>
-      <c r="U32" s="46"/>
-      <c r="V32" s="46"/>
-      <c r="W32" s="46"/>
-      <c r="X32" s="47"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="44"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="44"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="43"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="43"/>
+      <c r="W32" s="43"/>
+      <c r="X32" s="44"/>
     </row>
     <row r="33" spans="3:24">
-      <c r="C33" s="48"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="47"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="46"/>
-      <c r="P33" s="47"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="46"/>
-      <c r="U33" s="46"/>
-      <c r="V33" s="46"/>
-      <c r="W33" s="46"/>
-      <c r="X33" s="47"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="44"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="44"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="43"/>
+      <c r="U33" s="43"/>
+      <c r="V33" s="43"/>
+      <c r="W33" s="43"/>
+      <c r="X33" s="44"/>
     </row>
     <row r="34" spans="3:24">
-      <c r="C34" s="48"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="47"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="46"/>
-      <c r="P34" s="47"/>
-      <c r="S34" s="48"/>
-      <c r="T34" s="46"/>
-      <c r="U34" s="46"/>
-      <c r="V34" s="46"/>
-      <c r="W34" s="46"/>
-      <c r="X34" s="47"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="44"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="44"/>
     </row>
     <row r="35" spans="3:24">
-      <c r="C35" s="48"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="47"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="46"/>
-      <c r="P35" s="47"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="46"/>
-      <c r="U35" s="46"/>
-      <c r="V35" s="46"/>
-      <c r="W35" s="46"/>
-      <c r="X35" s="47"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="44"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="44"/>
+      <c r="S35" s="45"/>
+      <c r="T35" s="43"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
+      <c r="W35" s="43"/>
+      <c r="X35" s="44"/>
     </row>
     <row r="36" spans="3:24">
-      <c r="C36" s="48"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="47"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="46"/>
-      <c r="P36" s="47"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="46"/>
-      <c r="U36" s="46"/>
-      <c r="V36" s="46"/>
-      <c r="W36" s="46"/>
-      <c r="X36" s="47"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="44"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="44"/>
+      <c r="S36" s="45"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
+      <c r="W36" s="43"/>
+      <c r="X36" s="44"/>
     </row>
     <row r="37" spans="3:24">
-      <c r="C37" s="48"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="47"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-      <c r="O37" s="46"/>
-      <c r="P37" s="47"/>
-      <c r="S37" s="48"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="46"/>
-      <c r="W37" s="46"/>
-      <c r="X37" s="47"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="44"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="44"/>
+      <c r="S37" s="45"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="43"/>
+      <c r="V37" s="43"/>
+      <c r="W37" s="43"/>
+      <c r="X37" s="44"/>
     </row>
     <row r="38" spans="3:24">
-      <c r="C38" s="48"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="47"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-      <c r="O38" s="46"/>
-      <c r="P38" s="47"/>
-      <c r="S38" s="48"/>
-      <c r="T38" s="46"/>
-      <c r="U38" s="46"/>
-      <c r="V38" s="46"/>
-      <c r="W38" s="46"/>
-      <c r="X38" s="47"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="44"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="44"/>
+      <c r="S38" s="45"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="43"/>
+      <c r="V38" s="43"/>
+      <c r="W38" s="43"/>
+      <c r="X38" s="44"/>
     </row>
     <row r="39" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C39" s="49"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="51"/>
-      <c r="S39" s="49"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="51"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="48"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="47"/>
+      <c r="N39" s="47"/>
+      <c r="O39" s="47"/>
+      <c r="P39" s="48"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="47"/>
+      <c r="U39" s="47"/>
+      <c r="V39" s="47"/>
+      <c r="W39" s="47"/>
+      <c r="X39" s="48"/>
     </row>
     <row r="41" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="42" spans="3:24">
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="53"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="54"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="51"/>
     </row>
     <row r="43" spans="3:24">
-      <c r="C43" s="48"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="47"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="44"/>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
@@ -5817,31 +5871,31 @@
       <c r="P43" s="28"/>
     </row>
     <row r="44" spans="3:24" ht="21" customHeight="1">
-      <c r="C44" s="56">
+      <c r="C44" s="53">
         <f>C25/C5</f>
-        <v>0.54966887417218546</v>
-      </c>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="47"/>
+        <v>0.55844155844155841</v>
+      </c>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="44"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="55" t="s">
+      <c r="L44" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
-      <c r="O44" s="46"/>
+      <c r="M44" s="43"/>
+      <c r="N44" s="43"/>
+      <c r="O44" s="43"/>
       <c r="P44" s="29"/>
     </row>
     <row r="45" spans="3:24">
-      <c r="C45" s="48"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="47"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="44"/>
       <c r="K45" s="28"/>
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
@@ -5850,12 +5904,12 @@
       <c r="P45" s="29"/>
     </row>
     <row r="46" spans="3:24">
-      <c r="C46" s="48"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="47"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="44"/>
       <c r="K46" s="28"/>
       <c r="L46" s="31"/>
       <c r="M46" s="28" t="s">
@@ -5866,12 +5920,12 @@
       <c r="P46" s="28"/>
     </row>
     <row r="47" spans="3:24">
-      <c r="C47" s="48"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="47"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="44"/>
       <c r="K47" s="28"/>
       <c r="L47" s="32"/>
       <c r="M47" s="28" t="s">
@@ -5882,12 +5936,12 @@
       <c r="P47" s="28"/>
     </row>
     <row r="48" spans="3:24">
-      <c r="C48" s="48"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="47"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="44"/>
       <c r="K48" s="28"/>
       <c r="L48" s="33"/>
       <c r="M48" s="28" t="s">
@@ -5898,12 +5952,12 @@
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="3:16">
-      <c r="C49" s="48"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="47"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="44"/>
       <c r="K49" s="28"/>
       <c r="L49" s="34"/>
       <c r="M49" s="28" t="s">
@@ -5914,12 +5968,12 @@
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="3:16">
-      <c r="C50" s="48"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="47"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="44"/>
       <c r="K50" s="28"/>
       <c r="L50" s="35"/>
       <c r="M50" s="28" t="s">
@@ -5930,12 +5984,12 @@
       <c r="P50" s="28"/>
     </row>
     <row r="51" spans="3:16">
-      <c r="C51" s="48"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="47"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="44"/>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -5944,230 +5998,230 @@
       <c r="P51" s="28"/>
     </row>
     <row r="52" spans="3:16">
-      <c r="C52" s="48"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="47"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="44"/>
     </row>
     <row r="53" spans="3:16">
-      <c r="C53" s="48"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="47"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="44"/>
     </row>
     <row r="54" spans="3:16">
-      <c r="C54" s="48"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="47"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="44"/>
     </row>
     <row r="55" spans="3:16">
-      <c r="C55" s="48"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="47"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="44"/>
     </row>
     <row r="56" spans="3:16">
-      <c r="C56" s="48"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="47"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="44"/>
     </row>
     <row r="57" spans="3:16">
-      <c r="C57" s="48"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="47"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="44"/>
     </row>
     <row r="58" spans="3:16" ht="15.75" customHeight="1">
-      <c r="C58" s="49"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
-      <c r="H58" s="51"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="48"/>
     </row>
     <row r="62" spans="3:16">
-      <c r="C62" s="42" t="s">
+      <c r="C62" s="54" t="s">
         <v>585</v>
       </c>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="H62" s="42" t="s">
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="H62" s="54" t="s">
         <v>586</v>
       </c>
-      <c r="I62" s="42"/>
-      <c r="J62" s="42"/>
-      <c r="K62" s="42"/>
-      <c r="M62" s="42" t="s">
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
+      <c r="M62" s="54" t="s">
         <v>587</v>
       </c>
-      <c r="N62" s="42"/>
-      <c r="O62" s="42"/>
-      <c r="P62" s="42"/>
+      <c r="N62" s="54"/>
+      <c r="O62" s="54"/>
+      <c r="P62" s="54"/>
     </row>
     <row r="63" spans="3:16">
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="42"/>
-      <c r="K63" s="42"/>
-      <c r="M63" s="42"/>
-      <c r="N63" s="42"/>
-      <c r="O63" s="42"/>
-      <c r="P63" s="42"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="H63" s="54"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
+      <c r="M63" s="54"/>
+      <c r="N63" s="54"/>
+      <c r="O63" s="54"/>
+      <c r="P63" s="54"/>
     </row>
     <row r="64" spans="3:16">
-      <c r="C64" s="43">
+      <c r="C64" s="55">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
         <v>252</v>
       </c>
-      <c r="D64" s="43"/>
-      <c r="E64" s="43"/>
-      <c r="F64" s="43"/>
-      <c r="H64" s="43">
+      <c r="D64" s="55"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="55"/>
+      <c r="H64" s="55">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
         <v>195</v>
       </c>
-      <c r="I64" s="43"/>
-      <c r="J64" s="43"/>
-      <c r="K64" s="43"/>
-      <c r="M64" s="44">
+      <c r="I64" s="55"/>
+      <c r="J64" s="55"/>
+      <c r="K64" s="55"/>
+      <c r="M64" s="56">
         <f t="shared" ref="M64" si="0">H64/C64</f>
         <v>0.77380952380952384</v>
       </c>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
-      <c r="P64" s="44"/>
+      <c r="N64" s="56"/>
+      <c r="O64" s="56"/>
+      <c r="P64" s="56"/>
     </row>
     <row r="65" spans="3:16">
-      <c r="C65" s="43"/>
-      <c r="D65" s="43"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
-      <c r="H65" s="43"/>
-      <c r="I65" s="43"/>
-      <c r="J65" s="43"/>
-      <c r="K65" s="43"/>
-      <c r="M65" s="44"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="44"/>
-      <c r="P65" s="44"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="H65" s="55"/>
+      <c r="I65" s="55"/>
+      <c r="J65" s="55"/>
+      <c r="K65" s="55"/>
+      <c r="M65" s="56"/>
+      <c r="N65" s="56"/>
+      <c r="O65" s="56"/>
+      <c r="P65" s="56"/>
     </row>
     <row r="66" spans="3:16">
-      <c r="C66" s="43"/>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="H66" s="43"/>
-      <c r="I66" s="43"/>
-      <c r="J66" s="43"/>
-      <c r="K66" s="43"/>
-      <c r="M66" s="44"/>
-      <c r="N66" s="44"/>
-      <c r="O66" s="44"/>
-      <c r="P66" s="44"/>
+      <c r="C66" s="55"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="H66" s="55"/>
+      <c r="I66" s="55"/>
+      <c r="J66" s="55"/>
+      <c r="K66" s="55"/>
+      <c r="M66" s="56"/>
+      <c r="N66" s="56"/>
+      <c r="O66" s="56"/>
+      <c r="P66" s="56"/>
     </row>
     <row r="69" spans="3:16">
-      <c r="C69" s="42" t="s">
+      <c r="C69" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="H69" s="42" t="s">
+      <c r="D69" s="54"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="54"/>
+      <c r="H69" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="I69" s="42"/>
-      <c r="J69" s="42"/>
-      <c r="K69" s="42"/>
-      <c r="M69" s="42" t="s">
+      <c r="I69" s="54"/>
+      <c r="J69" s="54"/>
+      <c r="K69" s="54"/>
+      <c r="M69" s="54" t="s">
         <v>587</v>
       </c>
-      <c r="N69" s="42"/>
-      <c r="O69" s="42"/>
-      <c r="P69" s="42"/>
+      <c r="N69" s="54"/>
+      <c r="O69" s="54"/>
+      <c r="P69" s="54"/>
     </row>
     <row r="70" spans="3:16">
-      <c r="C70" s="42"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="H70" s="42"/>
-      <c r="I70" s="42"/>
-      <c r="J70" s="42"/>
-      <c r="K70" s="42"/>
-      <c r="M70" s="42"/>
-      <c r="N70" s="42"/>
-      <c r="O70" s="42"/>
-      <c r="P70" s="42"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="H70" s="54"/>
+      <c r="I70" s="54"/>
+      <c r="J70" s="54"/>
+      <c r="K70" s="54"/>
+      <c r="M70" s="54"/>
+      <c r="N70" s="54"/>
+      <c r="O70" s="54"/>
+      <c r="P70" s="54"/>
     </row>
     <row r="71" spans="3:16">
-      <c r="C71" s="43">
+      <c r="C71" s="55">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
         <v>73</v>
       </c>
-      <c r="D71" s="43"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="H71" s="43">
+      <c r="D71" s="55"/>
+      <c r="E71" s="55"/>
+      <c r="F71" s="55"/>
+      <c r="H71" s="55">
         <f>COUNTIF(Perfil!I:I,"Si")+COUNTIF(Credenciales!I:I,"Si")+COUNTIF(Videollamadas!I:I,"Si")</f>
         <v>60</v>
       </c>
-      <c r="I71" s="43"/>
-      <c r="J71" s="43"/>
-      <c r="K71" s="43"/>
-      <c r="M71" s="44">
+      <c r="I71" s="55"/>
+      <c r="J71" s="55"/>
+      <c r="K71" s="55"/>
+      <c r="M71" s="56">
         <f t="shared" ref="M71" si="1">H71/C71</f>
         <v>0.82191780821917804</v>
       </c>
-      <c r="N71" s="44"/>
-      <c r="O71" s="44"/>
-      <c r="P71" s="44"/>
+      <c r="N71" s="56"/>
+      <c r="O71" s="56"/>
+      <c r="P71" s="56"/>
     </row>
     <row r="72" spans="3:16">
-      <c r="C72" s="43"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="H72" s="43"/>
-      <c r="I72" s="43"/>
-      <c r="J72" s="43"/>
-      <c r="K72" s="43"/>
-      <c r="M72" s="44"/>
-      <c r="N72" s="44"/>
-      <c r="O72" s="44"/>
-      <c r="P72" s="44"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="55"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="55"/>
+      <c r="M72" s="56"/>
+      <c r="N72" s="56"/>
+      <c r="O72" s="56"/>
+      <c r="P72" s="56"/>
     </row>
     <row r="73" spans="3:16">
-      <c r="C73" s="43"/>
-      <c r="D73" s="43"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
-      <c r="H73" s="43"/>
-      <c r="I73" s="43"/>
-      <c r="J73" s="43"/>
-      <c r="K73" s="43"/>
-      <c r="M73" s="44"/>
-      <c r="N73" s="44"/>
-      <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="55"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="55"/>
+      <c r="J73" s="55"/>
+      <c r="K73" s="55"/>
+      <c r="M73" s="56"/>
+      <c r="N73" s="56"/>
+      <c r="O73" s="56"/>
+      <c r="P73" s="56"/>
     </row>
     <row r="76" spans="3:16">
       <c r="C76" s="36" t="s">
@@ -6176,6 +6230,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C69:F70"/>
+    <mergeCell ref="C71:F73"/>
+    <mergeCell ref="H69:K70"/>
+    <mergeCell ref="H71:K73"/>
+    <mergeCell ref="M69:P70"/>
+    <mergeCell ref="M71:P73"/>
+    <mergeCell ref="C62:F63"/>
+    <mergeCell ref="C64:F66"/>
+    <mergeCell ref="H62:K63"/>
+    <mergeCell ref="H64:K66"/>
+    <mergeCell ref="M62:P63"/>
+    <mergeCell ref="M64:P66"/>
     <mergeCell ref="K5:P19"/>
     <mergeCell ref="K25:P39"/>
     <mergeCell ref="S3:X4"/>
@@ -6191,18 +6257,6 @@
     <mergeCell ref="C3:H4"/>
     <mergeCell ref="C25:H39"/>
     <mergeCell ref="K23:P24"/>
-    <mergeCell ref="C62:F63"/>
-    <mergeCell ref="C64:F66"/>
-    <mergeCell ref="H62:K63"/>
-    <mergeCell ref="H64:K66"/>
-    <mergeCell ref="M62:P63"/>
-    <mergeCell ref="M64:P66"/>
-    <mergeCell ref="C69:F70"/>
-    <mergeCell ref="C71:F73"/>
-    <mergeCell ref="H69:K70"/>
-    <mergeCell ref="H71:K73"/>
-    <mergeCell ref="M69:P70"/>
-    <mergeCell ref="M71:P73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6369,7 +6423,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6B8ACB-ADC5-47C1-A8C9-3AE499AC78D8}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6956,6 +7010,165 @@
         <v>27</v>
       </c>
       <c r="I26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" t="s">
+        <v>786</v>
+      </c>
+      <c r="C27" t="s">
+        <v>787</v>
+      </c>
+      <c r="D27" t="s">
+        <v>788</v>
+      </c>
+      <c r="E27" t="s">
+        <v>789</v>
+      </c>
+      <c r="F27" t="s">
+        <v>790</v>
+      </c>
+      <c r="G27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" t="s">
+        <v>791</v>
+      </c>
+      <c r="D28" t="s">
+        <v>792</v>
+      </c>
+      <c r="E28" t="s">
+        <v>789</v>
+      </c>
+      <c r="F28" t="s">
+        <v>793</v>
+      </c>
+      <c r="G28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" t="s">
+        <v>794</v>
+      </c>
+      <c r="D29" t="s">
+        <v>795</v>
+      </c>
+      <c r="E29" t="s">
+        <v>789</v>
+      </c>
+      <c r="F29" t="s">
+        <v>796</v>
+      </c>
+      <c r="G29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" t="s">
+        <v>797</v>
+      </c>
+      <c r="D30" t="s">
+        <v>788</v>
+      </c>
+      <c r="E30" t="s">
+        <v>798</v>
+      </c>
+      <c r="F30" t="s">
+        <v>799</v>
+      </c>
+      <c r="G30" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" t="s">
+        <v>800</v>
+      </c>
+      <c r="D31" t="s">
+        <v>792</v>
+      </c>
+      <c r="E31" t="s">
+        <v>798</v>
+      </c>
+      <c r="F31" t="s">
+        <v>801</v>
+      </c>
+      <c r="G31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H31" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>270</v>
+      </c>
+      <c r="C32" t="s">
+        <v>802</v>
+      </c>
+      <c r="D32" t="s">
+        <v>792</v>
+      </c>
+      <c r="E32" t="s">
+        <v>798</v>
+      </c>
+      <c r="F32" t="s">
+        <v>803</v>
+      </c>
+      <c r="G32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7014,7 +7227,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="57" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -7023,7 +7236,7 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="61"/>
+      <c r="H2" s="59"/>
       <c r="I2" s="12" t="s">
         <v>27</v>
       </c>
@@ -7032,7 +7245,7 @@
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -7260,7 +7473,7 @@
       <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="60" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -7326,7 +7539,7 @@
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="61" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -7419,7 +7632,7 @@
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="60" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -7620,7 +7833,7 @@
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="61" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -7740,7 +7953,7 @@
       <c r="A32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="60" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="22" t="s">
@@ -7887,7 +8100,7 @@
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="61" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -7940,7 +8153,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="57" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="58"/>
@@ -7949,7 +8162,7 @@
       <c r="E40" s="58"/>
       <c r="F40" s="58"/>
       <c r="G40" s="58"/>
-      <c r="H40" s="61"/>
+      <c r="H40" s="59"/>
       <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
@@ -7958,7 +8171,7 @@
       <c r="A41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="57" t="s">
+      <c r="B41" s="60" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="22" t="s">
@@ -8186,7 +8399,7 @@
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="61" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -8252,7 +8465,7 @@
       <c r="A53" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="60" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="22" t="s">
@@ -8345,7 +8558,7 @@
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="59" t="s">
+      <c r="B57" s="61" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -8546,7 +8759,7 @@
       <c r="A65" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="57" t="s">
+      <c r="B65" s="60" t="s">
         <v>90</v>
       </c>
       <c r="C65" s="22" t="s">
@@ -8666,7 +8879,7 @@
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="59" t="s">
+      <c r="B70" s="61" t="s">
         <v>104</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -8813,7 +9026,7 @@
       <c r="A76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="60" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -8866,7 +9079,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A78" s="60" t="s">
+      <c r="A78" s="57" t="s">
         <v>140</v>
       </c>
       <c r="B78" s="58"/>
@@ -8875,7 +9088,7 @@
       <c r="E78" s="58"/>
       <c r="F78" s="58"/>
       <c r="G78" s="58"/>
-      <c r="H78" s="61"/>
+      <c r="H78" s="59"/>
       <c r="I78" s="12" t="s">
         <v>27</v>
       </c>
@@ -8884,7 +9097,7 @@
       <c r="A79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="59" t="s">
+      <c r="B79" s="61" t="s">
         <v>141</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -8975,7 +9188,7 @@
       <c r="A83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B83" s="57" t="s">
+      <c r="B83" s="60" t="s">
         <v>153</v>
       </c>
       <c r="C83" s="22" t="s">
@@ -9024,7 +9237,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A85" s="60" t="s">
+      <c r="A85" s="57" t="s">
         <v>159</v>
       </c>
       <c r="B85" s="58"/>
@@ -9033,7 +9246,7 @@
       <c r="E85" s="58"/>
       <c r="F85" s="58"/>
       <c r="G85" s="58"/>
-      <c r="H85" s="61"/>
+      <c r="H85" s="59"/>
       <c r="I85" s="12" t="s">
         <v>27</v>
       </c>
@@ -9042,7 +9255,7 @@
       <c r="A86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="59" t="s">
+      <c r="B86" s="61" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -9133,7 +9346,7 @@
       <c r="A90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="57" t="s">
+      <c r="B90" s="60" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -9193,6 +9406,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B86:B88"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="B32:B36"/>
@@ -9209,12 +9428,6 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="B19:B25"/>
     <mergeCell ref="B57:B63"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B86:B88"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="153" priority="564" operator="equal">
@@ -9444,7 +9657,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="57" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -9453,13 +9666,13 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="61"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:9" ht="76.5" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -9600,7 +9813,7 @@
       <c r="A9" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -9718,7 +9931,7 @@
       <c r="A14" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -9865,7 +10078,7 @@
       <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>612</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -10009,7 +10222,7 @@
       <c r="A26" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -10098,7 +10311,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="57" t="s">
         <v>213</v>
       </c>
       <c r="B31" s="58"/>
@@ -10107,13 +10320,13 @@
       <c r="E31" s="58"/>
       <c r="F31" s="58"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="61"/>
+      <c r="H31" s="59"/>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C32" s="18" t="s">
@@ -10254,7 +10467,7 @@
       <c r="A38" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C38" s="22" t="s">
@@ -10372,7 +10585,7 @@
       <c r="A43" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="59" t="s">
+      <c r="B43" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C43" s="18" t="s">
@@ -10519,7 +10732,7 @@
       <c r="A49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="61" t="s">
+      <c r="B49" s="59" t="s">
         <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -10663,7 +10876,7 @@
       <c r="A55" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="61" t="s">
+      <c r="B55" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -10752,7 +10965,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A60" s="60" t="s">
+      <c r="A60" s="57" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="58"/>
@@ -10761,13 +10974,13 @@
       <c r="E60" s="58"/>
       <c r="F60" s="58"/>
       <c r="G60" s="58"/>
-      <c r="H60" s="61"/>
+      <c r="H60" s="59"/>
     </row>
     <row r="61" spans="1:9" ht="76.5" customHeight="1">
       <c r="A61" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="59" t="s">
+      <c r="B61" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -10908,7 +11121,7 @@
       <c r="A67" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B67" s="57" t="s">
+      <c r="B67" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C67" s="22" t="s">
@@ -11026,7 +11239,7 @@
       <c r="A72" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="59" t="s">
+      <c r="B72" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C72" s="18" t="s">
@@ -11173,7 +11386,7 @@
       <c r="A78" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="61" t="s">
+      <c r="B78" s="59" t="s">
         <v>611</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -11317,7 +11530,7 @@
       <c r="A84" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="61" t="s">
+      <c r="B84" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -11406,7 +11619,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A89" s="60" t="s">
+      <c r="A89" s="57" t="s">
         <v>159</v>
       </c>
       <c r="B89" s="58"/>
@@ -11415,13 +11628,13 @@
       <c r="E89" s="58"/>
       <c r="F89" s="58"/>
       <c r="G89" s="58"/>
-      <c r="H89" s="61"/>
+      <c r="H89" s="59"/>
     </row>
     <row r="90" spans="1:9" ht="76.5" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="59" t="s">
+      <c r="B90" s="61" t="s">
         <v>162</v>
       </c>
       <c r="C90" s="18" t="s">
@@ -11562,7 +11775,7 @@
       <c r="A96" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B96" s="57" t="s">
+      <c r="B96" s="60" t="s">
         <v>182</v>
       </c>
       <c r="C96" s="22" t="s">
@@ -11680,7 +11893,7 @@
       <c r="A101" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="59" t="s">
+      <c r="B101" s="61" t="s">
         <v>192</v>
       </c>
       <c r="C101" s="18" t="s">
@@ -11827,7 +12040,7 @@
       <c r="A107" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B107" s="61" t="s">
+      <c r="B107" s="59" t="s">
         <v>591</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -11971,7 +12184,7 @@
       <c r="A113" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B113" s="61" t="s">
+      <c r="B113" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -12061,14 +12274,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B113:B117"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B107:B108"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B96:B99"/>
     <mergeCell ref="A2:H2"/>
@@ -12085,6 +12290,14 @@
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="B43:B47"/>
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="B107:B108"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="111" priority="525" operator="equal">
@@ -12490,7 +12703,7 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="61"/>
+      <c r="B2" s="59"/>
       <c r="C2" s="63"/>
       <c r="D2" s="58"/>
       <c r="E2" s="63"/>
@@ -12499,7 +12712,7 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="198" customHeight="1">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -12531,8 +12744,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
       <c r="C4" s="63" t="s">
         <v>221</v>
       </c>
@@ -12563,7 +12776,7 @@
     </row>
     <row r="5" spans="1:11" ht="45.75" customHeight="1">
       <c r="A5" s="63"/>
-      <c r="B5" s="61"/>
+      <c r="B5" s="59"/>
       <c r="C5" s="63"/>
       <c r="D5" s="58"/>
       <c r="E5" s="6" t="s">
@@ -12575,7 +12788,7 @@
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="121.5" customHeight="1">
-      <c r="B6" s="61"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="63" t="s">
         <v>226</v>
       </c>
@@ -12605,7 +12818,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="45.75" customHeight="1">
-      <c r="B7" s="61"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="63"/>
       <c r="D7" s="58"/>
       <c r="E7" s="13" t="s">
@@ -12617,7 +12830,7 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B8" s="61"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="13" t="s">
         <v>229</v>
       </c>
@@ -12633,7 +12846,7 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B9" s="61"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="13" t="s">
         <v>231</v>
       </c>
@@ -12649,7 +12862,7 @@
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
-      <c r="B10" s="61"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="13" t="s">
         <v>232</v>
       </c>
@@ -12679,7 +12892,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="140.25" customHeight="1">
-      <c r="B11" s="61"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="13" t="s">
         <v>235</v>
       </c>
@@ -12722,7 +12935,7 @@
       <c r="A13" s="62" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="61"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="63"/>
       <c r="D13" s="58"/>
       <c r="E13" s="63"/>
@@ -12921,7 +13134,7 @@
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>239</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -12956,7 +13169,7 @@
       <c r="A4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="61"/>
+      <c r="B4" s="59"/>
       <c r="C4" s="18" t="s">
         <v>244</v>
       </c>
@@ -12989,7 +13202,7 @@
       <c r="A5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="61"/>
+      <c r="B5" s="59"/>
       <c r="C5" s="18" t="s">
         <v>247</v>
       </c>
@@ -13022,7 +13235,7 @@
       <c r="A6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="61"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="18" t="s">
         <v>251</v>
       </c>
@@ -13065,7 +13278,7 @@
       <c r="A8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="60" t="s">
         <v>254</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -13100,7 +13313,7 @@
       <c r="A9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="61"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="22" t="s">
         <v>259</v>
       </c>
@@ -13133,7 +13346,7 @@
       <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="61"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="64" t="s">
         <v>262</v>
       </c>
@@ -13146,7 +13359,7 @@
       <c r="F10" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G10" s="61" t="s">
+      <c r="G10" s="59" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -13166,7 +13379,7 @@
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="61"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="58"/>
       <c r="D11" s="63"/>
       <c r="E11" s="11" t="s">
@@ -13175,7 +13388,7 @@
       <c r="F11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G11" s="61"/>
+      <c r="G11" s="59"/>
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
@@ -13193,7 +13406,7 @@
       <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="61"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="22" t="s">
         <v>267</v>
       </c>
@@ -13226,7 +13439,7 @@
       <c r="A13" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="61"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="22" t="s">
         <v>271</v>
       </c>
@@ -13259,7 +13472,7 @@
       <c r="A14" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B14" s="61"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="22" t="s">
         <v>274</v>
       </c>
@@ -13292,7 +13505,7 @@
       <c r="A15" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="61"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="22" t="s">
         <v>279</v>
       </c>
@@ -13325,7 +13538,7 @@
       <c r="A16" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="22" t="s">
         <v>282</v>
       </c>
@@ -13358,7 +13571,7 @@
       <c r="A17" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="61"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="22" t="s">
         <v>286</v>
       </c>
@@ -13391,7 +13604,7 @@
       <c r="A18" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B18" s="61"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="22" t="s">
         <v>289</v>
       </c>
@@ -13424,7 +13637,7 @@
       <c r="A19" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="22" t="s">
         <v>294</v>
       </c>
@@ -13457,7 +13670,7 @@
       <c r="A20" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="61"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="22" t="s">
         <v>298</v>
       </c>
@@ -13490,7 +13703,7 @@
       <c r="A21" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="61"/>
+      <c r="B21" s="59"/>
       <c r="C21" s="22" t="s">
         <v>303</v>
       </c>
@@ -13523,7 +13736,7 @@
       <c r="A22" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="59"/>
       <c r="C22" s="22" t="s">
         <v>305</v>
       </c>
@@ -13556,7 +13769,7 @@
       <c r="A23" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="61"/>
+      <c r="B23" s="59"/>
       <c r="C23" s="22" t="s">
         <v>310</v>
       </c>
@@ -13589,7 +13802,7 @@
       <c r="A24" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B24" s="61"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="22" t="s">
         <v>314</v>
       </c>
@@ -13622,7 +13835,7 @@
       <c r="A25" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="61"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="22" t="s">
         <v>316</v>
       </c>
@@ -13652,7 +13865,7 @@
       <c r="A26" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="61"/>
+      <c r="B26" s="59"/>
       <c r="C26" s="64" t="s">
         <v>321</v>
       </c>
@@ -13665,10 +13878,10 @@
       <c r="F26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="G26" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="61" t="s">
+      <c r="G26" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="59" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
@@ -13682,7 +13895,7 @@
       <c r="A27" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="61"/>
+      <c r="B27" s="59"/>
       <c r="C27" s="58"/>
       <c r="D27" s="63"/>
       <c r="E27" s="11" t="s">
@@ -13691,14 +13904,14 @@
       <c r="F27" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G27" s="61"/>
+      <c r="G27" s="59"/>
       <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:11" ht="76.5" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B28" s="61"/>
+      <c r="B28" s="59"/>
       <c r="C28" s="22" t="s">
         <v>329</v>
       </c>
@@ -13731,7 +13944,7 @@
       <c r="A29" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B29" s="61"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="22" t="s">
         <v>334</v>
       </c>
@@ -13764,7 +13977,7 @@
       <c r="A30" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B30" s="61"/>
+      <c r="B30" s="59"/>
       <c r="C30" s="22" t="s">
         <v>338</v>
       </c>
@@ -13797,7 +14010,7 @@
       <c r="A31" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B31" s="61"/>
+      <c r="B31" s="59"/>
       <c r="C31" s="22" t="s">
         <v>341</v>
       </c>
@@ -13912,7 +14125,7 @@
       <c r="A36" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="59" t="s">
+      <c r="B36" s="61" t="s">
         <v>349</v>
       </c>
       <c r="C36" s="22" t="s">
@@ -13947,7 +14160,7 @@
       <c r="A37" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="61"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="23" t="s">
         <v>354</v>
       </c>
@@ -14116,7 +14329,7 @@
       <c r="A3" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>359</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -14305,7 +14518,7 @@
       <c r="A10" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="60" t="s">
         <v>385</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -14593,7 +14806,7 @@
       <c r="A20" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="61" t="s">
         <v>422</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -15211,7 +15424,7 @@
       <c r="A40" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="60" t="s">
         <v>505</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -15367,7 +15580,7 @@
       <c r="A46" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B46" s="59" t="s">
+      <c r="B46" s="61" t="s">
         <v>526</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -15645,7 +15858,7 @@
       <c r="A56" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B56" s="46" t="s">
+      <c r="B56" s="43" t="s">
         <v>560</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -15922,13 +16135,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:9" ht="30">
       <c r="A3" t="s">
@@ -16149,13 +16362,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29E309-7E6E-4E39-9E79-7BE971ADC978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089ACAFD-0963-4ED9-B2AA-E9D22267A88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2746" uniqueCount="809">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -2811,6 +2811,21 @@
   </si>
   <si>
     <t>El item Cooper es visible dentro de Beneficios. Verificado en Desktop y Mobile (Android). Nota: el menu de OSDE Adquirente depende del producto real (policyId) de la cuenta, no del segmento -- no automatizado con una asercion fija a proposito, ver docs/conocimiento-sistema.md.</t>
+  </si>
+  <si>
+    <t>TS-06 Estado del plan (IMAS-4408)</t>
+  </si>
+  <si>
+    <t>Cuenta cuyo unico plan no esta operable no muestra ninguna credencial ni permite operar</t>
+  </si>
+  <si>
+    <t>Usuario cuyo unico plan paso a Inactivo (falta de pago) o fue Dado de baja definitivamente.</t>
+  </si>
+  <si>
+    <t>1. Cargar Home, Mascotas, Planes y coberturas. 2. Intentar agendar videollamada. 3. Intentar iniciar un reintegro nuevo.</t>
+  </si>
+  <si>
+    <t>Ninguna pantalla muestra credencial ni permite operar (Home vacio, Mascotas sin tarjetas, Planes No hay planes por el momento, Videollamada bloquea con Completa su credencial, Reintegros No hay mascotas registradas). Login sigue funcionando con normalidad. Simulado con mock de red (page.route) sobre pets/my-products y reintegros/mascotas, sin depender de una cuenta real con este estado (IMP-015: no hay self-service para conseguirla, escalado a Oscar 2026-08-31, respuesta no por ahora).</t>
   </si>
 </sst>
 </file>
@@ -3242,6 +3257,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3262,28 +3286,19 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5135,734 +5150,734 @@
   <sheetData>
     <row r="2" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="3" spans="3:24">
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51"/>
-      <c r="K3" s="49" t="s">
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
+      <c r="K3" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="51"/>
-      <c r="S3" s="49" t="s">
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="54"/>
+      <c r="S3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="51"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="54"/>
     </row>
     <row r="4" spans="3:24">
-      <c r="C4" s="45"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="44"/>
-      <c r="S4" s="45"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="44"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="47"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="47"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="47"/>
     </row>
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C5" s="42">
+      <c r="C5" s="45">
         <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C199,Credenciales!C3:C199,Videollamadas!C3:C199,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199,'Funcionalidades Pendientes'!C2:C199)</f>
-        <v>308</v>
-      </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
-      <c r="K5" s="42">
+        <v>309</v>
+      </c>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+      <c r="K5" s="45">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!H:H,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")+COUNTIF('Funcionalidades Pendientes'!H:H,"Si")</f>
-        <v>228</v>
-      </c>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="44"/>
-      <c r="S5" s="53">
+        <v>229</v>
+      </c>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="47"/>
+      <c r="S5" s="56">
         <f>K5/C5</f>
-        <v>0.74025974025974028</v>
-      </c>
-      <c r="T5" s="43"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="43"/>
-      <c r="X5" s="44"/>
+        <v>0.74110032362459544</v>
+      </c>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="47"/>
     </row>
     <row r="6" spans="3:24">
-      <c r="C6" s="45"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="44"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="44"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="47"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="47"/>
     </row>
     <row r="7" spans="3:24">
-      <c r="C7" s="45"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="44"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="43"/>
-      <c r="X7" s="44"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="47"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="47"/>
     </row>
     <row r="8" spans="3:24">
-      <c r="C8" s="45"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="44"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="43"/>
-      <c r="X8" s="44"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="47"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="47"/>
     </row>
     <row r="9" spans="3:24">
-      <c r="C9" s="45"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="44"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="44"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="47"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="47"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="47"/>
     </row>
     <row r="10" spans="3:24">
-      <c r="C10" s="45"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="44"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="44"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="47"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="47"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="47"/>
     </row>
     <row r="11" spans="3:24">
-      <c r="C11" s="45"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="44"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="44"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="44"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="47"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="47"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="47"/>
     </row>
     <row r="12" spans="3:24">
-      <c r="C12" s="45"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="44"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="44"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="47"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="47"/>
     </row>
     <row r="13" spans="3:24">
-      <c r="C13" s="45"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="44"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="44"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="47"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="46"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="47"/>
     </row>
     <row r="14" spans="3:24">
-      <c r="C14" s="45"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="44"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="44"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="47"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="47"/>
     </row>
     <row r="15" spans="3:24">
-      <c r="C15" s="45"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="44"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="44"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="47"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="47"/>
     </row>
     <row r="16" spans="3:24">
-      <c r="C16" s="45"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="44"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="44"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="47"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="47"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="47"/>
     </row>
     <row r="17" spans="3:24">
-      <c r="C17" s="45"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="44"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="44"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="43"/>
-      <c r="X17" s="44"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="47"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="47"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="47"/>
     </row>
     <row r="18" spans="3:24">
-      <c r="C18" s="45"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="44"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="44"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="44"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="47"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="47"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="47"/>
     </row>
     <row r="19" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C19" s="46"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="48"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="51"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="51"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="50"/>
+      <c r="X19" s="51"/>
     </row>
     <row r="22" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="23" spans="3:24">
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="51"/>
-      <c r="K23" s="49" t="s">
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="54"/>
+      <c r="K23" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="51"/>
-      <c r="S23" s="49" t="s">
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="54"/>
+      <c r="S23" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="51"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
+      <c r="V23" s="53"/>
+      <c r="W23" s="53"/>
+      <c r="X23" s="54"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="45"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="44"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="43"/>
-      <c r="X24" s="44"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="47"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="47"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="47"/>
     </row>
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C25" s="42">
+      <c r="C25" s="45">
         <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")+COUNTIF('Funcionalidades Pendientes'!G:G,"Si")</f>
-        <v>172</v>
-      </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44"/>
-      <c r="K25" s="42">
+        <v>173</v>
+      </c>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="47"/>
+      <c r="K25" s="45">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")+COUNTIFS('Funcionalidades Pendientes'!G:G,"Si",'Funcionalidades Pendientes'!H:H,"Si")</f>
-        <v>138</v>
-      </c>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="44"/>
-      <c r="S25" s="53">
+        <v>139</v>
+      </c>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="47"/>
+      <c r="S25" s="56">
         <f>K25/C25</f>
-        <v>0.80232558139534882</v>
-      </c>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="43"/>
-      <c r="X25" s="44"/>
+        <v>0.80346820809248554</v>
+      </c>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="47"/>
     </row>
     <row r="26" spans="3:24">
-      <c r="C26" s="45"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="44"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="X26" s="44"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="47"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="47"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="47"/>
     </row>
     <row r="27" spans="3:24">
-      <c r="C27" s="45"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="44"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="43"/>
-      <c r="U27" s="43"/>
-      <c r="V27" s="43"/>
-      <c r="W27" s="43"/>
-      <c r="X27" s="44"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="47"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="47"/>
     </row>
     <row r="28" spans="3:24">
-      <c r="C28" s="45"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="44"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="43"/>
-      <c r="W28" s="43"/>
-      <c r="X28" s="44"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="47"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="47"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="47"/>
     </row>
     <row r="29" spans="3:24">
-      <c r="C29" s="45"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="44"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="44"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="43"/>
-      <c r="V29" s="43"/>
-      <c r="W29" s="43"/>
-      <c r="X29" s="44"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="47"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="47"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="47"/>
     </row>
     <row r="30" spans="3:24">
-      <c r="C30" s="45"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="44"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="44"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="43"/>
-      <c r="U30" s="43"/>
-      <c r="V30" s="43"/>
-      <c r="W30" s="43"/>
-      <c r="X30" s="44"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="47"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="47"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="47"/>
     </row>
     <row r="31" spans="3:24">
-      <c r="C31" s="45"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="44"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="44"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="43"/>
-      <c r="V31" s="43"/>
-      <c r="W31" s="43"/>
-      <c r="X31" s="44"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="47"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="47"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="47"/>
     </row>
     <row r="32" spans="3:24">
-      <c r="C32" s="45"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="44"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="43"/>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="44"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="43"/>
-      <c r="U32" s="43"/>
-      <c r="V32" s="43"/>
-      <c r="W32" s="43"/>
-      <c r="X32" s="44"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="47"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
+      <c r="P32" s="47"/>
+      <c r="S32" s="48"/>
+      <c r="T32" s="46"/>
+      <c r="U32" s="46"/>
+      <c r="V32" s="46"/>
+      <c r="W32" s="46"/>
+      <c r="X32" s="47"/>
     </row>
     <row r="33" spans="3:24">
-      <c r="C33" s="45"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="44"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="44"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="43"/>
-      <c r="V33" s="43"/>
-      <c r="W33" s="43"/>
-      <c r="X33" s="44"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="47"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="47"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="47"/>
     </row>
     <row r="34" spans="3:24">
-      <c r="C34" s="45"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="44"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="44"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="43"/>
-      <c r="U34" s="43"/>
-      <c r="V34" s="43"/>
-      <c r="W34" s="43"/>
-      <c r="X34" s="44"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="47"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="47"/>
+      <c r="S34" s="48"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="V34" s="46"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="47"/>
     </row>
     <row r="35" spans="3:24">
-      <c r="C35" s="45"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="44"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="44"/>
-      <c r="S35" s="45"/>
-      <c r="T35" s="43"/>
-      <c r="U35" s="43"/>
-      <c r="V35" s="43"/>
-      <c r="W35" s="43"/>
-      <c r="X35" s="44"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="47"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="47"/>
+      <c r="S35" s="48"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="46"/>
+      <c r="V35" s="46"/>
+      <c r="W35" s="46"/>
+      <c r="X35" s="47"/>
     </row>
     <row r="36" spans="3:24">
-      <c r="C36" s="45"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="44"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="44"/>
-      <c r="S36" s="45"/>
-      <c r="T36" s="43"/>
-      <c r="U36" s="43"/>
-      <c r="V36" s="43"/>
-      <c r="W36" s="43"/>
-      <c r="X36" s="44"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="47"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="47"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="46"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="47"/>
     </row>
     <row r="37" spans="3:24">
-      <c r="C37" s="45"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="44"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="44"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="43"/>
-      <c r="U37" s="43"/>
-      <c r="V37" s="43"/>
-      <c r="W37" s="43"/>
-      <c r="X37" s="44"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="47"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="47"/>
+      <c r="S37" s="48"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="46"/>
+      <c r="W37" s="46"/>
+      <c r="X37" s="47"/>
     </row>
     <row r="38" spans="3:24">
-      <c r="C38" s="45"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="44"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="43"/>
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
-      <c r="O38" s="43"/>
-      <c r="P38" s="44"/>
-      <c r="S38" s="45"/>
-      <c r="T38" s="43"/>
-      <c r="U38" s="43"/>
-      <c r="V38" s="43"/>
-      <c r="W38" s="43"/>
-      <c r="X38" s="44"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="47"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="47"/>
+      <c r="S38" s="48"/>
+      <c r="T38" s="46"/>
+      <c r="U38" s="46"/>
+      <c r="V38" s="46"/>
+      <c r="W38" s="46"/>
+      <c r="X38" s="47"/>
     </row>
     <row r="39" spans="3:24" ht="15.75" customHeight="1">
-      <c r="C39" s="46"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="47"/>
-      <c r="O39" s="47"/>
-      <c r="P39" s="48"/>
-      <c r="S39" s="46"/>
-      <c r="T39" s="47"/>
-      <c r="U39" s="47"/>
-      <c r="V39" s="47"/>
-      <c r="W39" s="47"/>
-      <c r="X39" s="48"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="51"/>
+      <c r="K39" s="49"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="50"/>
+      <c r="P39" s="51"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="50"/>
+      <c r="V39" s="50"/>
+      <c r="W39" s="50"/>
+      <c r="X39" s="51"/>
     </row>
     <row r="41" spans="3:24" ht="15.75" customHeight="1"/>
     <row r="42" spans="3:24">
-      <c r="C42" s="49" t="s">
+      <c r="C42" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="51"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="54"/>
     </row>
     <row r="43" spans="3:24">
-      <c r="C43" s="45"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="44"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="47"/>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
@@ -5871,31 +5886,31 @@
       <c r="P43" s="28"/>
     </row>
     <row r="44" spans="3:24" ht="21" customHeight="1">
-      <c r="C44" s="53">
+      <c r="C44" s="56">
         <f>C25/C5</f>
-        <v>0.55844155844155841</v>
-      </c>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="44"/>
+        <v>0.55987055016181231</v>
+      </c>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="47"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="52" t="s">
+      <c r="L44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="M44" s="43"/>
-      <c r="N44" s="43"/>
-      <c r="O44" s="43"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="46"/>
+      <c r="O44" s="46"/>
       <c r="P44" s="29"/>
     </row>
     <row r="45" spans="3:24">
-      <c r="C45" s="45"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="44"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="47"/>
       <c r="K45" s="28"/>
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
@@ -5904,12 +5919,12 @@
       <c r="P45" s="29"/>
     </row>
     <row r="46" spans="3:24">
-      <c r="C46" s="45"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="44"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="47"/>
       <c r="K46" s="28"/>
       <c r="L46" s="31"/>
       <c r="M46" s="28" t="s">
@@ -5920,12 +5935,12 @@
       <c r="P46" s="28"/>
     </row>
     <row r="47" spans="3:24">
-      <c r="C47" s="45"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="44"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="47"/>
       <c r="K47" s="28"/>
       <c r="L47" s="32"/>
       <c r="M47" s="28" t="s">
@@ -5936,12 +5951,12 @@
       <c r="P47" s="28"/>
     </row>
     <row r="48" spans="3:24">
-      <c r="C48" s="45"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="44"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="47"/>
       <c r="K48" s="28"/>
       <c r="L48" s="33"/>
       <c r="M48" s="28" t="s">
@@ -5952,12 +5967,12 @@
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="3:16">
-      <c r="C49" s="45"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="44"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="47"/>
       <c r="K49" s="28"/>
       <c r="L49" s="34"/>
       <c r="M49" s="28" t="s">
@@ -5968,12 +5983,12 @@
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="3:16">
-      <c r="C50" s="45"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="44"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="47"/>
       <c r="K50" s="28"/>
       <c r="L50" s="35"/>
       <c r="M50" s="28" t="s">
@@ -5984,12 +5999,12 @@
       <c r="P50" s="28"/>
     </row>
     <row r="51" spans="3:16">
-      <c r="C51" s="45"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="44"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="47"/>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -5998,230 +6013,230 @@
       <c r="P51" s="28"/>
     </row>
     <row r="52" spans="3:16">
-      <c r="C52" s="45"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="44"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="47"/>
     </row>
     <row r="53" spans="3:16">
-      <c r="C53" s="45"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="44"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="47"/>
     </row>
     <row r="54" spans="3:16">
-      <c r="C54" s="45"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="44"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="47"/>
     </row>
     <row r="55" spans="3:16">
-      <c r="C55" s="45"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="44"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="47"/>
     </row>
     <row r="56" spans="3:16">
-      <c r="C56" s="45"/>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="43"/>
-      <c r="H56" s="44"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="47"/>
     </row>
     <row r="57" spans="3:16">
-      <c r="C57" s="45"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="44"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="47"/>
     </row>
     <row r="58" spans="3:16" ht="15.75" customHeight="1">
-      <c r="C58" s="46"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="48"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
+      <c r="H58" s="51"/>
     </row>
     <row r="62" spans="3:16">
-      <c r="C62" s="54" t="s">
+      <c r="C62" s="42" t="s">
         <v>585</v>
       </c>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="54"/>
-      <c r="H62" s="54" t="s">
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="H62" s="42" t="s">
         <v>586</v>
       </c>
-      <c r="I62" s="54"/>
-      <c r="J62" s="54"/>
-      <c r="K62" s="54"/>
-      <c r="M62" s="54" t="s">
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
+      <c r="M62" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="N62" s="54"/>
-      <c r="O62" s="54"/>
-      <c r="P62" s="54"/>
+      <c r="N62" s="42"/>
+      <c r="O62" s="42"/>
+      <c r="P62" s="42"/>
     </row>
     <row r="63" spans="3:16">
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="54"/>
-      <c r="H63" s="54"/>
-      <c r="I63" s="54"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
-      <c r="M63" s="54"/>
-      <c r="N63" s="54"/>
-      <c r="O63" s="54"/>
-      <c r="P63" s="54"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
+      <c r="M63" s="42"/>
+      <c r="N63" s="42"/>
+      <c r="O63" s="42"/>
+      <c r="P63" s="42"/>
     </row>
     <row r="64" spans="3:16">
-      <c r="C64" s="55">
+      <c r="C64" s="43">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
-        <v>252</v>
-      </c>
-      <c r="D64" s="55"/>
-      <c r="E64" s="55"/>
-      <c r="F64" s="55"/>
-      <c r="H64" s="55">
+        <v>253</v>
+      </c>
+      <c r="D64" s="43"/>
+      <c r="E64" s="43"/>
+      <c r="F64" s="43"/>
+      <c r="H64" s="43">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
-        <v>195</v>
-      </c>
-      <c r="I64" s="55"/>
-      <c r="J64" s="55"/>
-      <c r="K64" s="55"/>
-      <c r="M64" s="56">
+        <v>196</v>
+      </c>
+      <c r="I64" s="43"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="43"/>
+      <c r="M64" s="44">
         <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.77380952380952384</v>
-      </c>
-      <c r="N64" s="56"/>
-      <c r="O64" s="56"/>
-      <c r="P64" s="56"/>
+        <v>0.77470355731225293</v>
+      </c>
+      <c r="N64" s="44"/>
+      <c r="O64" s="44"/>
+      <c r="P64" s="44"/>
     </row>
     <row r="65" spans="3:16">
-      <c r="C65" s="55"/>
-      <c r="D65" s="55"/>
-      <c r="E65" s="55"/>
-      <c r="F65" s="55"/>
-      <c r="H65" s="55"/>
-      <c r="I65" s="55"/>
-      <c r="J65" s="55"/>
-      <c r="K65" s="55"/>
-      <c r="M65" s="56"/>
-      <c r="N65" s="56"/>
-      <c r="O65" s="56"/>
-      <c r="P65" s="56"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="43"/>
+      <c r="H65" s="43"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="44"/>
+      <c r="P65" s="44"/>
     </row>
     <row r="66" spans="3:16">
-      <c r="C66" s="55"/>
-      <c r="D66" s="55"/>
-      <c r="E66" s="55"/>
-      <c r="F66" s="55"/>
-      <c r="H66" s="55"/>
-      <c r="I66" s="55"/>
-      <c r="J66" s="55"/>
-      <c r="K66" s="55"/>
-      <c r="M66" s="56"/>
-      <c r="N66" s="56"/>
-      <c r="O66" s="56"/>
-      <c r="P66" s="56"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="43"/>
+      <c r="M66" s="44"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="44"/>
+      <c r="P66" s="44"/>
     </row>
     <row r="69" spans="3:16">
-      <c r="C69" s="54" t="s">
+      <c r="C69" s="42" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="54"/>
-      <c r="E69" s="54"/>
-      <c r="F69" s="54"/>
-      <c r="H69" s="54" t="s">
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="H69" s="42" t="s">
         <v>589</v>
       </c>
-      <c r="I69" s="54"/>
-      <c r="J69" s="54"/>
-      <c r="K69" s="54"/>
-      <c r="M69" s="54" t="s">
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
+      <c r="M69" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="N69" s="54"/>
-      <c r="O69" s="54"/>
-      <c r="P69" s="54"/>
+      <c r="N69" s="42"/>
+      <c r="O69" s="42"/>
+      <c r="P69" s="42"/>
     </row>
     <row r="70" spans="3:16">
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="54"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="54"/>
-      <c r="J70" s="54"/>
-      <c r="K70" s="54"/>
-      <c r="M70" s="54"/>
-      <c r="N70" s="54"/>
-      <c r="O70" s="54"/>
-      <c r="P70" s="54"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
+      <c r="M70" s="42"/>
+      <c r="N70" s="42"/>
+      <c r="O70" s="42"/>
+      <c r="P70" s="42"/>
     </row>
     <row r="71" spans="3:16">
-      <c r="C71" s="55">
+      <c r="C71" s="43">
         <f>COUNTIF(Perfil!K:K,"Si")+COUNTIF(Credenciales!K:K,"Si")+COUNTIF(Videollamadas!K:K,"Si")</f>
-        <v>73</v>
-      </c>
-      <c r="D71" s="55"/>
-      <c r="E71" s="55"/>
-      <c r="F71" s="55"/>
-      <c r="H71" s="55">
+        <v>74</v>
+      </c>
+      <c r="D71" s="43"/>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
+      <c r="H71" s="43">
         <f>COUNTIF(Perfil!I:I,"Si")+COUNTIF(Credenciales!I:I,"Si")+COUNTIF(Videollamadas!I:I,"Si")</f>
-        <v>60</v>
-      </c>
-      <c r="I71" s="55"/>
-      <c r="J71" s="55"/>
-      <c r="K71" s="55"/>
-      <c r="M71" s="56">
+        <v>61</v>
+      </c>
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+      <c r="M71" s="44">
         <f t="shared" ref="M71" si="1">H71/C71</f>
-        <v>0.82191780821917804</v>
-      </c>
-      <c r="N71" s="56"/>
-      <c r="O71" s="56"/>
-      <c r="P71" s="56"/>
+        <v>0.82432432432432434</v>
+      </c>
+      <c r="N71" s="44"/>
+      <c r="O71" s="44"/>
+      <c r="P71" s="44"/>
     </row>
     <row r="72" spans="3:16">
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="55"/>
-      <c r="H72" s="55"/>
-      <c r="I72" s="55"/>
-      <c r="J72" s="55"/>
-      <c r="K72" s="55"/>
-      <c r="M72" s="56"/>
-      <c r="N72" s="56"/>
-      <c r="O72" s="56"/>
-      <c r="P72" s="56"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+      <c r="M72" s="44"/>
+      <c r="N72" s="44"/>
+      <c r="O72" s="44"/>
+      <c r="P72" s="44"/>
     </row>
     <row r="73" spans="3:16">
-      <c r="C73" s="55"/>
-      <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="55"/>
-      <c r="H73" s="55"/>
-      <c r="I73" s="55"/>
-      <c r="J73" s="55"/>
-      <c r="K73" s="55"/>
-      <c r="M73" s="56"/>
-      <c r="N73" s="56"/>
-      <c r="O73" s="56"/>
-      <c r="P73" s="56"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="H73" s="43"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="43"/>
+      <c r="M73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
     </row>
     <row r="76" spans="3:16">
       <c r="C76" s="36" t="s">
@@ -6230,18 +6245,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C69:F70"/>
-    <mergeCell ref="C71:F73"/>
-    <mergeCell ref="H69:K70"/>
-    <mergeCell ref="H71:K73"/>
-    <mergeCell ref="M69:P70"/>
-    <mergeCell ref="M71:P73"/>
-    <mergeCell ref="C62:F63"/>
-    <mergeCell ref="C64:F66"/>
-    <mergeCell ref="H62:K63"/>
-    <mergeCell ref="H64:K66"/>
-    <mergeCell ref="M62:P63"/>
-    <mergeCell ref="M64:P66"/>
     <mergeCell ref="K5:P19"/>
     <mergeCell ref="K25:P39"/>
     <mergeCell ref="S3:X4"/>
@@ -6257,6 +6260,18 @@
     <mergeCell ref="C3:H4"/>
     <mergeCell ref="C25:H39"/>
     <mergeCell ref="K23:P24"/>
+    <mergeCell ref="C62:F63"/>
+    <mergeCell ref="C64:F66"/>
+    <mergeCell ref="H62:K63"/>
+    <mergeCell ref="H64:K66"/>
+    <mergeCell ref="M62:P63"/>
+    <mergeCell ref="M64:P66"/>
+    <mergeCell ref="C69:F70"/>
+    <mergeCell ref="C71:F73"/>
+    <mergeCell ref="H69:K70"/>
+    <mergeCell ref="H71:K73"/>
+    <mergeCell ref="M69:P70"/>
+    <mergeCell ref="M71:P73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7227,7 +7242,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -7236,7 +7251,7 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="H2" s="61"/>
       <c r="I2" s="12" t="s">
         <v>27</v>
       </c>
@@ -7245,7 +7260,7 @@
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -7473,7 +7488,7 @@
       <c r="A12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="57" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -7539,7 +7554,7 @@
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="59" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -7632,7 +7647,7 @@
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="57" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -7833,7 +7848,7 @@
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="59" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -7953,7 +7968,7 @@
       <c r="A32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="57" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="22" t="s">
@@ -8100,7 +8115,7 @@
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="59" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -8153,7 +8168,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="60" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="58"/>
@@ -8162,7 +8177,7 @@
       <c r="E40" s="58"/>
       <c r="F40" s="58"/>
       <c r="G40" s="58"/>
-      <c r="H40" s="59"/>
+      <c r="H40" s="61"/>
       <c r="I40" s="12" t="s">
         <v>27</v>
       </c>
@@ -8171,7 +8186,7 @@
       <c r="A41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="57" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="22" t="s">
@@ -8399,7 +8414,7 @@
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="61" t="s">
+      <c r="B50" s="59" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -8465,7 +8480,7 @@
       <c r="A53" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="57" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="22" t="s">
@@ -8558,7 +8573,7 @@
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="61" t="s">
+      <c r="B57" s="59" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -8759,7 +8774,7 @@
       <c r="A65" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="57" t="s">
         <v>90</v>
       </c>
       <c r="C65" s="22" t="s">
@@ -8879,7 +8894,7 @@
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="61" t="s">
+      <c r="B70" s="59" t="s">
         <v>104</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -9026,7 +9041,7 @@
       <c r="A76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="60" t="s">
+      <c r="B76" s="57" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -9079,7 +9094,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A78" s="57" t="s">
+      <c r="A78" s="60" t="s">
         <v>140</v>
       </c>
       <c r="B78" s="58"/>
@@ -9088,7 +9103,7 @@
       <c r="E78" s="58"/>
       <c r="F78" s="58"/>
       <c r="G78" s="58"/>
-      <c r="H78" s="59"/>
+      <c r="H78" s="61"/>
       <c r="I78" s="12" t="s">
         <v>27</v>
       </c>
@@ -9097,7 +9112,7 @@
       <c r="A79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="61" t="s">
+      <c r="B79" s="59" t="s">
         <v>141</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -9188,7 +9203,7 @@
       <c r="A83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B83" s="60" t="s">
+      <c r="B83" s="57" t="s">
         <v>153</v>
       </c>
       <c r="C83" s="22" t="s">
@@ -9237,7 +9252,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A85" s="57" t="s">
+      <c r="A85" s="60" t="s">
         <v>159</v>
       </c>
       <c r="B85" s="58"/>
@@ -9246,7 +9261,7 @@
       <c r="E85" s="58"/>
       <c r="F85" s="58"/>
       <c r="G85" s="58"/>
-      <c r="H85" s="59"/>
+      <c r="H85" s="61"/>
       <c r="I85" s="12" t="s">
         <v>27</v>
       </c>
@@ -9255,7 +9270,7 @@
       <c r="A86" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="61" t="s">
+      <c r="B86" s="59" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -9346,7 +9361,7 @@
       <c r="A90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B90" s="60" t="s">
+      <c r="B90" s="57" t="s">
         <v>153</v>
       </c>
       <c r="C90" s="22" t="s">
@@ -9406,12 +9421,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B86:B88"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A85:H85"/>
     <mergeCell ref="B32:B36"/>
@@ -9428,6 +9437,12 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="B19:B25"/>
     <mergeCell ref="B57:B63"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B86:B88"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="153" priority="564" operator="equal">
@@ -9657,7 +9672,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="58"/>
@@ -9666,13 +9681,13 @@
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="1:9" ht="76.5" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -9813,7 +9828,7 @@
       <c r="A9" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -9931,7 +9946,7 @@
       <c r="A14" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -10078,7 +10093,7 @@
       <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="61" t="s">
         <v>612</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -10222,7 +10237,7 @@
       <c r="A26" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -10311,7 +10326,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="60" t="s">
         <v>213</v>
       </c>
       <c r="B31" s="58"/>
@@ -10320,13 +10335,13 @@
       <c r="E31" s="58"/>
       <c r="F31" s="58"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="59"/>
+      <c r="H31" s="61"/>
     </row>
     <row r="32" spans="1:9" ht="76.5" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C32" s="18" t="s">
@@ -10467,7 +10482,7 @@
       <c r="A38" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C38" s="22" t="s">
@@ -10585,7 +10600,7 @@
       <c r="A43" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C43" s="18" t="s">
@@ -10732,7 +10747,7 @@
       <c r="A49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="59" t="s">
+      <c r="B49" s="61" t="s">
         <v>612</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -10876,7 +10891,7 @@
       <c r="A55" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="59" t="s">
+      <c r="B55" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -10965,7 +10980,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A60" s="57" t="s">
+      <c r="A60" s="60" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="58"/>
@@ -10974,13 +10989,13 @@
       <c r="E60" s="58"/>
       <c r="F60" s="58"/>
       <c r="G60" s="58"/>
-      <c r="H60" s="59"/>
+      <c r="H60" s="61"/>
     </row>
     <row r="61" spans="1:9" ht="76.5" customHeight="1">
       <c r="A61" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="61" t="s">
+      <c r="B61" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -11121,7 +11136,7 @@
       <c r="A67" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B67" s="60" t="s">
+      <c r="B67" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C67" s="22" t="s">
@@ -11239,7 +11254,7 @@
       <c r="A72" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="61" t="s">
+      <c r="B72" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C72" s="18" t="s">
@@ -11386,7 +11401,7 @@
       <c r="A78" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="59" t="s">
+      <c r="B78" s="61" t="s">
         <v>611</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -11530,7 +11545,7 @@
       <c r="A84" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="59" t="s">
+      <c r="B84" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -11619,7 +11634,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A89" s="57" t="s">
+      <c r="A89" s="60" t="s">
         <v>159</v>
       </c>
       <c r="B89" s="58"/>
@@ -11628,13 +11643,13 @@
       <c r="E89" s="58"/>
       <c r="F89" s="58"/>
       <c r="G89" s="58"/>
-      <c r="H89" s="59"/>
+      <c r="H89" s="61"/>
     </row>
     <row r="90" spans="1:9" ht="76.5" customHeight="1">
       <c r="A90" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="61" t="s">
+      <c r="B90" s="59" t="s">
         <v>162</v>
       </c>
       <c r="C90" s="18" t="s">
@@ -11775,7 +11790,7 @@
       <c r="A96" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B96" s="60" t="s">
+      <c r="B96" s="57" t="s">
         <v>182</v>
       </c>
       <c r="C96" s="22" t="s">
@@ -11893,7 +11908,7 @@
       <c r="A101" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B101" s="61" t="s">
+      <c r="B101" s="59" t="s">
         <v>192</v>
       </c>
       <c r="C101" s="18" t="s">
@@ -12040,7 +12055,7 @@
       <c r="A107" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B107" s="59" t="s">
+      <c r="B107" s="61" t="s">
         <v>591</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -12184,7 +12199,7 @@
       <c r="A113" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B113" s="59" t="s">
+      <c r="B113" s="61" t="s">
         <v>208</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -12274,6 +12289,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="B107:B108"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B96:B99"/>
     <mergeCell ref="A2:H2"/>
@@ -12290,14 +12313,6 @@
     <mergeCell ref="B61:B65"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="B43:B47"/>
-    <mergeCell ref="B113:B117"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B107:B108"/>
   </mergeCells>
   <conditionalFormatting sqref="G1">
     <cfRule type="cellIs" dxfId="111" priority="525" operator="equal">
@@ -12703,7 +12718,7 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="59"/>
+      <c r="B2" s="61"/>
       <c r="C2" s="63"/>
       <c r="D2" s="58"/>
       <c r="E2" s="63"/>
@@ -12712,7 +12727,7 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="198" customHeight="1">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -12744,8 +12759,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="59"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="63" t="s">
         <v>221</v>
       </c>
@@ -12776,7 +12791,7 @@
     </row>
     <row r="5" spans="1:11" ht="45.75" customHeight="1">
       <c r="A5" s="63"/>
-      <c r="B5" s="59"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="63"/>
       <c r="D5" s="58"/>
       <c r="E5" s="6" t="s">
@@ -12788,7 +12803,7 @@
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="121.5" customHeight="1">
-      <c r="B6" s="59"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="63" t="s">
         <v>226</v>
       </c>
@@ -12818,7 +12833,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="45.75" customHeight="1">
-      <c r="B7" s="59"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="63"/>
       <c r="D7" s="58"/>
       <c r="E7" s="13" t="s">
@@ -12830,7 +12845,7 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B8" s="59"/>
+      <c r="B8" s="61"/>
       <c r="C8" s="13" t="s">
         <v>229</v>
       </c>
@@ -12846,7 +12861,7 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="30.75" customHeight="1">
-      <c r="B9" s="59"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="13" t="s">
         <v>231</v>
       </c>
@@ -12862,7 +12877,7 @@
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
-      <c r="B10" s="59"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="13" t="s">
         <v>232</v>
       </c>
@@ -12892,7 +12907,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="140.25" customHeight="1">
-      <c r="B11" s="59"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="13" t="s">
         <v>235</v>
       </c>
@@ -12935,7 +12950,7 @@
       <c r="A13" s="62" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="59"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="63"/>
       <c r="D13" s="58"/>
       <c r="E13" s="63"/>
@@ -13069,7 +13084,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12" customWidth="1"/>
@@ -13134,7 +13149,7 @@
       <c r="A3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>239</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -13169,7 +13184,7 @@
       <c r="A4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="59"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="18" t="s">
         <v>244</v>
       </c>
@@ -13202,7 +13217,7 @@
       <c r="A5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="59"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="18" t="s">
         <v>247</v>
       </c>
@@ -13235,7 +13250,7 @@
       <c r="A6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B6" s="59"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="18" t="s">
         <v>251</v>
       </c>
@@ -13278,7 +13293,7 @@
       <c r="A8" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="57" t="s">
         <v>254</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -13313,7 +13328,7 @@
       <c r="A9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="59"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="22" t="s">
         <v>259</v>
       </c>
@@ -13346,7 +13361,7 @@
       <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="59"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="64" t="s">
         <v>262</v>
       </c>
@@ -13359,7 +13374,7 @@
       <c r="F10" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="61" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -13379,7 +13394,7 @@
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="59"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="58"/>
       <c r="D11" s="63"/>
       <c r="E11" s="11" t="s">
@@ -13388,7 +13403,7 @@
       <c r="F11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G11" s="59"/>
+      <c r="G11" s="61"/>
       <c r="H11" s="12" t="s">
         <v>27</v>
       </c>
@@ -13406,7 +13421,7 @@
       <c r="A12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="59"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="22" t="s">
         <v>267</v>
       </c>
@@ -13439,7 +13454,7 @@
       <c r="A13" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="59"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="22" t="s">
         <v>271</v>
       </c>
@@ -13472,7 +13487,7 @@
       <c r="A14" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B14" s="59"/>
+      <c r="B14" s="61"/>
       <c r="C14" s="22" t="s">
         <v>274</v>
       </c>
@@ -13505,7 +13520,7 @@
       <c r="A15" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="59"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="22" t="s">
         <v>279</v>
       </c>
@@ -13538,7 +13553,7 @@
       <c r="A16" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B16" s="59"/>
+      <c r="B16" s="61"/>
       <c r="C16" s="22" t="s">
         <v>282</v>
       </c>
@@ -13571,7 +13586,7 @@
       <c r="A17" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="59"/>
+      <c r="B17" s="61"/>
       <c r="C17" s="22" t="s">
         <v>286</v>
       </c>
@@ -13604,7 +13619,7 @@
       <c r="A18" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B18" s="59"/>
+      <c r="B18" s="61"/>
       <c r="C18" s="22" t="s">
         <v>289</v>
       </c>
@@ -13637,7 +13652,7 @@
       <c r="A19" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="59"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="22" t="s">
         <v>294</v>
       </c>
@@ -13670,7 +13685,7 @@
       <c r="A20" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="59"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="22" t="s">
         <v>298</v>
       </c>
@@ -13703,7 +13718,7 @@
       <c r="A21" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="59"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="22" t="s">
         <v>303</v>
       </c>
@@ -13736,7 +13751,7 @@
       <c r="A22" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="59"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="22" t="s">
         <v>305</v>
       </c>
@@ -13769,7 +13784,7 @@
       <c r="A23" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="59"/>
+      <c r="B23" s="61"/>
       <c r="C23" s="22" t="s">
         <v>310</v>
       </c>
@@ -13802,7 +13817,7 @@
       <c r="A24" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B24" s="59"/>
+      <c r="B24" s="61"/>
       <c r="C24" s="22" t="s">
         <v>314</v>
       </c>
@@ -13835,7 +13850,7 @@
       <c r="A25" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="59"/>
+      <c r="B25" s="61"/>
       <c r="C25" s="22" t="s">
         <v>316</v>
       </c>
@@ -13865,7 +13880,7 @@
       <c r="A26" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="59"/>
+      <c r="B26" s="61"/>
       <c r="C26" s="64" t="s">
         <v>321</v>
       </c>
@@ -13878,10 +13893,10 @@
       <c r="F26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="G26" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="59" t="s">
+      <c r="G26" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="61" t="s">
         <v>28</v>
       </c>
       <c r="I26" s="12" t="s">
@@ -13895,7 +13910,7 @@
       <c r="A27" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="59"/>
+      <c r="B27" s="61"/>
       <c r="C27" s="58"/>
       <c r="D27" s="63"/>
       <c r="E27" s="11" t="s">
@@ -13904,14 +13919,14 @@
       <c r="F27" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G27" s="59"/>
+      <c r="G27" s="61"/>
       <c r="H27" s="63"/>
     </row>
     <row r="28" spans="1:11" ht="76.5" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B28" s="59"/>
+      <c r="B28" s="61"/>
       <c r="C28" s="22" t="s">
         <v>329</v>
       </c>
@@ -13944,7 +13959,7 @@
       <c r="A29" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B29" s="59"/>
+      <c r="B29" s="61"/>
       <c r="C29" s="22" t="s">
         <v>334</v>
       </c>
@@ -13977,7 +13992,7 @@
       <c r="A30" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B30" s="59"/>
+      <c r="B30" s="61"/>
       <c r="C30" s="22" t="s">
         <v>338</v>
       </c>
@@ -14010,7 +14025,7 @@
       <c r="A31" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B31" s="59"/>
+      <c r="B31" s="61"/>
       <c r="C31" s="22" t="s">
         <v>341</v>
       </c>
@@ -14125,7 +14140,7 @@
       <c r="A36" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="61" t="s">
+      <c r="B36" s="59" t="s">
         <v>349</v>
       </c>
       <c r="C36" s="22" t="s">
@@ -14160,7 +14175,7 @@
       <c r="A37" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="59"/>
+      <c r="B37" s="61"/>
       <c r="C37" s="23" t="s">
         <v>354</v>
       </c>
@@ -14219,6 +14234,41 @@
       </c>
       <c r="K38" s="13" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="255">
+      <c r="A39" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>806</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>807</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -14329,7 +14379,7 @@
       <c r="A3" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>359</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -14518,7 +14568,7 @@
       <c r="A10" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="57" t="s">
         <v>385</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -14806,7 +14856,7 @@
       <c r="A20" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>422</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -15424,7 +15474,7 @@
       <c r="A40" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="57" t="s">
         <v>505</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -15580,7 +15630,7 @@
       <c r="A46" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="59" t="s">
         <v>526</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -15858,7 +15908,7 @@
       <c r="A56" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B56" s="43" t="s">
+      <c r="B56" s="46" t="s">
         <v>560</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -16135,13 +16185,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:9" ht="30">
       <c r="A3" t="s">
@@ -16362,13 +16412,13 @@
       <c r="A2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">

--- a/documentation/Casos de Prueba.xlsx
+++ b/documentation/Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595B12CF-18C9-4242-A046-DF70AB76992A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A7401A-53F6-4797-A51C-01D2485768D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2803" uniqueCount="852">
   <si>
     <t>Total de Casos de Prueba</t>
   </si>
@@ -2905,6 +2905,88 @@
   <si>
     <t>El sistema lee automaticamente via OCR los datos del comprobante (numero de comprobante, CUIT, monto) y los precarga en el formulario. Verificado en vivo 2026-08-22 (mismo hallazgo que CP-02, ver IMP-013). Ya no bloqueado por IMAS-4279 (resuelto 2026-09-02).
 CORRECCION 2026-09-10 (mas tarde el mismo dia): al intentar escribir el codigo real, se reconfirmo IMP-016 con esta misma cuenta -- el endpoint ya no da [] pero ahora da un registro con mascotaId/nombre en null, mismo bloqueo practico (UI sigue sin mostrar mascota utilizable). Este CP SI esta bloqueado por IMP-016, no es backlog libre como se dijo antes. Ver docs/impedimentos-bloqueos.md.</t>
+  </si>
+  <si>
+    <t>IMAS-4546 - Limite de videollamadas por plan (cupo parametrizable)</t>
+  </si>
+  <si>
+    <t>IMAS-4546</t>
+  </si>
+  <si>
+    <t>Validar plan ilimitado sin contador de cupo (AC1)</t>
+  </si>
+  <si>
+    <t>Tutor con mascota en un plan de videollamadas ilimitado (ej. Emergencias/Cachorro)</t>
+  </si>
+  <si>
+    <t>No se muestra ningun contador ni limite - se mantiene la experiencia actual. En cuentas multi-mascota, el selector muestra 'Cupo ilimitado' junto al nombre (sin numero), nunca un contador</t>
+  </si>
+  <si>
+    <t>1. Iniciar solicitud de videollamada
+2. Llegar a la pantalla de motivo</t>
+  </si>
+  <si>
+    <t>Validar contador Cupo disponible X de Y - sin consumidas y con consumidas (AC2)</t>
+  </si>
+  <si>
+    <t>Tutor OSDE Capitado Esencial (plan limitado) con cupo disponible</t>
+  </si>
+  <si>
+    <t>1. Llegar a la pantalla de motivo
+2. Agendar 1 videollamada sin consumirla y volver a Agendar nueva videollamada</t>
+  </si>
+  <si>
+    <t>El contador informa el disponible real; baja en 1 apenas se agenda el turno, aunque no se haya consumido - Caso especial 01: el cupo se descuenta al agendar, no al consumir</t>
+  </si>
+  <si>
+    <t>Validar bloqueo al agotar el cupo anual (AC2, sin disponibles)</t>
+  </si>
+  <si>
+    <t>Tutor OSDE Capitado Esencial con el cupo anual en 0</t>
+  </si>
+  <si>
+    <t>1. Intentar agendar una nueva videollamada</t>
+  </si>
+  <si>
+    <t>Bloquea con 1 de 2 modales segun el caso: Superaste el limite de videollamadas por mascota (si ademas hay 2 turnos concurrentes agendados, mecanismo heredado de IMAS-3909) o Alcanzaste el limite de X videollamadas anuales / Para agendar una nueva, tendras que esperar que se renueve tu cupo (si el cupo se agota con menos de 2 turnos concurrentes - modal nuevo de esta HU)</t>
+  </si>
+  <si>
+    <t>Validar que cancelar con mas de 30 min de anticipacion restituye el cupo (AC2, cancelacion)</t>
+  </si>
+  <si>
+    <t>Tutor OSDE Capitado Esencial con 1 videollamada agendada con varios dias de anticipacion</t>
+  </si>
+  <si>
+    <t>1. Cancelar el turno desde el detalle</t>
+  </si>
+  <si>
+    <t>El cupo disponible vuelve a su valor previo al agendado. Complementa el caso menos de 30 min (evidencia de Paula Scalzo en video: ahi el cupo NO se restituye)</t>
+  </si>
+  <si>
+    <t>Validar cupo independiente por mascota en cuentas multi-mascota (Caso especial 02)</t>
+  </si>
+  <si>
+    <t>Tutor con 2+ mascotas, todas en plan limitado, sin videollamadas consumidas</t>
+  </si>
+  <si>
+    <t>1. Abrir el selector de mascota y verificar el cupo de cada una
+2. Agendar 1 videollamada para una mascota (sin consumirla)
+3. Volver a abrir el selector</t>
+  </si>
+  <si>
+    <t>Cada mascota muestra su propio cupo de forma independiente; tras agendar, solo baja el cupo de la mascota agendada - la otra queda intacta</t>
+  </si>
+  <si>
+    <t>[Brecha de cobertura] Validar pantalla de plan sin videollamada incluida (Caso especial 04)</t>
+  </si>
+  <si>
+    <t>No confirmado - no se encontro ningun producto/plan real en QA que no incluya videollamada. No es AC formal de la HU (es una de 5 subtareas casos especiales del dev, IMAS-4712/4713)</t>
+  </si>
+  <si>
+    <t>Pendiente: cuenta real del dev con este plan configurado</t>
+  </si>
+  <si>
+    <t>Pendiente de definir - pregunta enviada al equipo de dev (ver docs/user-stories/IMAS-4546-limitar-videollamadas.tests.md, seccion 7)</t>
   </si>
 </sst>
 </file>
@@ -3227,7 +3309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3385,6 +3467,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5252,7 +5337,7 @@
     <row r="5" spans="3:24" ht="15.75" customHeight="1">
       <c r="C5" s="44">
         <f>COUNTA('Flujo de Compra'!C3:C496,'Gestión de Usuario'!C3:C357,Perfil!C3:C197,Credenciales!C3:C198,Videollamadas!C3:C197,Reintegros!C2:C199,Misceláneas!C2:C199,'Control de Acceso'!C2:C199,'Sistema Caído'!C2:C199,'Funcionalidades Pendientes'!C2:C199)-COUNTIF('Flujo de Compra'!I:I,"No")-COUNTIF('Gestión de Usuario'!I:I,"No")-COUNTIF(Reintegros!I:I,"No")-COUNTIF('Funcionalidades Pendientes'!I:I,"No")-COUNTIFS(Perfil!J:J,"No",Perfil!K:K,"No")-COUNTIFS(Credenciales!J:J,"No",Credenciales!K:K,"No")-COUNTIFS(Videollamadas!J:J,"No",Videollamadas!K:K,"No")</f>
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D5" s="45"/>
       <c r="E5" s="45"/>
@@ -5261,7 +5346,7 @@
       <c r="H5" s="46"/>
       <c r="K5" s="44">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")+COUNTIF(Reintegros!H:H,"Si")+COUNTIF(Misceláneas!H:H,"Si")+COUNTIF('Control de Acceso'!H:H,"Si")+COUNTIF('Sistema Caído'!H:H,"Si")+COUNTIF('Funcionalidades Pendientes'!H:H,"Si")</f>
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="L5" s="45"/>
       <c r="M5" s="45"/>
@@ -5270,7 +5355,7 @@
       <c r="P5" s="46"/>
       <c r="S5" s="55">
         <f>K5/C5</f>
-        <v>0.865979381443299</v>
+        <v>0.8682432432432432</v>
       </c>
       <c r="T5" s="45"/>
       <c r="U5" s="45"/>
@@ -5608,7 +5693,7 @@
     <row r="25" spans="3:24" ht="15.75" customHeight="1">
       <c r="C25" s="44">
         <f>COUNTIF('Flujo de Compra'!G:G,"Si")+COUNTIF('Gestión de Usuario'!G:G,"Si")+COUNTIF(Perfil!G:G,"Si")+COUNTIF(Credenciales!G:G,"Si")+COUNTIF(Videollamadas!G:G,"Si")+COUNTIF(Reintegros!G:G,"Si")+COUNTIF(Misceláneas!G:G,"Si")+COUNTIF('Control de Acceso'!G:G,"Si")+COUNTIF('Sistema Caído'!G:G,"Si")+COUNTIF('Funcionalidades Pendientes'!G:G,"Si")-COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!I:I,"No")-COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!I:I,"No")-COUNTIFS(Reintegros!G:G,"Si",Reintegros!I:I,"No")-COUNTIFS('Funcionalidades Pendientes'!G:G,"Si",'Funcionalidades Pendientes'!I:I,"No")-COUNTIFS(Perfil!G:G,"Si",Perfil!J:J,"No",Perfil!K:K,"No")-COUNTIFS(Credenciales!G:G,"Si",Credenciales!J:J,"No",Credenciales!K:K,"No")-COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!J:J,"No",Videollamadas!K:K,"No")</f>
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D25" s="45"/>
       <c r="E25" s="45"/>
@@ -5617,7 +5702,7 @@
       <c r="H25" s="46"/>
       <c r="K25" s="44">
         <f>COUNTIFS('Flujo de Compra'!G:G,"Si",'Flujo de Compra'!H:H,"Si")+COUNTIFS('Gestión de Usuario'!G:G,"Si",'Gestión de Usuario'!H:H,"Si")+COUNTIFS(Perfil!G:G,"Si",Perfil!H:H,"Si")+COUNTIFS(Credenciales!G:G,"Si",Credenciales!H:H,"Si")+COUNTIFS(Videollamadas!G:G,"Si",Videollamadas!H:H,"Si")+COUNTIFS(Reintegros!G:G,"Si",Reintegros!H:H,"Si")+COUNTIFS(Misceláneas!G:G,"Si",Misceláneas!H:H,"Si")+COUNTIFS('Control de Acceso'!G:G,"Si",'Control de Acceso'!H:H,"Si")+COUNTIFS('Sistema Caído'!G:G,"Si",'Sistema Caído'!H:H,"Si")+COUNTIFS('Funcionalidades Pendientes'!G:G,"Si",'Funcionalidades Pendientes'!H:H,"Si")</f>
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L25" s="45"/>
       <c r="M25" s="45"/>
@@ -5626,7 +5711,7 @@
       <c r="P25" s="46"/>
       <c r="S25" s="55">
         <f>K25/C25</f>
-        <v>0.90303030303030307</v>
+        <v>0.90588235294117647</v>
       </c>
       <c r="T25" s="45"/>
       <c r="U25" s="45"/>
@@ -5942,7 +6027,7 @@
     <row r="44" spans="3:24" ht="21" customHeight="1">
       <c r="C44" s="55">
         <f>C25/C5</f>
-        <v>0.5670103092783505</v>
+        <v>0.57432432432432434</v>
       </c>
       <c r="D44" s="45"/>
       <c r="E44" s="45"/>
@@ -6159,21 +6244,21 @@
     <row r="64" spans="3:16">
       <c r="C64" s="42">
         <f>COUNTIF('Flujo de Compra'!I:I,"Si")+COUNTIF('Gestión de Usuario'!I:I,"Si")+COUNTIF(Perfil!J:J,"Si")+COUNTIF(Credenciales!J:J,"Si")+COUNTIF(Videollamadas!J:J,"Si")</f>
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D64" s="42"/>
       <c r="E64" s="42"/>
       <c r="F64" s="42"/>
       <c r="H64" s="42">
         <f>COUNTIF('Flujo de Compra'!H:H,"Si")+COUNTIF('Gestión de Usuario'!H:H,"Si")+COUNTIF(Perfil!H:H,"Si")+COUNTIF(Credenciales!H:H,"Si")+COUNTIF(Videollamadas!H:H,"Si")</f>
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I64" s="42"/>
       <c r="J64" s="42"/>
       <c r="K64" s="42"/>
       <c r="M64" s="43">
         <f t="shared" ref="M64" si="0">H64/C64</f>
-        <v>0.87903225806451613</v>
+        <v>0.88142292490118579</v>
       </c>
       <c r="N64" s="43"/>
       <c r="O64" s="43"/>
@@ -14402,7 +14487,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -14455,13 +14540,13 @@
       <c r="A2" s="61" t="s">
         <v>343</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
     </row>
     <row r="3" spans="1:11" ht="30.75" customHeight="1">
       <c r="A3" s="7" t="s">
@@ -14502,7 +14587,7 @@
       <c r="A4" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B4" s="64"/>
+      <c r="B4" s="65"/>
       <c r="C4" s="8" t="s">
         <v>351</v>
       </c>
@@ -14535,7 +14620,7 @@
       <c r="A5" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B5" s="64"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="8" t="s">
         <v>356</v>
       </c>
@@ -14568,7 +14653,7 @@
       <c r="A6" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="B6" s="64"/>
+      <c r="B6" s="65"/>
       <c r="C6" s="8" t="s">
         <v>361</v>
       </c>
@@ -14601,7 +14686,7 @@
       <c r="A7" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="B7" s="64"/>
+      <c r="B7" s="65"/>
       <c r="C7" s="8" t="s">
         <v>366</v>
       </c>
@@ -14644,13 +14729,13 @@
       <c r="A9" s="61" t="s">
         <v>370</v>
       </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="64"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:11" ht="91.5" customHeight="1">
       <c r="A10" s="10" t="s">
@@ -14691,7 +14776,7 @@
       <c r="A11" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="B11" s="64"/>
+      <c r="B11" s="65"/>
       <c r="C11" s="11" t="s">
         <v>376</v>
       </c>
@@ -14724,7 +14809,7 @@
       <c r="A12" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="B12" s="64"/>
+      <c r="B12" s="65"/>
       <c r="C12" s="11" t="s">
         <v>380</v>
       </c>
@@ -14757,7 +14842,7 @@
       <c r="A13" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="B13" s="64"/>
+      <c r="B13" s="65"/>
       <c r="C13" s="11" t="s">
         <v>384</v>
       </c>
@@ -14790,7 +14875,7 @@
       <c r="A14" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="B14" s="64"/>
+      <c r="B14" s="65"/>
       <c r="C14" s="11" t="s">
         <v>388</v>
       </c>
@@ -14823,7 +14908,7 @@
       <c r="A15" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B15" s="64"/>
+      <c r="B15" s="65"/>
       <c r="C15" s="11" t="s">
         <v>393</v>
       </c>
@@ -14856,7 +14941,7 @@
       <c r="A16" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B16" s="64"/>
+      <c r="B16" s="65"/>
       <c r="C16" s="11" t="s">
         <v>398</v>
       </c>
@@ -14889,7 +14974,7 @@
       <c r="A17" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B17" s="64"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="11" t="s">
         <v>403</v>
       </c>
@@ -14932,13 +15017,13 @@
       <c r="A19" s="61" t="s">
         <v>407</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
       <c r="F19" s="57"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="64"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="65"/>
     </row>
     <row r="20" spans="1:11" ht="106.5" customHeight="1">
       <c r="A20" s="7" t="s">
@@ -14979,7 +15064,7 @@
       <c r="A21" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B21" s="64"/>
+      <c r="B21" s="65"/>
       <c r="C21" s="8" t="s">
         <v>413</v>
       </c>
@@ -15012,7 +15097,7 @@
       <c r="A22" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B22" s="64"/>
+      <c r="B22" s="65"/>
       <c r="C22" s="8" t="s">
         <v>417</v>
       </c>
@@ -15045,7 +15130,7 @@
       <c r="A23" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="B23" s="64"/>
+      <c r="B23" s="65"/>
       <c r="C23" s="8" t="s">
         <v>421</v>
       </c>
@@ -15078,7 +15163,7 @@
       <c r="A24" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="B24" s="64"/>
+      <c r="B24" s="65"/>
       <c r="C24" s="8" t="s">
         <v>425</v>
       </c>
@@ -15111,7 +15196,7 @@
       <c r="A25" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="B25" s="64"/>
+      <c r="B25" s="65"/>
       <c r="C25" s="8" t="s">
         <v>429</v>
       </c>
@@ -15144,7 +15229,7 @@
       <c r="A26" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B26" s="64"/>
+      <c r="B26" s="65"/>
       <c r="C26" s="8" t="s">
         <v>433</v>
       </c>
@@ -15177,7 +15262,7 @@
       <c r="A27" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B27" s="64"/>
+      <c r="B27" s="65"/>
       <c r="C27" s="8" t="s">
         <v>437</v>
       </c>
@@ -15210,7 +15295,7 @@
       <c r="A28" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="B28" s="64"/>
+      <c r="B28" s="65"/>
       <c r="C28" s="8" t="s">
         <v>442</v>
       </c>
@@ -15243,7 +15328,7 @@
       <c r="A29" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B29" s="64"/>
+      <c r="B29" s="65"/>
       <c r="C29" s="8" t="s">
         <v>447</v>
       </c>
@@ -15276,7 +15361,7 @@
       <c r="A30" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="B30" s="64"/>
+      <c r="B30" s="65"/>
       <c r="C30" s="8" t="s">
         <v>452</v>
       </c>
@@ -15309,7 +15394,7 @@
       <c r="A31" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="B31" s="64"/>
+      <c r="B31" s="65"/>
       <c r="C31" s="8" t="s">
         <v>457</v>
       </c>
@@ -15342,7 +15427,7 @@
       <c r="A32" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="B32" s="64"/>
+      <c r="B32" s="65"/>
       <c r="C32" s="8" t="s">
         <v>462</v>
       </c>
@@ -15375,7 +15460,7 @@
       <c r="A33" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="B33" s="64"/>
+      <c r="B33" s="65"/>
       <c r="C33" s="8" t="s">
         <v>467</v>
       </c>
@@ -15408,7 +15493,7 @@
       <c r="A34" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="B34" s="64"/>
+      <c r="B34" s="65"/>
       <c r="C34" s="8" t="s">
         <v>474</v>
       </c>
@@ -15441,7 +15526,7 @@
       <c r="A35" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="B35" s="64"/>
+      <c r="B35" s="65"/>
       <c r="C35" s="8" t="s">
         <v>479</v>
       </c>
@@ -15474,7 +15559,7 @@
       <c r="A36" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="B36" s="64"/>
+      <c r="B36" s="65"/>
       <c r="C36" s="8" t="s">
         <v>482</v>
       </c>
@@ -15517,13 +15602,13 @@
       <c r="A38" s="61" t="s">
         <v>486</v>
       </c>
-      <c r="B38" s="64"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
       <c r="F38" s="57"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="64"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="65"/>
     </row>
     <row r="39" spans="1:11" ht="45" customHeight="1">
       <c r="A39" s="10" t="s">
@@ -15564,7 +15649,7 @@
       <c r="A40" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="B40" s="64"/>
+      <c r="B40" s="65"/>
       <c r="C40" s="11" t="s">
         <v>494</v>
       </c>
@@ -15597,7 +15682,7 @@
       <c r="A41" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="B41" s="64"/>
+      <c r="B41" s="65"/>
       <c r="C41" s="11" t="s">
         <v>499</v>
       </c>
@@ -15630,7 +15715,7 @@
       <c r="A42" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="B42" s="64"/>
+      <c r="B42" s="65"/>
       <c r="C42" s="11" t="s">
         <v>504</v>
       </c>
@@ -15673,13 +15758,13 @@
       <c r="A44" s="61" t="s">
         <v>508</v>
       </c>
-      <c r="B44" s="64"/>
-      <c r="C44" s="64"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
       <c r="F44" s="57"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="64"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="65"/>
     </row>
     <row r="45" spans="1:11" ht="60" customHeight="1">
       <c r="A45" s="7" t="s">
@@ -15720,7 +15805,7 @@
       <c r="A46" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B46" s="64"/>
+      <c r="B46" s="65"/>
       <c r="C46" s="8" t="s">
         <v>514</v>
       </c>
@@ -15753,7 +15838,7 @@
       <c r="A47" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B47" s="64"/>
+      <c r="B47" s="65"/>
       <c r="C47" s="8" t="s">
         <v>518</v>
       </c>
@@ -15786,7 +15871,7 @@
       <c r="A48" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="B48" s="64"/>
+      <c r="B48" s="65"/>
       <c r="C48" s="8" t="s">
         <v>522</v>
       </c>
@@ -15819,7 +15904,7 @@
       <c r="A49" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="B49" s="64"/>
+      <c r="B49" s="65"/>
       <c r="C49" s="8" t="s">
         <v>526</v>
       </c>
@@ -15852,7 +15937,7 @@
       <c r="A50" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="B50" s="64"/>
+      <c r="B50" s="65"/>
       <c r="C50" s="8" t="s">
         <v>530</v>
       </c>
@@ -15885,7 +15970,7 @@
       <c r="A51" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B51" s="64"/>
+      <c r="B51" s="65"/>
       <c r="C51" s="8" t="s">
         <v>534</v>
       </c>
@@ -15918,7 +16003,7 @@
       <c r="A52" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B52" s="64"/>
+      <c r="B52" s="65"/>
       <c r="C52" s="8" t="s">
         <v>538</v>
       </c>
@@ -15951,13 +16036,13 @@
       <c r="A54" s="61" t="s">
         <v>542</v>
       </c>
-      <c r="B54" s="64"/>
-      <c r="C54" s="64"/>
-      <c r="D54" s="64"/>
-      <c r="E54" s="64"/>
+      <c r="B54" s="65"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="65"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="65"/>
-      <c r="H54" s="64"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="65"/>
     </row>
     <row r="55" spans="1:11" ht="60" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -15998,7 +16083,7 @@
       <c r="A56" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B56" s="64"/>
+      <c r="B56" s="65"/>
       <c r="C56" s="8" t="s">
         <v>547</v>
       </c>
@@ -16031,7 +16116,7 @@
       <c r="A57" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B57" s="64"/>
+      <c r="B57" s="65"/>
       <c r="C57" s="8" t="s">
         <v>551</v>
       </c>
@@ -16064,7 +16149,7 @@
       <c r="A58" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="B58" s="64"/>
+      <c r="B58" s="65"/>
       <c r="C58" s="8" t="s">
         <v>555</v>
       </c>
@@ -16093,8 +16178,216 @@
         <v>28</v>
       </c>
     </row>
+    <row r="60" spans="1:11" ht="15" customHeight="1">
+      <c r="A60" s="64" t="s">
+        <v>826</v>
+      </c>
+      <c r="B60" s="64"/>
+      <c r="C60" s="64"/>
+      <c r="D60" s="64"/>
+      <c r="E60" s="64"/>
+      <c r="F60" s="64"/>
+      <c r="G60" s="64"/>
+      <c r="H60" s="64"/>
+    </row>
+    <row r="61" spans="1:11" ht="75">
+      <c r="A61" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="60">
+      <c r="A62" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="150">
+      <c r="A63" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="60">
+      <c r="A64" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="75">
+      <c r="A65" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="60">
+      <c r="A66" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="A60:H60"/>
     <mergeCell ref="A54:H54"/>
     <mergeCell ref="B55:B58"/>
     <mergeCell ref="A2:H2"/>
